--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1514"/>
+  <dimension ref="A1:H1515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33100,7 +33100,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59060651.66</v>
+        <v>59063934.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33122,7 +33122,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58393189.939</v>
+        <v>58399453.12</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58630763.23</v>
+        <v>58615488.572</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33166,7 +33166,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59756715.087</v>
+        <v>59746961.032</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58097718.062</v>
+        <v>58079904.81</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57318761.681</v>
+        <v>57322044.862</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33232,7 +33232,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56291141.713</v>
+        <v>56268320.894</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33253,15 +33253,21 @@
         <v>28.6875</v>
       </c>
       <c r="F1512" t="inlineStr"/>
-      <c r="G1512" t="inlineStr"/>
+      <c r="G1512" t="n">
+        <v>56584347.389</v>
+      </c>
       <c r="H1512" t="inlineStr"/>
     </row>
     <row r="1513">
       <c r="A1513" s="2" t="n">
         <v>46065</v>
       </c>
-      <c r="B1513" t="inlineStr"/>
-      <c r="C1513" t="inlineStr"/>
+      <c r="B1513" t="n">
+        <v>45053</v>
+      </c>
+      <c r="C1513" t="n">
+        <v>42461589</v>
+      </c>
       <c r="D1513" t="n">
         <v>1420.27</v>
       </c>
@@ -33281,10 +33287,26 @@
       <c r="D1514" t="n">
         <v>1420.64</v>
       </c>
-      <c r="E1514" t="inlineStr"/>
+      <c r="E1514" t="n">
+        <v>31.3125</v>
+      </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="inlineStr"/>
       <c r="H1514" t="inlineStr"/>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B1515" t="inlineStr"/>
+      <c r="C1515" t="inlineStr"/>
+      <c r="D1515" t="n">
+        <v>1424.61</v>
+      </c>
+      <c r="E1515" t="inlineStr"/>
+      <c r="F1515" t="inlineStr"/>
+      <c r="G1515" t="inlineStr"/>
+      <c r="H1515" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1515"/>
+  <dimension ref="A1:H1517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32584,7 +32584,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65307705.61</v>
+        <v>65308063.61</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -32798,7 +32798,7 @@
       </c>
       <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="n">
-        <v>57150998.244</v>
+        <v>57149998.244</v>
       </c>
       <c r="H1491" t="inlineStr"/>
     </row>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60049388.632</v>
+        <v>60049377.632</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33100,7 +33100,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59063934.841</v>
+        <v>59063941.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33122,7 +33122,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58399453.12</v>
+        <v>58399464.12</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58615488.572</v>
+        <v>58615865.572</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33166,7 +33166,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59746961.032</v>
+        <v>59732334.287</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58079904.81</v>
+        <v>58020066.753</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57322044.862</v>
+        <v>57297031.281</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33232,7 +33232,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56268320.894</v>
+        <v>56270232.925</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56584347.389</v>
+        <v>56472145.377</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33275,15 +33275,21 @@
         <v>29.875</v>
       </c>
       <c r="F1513" t="inlineStr"/>
-      <c r="G1513" t="inlineStr"/>
+      <c r="G1513" t="n">
+        <v>55963755.227</v>
+      </c>
       <c r="H1513" t="inlineStr"/>
     </row>
     <row r="1514">
       <c r="A1514" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="B1514" t="inlineStr"/>
-      <c r="C1514" t="inlineStr"/>
+      <c r="B1514" t="n">
+        <v>45164</v>
+      </c>
+      <c r="C1514" t="n">
+        <v>40956503</v>
+      </c>
       <c r="D1514" t="n">
         <v>1420.64</v>
       </c>
@@ -33291,22 +33297,60 @@
         <v>31.3125</v>
       </c>
       <c r="F1514" t="inlineStr"/>
-      <c r="G1514" t="inlineStr"/>
+      <c r="G1514" t="n">
+        <v>55668314.512</v>
+      </c>
       <c r="H1514" t="inlineStr"/>
     </row>
     <row r="1515">
       <c r="A1515" s="2" t="n">
         <v>46071</v>
       </c>
-      <c r="B1515" t="inlineStr"/>
-      <c r="C1515" t="inlineStr"/>
+      <c r="B1515" t="n">
+        <v>45130</v>
+      </c>
+      <c r="C1515" t="n">
+        <v>40986425</v>
+      </c>
       <c r="D1515" t="n">
         <v>1424.61</v>
       </c>
-      <c r="E1515" t="inlineStr"/>
+      <c r="E1515" t="n">
+        <v>30.5</v>
+      </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="inlineStr"/>
       <c r="H1515" t="inlineStr"/>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B1516" t="inlineStr"/>
+      <c r="C1516" t="inlineStr"/>
+      <c r="D1516" t="n">
+        <v>1419.32</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>31.8125</v>
+      </c>
+      <c r="F1516" t="inlineStr"/>
+      <c r="G1516" t="inlineStr"/>
+      <c r="H1516" t="inlineStr"/>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B1517" t="inlineStr"/>
+      <c r="C1517" t="inlineStr"/>
+      <c r="D1517" t="n">
+        <v>1399.15</v>
+      </c>
+      <c r="E1517" t="inlineStr"/>
+      <c r="F1517" t="inlineStr"/>
+      <c r="G1517" t="inlineStr"/>
+      <c r="H1517" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1517"/>
+  <dimension ref="A1:H1522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32584,7 +32584,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65308063.61</v>
+        <v>65308883.61</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60049377.632</v>
+        <v>60108752.892</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33100,7 +33100,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59063941.841</v>
+        <v>59041853.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33122,7 +33122,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58399464.12</v>
+        <v>58348680.12</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58615865.572</v>
+        <v>58614525.572</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33166,7 +33166,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59732334.287</v>
+        <v>59730996.287</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58020066.753</v>
+        <v>58026083.753</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57297031.281</v>
+        <v>57264286.356</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33232,7 +33232,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56270232.925</v>
+        <v>56146845.496</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56472145.377</v>
+        <v>56461607.389</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55963755.227</v>
+        <v>55883615.106</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33298,7 +33298,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55668314.512</v>
+        <v>55646411.029</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33319,15 +33319,21 @@
         <v>30.5</v>
       </c>
       <c r="F1515" t="inlineStr"/>
-      <c r="G1515" t="inlineStr"/>
+      <c r="G1515" t="n">
+        <v>55625534.938</v>
+      </c>
       <c r="H1515" t="inlineStr"/>
     </row>
     <row r="1516">
       <c r="A1516" s="2" t="n">
         <v>46072</v>
       </c>
-      <c r="B1516" t="inlineStr"/>
-      <c r="C1516" t="inlineStr"/>
+      <c r="B1516" t="n">
+        <v>44904</v>
+      </c>
+      <c r="C1516" t="n">
+        <v>41882460</v>
+      </c>
       <c r="D1516" t="n">
         <v>1419.32</v>
       </c>
@@ -33335,22 +33341,126 @@
         <v>31.8125</v>
       </c>
       <c r="F1516" t="inlineStr"/>
-      <c r="G1516" t="inlineStr"/>
+      <c r="G1516" t="n">
+        <v>55683614.207</v>
+      </c>
       <c r="H1516" t="inlineStr"/>
     </row>
     <row r="1517">
       <c r="A1517" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B1517" t="inlineStr"/>
-      <c r="C1517" t="inlineStr"/>
+      <c r="B1517" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C1517" t="n">
+        <v>42378425</v>
+      </c>
       <c r="D1517" t="n">
         <v>1399.15</v>
       </c>
-      <c r="E1517" t="inlineStr"/>
+      <c r="E1517" t="n">
+        <v>32.6875</v>
+      </c>
       <c r="F1517" t="inlineStr"/>
-      <c r="G1517" t="inlineStr"/>
+      <c r="G1517" t="n">
+        <v>55300100.573</v>
+      </c>
       <c r="H1517" t="inlineStr"/>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B1518" t="n">
+        <v>46635</v>
+      </c>
+      <c r="C1518" t="n">
+        <v>42646887</v>
+      </c>
+      <c r="D1518" t="n">
+        <v>1392.75</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>33.125</v>
+      </c>
+      <c r="F1518" t="inlineStr"/>
+      <c r="G1518" t="n">
+        <v>55317778.228</v>
+      </c>
+      <c r="H1518" t="inlineStr"/>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B1519" t="n">
+        <v>46663</v>
+      </c>
+      <c r="C1519" t="n">
+        <v>42600442</v>
+      </c>
+      <c r="D1519" t="n">
+        <v>1400.12</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>34.3125</v>
+      </c>
+      <c r="F1519" t="inlineStr"/>
+      <c r="G1519" t="n">
+        <v>54797460.909</v>
+      </c>
+      <c r="H1519" t="inlineStr"/>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B1520" t="n">
+        <v>46905</v>
+      </c>
+      <c r="C1520" t="n">
+        <v>41232963</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>1416.53</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="F1520" t="inlineStr"/>
+      <c r="G1520" t="inlineStr"/>
+      <c r="H1520" t="inlineStr"/>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B1521" t="inlineStr"/>
+      <c r="C1521" t="inlineStr"/>
+      <c r="D1521" t="n">
+        <v>1429.59</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="F1521" t="inlineStr"/>
+      <c r="G1521" t="inlineStr"/>
+      <c r="H1521" t="inlineStr"/>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B1522" t="inlineStr"/>
+      <c r="C1522" t="inlineStr"/>
+      <c r="D1522" t="n">
+        <v>1426.45</v>
+      </c>
+      <c r="E1522" t="inlineStr"/>
+      <c r="F1522" t="inlineStr"/>
+      <c r="G1522" t="inlineStr"/>
+      <c r="H1522" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1522"/>
+  <dimension ref="A1:H1528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10869,7 +10869,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.48</v>
+        <v>108.29</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10891,7 +10891,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.61</v>
+        <v>108.48</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10913,7 +10913,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.63</v>
+        <v>108.61</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10935,7 +10935,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.72</v>
+        <v>108.63</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10957,7 +10957,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.86</v>
+        <v>108.72</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10979,7 +10979,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.96</v>
+        <v>108.86</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -11001,7 +11001,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.97</v>
+        <v>108.96</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11023,7 +11023,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>109.05</v>
+        <v>108.97</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11045,7 +11045,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.11</v>
+        <v>109.05</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11067,7 +11067,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.21</v>
+        <v>109.11</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11089,7 +11089,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.46</v>
+        <v>109.21</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11111,7 +11111,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.64</v>
+        <v>109.46</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11133,7 +11133,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.67</v>
+        <v>109.64</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11155,7 +11155,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.71</v>
+        <v>109.67</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11177,7 +11177,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.79</v>
+        <v>109.71</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11199,7 +11199,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>110.08</v>
+        <v>109.79</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11221,7 +11221,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.11</v>
+        <v>110.08</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11243,7 +11243,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.15</v>
+        <v>110.11</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11265,7 +11265,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.5</v>
+        <v>110.15</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11287,7 +11287,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.68</v>
+        <v>110.5</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11309,7 +11309,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.71</v>
+        <v>110.68</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11335,7 +11335,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11357,7 +11357,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.92</v>
+        <v>110.75</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11401,7 +11401,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>111.37</v>
+        <v>110.92</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11423,7 +11423,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.46</v>
+        <v>111.37</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11445,7 +11445,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.49</v>
+        <v>111.46</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11467,7 +11467,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.52</v>
+        <v>111.49</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11489,7 +11489,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.59</v>
+        <v>111.52</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11511,7 +11511,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.67</v>
+        <v>111.59</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11533,7 +11533,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>112.01</v>
+        <v>111.67</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11555,7 +11555,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.17</v>
+        <v>112.01</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11577,7 +11577,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.21</v>
+        <v>112.17</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11599,7 +11599,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.24</v>
+        <v>112.21</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11621,7 +11621,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.48</v>
+        <v>112.24</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11643,7 +11643,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.71</v>
+        <v>112.48</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11665,7 +11665,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.8</v>
+        <v>112.71</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11687,7 +11687,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.83</v>
+        <v>112.8</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11709,7 +11709,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.89</v>
+        <v>112.83</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11731,7 +11731,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.95</v>
+        <v>112.89</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65308883.61</v>
+        <v>65308917.61</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -32622,7 +32622,7 @@
       </c>
       <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="n">
-        <v>64570493.281</v>
+        <v>64570686.281</v>
       </c>
       <c r="H1483" t="inlineStr"/>
     </row>
@@ -32644,7 +32644,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61922337.993</v>
+        <v>61922589.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32666,7 +32666,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61171357.519</v>
+        <v>61171495.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -32688,7 +32688,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61771862.076</v>
+        <v>61772229.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32710,7 +32710,7 @@
       </c>
       <c r="F1487" t="inlineStr"/>
       <c r="G1487" t="n">
-        <v>60493436.004</v>
+        <v>60494236.004</v>
       </c>
       <c r="H1487" t="inlineStr"/>
     </row>
@@ -32732,7 +32732,7 @@
       </c>
       <c r="F1488" t="inlineStr"/>
       <c r="G1488" t="n">
-        <v>59510428.211</v>
+        <v>59514024.211</v>
       </c>
       <c r="H1488" t="inlineStr"/>
     </row>
@@ -32754,7 +32754,7 @@
       </c>
       <c r="F1489" t="inlineStr"/>
       <c r="G1489" t="n">
-        <v>57920324.381</v>
+        <v>57923945.381</v>
       </c>
       <c r="H1489" t="inlineStr"/>
     </row>
@@ -32776,7 +32776,7 @@
       </c>
       <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="n">
-        <v>57294200.101</v>
+        <v>57294196.101</v>
       </c>
       <c r="H1490" t="inlineStr"/>
     </row>
@@ -32798,7 +32798,7 @@
       </c>
       <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="n">
-        <v>57149998.244</v>
+        <v>57150504.244</v>
       </c>
       <c r="H1491" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
       </c>
       <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="n">
-        <v>57548487.399</v>
+        <v>57549505.399</v>
       </c>
       <c r="H1492" t="inlineStr"/>
     </row>
@@ -32842,7 +32842,7 @@
       </c>
       <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="n">
-        <v>56304767.088</v>
+        <v>56304830.088</v>
       </c>
       <c r="H1493" t="inlineStr"/>
     </row>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="n">
-        <v>55619285.47</v>
+        <v>55619308.47</v>
       </c>
       <c r="H1494" t="inlineStr"/>
     </row>
@@ -32886,7 +32886,7 @@
       </c>
       <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="n">
-        <v>55472133.492</v>
+        <v>55472262.492</v>
       </c>
       <c r="H1495" t="inlineStr"/>
     </row>
@@ -32908,7 +32908,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55281712.796</v>
+        <v>55281773.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -32930,7 +32930,7 @@
       </c>
       <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="n">
-        <v>55035212.613</v>
+        <v>55035213.613</v>
       </c>
       <c r="H1497" t="inlineStr"/>
     </row>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="n">
-        <v>54744992.758</v>
+        <v>54745006.758</v>
       </c>
       <c r="H1498" t="inlineStr"/>
     </row>
@@ -32974,7 +32974,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54891483.349</v>
+        <v>54891516.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -32996,7 +32996,7 @@
       </c>
       <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="n">
-        <v>55151707.773</v>
+        <v>55154671.773</v>
       </c>
       <c r="H1500" t="inlineStr"/>
     </row>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="n">
-        <v>55910449.062</v>
+        <v>55910615.062</v>
       </c>
       <c r="H1501" t="inlineStr"/>
     </row>
@@ -33040,7 +33040,7 @@
       </c>
       <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="n">
-        <v>57600349.416</v>
+        <v>57600386.416</v>
       </c>
       <c r="H1502" t="inlineStr"/>
     </row>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60108752.892</v>
+        <v>60123806.451</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33122,7 +33122,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58348680.12</v>
+        <v>58346511.213</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58614525.572</v>
+        <v>58621586.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33166,7 +33166,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59730996.287</v>
+        <v>59728464.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58026083.753</v>
+        <v>58023379.8</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57264286.356</v>
+        <v>57262947.786</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33232,7 +33232,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56146845.496</v>
+        <v>56144479.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56461607.389</v>
+        <v>56459959.744</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55883615.106</v>
+        <v>55872022.876</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33298,7 +33298,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55646411.029</v>
+        <v>55653355.799</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55625534.938</v>
+        <v>55628089.185</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33342,7 +33342,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55683614.207</v>
+        <v>55673366.325</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33364,7 +33364,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55300100.573</v>
+        <v>55267186.56</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33386,7 +33386,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55317778.228</v>
+        <v>55301168.252</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33408,7 +33408,7 @@
       </c>
       <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="n">
-        <v>54797460.909</v>
+        <v>54751669.522</v>
       </c>
       <c r="H1519" t="inlineStr"/>
     </row>
@@ -33429,15 +33429,21 @@
         <v>30.75</v>
       </c>
       <c r="F1520" t="inlineStr"/>
-      <c r="G1520" t="inlineStr"/>
+      <c r="G1520" t="n">
+        <v>55619159.751</v>
+      </c>
       <c r="H1520" t="inlineStr"/>
     </row>
     <row r="1521">
       <c r="A1521" s="2" t="n">
         <v>46079</v>
       </c>
-      <c r="B1521" t="inlineStr"/>
-      <c r="C1521" t="inlineStr"/>
+      <c r="B1521" t="n">
+        <v>46158</v>
+      </c>
+      <c r="C1521" t="n">
+        <v>41414239</v>
+      </c>
       <c r="D1521" t="n">
         <v>1429.59</v>
       </c>
@@ -33445,22 +33451,140 @@
         <v>30.25</v>
       </c>
       <c r="F1521" t="inlineStr"/>
-      <c r="G1521" t="inlineStr"/>
+      <c r="G1521" t="n">
+        <v>57379642.285</v>
+      </c>
       <c r="H1521" t="inlineStr"/>
     </row>
     <row r="1522">
       <c r="A1522" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="B1522" t="inlineStr"/>
-      <c r="C1522" t="inlineStr"/>
+      <c r="B1522" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C1522" t="n">
+        <v>40986704</v>
+      </c>
       <c r="D1522" t="n">
         <v>1426.45</v>
       </c>
-      <c r="E1522" t="inlineStr"/>
+      <c r="E1522" t="n">
+        <v>29.5</v>
+      </c>
       <c r="F1522" t="inlineStr"/>
-      <c r="G1522" t="inlineStr"/>
+      <c r="G1522" t="n">
+        <v>60241913.034</v>
+      </c>
       <c r="H1522" t="inlineStr"/>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B1523" t="inlineStr"/>
+      <c r="C1523" t="inlineStr"/>
+      <c r="D1523" t="inlineStr"/>
+      <c r="E1523" t="inlineStr"/>
+      <c r="F1523" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G1523" t="inlineStr"/>
+      <c r="H1523" t="inlineStr"/>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B1524" t="n">
+        <v>46519</v>
+      </c>
+      <c r="C1524" t="n">
+        <v>42499111</v>
+      </c>
+      <c r="D1524" t="n">
+        <v>1417.21</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>28.9375</v>
+      </c>
+      <c r="F1524" t="inlineStr"/>
+      <c r="G1524" t="n">
+        <v>59240937.17</v>
+      </c>
+      <c r="H1524" t="inlineStr"/>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B1525" t="n">
+        <v>46137</v>
+      </c>
+      <c r="C1525" t="n">
+        <v>42641381</v>
+      </c>
+      <c r="D1525" t="n">
+        <v>1433.4</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F1525" t="inlineStr"/>
+      <c r="G1525" t="n">
+        <v>58662705.075</v>
+      </c>
+      <c r="H1525" t="inlineStr"/>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B1526" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C1526" t="n">
+        <v>42455350</v>
+      </c>
+      <c r="D1526" t="n">
+        <v>1427.83</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>28.4375</v>
+      </c>
+      <c r="F1526" t="inlineStr"/>
+      <c r="G1526" t="inlineStr"/>
+      <c r="H1526" t="inlineStr"/>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B1527" t="inlineStr"/>
+      <c r="C1527" t="inlineStr"/>
+      <c r="D1527" t="n">
+        <v>1425.47</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F1527" t="inlineStr"/>
+      <c r="G1527" t="inlineStr"/>
+      <c r="H1527" t="inlineStr"/>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B1528" t="inlineStr"/>
+      <c r="C1528" t="inlineStr"/>
+      <c r="D1528" t="n">
+        <v>1436.18</v>
+      </c>
+      <c r="E1528" t="inlineStr"/>
+      <c r="F1528" t="inlineStr"/>
+      <c r="G1528" t="inlineStr"/>
+      <c r="H1528" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1528"/>
+  <dimension ref="A1:H1534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10869,7 +10869,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.29</v>
+        <v>108.48</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10891,7 +10891,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.48</v>
+        <v>108.61</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10913,7 +10913,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.61</v>
+        <v>108.63</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10935,7 +10935,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.63</v>
+        <v>108.72</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10957,7 +10957,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.72</v>
+        <v>108.86</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10979,7 +10979,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.86</v>
+        <v>108.96</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -11001,7 +11001,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.96</v>
+        <v>108.97</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11023,7 +11023,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>108.97</v>
+        <v>109.05</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11045,7 +11045,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.05</v>
+        <v>109.11</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11067,7 +11067,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.11</v>
+        <v>109.21</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11089,7 +11089,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.21</v>
+        <v>109.46</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11111,7 +11111,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.46</v>
+        <v>109.64</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11133,7 +11133,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.64</v>
+        <v>109.67</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11155,7 +11155,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.67</v>
+        <v>109.71</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11177,7 +11177,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.71</v>
+        <v>109.79</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11199,7 +11199,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>109.79</v>
+        <v>110.08</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11221,7 +11221,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.08</v>
+        <v>110.11</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11243,7 +11243,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.11</v>
+        <v>110.15</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11265,7 +11265,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.15</v>
+        <v>110.5</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11287,7 +11287,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.5</v>
+        <v>110.68</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11309,7 +11309,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.68</v>
+        <v>110.71</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11335,7 +11335,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.71</v>
+        <v>110.75</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11357,7 +11357,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.75</v>
+        <v>110.92</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11401,7 +11401,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>110.92</v>
+        <v>111.37</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11423,7 +11423,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.37</v>
+        <v>111.46</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11445,7 +11445,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.46</v>
+        <v>111.49</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11467,7 +11467,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.49</v>
+        <v>111.52</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11489,7 +11489,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.52</v>
+        <v>111.59</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11511,7 +11511,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.59</v>
+        <v>111.67</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11533,7 +11533,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>111.67</v>
+        <v>112.01</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11555,7 +11555,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.01</v>
+        <v>112.17</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11577,7 +11577,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.17</v>
+        <v>112.21</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11599,7 +11599,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.21</v>
+        <v>112.24</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11621,7 +11621,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.24</v>
+        <v>112.48</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11643,7 +11643,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.48</v>
+        <v>112.71</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11665,7 +11665,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.71</v>
+        <v>112.8</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11687,7 +11687,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.8</v>
+        <v>112.83</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11709,7 +11709,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.83</v>
+        <v>112.89</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11731,7 +11731,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.89</v>
+        <v>112.95</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -31310,7 +31310,7 @@
       </c>
       <c r="F1423" t="inlineStr"/>
       <c r="G1423" t="n">
-        <v>55657209.331</v>
+        <v>55657247.331</v>
       </c>
       <c r="H1423" t="inlineStr"/>
     </row>
@@ -31332,7 +31332,7 @@
       </c>
       <c r="F1424" t="inlineStr"/>
       <c r="G1424" t="n">
-        <v>55719168.151</v>
+        <v>55719173.151</v>
       </c>
       <c r="H1424" t="inlineStr"/>
     </row>
@@ -31354,7 +31354,7 @@
       </c>
       <c r="F1425" t="inlineStr"/>
       <c r="G1425" t="n">
-        <v>55984869.978</v>
+        <v>55984884.978</v>
       </c>
       <c r="H1425" t="inlineStr"/>
     </row>
@@ -31376,7 +31376,7 @@
       </c>
       <c r="F1426" t="inlineStr"/>
       <c r="G1426" t="n">
-        <v>55756572.241</v>
+        <v>55756586.241</v>
       </c>
       <c r="H1426" t="inlineStr"/>
     </row>
@@ -31398,7 +31398,7 @@
       </c>
       <c r="F1427" t="inlineStr"/>
       <c r="G1427" t="n">
-        <v>54919761.217</v>
+        <v>54919763.217</v>
       </c>
       <c r="H1427" t="inlineStr"/>
     </row>
@@ -31420,7 +31420,7 @@
       </c>
       <c r="F1428" t="inlineStr"/>
       <c r="G1428" t="n">
-        <v>54798064.24</v>
+        <v>54798066.24</v>
       </c>
       <c r="H1428" t="inlineStr"/>
     </row>
@@ -31486,7 +31486,7 @@
       </c>
       <c r="F1431" t="inlineStr"/>
       <c r="G1431" t="n">
-        <v>51986044.914</v>
+        <v>51986047.914</v>
       </c>
       <c r="H1431" t="inlineStr"/>
     </row>
@@ -31508,7 +31508,7 @@
       </c>
       <c r="F1432" t="inlineStr"/>
       <c r="G1432" t="n">
-        <v>52549503.382</v>
+        <v>52549505.382</v>
       </c>
       <c r="H1432" t="inlineStr"/>
     </row>
@@ -31530,7 +31530,7 @@
       </c>
       <c r="F1433" t="inlineStr"/>
       <c r="G1433" t="n">
-        <v>51728720.388</v>
+        <v>51728729.388</v>
       </c>
       <c r="H1433" t="inlineStr"/>
     </row>
@@ -31552,7 +31552,7 @@
       </c>
       <c r="F1434" t="inlineStr"/>
       <c r="G1434" t="n">
-        <v>50521471.623</v>
+        <v>50521474.623</v>
       </c>
       <c r="H1434" t="inlineStr"/>
     </row>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="F1436" t="inlineStr"/>
       <c r="G1436" t="n">
-        <v>50103335.307</v>
+        <v>50103341.307</v>
       </c>
       <c r="H1436" t="inlineStr"/>
     </row>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="F1437" t="inlineStr"/>
       <c r="G1437" t="n">
-        <v>50820831.53</v>
+        <v>50820833.53</v>
       </c>
       <c r="H1437" t="inlineStr"/>
     </row>
@@ -31640,7 +31640,7 @@
       </c>
       <c r="F1438" t="inlineStr"/>
       <c r="G1438" t="n">
-        <v>50065784.981</v>
+        <v>50065829.981</v>
       </c>
       <c r="H1438" t="inlineStr"/>
     </row>
@@ -31662,7 +31662,7 @@
       </c>
       <c r="F1439" t="inlineStr"/>
       <c r="G1439" t="n">
-        <v>49910312.76</v>
+        <v>49910313.76</v>
       </c>
       <c r="H1439" t="inlineStr"/>
     </row>
@@ -31684,7 +31684,7 @@
       </c>
       <c r="F1440" t="inlineStr"/>
       <c r="G1440" t="n">
-        <v>49824712.195</v>
+        <v>49824719.195</v>
       </c>
       <c r="H1440" t="inlineStr"/>
     </row>
@@ -31706,7 +31706,7 @@
       </c>
       <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="n">
-        <v>49572872.045</v>
+        <v>49572899.045</v>
       </c>
       <c r="H1441" t="inlineStr"/>
     </row>
@@ -31728,7 +31728,7 @@
       </c>
       <c r="F1442" t="inlineStr"/>
       <c r="G1442" t="n">
-        <v>50116478.504</v>
+        <v>50116482.504</v>
       </c>
       <c r="H1442" t="inlineStr"/>
     </row>
@@ -31750,7 +31750,7 @@
       </c>
       <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="n">
-        <v>51564736.942</v>
+        <v>51564746.942</v>
       </c>
       <c r="H1443" t="inlineStr"/>
     </row>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="n">
-        <v>56166477.43</v>
+        <v>56166474.43</v>
       </c>
       <c r="H1461" t="inlineStr"/>
     </row>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65308917.61</v>
+        <v>65306830.61</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -32622,7 +32622,7 @@
       </c>
       <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="n">
-        <v>64570686.281</v>
+        <v>64564582.281</v>
       </c>
       <c r="H1483" t="inlineStr"/>
     </row>
@@ -32644,7 +32644,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61922589.993</v>
+        <v>61890800.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32666,7 +32666,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61171495.519</v>
+        <v>61171533.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -32688,7 +32688,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61772229.076</v>
+        <v>61722932.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32710,7 +32710,7 @@
       </c>
       <c r="F1487" t="inlineStr"/>
       <c r="G1487" t="n">
-        <v>60494236.004</v>
+        <v>60467765.004</v>
       </c>
       <c r="H1487" t="inlineStr"/>
     </row>
@@ -32732,7 +32732,7 @@
       </c>
       <c r="F1488" t="inlineStr"/>
       <c r="G1488" t="n">
-        <v>59514024.211</v>
+        <v>59514038.211</v>
       </c>
       <c r="H1488" t="inlineStr"/>
     </row>
@@ -32754,7 +32754,7 @@
       </c>
       <c r="F1489" t="inlineStr"/>
       <c r="G1489" t="n">
-        <v>57923945.381</v>
+        <v>57792547.381</v>
       </c>
       <c r="H1489" t="inlineStr"/>
     </row>
@@ -32776,7 +32776,7 @@
       </c>
       <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="n">
-        <v>57294196.101</v>
+        <v>57201233.101</v>
       </c>
       <c r="H1490" t="inlineStr"/>
     </row>
@@ -32798,7 +32798,7 @@
       </c>
       <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="n">
-        <v>57150504.244</v>
+        <v>57129183.244</v>
       </c>
       <c r="H1491" t="inlineStr"/>
     </row>
@@ -32842,7 +32842,7 @@
       </c>
       <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="n">
-        <v>56304830.088</v>
+        <v>56278446.088</v>
       </c>
       <c r="H1493" t="inlineStr"/>
     </row>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="n">
-        <v>55619308.47</v>
+        <v>55609088.47</v>
       </c>
       <c r="H1494" t="inlineStr"/>
     </row>
@@ -32886,7 +32886,7 @@
       </c>
       <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="n">
-        <v>55472262.492</v>
+        <v>55441553.492</v>
       </c>
       <c r="H1495" t="inlineStr"/>
     </row>
@@ -32908,7 +32908,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55281773.796</v>
+        <v>55270668.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="n">
-        <v>54745006.758</v>
+        <v>54730852.758</v>
       </c>
       <c r="H1498" t="inlineStr"/>
     </row>
@@ -32974,7 +32974,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54891516.349</v>
+        <v>54882455.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -32996,7 +32996,7 @@
       </c>
       <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="n">
-        <v>55154671.773</v>
+        <v>55143191.773</v>
       </c>
       <c r="H1500" t="inlineStr"/>
     </row>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="n">
-        <v>55910615.062</v>
+        <v>55902574.062</v>
       </c>
       <c r="H1501" t="inlineStr"/>
     </row>
@@ -33040,7 +33040,7 @@
       </c>
       <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="n">
-        <v>57600386.416</v>
+        <v>57593493.416</v>
       </c>
       <c r="H1502" t="inlineStr"/>
     </row>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60123806.451</v>
+        <v>60126514.867</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33122,7 +33122,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58346511.213</v>
+        <v>58347586.213</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58621586.727</v>
+        <v>58584047.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33166,7 +33166,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59728464.587</v>
+        <v>59669950.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58023379.8</v>
+        <v>58024518.8</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57262947.786</v>
+        <v>57264087.786</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33232,7 +33232,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56144479.11</v>
+        <v>56145678.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56459959.744</v>
+        <v>56460309.744</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55872022.876</v>
+        <v>55872372.876</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33298,7 +33298,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55653355.799</v>
+        <v>55629131.143</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55628089.185</v>
+        <v>55628650.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33342,7 +33342,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55673366.325</v>
+        <v>55674183.733</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33364,7 +33364,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55267186.56</v>
+        <v>55246747.15</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33386,7 +33386,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55301168.252</v>
+        <v>55300914.162</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33408,7 +33408,7 @@
       </c>
       <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="n">
-        <v>54751669.522</v>
+        <v>54752343.928</v>
       </c>
       <c r="H1519" t="inlineStr"/>
     </row>
@@ -33430,7 +33430,7 @@
       </c>
       <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="n">
-        <v>55619159.751</v>
+        <v>55615409.663</v>
       </c>
       <c r="H1520" t="inlineStr"/>
     </row>
@@ -33452,7 +33452,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57379642.285</v>
+        <v>57365625.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33474,7 +33474,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60241913.034</v>
+        <v>60258998.464</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33490,7 +33490,9 @@
         <v>22.3</v>
       </c>
       <c r="G1523" t="inlineStr"/>
-      <c r="H1523" t="inlineStr"/>
+      <c r="H1523" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="1524">
       <c r="A1524" s="2" t="n">
@@ -33510,7 +33512,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59240937.17</v>
+        <v>59185206.332</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33532,7 +33534,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58662705.075</v>
+        <v>58630095.585</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33553,15 +33555,21 @@
         <v>28.4375</v>
       </c>
       <c r="F1526" t="inlineStr"/>
-      <c r="G1526" t="inlineStr"/>
+      <c r="G1526" t="n">
+        <v>58657390.15</v>
+      </c>
       <c r="H1526" t="inlineStr"/>
     </row>
     <row r="1527">
       <c r="A1527" s="2" t="n">
         <v>46086</v>
       </c>
-      <c r="B1527" t="inlineStr"/>
-      <c r="C1527" t="inlineStr"/>
+      <c r="B1527" t="n">
+        <v>45825</v>
+      </c>
+      <c r="C1527" t="n">
+        <v>42491784</v>
+      </c>
       <c r="D1527" t="n">
         <v>1425.47</v>
       </c>
@@ -33569,22 +33577,148 @@
         <v>29.5</v>
       </c>
       <c r="F1527" t="inlineStr"/>
-      <c r="G1527" t="inlineStr"/>
+      <c r="G1527" t="n">
+        <v>59493716.987</v>
+      </c>
       <c r="H1527" t="inlineStr"/>
     </row>
     <row r="1528">
       <c r="A1528" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="B1528" t="inlineStr"/>
-      <c r="C1528" t="inlineStr"/>
+      <c r="B1528" t="n">
+        <v>46011</v>
+      </c>
+      <c r="C1528" t="n">
+        <v>42327455</v>
+      </c>
       <c r="D1528" t="n">
         <v>1436.18</v>
       </c>
-      <c r="E1528" t="inlineStr"/>
+      <c r="E1528" t="n">
+        <v>28.3125</v>
+      </c>
       <c r="F1528" t="inlineStr"/>
-      <c r="G1528" t="inlineStr"/>
+      <c r="G1528" t="n">
+        <v>57857771.996</v>
+      </c>
       <c r="H1528" t="inlineStr"/>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B1529" t="n">
+        <v>45767</v>
+      </c>
+      <c r="C1529" t="n">
+        <v>41337760</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>1440.91</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F1529" t="inlineStr"/>
+      <c r="G1529" t="n">
+        <v>57159241.72</v>
+      </c>
+      <c r="H1529" t="inlineStr"/>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1530" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C1530" t="n">
+        <v>40799134</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>1421.51</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>29.3125</v>
+      </c>
+      <c r="F1530" t="inlineStr"/>
+      <c r="G1530" t="n">
+        <v>56231677.504</v>
+      </c>
+      <c r="H1530" t="inlineStr"/>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1531" t="n">
+        <v>45770</v>
+      </c>
+      <c r="C1531" t="n">
+        <v>40736856</v>
+      </c>
+      <c r="D1531" t="n">
+        <v>1418.04</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>29</v>
+      </c>
+      <c r="F1531" t="inlineStr"/>
+      <c r="G1531" t="n">
+        <v>56032678.786</v>
+      </c>
+      <c r="H1531" t="inlineStr"/>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1532" t="n">
+        <v>45766</v>
+      </c>
+      <c r="C1532" t="n">
+        <v>41407606</v>
+      </c>
+      <c r="D1532" t="n">
+        <v>1419.08</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>29.375</v>
+      </c>
+      <c r="F1532" t="inlineStr"/>
+      <c r="G1532" t="inlineStr"/>
+      <c r="H1532" t="inlineStr"/>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1533" t="inlineStr"/>
+      <c r="C1533" t="inlineStr"/>
+      <c r="D1533" t="n">
+        <v>1415.85</v>
+      </c>
+      <c r="E1533" t="n">
+        <v>28.5625</v>
+      </c>
+      <c r="F1533" t="inlineStr"/>
+      <c r="G1533" t="inlineStr"/>
+      <c r="H1533" t="inlineStr"/>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1534" t="inlineStr"/>
+      <c r="C1534" t="inlineStr"/>
+      <c r="D1534" t="n">
+        <v>1417.58</v>
+      </c>
+      <c r="E1534" t="inlineStr"/>
+      <c r="F1534" t="inlineStr"/>
+      <c r="G1534" t="inlineStr"/>
+      <c r="H1534" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1534"/>
+  <dimension ref="A1:H1538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10869,7 +10869,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.48</v>
+        <v>108.29</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10891,7 +10891,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.61</v>
+        <v>108.48</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10913,7 +10913,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.63</v>
+        <v>108.61</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10935,7 +10935,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.72</v>
+        <v>108.63</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10957,7 +10957,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.86</v>
+        <v>108.72</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10979,7 +10979,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.96</v>
+        <v>108.86</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -11001,7 +11001,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.97</v>
+        <v>108.96</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11023,7 +11023,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>109.05</v>
+        <v>108.97</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11045,7 +11045,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.11</v>
+        <v>109.05</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11067,7 +11067,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.21</v>
+        <v>109.11</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11089,7 +11089,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.46</v>
+        <v>109.21</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11111,7 +11111,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.64</v>
+        <v>109.46</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11133,7 +11133,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.67</v>
+        <v>109.64</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11155,7 +11155,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.71</v>
+        <v>109.67</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11177,7 +11177,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.79</v>
+        <v>109.71</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11199,7 +11199,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>110.08</v>
+        <v>109.79</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11221,7 +11221,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.11</v>
+        <v>110.08</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11243,7 +11243,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.15</v>
+        <v>110.11</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11265,7 +11265,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.5</v>
+        <v>110.15</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11287,7 +11287,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.68</v>
+        <v>110.5</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11309,7 +11309,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.71</v>
+        <v>110.68</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11335,7 +11335,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11357,7 +11357,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.92</v>
+        <v>110.75</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11401,7 +11401,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>111.37</v>
+        <v>110.92</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11423,7 +11423,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.46</v>
+        <v>111.37</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11445,7 +11445,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.49</v>
+        <v>111.46</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11467,7 +11467,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.52</v>
+        <v>111.49</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11489,7 +11489,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.59</v>
+        <v>111.52</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11511,7 +11511,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.67</v>
+        <v>111.59</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11533,7 +11533,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>112.01</v>
+        <v>111.67</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11555,7 +11555,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.17</v>
+        <v>112.01</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11577,7 +11577,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.21</v>
+        <v>112.17</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11599,7 +11599,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.24</v>
+        <v>112.21</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11621,7 +11621,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.48</v>
+        <v>112.24</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11643,7 +11643,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.71</v>
+        <v>112.48</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11665,7 +11665,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.8</v>
+        <v>112.71</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11687,7 +11687,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.83</v>
+        <v>112.8</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11709,7 +11709,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.89</v>
+        <v>112.83</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11731,7 +11731,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.95</v>
+        <v>112.89</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -31798,7 +31798,7 @@
       </c>
       <c r="F1445" t="inlineStr"/>
       <c r="G1445" t="n">
-        <v>53501658.301</v>
+        <v>53502060.301</v>
       </c>
       <c r="H1445" t="inlineStr"/>
     </row>
@@ -31820,7 +31820,7 @@
       </c>
       <c r="F1446" t="inlineStr"/>
       <c r="G1446" t="n">
-        <v>53072198.662</v>
+        <v>53072225.662</v>
       </c>
       <c r="H1446" t="inlineStr"/>
     </row>
@@ -31842,7 +31842,7 @@
       </c>
       <c r="F1447" t="inlineStr"/>
       <c r="G1447" t="n">
-        <v>53737528.632</v>
+        <v>53737540.632</v>
       </c>
       <c r="H1447" t="inlineStr"/>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="F1448" t="inlineStr"/>
       <c r="G1448" t="n">
-        <v>53004483.148</v>
+        <v>53004506.148</v>
       </c>
       <c r="H1448" t="inlineStr"/>
     </row>
@@ -31886,7 +31886,7 @@
       </c>
       <c r="F1449" t="inlineStr"/>
       <c r="G1449" t="n">
-        <v>51790325.271</v>
+        <v>51790346.271</v>
       </c>
       <c r="H1449" t="inlineStr"/>
     </row>
@@ -31908,7 +31908,7 @@
       </c>
       <c r="F1450" t="inlineStr"/>
       <c r="G1450" t="n">
-        <v>50291580.976</v>
+        <v>50291607.976</v>
       </c>
       <c r="H1450" t="inlineStr"/>
     </row>
@@ -31930,7 +31930,7 @@
       </c>
       <c r="F1451" t="inlineStr"/>
       <c r="G1451" t="n">
-        <v>50852504.288</v>
+        <v>50852514.288</v>
       </c>
       <c r="H1451" t="inlineStr"/>
     </row>
@@ -31952,7 +31952,7 @@
       </c>
       <c r="F1452" t="inlineStr"/>
       <c r="G1452" t="n">
-        <v>50583314.336</v>
+        <v>50583333.336</v>
       </c>
       <c r="H1452" t="inlineStr"/>
     </row>
@@ -31974,7 +31974,7 @@
       </c>
       <c r="F1453" t="inlineStr"/>
       <c r="G1453" t="n">
-        <v>50577504.135</v>
+        <v>50577508.135</v>
       </c>
       <c r="H1453" t="inlineStr"/>
     </row>
@@ -31996,7 +31996,7 @@
       </c>
       <c r="F1454" t="inlineStr"/>
       <c r="G1454" t="n">
-        <v>50392233.524</v>
+        <v>50392239.524</v>
       </c>
       <c r="H1454" t="inlineStr"/>
     </row>
@@ -32018,7 +32018,7 @@
       </c>
       <c r="F1455" t="inlineStr"/>
       <c r="G1455" t="n">
-        <v>50230129.389</v>
+        <v>50230135.389</v>
       </c>
       <c r="H1455" t="inlineStr"/>
     </row>
@@ -32040,7 +32040,7 @@
       </c>
       <c r="F1456" t="inlineStr"/>
       <c r="G1456" t="n">
-        <v>50046773.804</v>
+        <v>50046797.804</v>
       </c>
       <c r="H1456" t="inlineStr"/>
     </row>
@@ -32062,7 +32062,7 @@
       </c>
       <c r="F1457" t="inlineStr"/>
       <c r="G1457" t="n">
-        <v>50642294.035</v>
+        <v>50642301.035</v>
       </c>
       <c r="H1457" t="inlineStr"/>
     </row>
@@ -32084,7 +32084,7 @@
       </c>
       <c r="F1458" t="inlineStr"/>
       <c r="G1458" t="n">
-        <v>51436730.263</v>
+        <v>51436763.263</v>
       </c>
       <c r="H1458" t="inlineStr"/>
     </row>
@@ -32106,7 +32106,7 @@
       </c>
       <c r="F1459" t="inlineStr"/>
       <c r="G1459" t="n">
-        <v>51920332.288</v>
+        <v>51920335.288</v>
       </c>
       <c r="H1459" t="inlineStr"/>
     </row>
@@ -32128,7 +32128,7 @@
       </c>
       <c r="F1460" t="inlineStr"/>
       <c r="G1460" t="n">
-        <v>53301783.364</v>
+        <v>53301794.364</v>
       </c>
       <c r="H1460" t="inlineStr"/>
     </row>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65306830.61</v>
+        <v>65307419.61</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -32622,7 +32622,7 @@
       </c>
       <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="n">
-        <v>64564582.281</v>
+        <v>64565663.281</v>
       </c>
       <c r="H1483" t="inlineStr"/>
     </row>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60126514.867</v>
+        <v>60129333.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33430,7 +33430,7 @@
       </c>
       <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="n">
-        <v>55615409.663</v>
+        <v>55611791.663</v>
       </c>
       <c r="H1520" t="inlineStr"/>
     </row>
@@ -33452,7 +33452,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57365625.612</v>
+        <v>57362057.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33474,7 +33474,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60258998.464</v>
+        <v>60268120.435</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33512,7 +33512,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59185206.332</v>
+        <v>59181531.332</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33534,7 +33534,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58630095.585</v>
+        <v>58626421.585</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58657390.15</v>
+        <v>58656769.15</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33578,7 +33578,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59493716.987</v>
+        <v>59433683.943</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33600,7 +33600,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57857771.996</v>
+        <v>57837850.784</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33622,7 +33622,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57159241.72</v>
+        <v>57131000.247</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33644,7 +33644,7 @@
       </c>
       <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="n">
-        <v>56231677.504</v>
+        <v>56136907.157</v>
       </c>
       <c r="H1530" t="inlineStr"/>
     </row>
@@ -33666,7 +33666,7 @@
       </c>
       <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="n">
-        <v>56032678.786</v>
+        <v>56027745.441</v>
       </c>
       <c r="H1531" t="inlineStr"/>
     </row>
@@ -33687,15 +33687,21 @@
         <v>29.375</v>
       </c>
       <c r="F1532" t="inlineStr"/>
-      <c r="G1532" t="inlineStr"/>
+      <c r="G1532" t="n">
+        <v>55941930.643</v>
+      </c>
       <c r="H1532" t="inlineStr"/>
     </row>
     <row r="1533">
       <c r="A1533" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="B1533" t="inlineStr"/>
-      <c r="C1533" t="inlineStr"/>
+      <c r="B1533" t="n">
+        <v>45661</v>
+      </c>
+      <c r="C1533" t="n">
+        <v>41185271</v>
+      </c>
       <c r="D1533" t="n">
         <v>1415.85</v>
       </c>
@@ -33703,22 +33709,104 @@
         <v>28.5625</v>
       </c>
       <c r="F1533" t="inlineStr"/>
-      <c r="G1533" t="inlineStr"/>
+      <c r="G1533" t="n">
+        <v>56199949.573</v>
+      </c>
       <c r="H1533" t="inlineStr"/>
     </row>
     <row r="1534">
       <c r="A1534" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="B1534" t="inlineStr"/>
-      <c r="C1534" t="inlineStr"/>
+      <c r="B1534" t="n">
+        <v>44790</v>
+      </c>
+      <c r="C1534" t="n">
+        <v>40219575</v>
+      </c>
       <c r="D1534" t="n">
         <v>1417.58</v>
       </c>
-      <c r="E1534" t="inlineStr"/>
+      <c r="E1534" t="n">
+        <v>28.5625</v>
+      </c>
       <c r="F1534" t="inlineStr"/>
-      <c r="G1534" t="inlineStr"/>
+      <c r="G1534" t="n">
+        <v>55902053.859</v>
+      </c>
       <c r="H1534" t="inlineStr"/>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1535" t="n">
+        <v>44722</v>
+      </c>
+      <c r="C1535" t="n">
+        <v>39541393</v>
+      </c>
+      <c r="D1535" t="n">
+        <v>1422.26</v>
+      </c>
+      <c r="E1535" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="F1535" t="inlineStr"/>
+      <c r="G1535" t="n">
+        <v>55057119.921</v>
+      </c>
+      <c r="H1535" t="inlineStr"/>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1536" t="n">
+        <v>44495</v>
+      </c>
+      <c r="C1536" t="n">
+        <v>39026567</v>
+      </c>
+      <c r="D1536" t="n">
+        <v>1418.18</v>
+      </c>
+      <c r="E1536" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="F1536" t="inlineStr"/>
+      <c r="G1536" t="inlineStr"/>
+      <c r="H1536" t="inlineStr"/>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1537" t="inlineStr"/>
+      <c r="C1537" t="inlineStr"/>
+      <c r="D1537" t="n">
+        <v>1416.66</v>
+      </c>
+      <c r="E1537" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F1537" t="inlineStr"/>
+      <c r="G1537" t="inlineStr"/>
+      <c r="H1537" t="inlineStr"/>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1538" t="inlineStr"/>
+      <c r="C1538" t="inlineStr"/>
+      <c r="D1538" t="n">
+        <v>1414.02</v>
+      </c>
+      <c r="E1538" t="inlineStr"/>
+      <c r="F1538" t="inlineStr"/>
+      <c r="G1538" t="inlineStr"/>
+      <c r="H1538" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1538"/>
+  <dimension ref="A1:H1541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10869,7 +10869,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.29</v>
+        <v>108.48</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10891,7 +10891,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.48</v>
+        <v>108.61</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10913,7 +10913,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.61</v>
+        <v>108.63</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10935,7 +10935,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.63</v>
+        <v>108.72</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10957,7 +10957,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.72</v>
+        <v>108.86</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10979,7 +10979,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.86</v>
+        <v>108.96</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -11001,7 +11001,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.96</v>
+        <v>108.97</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11023,7 +11023,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>108.97</v>
+        <v>109.05</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11045,7 +11045,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.05</v>
+        <v>109.11</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11067,7 +11067,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.11</v>
+        <v>109.21</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11089,7 +11089,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.21</v>
+        <v>109.46</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11111,7 +11111,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.46</v>
+        <v>109.64</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11133,7 +11133,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.64</v>
+        <v>109.67</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11155,7 +11155,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.67</v>
+        <v>109.71</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11177,7 +11177,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.71</v>
+        <v>109.79</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11199,7 +11199,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>109.79</v>
+        <v>110.08</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11221,7 +11221,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.08</v>
+        <v>110.11</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11243,7 +11243,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.11</v>
+        <v>110.15</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11265,7 +11265,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.15</v>
+        <v>110.5</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11287,7 +11287,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.5</v>
+        <v>110.68</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11309,7 +11309,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.68</v>
+        <v>110.71</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11335,7 +11335,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.71</v>
+        <v>110.75</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11357,7 +11357,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.75</v>
+        <v>110.92</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11401,7 +11401,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>110.92</v>
+        <v>111.37</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11423,7 +11423,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.37</v>
+        <v>111.46</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11445,7 +11445,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.46</v>
+        <v>111.49</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11467,7 +11467,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.49</v>
+        <v>111.52</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11489,7 +11489,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.52</v>
+        <v>111.59</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11511,7 +11511,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.59</v>
+        <v>111.67</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11533,7 +11533,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>111.67</v>
+        <v>112.01</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11555,7 +11555,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.01</v>
+        <v>112.17</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11577,7 +11577,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.17</v>
+        <v>112.21</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11599,7 +11599,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.21</v>
+        <v>112.24</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11621,7 +11621,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.24</v>
+        <v>112.48</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11643,7 +11643,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.48</v>
+        <v>112.71</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11665,7 +11665,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.71</v>
+        <v>112.8</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11687,7 +11687,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.8</v>
+        <v>112.83</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11709,7 +11709,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.83</v>
+        <v>112.89</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11731,7 +11731,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.89</v>
+        <v>112.95</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -27444,7 +27444,7 @@
       </c>
       <c r="F1248" t="inlineStr"/>
       <c r="G1248" t="n">
-        <v>45850028.058</v>
+        <v>45851403.058</v>
       </c>
       <c r="H1248" t="inlineStr"/>
     </row>
@@ -27932,7 +27932,7 @@
       </c>
       <c r="F1270" t="inlineStr"/>
       <c r="G1270" t="n">
-        <v>44366370.032</v>
+        <v>44364803.032</v>
       </c>
       <c r="H1270" t="inlineStr"/>
     </row>
@@ -28130,7 +28130,7 @@
       </c>
       <c r="F1279" t="inlineStr"/>
       <c r="G1279" t="n">
-        <v>46463143.168</v>
+        <v>46456855.168</v>
       </c>
       <c r="H1279" t="inlineStr"/>
     </row>
@@ -28554,7 +28554,7 @@
         <v>24.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>50397333.558</v>
+        <v>50397340.558</v>
       </c>
       <c r="H1298" t="n">
         <v>3.7</v>
@@ -28842,7 +28842,7 @@
       </c>
       <c r="F1311" t="inlineStr"/>
       <c r="G1311" t="n">
-        <v>46099706.74</v>
+        <v>46099051.74</v>
       </c>
       <c r="H1311" t="inlineStr"/>
     </row>
@@ -29286,7 +29286,7 @@
       </c>
       <c r="F1331" t="inlineStr"/>
       <c r="G1331" t="n">
-        <v>46113456.925</v>
+        <v>46112471.925</v>
       </c>
       <c r="H1331" t="inlineStr"/>
     </row>
@@ -29808,7 +29808,7 @@
       </c>
       <c r="F1355" t="inlineStr"/>
       <c r="G1355" t="n">
-        <v>52878081.995</v>
+        <v>52884083.995</v>
       </c>
       <c r="H1355" t="inlineStr"/>
     </row>
@@ -29944,7 +29944,7 @@
       </c>
       <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="n">
-        <v>56867685.839</v>
+        <v>56845127.839</v>
       </c>
       <c r="H1361" t="inlineStr"/>
     </row>
@@ -30120,7 +30120,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53014000.434</v>
+        <v>53027472.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30388,7 +30388,7 @@
       </c>
       <c r="F1381" t="inlineStr"/>
       <c r="G1381" t="n">
-        <v>55301191.451</v>
+        <v>55280766.451</v>
       </c>
       <c r="H1381" t="inlineStr"/>
     </row>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="F1409" t="inlineStr"/>
       <c r="G1409" t="n">
-        <v>51697351.007</v>
+        <v>51694778.007</v>
       </c>
       <c r="H1409" t="inlineStr"/>
     </row>
@@ -31706,7 +31706,7 @@
       </c>
       <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="n">
-        <v>49572899.045</v>
+        <v>49572968.045</v>
       </c>
       <c r="H1441" t="inlineStr"/>
     </row>
@@ -32128,7 +32128,7 @@
       </c>
       <c r="F1460" t="inlineStr"/>
       <c r="G1460" t="n">
-        <v>53301794.364</v>
+        <v>53428777.364</v>
       </c>
       <c r="H1460" t="inlineStr"/>
     </row>
@@ -32540,7 +32540,7 @@
       </c>
       <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="n">
-        <v>60741538.187</v>
+        <v>60737838.187</v>
       </c>
       <c r="H1479" t="inlineStr"/>
     </row>
@@ -32908,7 +32908,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55270668.796</v>
+        <v>55270560.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -33100,7 +33100,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59041853.841</v>
+        <v>59046331.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33232,7 +33232,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56145678.11</v>
+        <v>56145981.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33386,7 +33386,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55300914.162</v>
+        <v>55295684.162</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33474,7 +33474,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60268120.435</v>
+        <v>60323415.161</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33512,7 +33512,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59181531.332</v>
+        <v>59183835.726</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33534,7 +33534,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58626421.585</v>
+        <v>58628283.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33556,7 +33556,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58656769.15</v>
+        <v>58658918.045</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33578,7 +33578,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59433683.943</v>
+        <v>59434659.058</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33600,7 +33600,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57837850.784</v>
+        <v>57841671.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33622,7 +33622,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57131000.247</v>
+        <v>57131896.668</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33644,7 +33644,7 @@
       </c>
       <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="n">
-        <v>56136907.157</v>
+        <v>56155413.566</v>
       </c>
       <c r="H1530" t="inlineStr"/>
     </row>
@@ -33666,7 +33666,7 @@
       </c>
       <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="n">
-        <v>56027745.441</v>
+        <v>56042288.838</v>
       </c>
       <c r="H1531" t="inlineStr"/>
     </row>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55941930.643</v>
+        <v>55981559.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56199949.573</v>
+        <v>57182086.585</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33732,7 +33732,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55902053.859</v>
+        <v>55951832.971</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33754,7 +33754,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55057119.921</v>
+        <v>55098019.615</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33775,15 +33775,21 @@
         <v>26.875</v>
       </c>
       <c r="F1536" t="inlineStr"/>
-      <c r="G1536" t="inlineStr"/>
+      <c r="G1536" t="n">
+        <v>54572458.523</v>
+      </c>
       <c r="H1536" t="inlineStr"/>
     </row>
     <row r="1537">
       <c r="A1537" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="B1537" t="inlineStr"/>
-      <c r="C1537" t="inlineStr"/>
+      <c r="B1537" t="n">
+        <v>43713</v>
+      </c>
+      <c r="C1537" t="n">
+        <v>40008553</v>
+      </c>
       <c r="D1537" t="n">
         <v>1416.66</v>
       </c>
@@ -33791,22 +33797,82 @@
         <v>26.25</v>
       </c>
       <c r="F1537" t="inlineStr"/>
-      <c r="G1537" t="inlineStr"/>
+      <c r="G1537" t="n">
+        <v>54548188.249</v>
+      </c>
       <c r="H1537" t="inlineStr"/>
     </row>
     <row r="1538">
       <c r="A1538" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="B1538" t="inlineStr"/>
-      <c r="C1538" t="inlineStr"/>
+      <c r="B1538" t="n">
+        <v>43806</v>
+      </c>
+      <c r="C1538" t="n">
+        <v>40514585</v>
+      </c>
       <c r="D1538" t="n">
         <v>1414.02</v>
       </c>
-      <c r="E1538" t="inlineStr"/>
+      <c r="E1538" t="n">
+        <v>25.6875</v>
+      </c>
       <c r="F1538" t="inlineStr"/>
-      <c r="G1538" t="inlineStr"/>
+      <c r="G1538" t="n">
+        <v>54931152.1</v>
+      </c>
       <c r="H1538" t="inlineStr"/>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B1539" t="n">
+        <v>43841</v>
+      </c>
+      <c r="C1539" t="n">
+        <v>41175029</v>
+      </c>
+      <c r="D1539" t="n">
+        <v>1402.6</v>
+      </c>
+      <c r="E1539" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="F1539" t="inlineStr"/>
+      <c r="G1539" t="inlineStr"/>
+      <c r="H1539" t="inlineStr"/>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B1540" t="inlineStr"/>
+      <c r="C1540" t="inlineStr"/>
+      <c r="D1540" t="n">
+        <v>1392.39</v>
+      </c>
+      <c r="E1540" t="n">
+        <v>25.6875</v>
+      </c>
+      <c r="F1540" t="inlineStr"/>
+      <c r="G1540" t="inlineStr"/>
+      <c r="H1540" t="inlineStr"/>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B1541" t="inlineStr"/>
+      <c r="C1541" t="inlineStr"/>
+      <c r="D1541" t="n">
+        <v>1404.43</v>
+      </c>
+      <c r="E1541" t="inlineStr"/>
+      <c r="F1541" t="inlineStr"/>
+      <c r="G1541" t="inlineStr"/>
+      <c r="H1541" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1541"/>
+  <dimension ref="A1:H1542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10869,7 +10869,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.48</v>
+        <v>108.29</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10891,7 +10891,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.61</v>
+        <v>108.48</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10913,7 +10913,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.63</v>
+        <v>108.61</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10935,7 +10935,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.72</v>
+        <v>108.63</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10957,7 +10957,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.86</v>
+        <v>108.72</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10979,7 +10979,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.96</v>
+        <v>108.86</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -11001,7 +11001,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.97</v>
+        <v>108.96</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11023,7 +11023,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>109.05</v>
+        <v>108.97</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11045,7 +11045,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.11</v>
+        <v>109.05</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11067,7 +11067,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.21</v>
+        <v>109.11</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11089,7 +11089,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.46</v>
+        <v>109.21</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11111,7 +11111,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.64</v>
+        <v>109.46</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11133,7 +11133,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.67</v>
+        <v>109.64</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11155,7 +11155,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.71</v>
+        <v>109.67</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11177,7 +11177,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.79</v>
+        <v>109.71</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11199,7 +11199,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>110.08</v>
+        <v>109.79</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11221,7 +11221,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.11</v>
+        <v>110.08</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11243,7 +11243,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.15</v>
+        <v>110.11</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11265,7 +11265,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.5</v>
+        <v>110.15</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11287,7 +11287,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.68</v>
+        <v>110.5</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11309,7 +11309,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.71</v>
+        <v>110.68</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11335,7 +11335,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11357,7 +11357,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.92</v>
+        <v>110.75</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11401,7 +11401,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>111.37</v>
+        <v>110.92</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11423,7 +11423,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.46</v>
+        <v>111.37</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11445,7 +11445,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.49</v>
+        <v>111.46</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11467,7 +11467,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.52</v>
+        <v>111.49</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11489,7 +11489,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.59</v>
+        <v>111.52</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11511,7 +11511,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.67</v>
+        <v>111.59</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11533,7 +11533,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>112.01</v>
+        <v>111.67</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11555,7 +11555,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.17</v>
+        <v>112.01</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11577,7 +11577,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.21</v>
+        <v>112.17</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11599,7 +11599,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.24</v>
+        <v>112.21</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11621,7 +11621,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.48</v>
+        <v>112.24</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11643,7 +11643,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.71</v>
+        <v>112.48</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11665,7 +11665,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.8</v>
+        <v>112.71</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11687,7 +11687,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.83</v>
+        <v>112.8</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11709,7 +11709,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.89</v>
+        <v>112.83</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11731,7 +11731,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.95</v>
+        <v>112.89</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="F1273" t="inlineStr"/>
       <c r="G1273" t="n">
-        <v>44054294.14</v>
+        <v>44057000.14</v>
       </c>
       <c r="H1273" t="inlineStr"/>
     </row>
@@ -31196,7 +31196,7 @@
       </c>
       <c r="F1418" t="inlineStr"/>
       <c r="G1418" t="n">
-        <v>50598545.87</v>
+        <v>50628066.87</v>
       </c>
       <c r="H1418" t="inlineStr"/>
     </row>
@@ -31218,7 +31218,7 @@
       </c>
       <c r="F1419" t="inlineStr"/>
       <c r="G1419" t="n">
-        <v>51157559.993</v>
+        <v>51182478.993</v>
       </c>
       <c r="H1419" t="inlineStr"/>
     </row>
@@ -31750,7 +31750,7 @@
       </c>
       <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="n">
-        <v>51564746.942</v>
+        <v>51569146.942</v>
       </c>
       <c r="H1443" t="inlineStr"/>
     </row>
@@ -32128,7 +32128,7 @@
       </c>
       <c r="F1460" t="inlineStr"/>
       <c r="G1460" t="n">
-        <v>53428777.364</v>
+        <v>53303363.364</v>
       </c>
       <c r="H1460" t="inlineStr"/>
     </row>
@@ -32364,7 +32364,7 @@
       </c>
       <c r="F1471" t="inlineStr"/>
       <c r="G1471" t="n">
-        <v>55081107.553</v>
+        <v>55084943.553</v>
       </c>
       <c r="H1471" t="inlineStr"/>
     </row>
@@ -32644,7 +32644,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61890800.993</v>
+        <v>61891566.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32688,7 +32688,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61722932.076</v>
+        <v>61717759.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32820,7 +32820,7 @@
       </c>
       <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="n">
-        <v>57549505.399</v>
+        <v>57556557.399</v>
       </c>
       <c r="H1492" t="inlineStr"/>
     </row>
@@ -32842,7 +32842,7 @@
       </c>
       <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="n">
-        <v>56278446.088</v>
+        <v>56231542.088</v>
       </c>
       <c r="H1493" t="inlineStr"/>
     </row>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60129333.818</v>
+        <v>60130226.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33100,7 +33100,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59046331.841</v>
+        <v>59046653.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33122,7 +33122,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58347586.213</v>
+        <v>58347731.213</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33144,7 +33144,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58584047.727</v>
+        <v>58584994.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33166,7 +33166,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59669950.587</v>
+        <v>59670177.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58024518.8</v>
+        <v>58024789.8</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57264087.786</v>
+        <v>57264548.786</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33232,7 +33232,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56145981.11</v>
+        <v>56146237.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56460309.744</v>
+        <v>56460373.744</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55872372.876</v>
+        <v>55872398.876</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33298,7 +33298,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55629131.143</v>
+        <v>55629217.143</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55628650.479</v>
+        <v>55628892.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33342,7 +33342,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55674183.733</v>
+        <v>55674505.733</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33364,7 +33364,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55246747.15</v>
+        <v>55246756.15</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33386,7 +33386,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55295684.162</v>
+        <v>55295794.162</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33408,7 +33408,7 @@
       </c>
       <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="n">
-        <v>54752343.928</v>
+        <v>54752329.928</v>
       </c>
       <c r="H1519" t="inlineStr"/>
     </row>
@@ -33430,7 +33430,7 @@
       </c>
       <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="n">
-        <v>55611791.663</v>
+        <v>55612023.663</v>
       </c>
       <c r="H1520" t="inlineStr"/>
     </row>
@@ -33452,7 +33452,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57362057.612</v>
+        <v>57362158.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33474,7 +33474,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60323415.161</v>
+        <v>60314877.836</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33710,7 +33710,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>57182086.585</v>
+        <v>57181433.585</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33732,7 +33732,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55951832.971</v>
+        <v>55945733.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33754,7 +33754,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55098019.615</v>
+        <v>55098036.615</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33776,7 +33776,7 @@
       </c>
       <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="n">
-        <v>54572458.523</v>
+        <v>54572824.523</v>
       </c>
       <c r="H1536" t="inlineStr"/>
     </row>
@@ -33820,7 +33820,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54931152.1</v>
+        <v>54914169.986</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33841,15 +33841,21 @@
         <v>25.375</v>
       </c>
       <c r="F1539" t="inlineStr"/>
-      <c r="G1539" t="inlineStr"/>
+      <c r="G1539" t="n">
+        <v>56070015.35</v>
+      </c>
       <c r="H1539" t="inlineStr"/>
     </row>
     <row r="1540">
       <c r="A1540" s="2" t="n">
         <v>46107</v>
       </c>
-      <c r="B1540" t="inlineStr"/>
-      <c r="C1540" t="inlineStr"/>
+      <c r="B1540" t="n">
+        <v>43534</v>
+      </c>
+      <c r="C1540" t="n">
+        <v>40433607</v>
+      </c>
       <c r="D1540" t="n">
         <v>1392.39</v>
       </c>
@@ -33869,10 +33875,26 @@
       <c r="D1541" t="n">
         <v>1404.43</v>
       </c>
-      <c r="E1541" t="inlineStr"/>
+      <c r="E1541" t="n">
+        <v>24.8125</v>
+      </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="inlineStr"/>
       <c r="H1541" t="inlineStr"/>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B1542" t="inlineStr"/>
+      <c r="C1542" t="inlineStr"/>
+      <c r="D1542" t="n">
+        <v>1419.32</v>
+      </c>
+      <c r="E1542" t="inlineStr"/>
+      <c r="F1542" t="inlineStr"/>
+      <c r="G1542" t="inlineStr"/>
+      <c r="H1542" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1544"/>
+  <dimension ref="A1:H1549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.48</v>
+        <v>108.29</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.61</v>
+        <v>108.48</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.63</v>
+        <v>108.61</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.72</v>
+        <v>108.63</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.86</v>
+        <v>108.72</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.96</v>
+        <v>108.86</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.97</v>
+        <v>108.96</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>109.05</v>
+        <v>108.97</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.11</v>
+        <v>109.05</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.21</v>
+        <v>109.11</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.46</v>
+        <v>109.21</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.64</v>
+        <v>109.46</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.67</v>
+        <v>109.64</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.71</v>
+        <v>109.67</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.79</v>
+        <v>109.71</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>110.08</v>
+        <v>109.79</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.11</v>
+        <v>110.08</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.15</v>
+        <v>110.11</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.5</v>
+        <v>110.15</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.68</v>
+        <v>110.5</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.71</v>
+        <v>110.68</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.92</v>
+        <v>110.75</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>111.37</v>
+        <v>110.92</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.46</v>
+        <v>111.37</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.49</v>
+        <v>111.46</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.52</v>
+        <v>111.49</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.59</v>
+        <v>111.52</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.67</v>
+        <v>111.59</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>112.01</v>
+        <v>111.67</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.17</v>
+        <v>112.01</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.21</v>
+        <v>112.17</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.24</v>
+        <v>112.21</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.48</v>
+        <v>112.24</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.71</v>
+        <v>112.48</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.8</v>
+        <v>112.71</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.83</v>
+        <v>112.8</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.89</v>
+        <v>112.83</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.95</v>
+        <v>112.89</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -27234,7 +27234,7 @@
       </c>
       <c r="F1239" t="inlineStr"/>
       <c r="G1239" t="n">
-        <v>48766786.041</v>
+        <v>48765096.041</v>
       </c>
       <c r="H1239" t="inlineStr"/>
     </row>
@@ -27300,7 +27300,7 @@
       </c>
       <c r="F1242" t="inlineStr"/>
       <c r="G1242" t="n">
-        <v>47228280.385</v>
+        <v>47228254.385</v>
       </c>
       <c r="H1242" t="inlineStr"/>
     </row>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="F1243" t="inlineStr"/>
       <c r="G1243" t="n">
-        <v>46429946.055</v>
+        <v>46430013.055</v>
       </c>
       <c r="H1243" t="inlineStr"/>
     </row>
@@ -27366,7 +27366,7 @@
       </c>
       <c r="F1245" t="inlineStr"/>
       <c r="G1245" t="n">
-        <v>45679950.724</v>
+        <v>45681358.724</v>
       </c>
       <c r="H1245" t="inlineStr"/>
     </row>
@@ -27388,7 +27388,7 @@
       </c>
       <c r="F1246" t="inlineStr"/>
       <c r="G1246" t="n">
-        <v>44904105.327</v>
+        <v>44908079.327</v>
       </c>
       <c r="H1246" t="inlineStr"/>
     </row>
@@ -27410,7 +27410,7 @@
       </c>
       <c r="F1247" t="inlineStr"/>
       <c r="G1247" t="n">
-        <v>45025984.102</v>
+        <v>45025657.102</v>
       </c>
       <c r="H1247" t="inlineStr"/>
     </row>
@@ -27454,7 +27454,7 @@
       </c>
       <c r="F1249" t="inlineStr"/>
       <c r="G1249" t="n">
-        <v>45169820.93</v>
+        <v>45171259.93</v>
       </c>
       <c r="H1249" t="inlineStr"/>
     </row>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="F1255" t="inlineStr"/>
       <c r="G1255" t="n">
-        <v>43716381.877</v>
+        <v>43738863.877</v>
       </c>
       <c r="H1255" t="inlineStr"/>
     </row>
@@ -27608,7 +27608,7 @@
       </c>
       <c r="F1256" t="inlineStr"/>
       <c r="G1256" t="n">
-        <v>44214661.503</v>
+        <v>44205665.503</v>
       </c>
       <c r="H1256" t="inlineStr"/>
     </row>
@@ -27652,7 +27652,7 @@
       </c>
       <c r="F1258" t="inlineStr"/>
       <c r="G1258" t="n">
-        <v>44694997.844</v>
+        <v>44695331.844</v>
       </c>
       <c r="H1258" t="inlineStr"/>
     </row>
@@ -27832,7 +27832,7 @@
       </c>
       <c r="F1266" t="inlineStr"/>
       <c r="G1266" t="n">
-        <v>44761742.029</v>
+        <v>44762208.029</v>
       </c>
       <c r="H1266" t="inlineStr"/>
     </row>
@@ -28052,7 +28052,7 @@
       </c>
       <c r="F1276" t="inlineStr"/>
       <c r="G1276" t="n">
-        <v>43829604.898</v>
+        <v>43830120.898</v>
       </c>
       <c r="H1276" t="inlineStr"/>
     </row>
@@ -28142,7 +28142,7 @@
         <v>22.2</v>
       </c>
       <c r="G1280" t="n">
-        <v>48781028.892</v>
+        <v>48781319.892</v>
       </c>
       <c r="H1280" t="n">
         <v>2.4</v>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="F1281" t="inlineStr"/>
       <c r="G1281" t="n">
-        <v>48131887.128</v>
+        <v>48132691.128</v>
       </c>
       <c r="H1281" t="inlineStr"/>
     </row>
@@ -28188,7 +28188,7 @@
       </c>
       <c r="F1282" t="inlineStr"/>
       <c r="G1282" t="n">
-        <v>48340419.475</v>
+        <v>48339918.475</v>
       </c>
       <c r="H1282" t="inlineStr"/>
     </row>
@@ -28210,7 +28210,7 @@
       </c>
       <c r="F1283" t="inlineStr"/>
       <c r="G1283" t="n">
-        <v>48345593.734</v>
+        <v>48345775.734</v>
       </c>
       <c r="H1283" t="inlineStr"/>
     </row>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="F1284" t="inlineStr"/>
       <c r="G1284" t="n">
-        <v>46578599.614</v>
+        <v>46579969.614</v>
       </c>
       <c r="H1284" t="inlineStr"/>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="F1285" t="inlineStr"/>
       <c r="G1285" t="n">
-        <v>46029754.384</v>
+        <v>46030984.384</v>
       </c>
       <c r="H1285" t="inlineStr"/>
     </row>
@@ -28276,7 +28276,7 @@
       </c>
       <c r="F1286" t="inlineStr"/>
       <c r="G1286" t="n">
-        <v>45861660.451</v>
+        <v>45862818.451</v>
       </c>
       <c r="H1286" t="inlineStr"/>
     </row>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="F1287" t="inlineStr"/>
       <c r="G1287" t="n">
-        <v>46142671.268</v>
+        <v>46142350.268</v>
       </c>
       <c r="H1287" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
       </c>
       <c r="F1288" t="inlineStr"/>
       <c r="G1288" t="n">
-        <v>46150972.624</v>
+        <v>46152081.624</v>
       </c>
       <c r="H1288" t="inlineStr"/>
     </row>
@@ -28342,7 +28342,7 @@
       </c>
       <c r="F1289" t="inlineStr"/>
       <c r="G1289" t="n">
-        <v>45435594.744</v>
+        <v>45436255.744</v>
       </c>
       <c r="H1289" t="inlineStr"/>
     </row>
@@ -28364,7 +28364,7 @@
       </c>
       <c r="F1290" t="inlineStr"/>
       <c r="G1290" t="n">
-        <v>45455745.72</v>
+        <v>45458495.72</v>
       </c>
       <c r="H1290" t="inlineStr"/>
     </row>
@@ -28386,7 +28386,7 @@
       </c>
       <c r="F1291" t="inlineStr"/>
       <c r="G1291" t="n">
-        <v>45746743.502</v>
+        <v>45748113.502</v>
       </c>
       <c r="H1291" t="inlineStr"/>
     </row>
@@ -28408,7 +28408,7 @@
       </c>
       <c r="F1292" t="inlineStr"/>
       <c r="G1292" t="n">
-        <v>45677683.131</v>
+        <v>45678365.131</v>
       </c>
       <c r="H1292" t="inlineStr"/>
     </row>
@@ -28518,7 +28518,7 @@
       </c>
       <c r="F1297" t="inlineStr"/>
       <c r="G1297" t="n">
-        <v>47965209.473</v>
+        <v>47960107.473</v>
       </c>
       <c r="H1297" t="inlineStr"/>
     </row>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="F1318" t="inlineStr"/>
       <c r="G1318" t="n">
-        <v>50594917.384</v>
+        <v>50596284.384</v>
       </c>
       <c r="H1318" t="inlineStr"/>
     </row>
@@ -29054,7 +29054,7 @@
       </c>
       <c r="F1321" t="inlineStr"/>
       <c r="G1321" t="n">
-        <v>49887186.095</v>
+        <v>49899417.095</v>
       </c>
       <c r="H1321" t="inlineStr"/>
     </row>
@@ -29230,7 +29230,7 @@
       </c>
       <c r="F1329" t="inlineStr"/>
       <c r="G1329" t="n">
-        <v>45989235.839</v>
+        <v>45989440.839</v>
       </c>
       <c r="H1329" t="inlineStr"/>
     </row>
@@ -29598,7 +29598,7 @@
       </c>
       <c r="F1346" t="inlineStr"/>
       <c r="G1346" t="n">
-        <v>49437855.152</v>
+        <v>49433394.152</v>
       </c>
       <c r="H1346" t="inlineStr"/>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="F1351" t="inlineStr"/>
       <c r="G1351" t="n">
-        <v>49144270.391</v>
+        <v>49144215.391</v>
       </c>
       <c r="H1351" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="n">
-        <v>55337274.556</v>
+        <v>55335809.556</v>
       </c>
       <c r="H1363" t="inlineStr"/>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="n">
-        <v>53968442.241</v>
+        <v>53970696.241</v>
       </c>
       <c r="H1365" t="inlineStr"/>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53027472.434</v>
+        <v>53027151.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="n">
-        <v>52333858.713</v>
+        <v>52333645.713</v>
       </c>
       <c r="H1373" t="inlineStr"/>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="n">
-        <v>52874204.596</v>
+        <v>52877042.596</v>
       </c>
       <c r="H1374" t="inlineStr"/>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="n">
-        <v>52227412.178</v>
+        <v>52227623.178</v>
       </c>
       <c r="H1375" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="n">
-        <v>52827486.197</v>
+        <v>52828402.197</v>
       </c>
       <c r="H1377" t="inlineStr"/>
     </row>
@@ -30354,7 +30354,7 @@
       </c>
       <c r="F1380" t="inlineStr"/>
       <c r="G1380" t="n">
-        <v>56840706.779</v>
+        <v>56840496.779</v>
       </c>
       <c r="H1380" t="inlineStr"/>
     </row>
@@ -30464,7 +30464,7 @@
       </c>
       <c r="F1385" t="inlineStr"/>
       <c r="G1385" t="n">
-        <v>53822193.218</v>
+        <v>53824206.218</v>
       </c>
       <c r="H1385" t="inlineStr"/>
     </row>
@@ -30530,7 +30530,7 @@
       </c>
       <c r="F1388" t="inlineStr"/>
       <c r="G1388" t="n">
-        <v>51903016.889</v>
+        <v>51904016.889</v>
       </c>
       <c r="H1388" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
       </c>
       <c r="F1389" t="inlineStr"/>
       <c r="G1389" t="n">
-        <v>51864075.679</v>
+        <v>51865804.679</v>
       </c>
       <c r="H1389" t="inlineStr"/>
     </row>
@@ -30596,7 +30596,7 @@
       </c>
       <c r="F1391" t="inlineStr"/>
       <c r="G1391" t="n">
-        <v>51341677.283</v>
+        <v>51341659.283</v>
       </c>
       <c r="H1391" t="inlineStr"/>
     </row>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="F1394" t="inlineStr"/>
       <c r="G1394" t="n">
-        <v>50246035.764</v>
+        <v>50246145.764</v>
       </c>
       <c r="H1394" t="inlineStr"/>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="F1395" t="inlineStr"/>
       <c r="G1395" t="n">
-        <v>50130525.563</v>
+        <v>50131151.563</v>
       </c>
       <c r="H1395" t="inlineStr"/>
     </row>
@@ -30728,7 +30728,7 @@
       </c>
       <c r="F1397" t="inlineStr"/>
       <c r="G1397" t="n">
-        <v>51055902.556</v>
+        <v>51059146.556</v>
       </c>
       <c r="H1397" t="inlineStr"/>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="F1398" t="inlineStr"/>
       <c r="G1398" t="n">
-        <v>51932544.644</v>
+        <v>51932140.644</v>
       </c>
       <c r="H1398" t="inlineStr"/>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="F1401" t="inlineStr"/>
       <c r="G1401" t="n">
-        <v>53404813.53</v>
+        <v>53408818.53</v>
       </c>
       <c r="H1401" t="inlineStr"/>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="F1408" t="inlineStr"/>
       <c r="G1408" t="n">
-        <v>51824247.154</v>
+        <v>51819755.154</v>
       </c>
       <c r="H1408" t="inlineStr"/>
     </row>
@@ -31030,7 +31030,7 @@
       </c>
       <c r="F1411" t="inlineStr"/>
       <c r="G1411" t="n">
-        <v>51306330.064</v>
+        <v>51305982.064</v>
       </c>
       <c r="H1411" t="inlineStr"/>
     </row>
@@ -31096,7 +31096,7 @@
       </c>
       <c r="F1414" t="inlineStr"/>
       <c r="G1414" t="n">
-        <v>50498304.477</v>
+        <v>50498118.477</v>
       </c>
       <c r="H1414" t="inlineStr"/>
     </row>
@@ -31162,7 +31162,7 @@
       </c>
       <c r="F1417" t="inlineStr"/>
       <c r="G1417" t="n">
-        <v>50355311.92</v>
+        <v>50356100.92</v>
       </c>
       <c r="H1417" t="inlineStr"/>
     </row>
@@ -31184,7 +31184,7 @@
       </c>
       <c r="F1418" t="inlineStr"/>
       <c r="G1418" t="n">
-        <v>50628066.87</v>
+        <v>50630935.87</v>
       </c>
       <c r="H1418" t="inlineStr"/>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="F1419" t="inlineStr"/>
       <c r="G1419" t="n">
-        <v>51182478.993</v>
+        <v>51167693.993</v>
       </c>
       <c r="H1419" t="inlineStr"/>
     </row>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="F1431" t="inlineStr"/>
       <c r="G1431" t="n">
-        <v>51986047.914</v>
+        <v>51990681.914</v>
       </c>
       <c r="H1431" t="inlineStr"/>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="F1433" t="inlineStr"/>
       <c r="G1433" t="n">
-        <v>51728729.388</v>
+        <v>51727748.388</v>
       </c>
       <c r="H1433" t="inlineStr"/>
     </row>
@@ -31584,7 +31584,7 @@
       </c>
       <c r="F1436" t="inlineStr"/>
       <c r="G1436" t="n">
-        <v>50103341.307</v>
+        <v>50100424.307</v>
       </c>
       <c r="H1436" t="inlineStr"/>
     </row>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="F1437" t="inlineStr"/>
       <c r="G1437" t="n">
-        <v>50820833.53</v>
+        <v>50820771.53</v>
       </c>
       <c r="H1437" t="inlineStr"/>
     </row>
@@ -31650,7 +31650,7 @@
       </c>
       <c r="F1439" t="inlineStr"/>
       <c r="G1439" t="n">
-        <v>49910313.76</v>
+        <v>49910336.76</v>
       </c>
       <c r="H1439" t="inlineStr"/>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="F1440" t="inlineStr"/>
       <c r="G1440" t="n">
-        <v>49824719.195</v>
+        <v>49825955.195</v>
       </c>
       <c r="H1440" t="inlineStr"/>
     </row>
@@ -31694,7 +31694,7 @@
       </c>
       <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="n">
-        <v>49572968.045</v>
+        <v>49568790.045</v>
       </c>
       <c r="H1441" t="inlineStr"/>
     </row>
@@ -31738,7 +31738,7 @@
       </c>
       <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="n">
-        <v>51569146.942</v>
+        <v>51571164.942</v>
       </c>
       <c r="H1443" t="inlineStr"/>
     </row>
@@ -31786,7 +31786,7 @@
       </c>
       <c r="F1445" t="inlineStr"/>
       <c r="G1445" t="n">
-        <v>53502060.301</v>
+        <v>53498509.301</v>
       </c>
       <c r="H1445" t="inlineStr"/>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F1446" t="inlineStr"/>
       <c r="G1446" t="n">
-        <v>53072225.662</v>
+        <v>53071317.662</v>
       </c>
       <c r="H1446" t="inlineStr"/>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="F1472" t="inlineStr"/>
       <c r="G1472" t="n">
-        <v>56298233.969</v>
+        <v>56296028.969</v>
       </c>
       <c r="H1472" t="inlineStr"/>
     </row>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="F1473" t="inlineStr"/>
       <c r="G1473" t="n">
-        <v>56136723.492</v>
+        <v>56134162.492</v>
       </c>
       <c r="H1473" t="inlineStr"/>
     </row>
@@ -32440,7 +32440,7 @@
       </c>
       <c r="F1475" t="inlineStr"/>
       <c r="G1475" t="n">
-        <v>58736971.611</v>
+        <v>58741348.611</v>
       </c>
       <c r="H1475" t="inlineStr"/>
     </row>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="F1476" t="inlineStr"/>
       <c r="G1476" t="n">
-        <v>59895856.293</v>
+        <v>59898395.293</v>
       </c>
       <c r="H1476" t="inlineStr"/>
     </row>
@@ -32484,7 +32484,7 @@
       </c>
       <c r="F1477" t="inlineStr"/>
       <c r="G1477" t="n">
-        <v>60304303.984</v>
+        <v>60281584.984</v>
       </c>
       <c r="H1477" t="inlineStr"/>
     </row>
@@ -32506,7 +32506,7 @@
       </c>
       <c r="F1478" t="inlineStr"/>
       <c r="G1478" t="n">
-        <v>60806293.024</v>
+        <v>60806417.024</v>
       </c>
       <c r="H1478" t="inlineStr"/>
     </row>
@@ -32528,7 +32528,7 @@
       </c>
       <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="n">
-        <v>60737838.187</v>
+        <v>60734875.187</v>
       </c>
       <c r="H1479" t="inlineStr"/>
     </row>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="F1480" t="inlineStr"/>
       <c r="G1480" t="n">
-        <v>62897209.684</v>
+        <v>62897937.684</v>
       </c>
       <c r="H1480" t="inlineStr"/>
     </row>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61891566.993</v>
+        <v>61853845.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61717759.076</v>
+        <v>61706880.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32852,7 +32852,7 @@
       </c>
       <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="n">
-        <v>55609088.47</v>
+        <v>55608630.47</v>
       </c>
       <c r="H1494" t="inlineStr"/>
     </row>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="n">
-        <v>55441553.492</v>
+        <v>55435079.492</v>
       </c>
       <c r="H1495" t="inlineStr"/>
     </row>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55270560.796</v>
+        <v>55264394.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="n">
-        <v>55035213.613</v>
+        <v>55027126.613</v>
       </c>
       <c r="H1497" t="inlineStr"/>
     </row>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="n">
-        <v>54730852.758</v>
+        <v>54727700.758</v>
       </c>
       <c r="H1498" t="inlineStr"/>
     </row>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54882455.349</v>
+        <v>54876143.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -32984,7 +32984,7 @@
       </c>
       <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="n">
-        <v>55142189.773</v>
+        <v>55137368.773</v>
       </c>
       <c r="H1500" t="inlineStr"/>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="n">
-        <v>55898445.062</v>
+        <v>55893047.062</v>
       </c>
       <c r="H1501" t="inlineStr"/>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="n">
-        <v>57595625.416</v>
+        <v>57587918.416</v>
       </c>
       <c r="H1502" t="inlineStr"/>
     </row>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60130226.818</v>
+        <v>60129534.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33088,7 +33088,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59046653.841</v>
+        <v>59038355.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58347731.213</v>
+        <v>58336916.213</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58584994.727</v>
+        <v>58570208.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59667832.587</v>
+        <v>59657919.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58024695.8</v>
+        <v>58025381.8</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57265515.786</v>
+        <v>57255982.786</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33220,7 +33220,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56146237.11</v>
+        <v>56136065.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56458943.744</v>
+        <v>56448200.744</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33264,7 +33264,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55873354.876</v>
+        <v>55863429.876</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33286,7 +33286,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55597132.143</v>
+        <v>55586646.143</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55628892.479</v>
+        <v>55620380.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55674505.733</v>
+        <v>55670424.733</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33352,7 +33352,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55246756.15</v>
+        <v>55240472.15</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33374,7 +33374,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55295794.162</v>
+        <v>55285760.162</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
       </c>
       <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="n">
-        <v>54751424.928</v>
+        <v>54744555.928</v>
       </c>
       <c r="H1519" t="inlineStr"/>
     </row>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="n">
-        <v>55611291.663</v>
+        <v>55604268.663</v>
       </c>
       <c r="H1520" t="inlineStr"/>
     </row>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57362158.612</v>
+        <v>57356463.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60315071.843</v>
+        <v>60390554.02</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59183835.726</v>
+        <v>59181117.726</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58638491.442</v>
+        <v>58637414.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58665807.045</v>
+        <v>58664731.045</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59434659.058</v>
+        <v>59433583.058</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33588,7 +33588,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57841671.899</v>
+        <v>57840730.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57124172.668</v>
+        <v>57123080.668</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33632,7 +33632,7 @@
       </c>
       <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="n">
-        <v>56155841.566</v>
+        <v>56154766.566</v>
       </c>
       <c r="H1530" t="inlineStr"/>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="n">
-        <v>56042289.838</v>
+        <v>56041214.838</v>
       </c>
       <c r="H1531" t="inlineStr"/>
     </row>
@@ -33676,7 +33676,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55981562.807</v>
+        <v>55968261.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56237095.122</v>
+        <v>56236020.122</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55943108.807</v>
+        <v>55942031.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55096759.219</v>
+        <v>55084085.219</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="n">
-        <v>54559499.642</v>
+        <v>54532004.642</v>
       </c>
       <c r="H1536" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54551575.249</v>
+        <v>54593054.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54923001.986</v>
+        <v>54964416.638</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="n">
-        <v>56075062.35</v>
+        <v>56159241.153</v>
       </c>
       <c r="H1539" t="inlineStr"/>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="n">
-        <v>55866894.169</v>
+        <v>55836276.813</v>
       </c>
       <c r="H1540" t="inlineStr"/>
     </row>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="n">
-        <v>55979678.508</v>
+        <v>56011673.566</v>
       </c>
       <c r="H1541" t="inlineStr"/>
     </row>
@@ -33895,38 +33895,150 @@
         <v>25.0625</v>
       </c>
       <c r="F1542" t="inlineStr"/>
-      <c r="G1542" t="inlineStr"/>
+      <c r="G1542" t="n">
+        <v>57927002.958</v>
+      </c>
       <c r="H1542" t="inlineStr"/>
     </row>
     <row r="1543">
       <c r="A1543" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="B1543" t="inlineStr"/>
-      <c r="C1543" t="inlineStr"/>
+      <c r="B1543" t="n">
+        <v>42052</v>
+      </c>
+      <c r="C1543" t="n">
+        <v>41277771</v>
+      </c>
       <c r="D1543" t="n">
         <v>1409.48</v>
       </c>
       <c r="E1543" t="n">
         <v>25.375</v>
       </c>
-      <c r="F1543" t="inlineStr"/>
-      <c r="G1543" t="inlineStr"/>
+      <c r="F1543" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G1543" t="n">
+        <v>60635811.102</v>
+      </c>
       <c r="H1543" t="inlineStr"/>
     </row>
     <row r="1544">
       <c r="A1544" s="1" t="n">
         <v>46113</v>
       </c>
-      <c r="B1544" t="inlineStr"/>
-      <c r="C1544" t="inlineStr"/>
+      <c r="B1544" t="n">
+        <v>44445</v>
+      </c>
+      <c r="C1544" t="n">
+        <v>42128666</v>
+      </c>
       <c r="D1544" t="n">
-        <v>1418.99</v>
-      </c>
-      <c r="E1544" t="inlineStr"/>
+        <v>1419.32</v>
+      </c>
+      <c r="E1544" t="n">
+        <v>25.1875</v>
+      </c>
       <c r="F1544" t="inlineStr"/>
-      <c r="G1544" t="inlineStr"/>
+      <c r="G1544" t="n">
+        <v>59372298.293</v>
+      </c>
       <c r="H1544" t="inlineStr"/>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B1545" t="n">
+        <v>44248</v>
+      </c>
+      <c r="C1545" t="n">
+        <v>41983916</v>
+      </c>
+      <c r="D1545" t="n">
+        <v>1416.6</v>
+      </c>
+      <c r="E1545" t="n">
+        <v>24.4375</v>
+      </c>
+      <c r="F1545" t="inlineStr"/>
+      <c r="G1545" t="n">
+        <v>58890732.38</v>
+      </c>
+      <c r="H1545" t="inlineStr"/>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B1546" t="n">
+        <v>44445</v>
+      </c>
+      <c r="C1546" t="n">
+        <v>41976449</v>
+      </c>
+      <c r="D1546" t="n">
+        <v>1418.78</v>
+      </c>
+      <c r="E1546" t="n">
+        <v>25.3125</v>
+      </c>
+      <c r="F1546" t="inlineStr"/>
+      <c r="G1546" t="n">
+        <v>58478470.921</v>
+      </c>
+      <c r="H1546" t="inlineStr"/>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B1547" t="n">
+        <v>44759</v>
+      </c>
+      <c r="C1547" t="n">
+        <v>41265125</v>
+      </c>
+      <c r="D1547" t="n">
+        <v>1412.02</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>24.9375</v>
+      </c>
+      <c r="F1547" t="inlineStr"/>
+      <c r="G1547" t="inlineStr"/>
+      <c r="H1547" t="inlineStr"/>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B1548" t="inlineStr"/>
+      <c r="C1548" t="inlineStr"/>
+      <c r="D1548" t="n">
+        <v>1409.92</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="F1548" t="inlineStr"/>
+      <c r="G1548" t="inlineStr"/>
+      <c r="H1548" t="inlineStr"/>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B1549" t="inlineStr"/>
+      <c r="C1549" t="inlineStr"/>
+      <c r="D1549" t="n">
+        <v>1399.42</v>
+      </c>
+      <c r="E1549" t="inlineStr"/>
+      <c r="F1549" t="inlineStr"/>
+      <c r="G1549" t="inlineStr"/>
+      <c r="H1549" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1549"/>
+  <dimension ref="A1:H1554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.29</v>
+        <v>108.48</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.48</v>
+        <v>108.61</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.61</v>
+        <v>108.63</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.63</v>
+        <v>108.72</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.72</v>
+        <v>108.86</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.86</v>
+        <v>108.96</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.96</v>
+        <v>108.97</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>108.97</v>
+        <v>109.05</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.05</v>
+        <v>109.11</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.11</v>
+        <v>109.21</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.21</v>
+        <v>109.46</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.46</v>
+        <v>109.64</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.64</v>
+        <v>109.67</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.67</v>
+        <v>109.71</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.71</v>
+        <v>109.79</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>109.79</v>
+        <v>110.08</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.08</v>
+        <v>110.11</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.11</v>
+        <v>110.15</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.15</v>
+        <v>110.5</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.5</v>
+        <v>110.68</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.68</v>
+        <v>110.71</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.71</v>
+        <v>110.75</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.75</v>
+        <v>110.92</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>110.92</v>
+        <v>111.37</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.37</v>
+        <v>111.46</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.46</v>
+        <v>111.49</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.49</v>
+        <v>111.52</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.52</v>
+        <v>111.59</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.59</v>
+        <v>111.67</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>111.67</v>
+        <v>112.01</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.01</v>
+        <v>112.17</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.17</v>
+        <v>112.21</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.21</v>
+        <v>112.24</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.24</v>
+        <v>112.48</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.48</v>
+        <v>112.71</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.71</v>
+        <v>112.8</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.8</v>
+        <v>112.83</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.83</v>
+        <v>112.89</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.89</v>
+        <v>112.95</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -27344,7 +27344,7 @@
       </c>
       <c r="F1244" t="inlineStr"/>
       <c r="G1244" t="n">
-        <v>46118961.769</v>
+        <v>46118039.769</v>
       </c>
       <c r="H1244" t="inlineStr"/>
     </row>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="F1248" t="inlineStr"/>
       <c r="G1248" t="n">
-        <v>45851403.058</v>
+        <v>45853149.058</v>
       </c>
       <c r="H1248" t="inlineStr"/>
     </row>
@@ -27520,7 +27520,7 @@
       </c>
       <c r="F1252" t="inlineStr"/>
       <c r="G1252" t="n">
-        <v>43856866.764</v>
+        <v>43857508.764</v>
       </c>
       <c r="H1252" t="inlineStr"/>
     </row>
@@ -27564,7 +27564,7 @@
       </c>
       <c r="F1254" t="inlineStr"/>
       <c r="G1254" t="n">
-        <v>43646564.643</v>
+        <v>43646668.643</v>
       </c>
       <c r="H1254" t="inlineStr"/>
     </row>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="F1255" t="inlineStr"/>
       <c r="G1255" t="n">
-        <v>43738863.877</v>
+        <v>43738927.877</v>
       </c>
       <c r="H1255" t="inlineStr"/>
     </row>
@@ -27608,7 +27608,7 @@
       </c>
       <c r="F1256" t="inlineStr"/>
       <c r="G1256" t="n">
-        <v>44205665.503</v>
+        <v>44204862.503</v>
       </c>
       <c r="H1256" t="inlineStr"/>
     </row>
@@ -27630,7 +27630,7 @@
       </c>
       <c r="F1257" t="inlineStr"/>
       <c r="G1257" t="n">
-        <v>44225494.241</v>
+        <v>44224105.241</v>
       </c>
       <c r="H1257" t="inlineStr"/>
     </row>
@@ -27652,7 +27652,7 @@
       </c>
       <c r="F1258" t="inlineStr"/>
       <c r="G1258" t="n">
-        <v>44695331.844</v>
+        <v>44694976.844</v>
       </c>
       <c r="H1258" t="inlineStr"/>
     </row>
@@ -27674,7 +27674,7 @@
       </c>
       <c r="F1259" t="inlineStr"/>
       <c r="G1259" t="n">
-        <v>45707231.753</v>
+        <v>45709831.753</v>
       </c>
       <c r="H1259" t="inlineStr"/>
     </row>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="F1281" t="inlineStr"/>
       <c r="G1281" t="n">
-        <v>48132691.128</v>
+        <v>48135143.128</v>
       </c>
       <c r="H1281" t="inlineStr"/>
     </row>
@@ -28188,7 +28188,7 @@
       </c>
       <c r="F1282" t="inlineStr"/>
       <c r="G1282" t="n">
-        <v>48339918.475</v>
+        <v>48342370.475</v>
       </c>
       <c r="H1282" t="inlineStr"/>
     </row>
@@ -28210,7 +28210,7 @@
       </c>
       <c r="F1283" t="inlineStr"/>
       <c r="G1283" t="n">
-        <v>48345775.734</v>
+        <v>48348228.734</v>
       </c>
       <c r="H1283" t="inlineStr"/>
     </row>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="F1284" t="inlineStr"/>
       <c r="G1284" t="n">
-        <v>46579969.614</v>
+        <v>46582422.614</v>
       </c>
       <c r="H1284" t="inlineStr"/>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="F1285" t="inlineStr"/>
       <c r="G1285" t="n">
-        <v>46030984.384</v>
+        <v>46033437.384</v>
       </c>
       <c r="H1285" t="inlineStr"/>
     </row>
@@ -28276,7 +28276,7 @@
       </c>
       <c r="F1286" t="inlineStr"/>
       <c r="G1286" t="n">
-        <v>45862818.451</v>
+        <v>45865271.451</v>
       </c>
       <c r="H1286" t="inlineStr"/>
     </row>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="F1287" t="inlineStr"/>
       <c r="G1287" t="n">
-        <v>46142350.268</v>
+        <v>46144803.268</v>
       </c>
       <c r="H1287" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
       </c>
       <c r="F1288" t="inlineStr"/>
       <c r="G1288" t="n">
-        <v>46152081.624</v>
+        <v>46154533.624</v>
       </c>
       <c r="H1288" t="inlineStr"/>
     </row>
@@ -28342,7 +28342,7 @@
       </c>
       <c r="F1289" t="inlineStr"/>
       <c r="G1289" t="n">
-        <v>45436255.744</v>
+        <v>45438707.744</v>
       </c>
       <c r="H1289" t="inlineStr"/>
     </row>
@@ -28364,7 +28364,7 @@
       </c>
       <c r="F1290" t="inlineStr"/>
       <c r="G1290" t="n">
-        <v>45458495.72</v>
+        <v>45460947.72</v>
       </c>
       <c r="H1290" t="inlineStr"/>
     </row>
@@ -28386,7 +28386,7 @@
       </c>
       <c r="F1291" t="inlineStr"/>
       <c r="G1291" t="n">
-        <v>45748113.502</v>
+        <v>45750566.502</v>
       </c>
       <c r="H1291" t="inlineStr"/>
     </row>
@@ -28408,7 +28408,7 @@
       </c>
       <c r="F1292" t="inlineStr"/>
       <c r="G1292" t="n">
-        <v>45678365.131</v>
+        <v>45680818.131</v>
       </c>
       <c r="H1292" t="inlineStr"/>
     </row>
@@ -28430,7 +28430,7 @@
       </c>
       <c r="F1293" t="inlineStr"/>
       <c r="G1293" t="n">
-        <v>45878863.473</v>
+        <v>45881315.473</v>
       </c>
       <c r="H1293" t="inlineStr"/>
     </row>
@@ -28452,7 +28452,7 @@
       </c>
       <c r="F1294" t="inlineStr"/>
       <c r="G1294" t="n">
-        <v>46100574.998</v>
+        <v>46103027.998</v>
       </c>
       <c r="H1294" t="inlineStr"/>
     </row>
@@ -28474,7 +28474,7 @@
       </c>
       <c r="F1295" t="inlineStr"/>
       <c r="G1295" t="n">
-        <v>46502788.702</v>
+        <v>46505241.702</v>
       </c>
       <c r="H1295" t="inlineStr"/>
     </row>
@@ -28496,7 +28496,7 @@
       </c>
       <c r="F1296" t="inlineStr"/>
       <c r="G1296" t="n">
-        <v>46837047.161</v>
+        <v>46839500.161</v>
       </c>
       <c r="H1296" t="inlineStr"/>
     </row>
@@ -28518,7 +28518,7 @@
       </c>
       <c r="F1297" t="inlineStr"/>
       <c r="G1297" t="n">
-        <v>47960107.473</v>
+        <v>47962559.473</v>
       </c>
       <c r="H1297" t="inlineStr"/>
     </row>
@@ -28542,7 +28542,7 @@
         <v>24.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>50397340.558</v>
+        <v>50399793.558</v>
       </c>
       <c r="H1298" t="n">
         <v>3.7</v>
@@ -28566,7 +28566,7 @@
       </c>
       <c r="F1299" t="inlineStr"/>
       <c r="G1299" t="n">
-        <v>50023535.041</v>
+        <v>50025987.041</v>
       </c>
       <c r="H1299" t="inlineStr"/>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="F1300" t="inlineStr"/>
       <c r="G1300" t="n">
-        <v>49203653.253</v>
+        <v>49206105.253</v>
       </c>
       <c r="H1300" t="inlineStr"/>
     </row>
@@ -28610,7 +28610,7 @@
       </c>
       <c r="F1301" t="inlineStr"/>
       <c r="G1301" t="n">
-        <v>49527733.809</v>
+        <v>49530185.809</v>
       </c>
       <c r="H1301" t="inlineStr"/>
     </row>
@@ -28632,7 +28632,7 @@
       </c>
       <c r="F1302" t="inlineStr"/>
       <c r="G1302" t="n">
-        <v>49335204.324</v>
+        <v>49337656.324</v>
       </c>
       <c r="H1302" t="inlineStr"/>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="F1303" t="inlineStr"/>
       <c r="G1303" t="n">
-        <v>48595321.632</v>
+        <v>48597774.632</v>
       </c>
       <c r="H1303" t="inlineStr"/>
     </row>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="F1304" t="inlineStr"/>
       <c r="G1304" t="n">
-        <v>48584600.939</v>
+        <v>48587053.939</v>
       </c>
       <c r="H1304" t="inlineStr"/>
     </row>
@@ -28698,7 +28698,7 @@
       </c>
       <c r="F1305" t="inlineStr"/>
       <c r="G1305" t="n">
-        <v>48401608.49</v>
+        <v>48404060.49</v>
       </c>
       <c r="H1305" t="inlineStr"/>
     </row>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="F1306" t="inlineStr"/>
       <c r="G1306" t="n">
-        <v>48280179.393</v>
+        <v>48282632.393</v>
       </c>
       <c r="H1306" t="inlineStr"/>
     </row>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="F1307" t="inlineStr"/>
       <c r="G1307" t="n">
-        <v>48072239.613</v>
+        <v>48074692.613</v>
       </c>
       <c r="H1307" t="inlineStr"/>
     </row>
@@ -28764,7 +28764,7 @@
       </c>
       <c r="F1308" t="inlineStr"/>
       <c r="G1308" t="n">
-        <v>48091703.875</v>
+        <v>48094155.875</v>
       </c>
       <c r="H1308" t="inlineStr"/>
     </row>
@@ -28786,7 +28786,7 @@
       </c>
       <c r="F1309" t="inlineStr"/>
       <c r="G1309" t="n">
-        <v>46986949.386</v>
+        <v>46989402.386</v>
       </c>
       <c r="H1309" t="inlineStr"/>
     </row>
@@ -28808,7 +28808,7 @@
       </c>
       <c r="F1310" t="inlineStr"/>
       <c r="G1310" t="n">
-        <v>46496712.28</v>
+        <v>46587857.28</v>
       </c>
       <c r="H1310" t="inlineStr"/>
     </row>
@@ -28830,7 +28830,7 @@
       </c>
       <c r="F1311" t="inlineStr"/>
       <c r="G1311" t="n">
-        <v>46099051.74</v>
+        <v>46101504.74</v>
       </c>
       <c r="H1311" t="inlineStr"/>
     </row>
@@ -28852,7 +28852,7 @@
       </c>
       <c r="F1312" t="inlineStr"/>
       <c r="G1312" t="n">
-        <v>45473416.696</v>
+        <v>45475868.696</v>
       </c>
       <c r="H1312" t="inlineStr"/>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="F1313" t="inlineStr"/>
       <c r="G1313" t="n">
-        <v>45517975.554</v>
+        <v>45520427.554</v>
       </c>
       <c r="H1313" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
       </c>
       <c r="F1314" t="inlineStr"/>
       <c r="G1314" t="n">
-        <v>45631839.123</v>
+        <v>45634291.123</v>
       </c>
       <c r="H1314" t="inlineStr"/>
     </row>
@@ -28918,7 +28918,7 @@
       </c>
       <c r="F1315" t="inlineStr"/>
       <c r="G1315" t="n">
-        <v>47020144.258</v>
+        <v>47022597.258</v>
       </c>
       <c r="H1315" t="inlineStr"/>
     </row>
@@ -28940,7 +28940,7 @@
       </c>
       <c r="F1316" t="inlineStr"/>
       <c r="G1316" t="n">
-        <v>48545880.287</v>
+        <v>48548333.287</v>
       </c>
       <c r="H1316" t="inlineStr"/>
     </row>
@@ -28964,7 +28964,7 @@
         <v>26.3</v>
       </c>
       <c r="G1317" t="n">
-        <v>51149230.522</v>
+        <v>51151683.522</v>
       </c>
       <c r="H1317" t="n">
         <v>2.8</v>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="F1318" t="inlineStr"/>
       <c r="G1318" t="n">
-        <v>50596284.384</v>
+        <v>50598736.384</v>
       </c>
       <c r="H1318" t="inlineStr"/>
     </row>
@@ -29010,7 +29010,7 @@
       </c>
       <c r="F1319" t="inlineStr"/>
       <c r="G1319" t="n">
-        <v>50057151.371</v>
+        <v>50059603.371</v>
       </c>
       <c r="H1319" t="inlineStr"/>
     </row>
@@ -29032,7 +29032,7 @@
       </c>
       <c r="F1320" t="inlineStr"/>
       <c r="G1320" t="n">
-        <v>50536857.593</v>
+        <v>50539310.593</v>
       </c>
       <c r="H1320" t="inlineStr"/>
     </row>
@@ -29054,7 +29054,7 @@
       </c>
       <c r="F1321" t="inlineStr"/>
       <c r="G1321" t="n">
-        <v>49899417.095</v>
+        <v>49901869.095</v>
       </c>
       <c r="H1321" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="F1322" t="inlineStr"/>
       <c r="G1322" t="n">
-        <v>48797306.5</v>
+        <v>48799759.5</v>
       </c>
       <c r="H1322" t="inlineStr"/>
     </row>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="F1323" t="inlineStr"/>
       <c r="G1323" t="n">
-        <v>47619995.888</v>
+        <v>47622448.888</v>
       </c>
       <c r="H1323" t="inlineStr"/>
     </row>
@@ -29120,7 +29120,7 @@
       </c>
       <c r="F1324" t="inlineStr"/>
       <c r="G1324" t="n">
-        <v>47083038.957</v>
+        <v>47085491.957</v>
       </c>
       <c r="H1324" t="inlineStr"/>
     </row>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="F1325" t="inlineStr"/>
       <c r="G1325" t="n">
-        <v>47068442.466</v>
+        <v>47070895.466</v>
       </c>
       <c r="H1325" t="inlineStr"/>
     </row>
@@ -29164,7 +29164,7 @@
       </c>
       <c r="F1326" t="inlineStr"/>
       <c r="G1326" t="n">
-        <v>47329015.259</v>
+        <v>47331467.259</v>
       </c>
       <c r="H1326" t="inlineStr"/>
     </row>
@@ -29186,7 +29186,7 @@
       </c>
       <c r="F1327" t="inlineStr"/>
       <c r="G1327" t="n">
-        <v>46639096.658</v>
+        <v>46641548.658</v>
       </c>
       <c r="H1327" t="inlineStr"/>
     </row>
@@ -29208,7 +29208,7 @@
       </c>
       <c r="F1328" t="inlineStr"/>
       <c r="G1328" t="n">
-        <v>46269941.919</v>
+        <v>46272394.919</v>
       </c>
       <c r="H1328" t="inlineStr"/>
     </row>
@@ -29230,7 +29230,7 @@
       </c>
       <c r="F1329" t="inlineStr"/>
       <c r="G1329" t="n">
-        <v>45989440.839</v>
+        <v>45991893.839</v>
       </c>
       <c r="H1329" t="inlineStr"/>
     </row>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="F1330" t="inlineStr"/>
       <c r="G1330" t="n">
-        <v>46119624.497</v>
+        <v>46122077.497</v>
       </c>
       <c r="H1330" t="inlineStr"/>
     </row>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="F1331" t="inlineStr"/>
       <c r="G1331" t="n">
-        <v>46112471.925</v>
+        <v>46114923.925</v>
       </c>
       <c r="H1331" t="inlineStr"/>
     </row>
@@ -29296,7 +29296,7 @@
       </c>
       <c r="F1332" t="inlineStr"/>
       <c r="G1332" t="n">
-        <v>45974704.945</v>
+        <v>45977156.945</v>
       </c>
       <c r="H1332" t="inlineStr"/>
     </row>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="F1333" t="inlineStr"/>
       <c r="G1333" t="n">
-        <v>46250497.278</v>
+        <v>46252950.278</v>
       </c>
       <c r="H1333" t="inlineStr"/>
     </row>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="F1334" t="inlineStr"/>
       <c r="G1334" t="n">
-        <v>46647670.056</v>
+        <v>46650122.056</v>
       </c>
       <c r="H1334" t="inlineStr"/>
     </row>
@@ -29362,7 +29362,7 @@
       </c>
       <c r="F1335" t="inlineStr"/>
       <c r="G1335" t="n">
-        <v>47638720.807</v>
+        <v>47641172.807</v>
       </c>
       <c r="H1335" t="inlineStr"/>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="F1336" t="inlineStr"/>
       <c r="G1336" t="n">
-        <v>48897638.485</v>
+        <v>48900090.485</v>
       </c>
       <c r="H1336" t="inlineStr"/>
     </row>
@@ -29406,7 +29406,7 @@
       </c>
       <c r="F1337" t="inlineStr"/>
       <c r="G1337" t="n">
-        <v>51145099.335</v>
+        <v>51147551.335</v>
       </c>
       <c r="H1337" t="inlineStr"/>
     </row>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="F1339" t="inlineStr"/>
       <c r="G1339" t="n">
-        <v>50299689.099</v>
+        <v>50302142.099</v>
       </c>
       <c r="H1339" t="inlineStr"/>
     </row>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="F1340" t="inlineStr"/>
       <c r="G1340" t="n">
-        <v>50141301.2</v>
+        <v>50143754.2</v>
       </c>
       <c r="H1340" t="inlineStr"/>
     </row>
@@ -29488,7 +29488,7 @@
       </c>
       <c r="F1341" t="inlineStr"/>
       <c r="G1341" t="n">
-        <v>50668620.622</v>
+        <v>50671072.622</v>
       </c>
       <c r="H1341" t="inlineStr"/>
     </row>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="F1342" t="inlineStr"/>
       <c r="G1342" t="n">
-        <v>51350944.846</v>
+        <v>51353396.846</v>
       </c>
       <c r="H1342" t="inlineStr"/>
     </row>
@@ -29532,7 +29532,7 @@
       </c>
       <c r="F1343" t="inlineStr"/>
       <c r="G1343" t="n">
-        <v>49829581.676</v>
+        <v>49832034.676</v>
       </c>
       <c r="H1343" t="inlineStr"/>
     </row>
@@ -29554,7 +29554,7 @@
       </c>
       <c r="F1344" t="inlineStr"/>
       <c r="G1344" t="n">
-        <v>49552856.468</v>
+        <v>49555309.468</v>
       </c>
       <c r="H1344" t="inlineStr"/>
     </row>
@@ -29576,7 +29576,7 @@
       </c>
       <c r="F1345" t="inlineStr"/>
       <c r="G1345" t="n">
-        <v>48961618.358</v>
+        <v>48964071.358</v>
       </c>
       <c r="H1345" t="inlineStr"/>
     </row>
@@ -29598,7 +29598,7 @@
       </c>
       <c r="F1346" t="inlineStr"/>
       <c r="G1346" t="n">
-        <v>49433394.152</v>
+        <v>49435847.152</v>
       </c>
       <c r="H1346" t="inlineStr"/>
     </row>
@@ -29620,7 +29620,7 @@
       </c>
       <c r="F1347" t="inlineStr"/>
       <c r="G1347" t="n">
-        <v>49105761.486</v>
+        <v>49108213.486</v>
       </c>
       <c r="H1347" t="inlineStr"/>
     </row>
@@ -29642,7 +29642,7 @@
       </c>
       <c r="F1348" t="inlineStr"/>
       <c r="G1348" t="n">
-        <v>49168402.452</v>
+        <v>49170854.452</v>
       </c>
       <c r="H1348" t="inlineStr"/>
     </row>
@@ -29664,7 +29664,7 @@
       </c>
       <c r="F1349" t="inlineStr"/>
       <c r="G1349" t="n">
-        <v>49234771.726</v>
+        <v>49237224.726</v>
       </c>
       <c r="H1349" t="inlineStr"/>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="F1350" t="inlineStr"/>
       <c r="G1350" t="n">
-        <v>49634201.914</v>
+        <v>49636653.914</v>
       </c>
       <c r="H1350" t="inlineStr"/>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="F1351" t="inlineStr"/>
       <c r="G1351" t="n">
-        <v>49144215.391</v>
+        <v>49146668.391</v>
       </c>
       <c r="H1351" t="inlineStr"/>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="F1352" t="inlineStr"/>
       <c r="G1352" t="n">
-        <v>49728194.724</v>
+        <v>49730646.724</v>
       </c>
       <c r="H1352" t="inlineStr"/>
     </row>
@@ -29752,7 +29752,7 @@
       </c>
       <c r="F1353" t="inlineStr"/>
       <c r="G1353" t="n">
-        <v>50200735.696</v>
+        <v>50203187.696</v>
       </c>
       <c r="H1353" t="inlineStr"/>
     </row>
@@ -29774,7 +29774,7 @@
       </c>
       <c r="F1354" t="inlineStr"/>
       <c r="G1354" t="n">
-        <v>50613649.767</v>
+        <v>50616102.767</v>
       </c>
       <c r="H1354" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
       </c>
       <c r="F1355" t="inlineStr"/>
       <c r="G1355" t="n">
-        <v>52884083.995</v>
+        <v>52886535.995</v>
       </c>
       <c r="H1355" t="inlineStr"/>
     </row>
@@ -29818,7 +29818,7 @@
       </c>
       <c r="F1356" t="inlineStr"/>
       <c r="G1356" t="n">
-        <v>53937382.682</v>
+        <v>53939835.682</v>
       </c>
       <c r="H1356" t="inlineStr"/>
     </row>
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57867722.056</v>
+        <v>57870174.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="n">
-        <v>56688386.267</v>
+        <v>56690839.267</v>
       </c>
       <c r="H1358" t="inlineStr"/>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="F1359" t="inlineStr"/>
       <c r="G1359" t="n">
-        <v>56048300.372</v>
+        <v>56050753.372</v>
       </c>
       <c r="H1359" t="inlineStr"/>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="n">
-        <v>56607258.504</v>
+        <v>56609711.504</v>
       </c>
       <c r="H1360" t="inlineStr"/>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="n">
-        <v>56845127.839</v>
+        <v>56847580.839</v>
       </c>
       <c r="H1361" t="inlineStr"/>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="n">
-        <v>55525806.571</v>
+        <v>55528259.571</v>
       </c>
       <c r="H1362" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="n">
-        <v>55335809.556</v>
+        <v>55338261.556</v>
       </c>
       <c r="H1363" t="inlineStr"/>
     </row>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="n">
-        <v>54549283.68</v>
+        <v>54551736.68</v>
       </c>
       <c r="H1364" t="inlineStr"/>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="n">
-        <v>53970696.241</v>
+        <v>53973149.241</v>
       </c>
       <c r="H1365" t="inlineStr"/>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="n">
-        <v>53578100.918</v>
+        <v>53580553.918</v>
       </c>
       <c r="H1366" t="inlineStr"/>
     </row>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F1367" t="inlineStr"/>
       <c r="G1367" t="n">
-        <v>53711893.53</v>
+        <v>53714345.53</v>
       </c>
       <c r="H1367" t="inlineStr"/>
     </row>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="n">
-        <v>52808306.228</v>
+        <v>52810758.228</v>
       </c>
       <c r="H1368" t="inlineStr"/>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53027151.434</v>
+        <v>53029604.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30130,7 +30130,7 @@
       </c>
       <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="n">
-        <v>52808582.166</v>
+        <v>52811035.166</v>
       </c>
       <c r="H1370" t="inlineStr"/>
     </row>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="F1371" t="inlineStr"/>
       <c r="G1371" t="n">
-        <v>52598271.418</v>
+        <v>52600723.418</v>
       </c>
       <c r="H1371" t="inlineStr"/>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="n">
-        <v>52238253.099</v>
+        <v>52240705.099</v>
       </c>
       <c r="H1372" t="inlineStr"/>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="n">
-        <v>52333645.713</v>
+        <v>52336098.713</v>
       </c>
       <c r="H1373" t="inlineStr"/>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="n">
-        <v>52877042.596</v>
+        <v>52879495.596</v>
       </c>
       <c r="H1374" t="inlineStr"/>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="n">
-        <v>52227623.178</v>
+        <v>52230075.178</v>
       </c>
       <c r="H1375" t="inlineStr"/>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="n">
-        <v>52608998.503</v>
+        <v>52611451.503</v>
       </c>
       <c r="H1376" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="n">
-        <v>52828402.197</v>
+        <v>52830854.197</v>
       </c>
       <c r="H1377" t="inlineStr"/>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="n">
-        <v>54101313.568</v>
+        <v>54103765.568</v>
       </c>
       <c r="H1378" t="inlineStr"/>
     </row>
@@ -30330,7 +30330,7 @@
         <v>21.1</v>
       </c>
       <c r="G1379" t="n">
-        <v>56529754.897</v>
+        <v>56532206.897</v>
       </c>
       <c r="H1379" t="n">
         <v>1.9</v>
@@ -30354,7 +30354,7 @@
       </c>
       <c r="F1380" t="inlineStr"/>
       <c r="G1380" t="n">
-        <v>56840496.779</v>
+        <v>56842949.779</v>
       </c>
       <c r="H1380" t="inlineStr"/>
     </row>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="F1381" t="inlineStr"/>
       <c r="G1381" t="n">
-        <v>55280766.451</v>
+        <v>55283219.451</v>
       </c>
       <c r="H1381" t="inlineStr"/>
     </row>
@@ -30398,7 +30398,7 @@
       </c>
       <c r="F1382" t="inlineStr"/>
       <c r="G1382" t="n">
-        <v>55322654.742</v>
+        <v>55325106.742</v>
       </c>
       <c r="H1382" t="inlineStr"/>
     </row>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="F1383" t="inlineStr"/>
       <c r="G1383" t="n">
-        <v>55597419.888</v>
+        <v>55599872.888</v>
       </c>
       <c r="H1383" t="inlineStr"/>
     </row>
@@ -30442,7 +30442,7 @@
       </c>
       <c r="F1384" t="inlineStr"/>
       <c r="G1384" t="n">
-        <v>55078570.049</v>
+        <v>55081022.049</v>
       </c>
       <c r="H1384" t="inlineStr"/>
     </row>
@@ -30464,7 +30464,7 @@
       </c>
       <c r="F1385" t="inlineStr"/>
       <c r="G1385" t="n">
-        <v>53824206.218</v>
+        <v>53826659.218</v>
       </c>
       <c r="H1385" t="inlineStr"/>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="F1386" t="inlineStr"/>
       <c r="G1386" t="n">
-        <v>52851231.644</v>
+        <v>52853683.644</v>
       </c>
       <c r="H1386" t="inlineStr"/>
     </row>
@@ -30508,7 +30508,7 @@
       </c>
       <c r="F1387" t="inlineStr"/>
       <c r="G1387" t="n">
-        <v>52131240.57</v>
+        <v>52133693.57</v>
       </c>
       <c r="H1387" t="inlineStr"/>
     </row>
@@ -30530,7 +30530,7 @@
       </c>
       <c r="F1388" t="inlineStr"/>
       <c r="G1388" t="n">
-        <v>51904016.889</v>
+        <v>51906469.889</v>
       </c>
       <c r="H1388" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
       </c>
       <c r="F1389" t="inlineStr"/>
       <c r="G1389" t="n">
-        <v>51865804.679</v>
+        <v>51868256.679</v>
       </c>
       <c r="H1389" t="inlineStr"/>
     </row>
@@ -30574,7 +30574,7 @@
       </c>
       <c r="F1390" t="inlineStr"/>
       <c r="G1390" t="n">
-        <v>51489334.828</v>
+        <v>51761402.828</v>
       </c>
       <c r="H1390" t="inlineStr"/>
     </row>
@@ -30596,7 +30596,7 @@
       </c>
       <c r="F1391" t="inlineStr"/>
       <c r="G1391" t="n">
-        <v>51341659.283</v>
+        <v>51344112.283</v>
       </c>
       <c r="H1391" t="inlineStr"/>
     </row>
@@ -30618,7 +30618,7 @@
       </c>
       <c r="F1392" t="inlineStr"/>
       <c r="G1392" t="n">
-        <v>50738415.116</v>
+        <v>50740868.116</v>
       </c>
       <c r="H1392" t="inlineStr"/>
     </row>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="F1393" t="inlineStr"/>
       <c r="G1393" t="n">
-        <v>50590483.926</v>
+        <v>50592936.926</v>
       </c>
       <c r="H1393" t="inlineStr"/>
     </row>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="F1394" t="inlineStr"/>
       <c r="G1394" t="n">
-        <v>50246145.764</v>
+        <v>50248598.764</v>
       </c>
       <c r="H1394" t="inlineStr"/>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="F1395" t="inlineStr"/>
       <c r="G1395" t="n">
-        <v>50131151.563</v>
+        <v>50133603.563</v>
       </c>
       <c r="H1395" t="inlineStr"/>
     </row>
@@ -30706,7 +30706,7 @@
       </c>
       <c r="F1396" t="inlineStr"/>
       <c r="G1396" t="n">
-        <v>49663616.924</v>
+        <v>49666069.924</v>
       </c>
       <c r="H1396" t="inlineStr"/>
     </row>
@@ -30728,7 +30728,7 @@
       </c>
       <c r="F1397" t="inlineStr"/>
       <c r="G1397" t="n">
-        <v>51059146.556</v>
+        <v>51061598.556</v>
       </c>
       <c r="H1397" t="inlineStr"/>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="F1398" t="inlineStr"/>
       <c r="G1398" t="n">
-        <v>51932140.644</v>
+        <v>51934592.644</v>
       </c>
       <c r="H1398" t="inlineStr"/>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="F1399" t="inlineStr"/>
       <c r="G1399" t="n">
-        <v>54293052.622</v>
+        <v>54295505.622</v>
       </c>
       <c r="H1399" t="inlineStr"/>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="F1401" t="inlineStr"/>
       <c r="G1401" t="n">
-        <v>53408818.53</v>
+        <v>53411271.53</v>
       </c>
       <c r="H1401" t="inlineStr"/>
     </row>
@@ -30832,7 +30832,7 @@
       </c>
       <c r="F1402" t="inlineStr"/>
       <c r="G1402" t="n">
-        <v>52801375.855</v>
+        <v>52803828.855</v>
       </c>
       <c r="H1402" t="inlineStr"/>
     </row>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="F1403" t="inlineStr"/>
       <c r="G1403" t="n">
-        <v>53285956.593</v>
+        <v>53288409.593</v>
       </c>
       <c r="H1403" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
       </c>
       <c r="F1404" t="inlineStr"/>
       <c r="G1404" t="n">
-        <v>54225039.308</v>
+        <v>54227491.308</v>
       </c>
       <c r="H1404" t="inlineStr"/>
     </row>
@@ -30898,7 +30898,7 @@
       </c>
       <c r="F1405" t="inlineStr"/>
       <c r="G1405" t="n">
-        <v>53235354.494</v>
+        <v>53237806.494</v>
       </c>
       <c r="H1405" t="inlineStr"/>
     </row>
@@ -30920,7 +30920,7 @@
       </c>
       <c r="F1406" t="inlineStr"/>
       <c r="G1406" t="n">
-        <v>52668472.98</v>
+        <v>52670925.98</v>
       </c>
       <c r="H1406" t="inlineStr"/>
     </row>
@@ -30942,7 +30942,7 @@
       </c>
       <c r="F1407" t="inlineStr"/>
       <c r="G1407" t="n">
-        <v>51812015.704</v>
+        <v>51814468.704</v>
       </c>
       <c r="H1407" t="inlineStr"/>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="F1408" t="inlineStr"/>
       <c r="G1408" t="n">
-        <v>51819755.154</v>
+        <v>51822208.154</v>
       </c>
       <c r="H1408" t="inlineStr"/>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="F1409" t="inlineStr"/>
       <c r="G1409" t="n">
-        <v>51694778.007</v>
+        <v>51697231.007</v>
       </c>
       <c r="H1409" t="inlineStr"/>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="F1410" t="inlineStr"/>
       <c r="G1410" t="n">
-        <v>50969934.014</v>
+        <v>50972387.014</v>
       </c>
       <c r="H1410" t="inlineStr"/>
     </row>
@@ -31030,7 +31030,7 @@
       </c>
       <c r="F1411" t="inlineStr"/>
       <c r="G1411" t="n">
-        <v>51305982.064</v>
+        <v>51308434.064</v>
       </c>
       <c r="H1411" t="inlineStr"/>
     </row>
@@ -31052,7 +31052,7 @@
       </c>
       <c r="F1412" t="inlineStr"/>
       <c r="G1412" t="n">
-        <v>50251553.352</v>
+        <v>50254006.352</v>
       </c>
       <c r="H1412" t="inlineStr"/>
     </row>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="F1413" t="inlineStr"/>
       <c r="G1413" t="n">
-        <v>50403967.972</v>
+        <v>50406420.972</v>
       </c>
       <c r="H1413" t="inlineStr"/>
     </row>
@@ -31096,7 +31096,7 @@
       </c>
       <c r="F1414" t="inlineStr"/>
       <c r="G1414" t="n">
-        <v>50498118.477</v>
+        <v>50500571.477</v>
       </c>
       <c r="H1414" t="inlineStr"/>
     </row>
@@ -31118,7 +31118,7 @@
       </c>
       <c r="F1415" t="inlineStr"/>
       <c r="G1415" t="n">
-        <v>50437350.859</v>
+        <v>50439803.859</v>
       </c>
       <c r="H1415" t="inlineStr"/>
     </row>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="F1416" t="inlineStr"/>
       <c r="G1416" t="n">
-        <v>50478554.937</v>
+        <v>50481007.937</v>
       </c>
       <c r="H1416" t="inlineStr"/>
     </row>
@@ -31162,7 +31162,7 @@
       </c>
       <c r="F1417" t="inlineStr"/>
       <c r="G1417" t="n">
-        <v>50356100.92</v>
+        <v>50358553.92</v>
       </c>
       <c r="H1417" t="inlineStr"/>
     </row>
@@ -31184,7 +31184,7 @@
       </c>
       <c r="F1418" t="inlineStr"/>
       <c r="G1418" t="n">
-        <v>50630935.87</v>
+        <v>50633388.87</v>
       </c>
       <c r="H1418" t="inlineStr"/>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="F1419" t="inlineStr"/>
       <c r="G1419" t="n">
-        <v>51167693.993</v>
+        <v>51170146.993</v>
       </c>
       <c r="H1419" t="inlineStr"/>
     </row>
@@ -31228,7 +31228,7 @@
       </c>
       <c r="F1420" t="inlineStr"/>
       <c r="G1420" t="n">
-        <v>51147327.537</v>
+        <v>51149780.537</v>
       </c>
       <c r="H1420" t="inlineStr"/>
     </row>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="F1421" t="inlineStr"/>
       <c r="G1421" t="n">
-        <v>52959862.45</v>
+        <v>52962315.45</v>
       </c>
       <c r="H1421" t="inlineStr"/>
     </row>
@@ -31274,7 +31274,7 @@
         <v>21.9</v>
       </c>
       <c r="G1422" t="n">
-        <v>55418652.222</v>
+        <v>55421105.222</v>
       </c>
       <c r="H1422" t="n">
         <v>2.1</v>
@@ -31298,7 +31298,7 @@
       </c>
       <c r="F1423" t="inlineStr"/>
       <c r="G1423" t="n">
-        <v>55657247.331</v>
+        <v>55659699.331</v>
       </c>
       <c r="H1423" t="inlineStr"/>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="F1424" t="inlineStr"/>
       <c r="G1424" t="n">
-        <v>55719173.151</v>
+        <v>55721626.151</v>
       </c>
       <c r="H1424" t="inlineStr"/>
     </row>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="F1425" t="inlineStr"/>
       <c r="G1425" t="n">
-        <v>55984884.978</v>
+        <v>55987337.978</v>
       </c>
       <c r="H1425" t="inlineStr"/>
     </row>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="F1426" t="inlineStr"/>
       <c r="G1426" t="n">
-        <v>55756586.241</v>
+        <v>55759039.241</v>
       </c>
       <c r="H1426" t="inlineStr"/>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="F1427" t="inlineStr"/>
       <c r="G1427" t="n">
-        <v>54919763.217</v>
+        <v>54922215.217</v>
       </c>
       <c r="H1427" t="inlineStr"/>
     </row>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="F1428" t="inlineStr"/>
       <c r="G1428" t="n">
-        <v>54798066.24</v>
+        <v>54800519.24</v>
       </c>
       <c r="H1428" t="inlineStr"/>
     </row>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="F1429" t="inlineStr"/>
       <c r="G1429" t="n">
-        <v>54511194.576</v>
+        <v>54513647.576</v>
       </c>
       <c r="H1429" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="F1430" t="inlineStr"/>
       <c r="G1430" t="n">
-        <v>54522610.621</v>
+        <v>54525062.621</v>
       </c>
       <c r="H1430" t="inlineStr"/>
     </row>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="F1431" t="inlineStr"/>
       <c r="G1431" t="n">
-        <v>51990681.914</v>
+        <v>51993134.914</v>
       </c>
       <c r="H1431" t="inlineStr"/>
     </row>
@@ -31496,7 +31496,7 @@
       </c>
       <c r="F1432" t="inlineStr"/>
       <c r="G1432" t="n">
-        <v>52549505.382</v>
+        <v>52551957.382</v>
       </c>
       <c r="H1432" t="inlineStr"/>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="F1433" t="inlineStr"/>
       <c r="G1433" t="n">
-        <v>51727748.388</v>
+        <v>51756475.388</v>
       </c>
       <c r="H1433" t="inlineStr"/>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="F1434" t="inlineStr"/>
       <c r="G1434" t="n">
-        <v>50521474.623</v>
+        <v>50523927.623</v>
       </c>
       <c r="H1434" t="inlineStr"/>
     </row>
@@ -31562,7 +31562,7 @@
       </c>
       <c r="F1435" t="inlineStr"/>
       <c r="G1435" t="n">
-        <v>50566845.287</v>
+        <v>50569298.287</v>
       </c>
       <c r="H1435" t="inlineStr"/>
     </row>
@@ -31584,7 +31584,7 @@
       </c>
       <c r="F1436" t="inlineStr"/>
       <c r="G1436" t="n">
-        <v>50100424.307</v>
+        <v>50102876.307</v>
       </c>
       <c r="H1436" t="inlineStr"/>
     </row>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="F1437" t="inlineStr"/>
       <c r="G1437" t="n">
-        <v>50820771.53</v>
+        <v>50823224.53</v>
       </c>
       <c r="H1437" t="inlineStr"/>
     </row>
@@ -31628,7 +31628,7 @@
       </c>
       <c r="F1438" t="inlineStr"/>
       <c r="G1438" t="n">
-        <v>50064850.981</v>
+        <v>50067303.981</v>
       </c>
       <c r="H1438" t="inlineStr"/>
     </row>
@@ -31650,7 +31650,7 @@
       </c>
       <c r="F1439" t="inlineStr"/>
       <c r="G1439" t="n">
-        <v>49910336.76</v>
+        <v>49912789.76</v>
       </c>
       <c r="H1439" t="inlineStr"/>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="F1440" t="inlineStr"/>
       <c r="G1440" t="n">
-        <v>49825955.195</v>
+        <v>49828408.195</v>
       </c>
       <c r="H1440" t="inlineStr"/>
     </row>
@@ -31694,7 +31694,7 @@
       </c>
       <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="n">
-        <v>49568790.045</v>
+        <v>49571242.045</v>
       </c>
       <c r="H1441" t="inlineStr"/>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="F1442" t="inlineStr"/>
       <c r="G1442" t="n">
-        <v>50116482.504</v>
+        <v>50118935.504</v>
       </c>
       <c r="H1442" t="inlineStr"/>
     </row>
@@ -31738,7 +31738,7 @@
       </c>
       <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="n">
-        <v>51571164.942</v>
+        <v>51573617.942</v>
       </c>
       <c r="H1443" t="inlineStr"/>
     </row>
@@ -31762,7 +31762,7 @@
         <v>20.8</v>
       </c>
       <c r="G1444" t="n">
-        <v>53925867.608</v>
+        <v>53928320.608</v>
       </c>
       <c r="H1444" t="n">
         <v>2.3</v>
@@ -31786,7 +31786,7 @@
       </c>
       <c r="F1445" t="inlineStr"/>
       <c r="G1445" t="n">
-        <v>53498509.301</v>
+        <v>53500962.301</v>
       </c>
       <c r="H1445" t="inlineStr"/>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F1446" t="inlineStr"/>
       <c r="G1446" t="n">
-        <v>53071317.662</v>
+        <v>53073770.662</v>
       </c>
       <c r="H1446" t="inlineStr"/>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="F1447" t="inlineStr"/>
       <c r="G1447" t="n">
-        <v>53737540.632</v>
+        <v>53739993.632</v>
       </c>
       <c r="H1447" t="inlineStr"/>
     </row>
@@ -31852,7 +31852,7 @@
       </c>
       <c r="F1448" t="inlineStr"/>
       <c r="G1448" t="n">
-        <v>53004506.148</v>
+        <v>53006959.148</v>
       </c>
       <c r="H1448" t="inlineStr"/>
     </row>
@@ -31874,7 +31874,7 @@
       </c>
       <c r="F1449" t="inlineStr"/>
       <c r="G1449" t="n">
-        <v>51790346.271</v>
+        <v>51792799.271</v>
       </c>
       <c r="H1449" t="inlineStr"/>
     </row>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="F1450" t="inlineStr"/>
       <c r="G1450" t="n">
-        <v>50291607.976</v>
+        <v>50294060.976</v>
       </c>
       <c r="H1450" t="inlineStr"/>
     </row>
@@ -31918,7 +31918,7 @@
       </c>
       <c r="F1451" t="inlineStr"/>
       <c r="G1451" t="n">
-        <v>50852514.288</v>
+        <v>50854967.288</v>
       </c>
       <c r="H1451" t="inlineStr"/>
     </row>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="F1452" t="inlineStr"/>
       <c r="G1452" t="n">
-        <v>50583333.336</v>
+        <v>50585785.336</v>
       </c>
       <c r="H1452" t="inlineStr"/>
     </row>
@@ -31962,7 +31962,7 @@
       </c>
       <c r="F1453" t="inlineStr"/>
       <c r="G1453" t="n">
-        <v>50577508.135</v>
+        <v>50579961.135</v>
       </c>
       <c r="H1453" t="inlineStr"/>
     </row>
@@ -31984,7 +31984,7 @@
       </c>
       <c r="F1454" t="inlineStr"/>
       <c r="G1454" t="n">
-        <v>50392239.524</v>
+        <v>50394691.524</v>
       </c>
       <c r="H1454" t="inlineStr"/>
     </row>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="F1455" t="inlineStr"/>
       <c r="G1455" t="n">
-        <v>50230135.389</v>
+        <v>50232588.389</v>
       </c>
       <c r="H1455" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
       </c>
       <c r="F1456" t="inlineStr"/>
       <c r="G1456" t="n">
-        <v>50046797.804</v>
+        <v>50049249.804</v>
       </c>
       <c r="H1456" t="inlineStr"/>
     </row>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="F1457" t="inlineStr"/>
       <c r="G1457" t="n">
-        <v>50642301.035</v>
+        <v>50644753.035</v>
       </c>
       <c r="H1457" t="inlineStr"/>
     </row>
@@ -32072,7 +32072,7 @@
       </c>
       <c r="F1458" t="inlineStr"/>
       <c r="G1458" t="n">
-        <v>51436763.263</v>
+        <v>51439216.263</v>
       </c>
       <c r="H1458" t="inlineStr"/>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="F1459" t="inlineStr"/>
       <c r="G1459" t="n">
-        <v>51920335.288</v>
+        <v>51922788.288</v>
       </c>
       <c r="H1459" t="inlineStr"/>
     </row>
@@ -32116,7 +32116,7 @@
       </c>
       <c r="F1460" t="inlineStr"/>
       <c r="G1460" t="n">
-        <v>53303363.364</v>
+        <v>53305815.364</v>
       </c>
       <c r="H1460" t="inlineStr"/>
     </row>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="n">
-        <v>56166474.43</v>
+        <v>56168926.43</v>
       </c>
       <c r="H1461" t="inlineStr"/>
     </row>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="F1463" t="inlineStr"/>
       <c r="G1463" t="n">
-        <v>56168581.367</v>
+        <v>56171034.367</v>
       </c>
       <c r="H1463" t="inlineStr"/>
     </row>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="F1464" t="inlineStr"/>
       <c r="G1464" t="n">
-        <v>55037615.993</v>
+        <v>55040067.993</v>
       </c>
       <c r="H1464" t="inlineStr"/>
     </row>
@@ -32220,7 +32220,7 @@
       </c>
       <c r="F1465" t="inlineStr"/>
       <c r="G1465" t="n">
-        <v>55463889.785</v>
+        <v>55466342.785</v>
       </c>
       <c r="H1465" t="inlineStr"/>
     </row>
@@ -32242,7 +32242,7 @@
       </c>
       <c r="F1466" t="inlineStr"/>
       <c r="G1466" t="n">
-        <v>56340989.306</v>
+        <v>56346214.518</v>
       </c>
       <c r="H1466" t="inlineStr"/>
     </row>
@@ -32264,7 +32264,7 @@
       </c>
       <c r="F1467" t="inlineStr"/>
       <c r="G1467" t="n">
-        <v>55353494.095</v>
+        <v>55355946.095</v>
       </c>
       <c r="H1467" t="inlineStr"/>
     </row>
@@ -32286,7 +32286,7 @@
       </c>
       <c r="F1468" t="inlineStr"/>
       <c r="G1468" t="n">
-        <v>54687241.736</v>
+        <v>54689693.736</v>
       </c>
       <c r="H1468" t="inlineStr"/>
     </row>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="F1469" t="inlineStr"/>
       <c r="G1469" t="n">
-        <v>54563286.54</v>
+        <v>54565739.54</v>
       </c>
       <c r="H1469" t="inlineStr"/>
     </row>
@@ -32330,7 +32330,7 @@
       </c>
       <c r="F1470" t="inlineStr"/>
       <c r="G1470" t="n">
-        <v>55269857.358</v>
+        <v>55272312.612</v>
       </c>
       <c r="H1470" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
       </c>
       <c r="F1471" t="inlineStr"/>
       <c r="G1471" t="n">
-        <v>55084943.553</v>
+        <v>55087672.123</v>
       </c>
       <c r="H1471" t="inlineStr"/>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="F1472" t="inlineStr"/>
       <c r="G1472" t="n">
-        <v>56296028.969</v>
+        <v>56298633.956</v>
       </c>
       <c r="H1472" t="inlineStr"/>
     </row>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="F1473" t="inlineStr"/>
       <c r="G1473" t="n">
-        <v>56134162.492</v>
+        <v>56136793.885</v>
       </c>
       <c r="H1473" t="inlineStr"/>
     </row>
@@ -32418,7 +32418,7 @@
       </c>
       <c r="F1474" t="inlineStr"/>
       <c r="G1474" t="n">
-        <v>57309418.648</v>
+        <v>57312159.778</v>
       </c>
       <c r="H1474" t="inlineStr"/>
     </row>
@@ -32440,7 +32440,7 @@
       </c>
       <c r="F1475" t="inlineStr"/>
       <c r="G1475" t="n">
-        <v>58741348.611</v>
+        <v>58743801.611</v>
       </c>
       <c r="H1475" t="inlineStr"/>
     </row>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="F1476" t="inlineStr"/>
       <c r="G1476" t="n">
-        <v>59898395.293</v>
+        <v>59900847.332</v>
       </c>
       <c r="H1476" t="inlineStr"/>
     </row>
@@ -32484,7 +32484,7 @@
       </c>
       <c r="F1477" t="inlineStr"/>
       <c r="G1477" t="n">
-        <v>60281584.984</v>
+        <v>60284037.984</v>
       </c>
       <c r="H1477" t="inlineStr"/>
     </row>
@@ -32506,7 +32506,7 @@
       </c>
       <c r="F1478" t="inlineStr"/>
       <c r="G1478" t="n">
-        <v>60806417.024</v>
+        <v>60808869.024</v>
       </c>
       <c r="H1478" t="inlineStr"/>
     </row>
@@ -32528,7 +32528,7 @@
       </c>
       <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="n">
-        <v>60734875.187</v>
+        <v>60736112.044</v>
       </c>
       <c r="H1479" t="inlineStr"/>
     </row>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="F1480" t="inlineStr"/>
       <c r="G1480" t="n">
-        <v>62897937.684</v>
+        <v>62891128.767</v>
       </c>
       <c r="H1480" t="inlineStr"/>
     </row>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65307419.61</v>
+        <v>65285582.703</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -32610,7 +32610,7 @@
       </c>
       <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="n">
-        <v>64565663.281</v>
+        <v>64568116.281</v>
       </c>
       <c r="H1483" t="inlineStr"/>
     </row>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61853845.993</v>
+        <v>61856297.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61171533.519</v>
+        <v>61173985.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61706880.076</v>
+        <v>61709332.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32698,7 +32698,7 @@
       </c>
       <c r="F1487" t="inlineStr"/>
       <c r="G1487" t="n">
-        <v>60467765.004</v>
+        <v>60470218.004</v>
       </c>
       <c r="H1487" t="inlineStr"/>
     </row>
@@ -32720,7 +32720,7 @@
       </c>
       <c r="F1488" t="inlineStr"/>
       <c r="G1488" t="n">
-        <v>59514038.211</v>
+        <v>59516490.211</v>
       </c>
       <c r="H1488" t="inlineStr"/>
     </row>
@@ -32742,7 +32742,7 @@
       </c>
       <c r="F1489" t="inlineStr"/>
       <c r="G1489" t="n">
-        <v>57792547.381</v>
+        <v>57795000.381</v>
       </c>
       <c r="H1489" t="inlineStr"/>
     </row>
@@ -32764,7 +32764,7 @@
       </c>
       <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="n">
-        <v>57201233.101</v>
+        <v>57203686.101</v>
       </c>
       <c r="H1490" t="inlineStr"/>
     </row>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="n">
-        <v>57129183.244</v>
+        <v>57131635.244</v>
       </c>
       <c r="H1491" t="inlineStr"/>
     </row>
@@ -32808,7 +32808,7 @@
       </c>
       <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="n">
-        <v>57556557.399</v>
+        <v>57559010.399</v>
       </c>
       <c r="H1492" t="inlineStr"/>
     </row>
@@ -32830,7 +32830,7 @@
       </c>
       <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="n">
-        <v>56231542.088</v>
+        <v>56233995.088</v>
       </c>
       <c r="H1493" t="inlineStr"/>
     </row>
@@ -32852,7 +32852,7 @@
       </c>
       <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="n">
-        <v>55608630.47</v>
+        <v>55611083.47</v>
       </c>
       <c r="H1494" t="inlineStr"/>
     </row>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="n">
-        <v>55435079.492</v>
+        <v>55437531.492</v>
       </c>
       <c r="H1495" t="inlineStr"/>
     </row>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55264394.796</v>
+        <v>55266847.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="n">
-        <v>55027126.613</v>
+        <v>55029578.613</v>
       </c>
       <c r="H1497" t="inlineStr"/>
     </row>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="n">
-        <v>54727700.758</v>
+        <v>54730152.758</v>
       </c>
       <c r="H1498" t="inlineStr"/>
     </row>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54876143.349</v>
+        <v>54878596.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -32984,7 +32984,7 @@
       </c>
       <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="n">
-        <v>55137368.773</v>
+        <v>55139821.773</v>
       </c>
       <c r="H1500" t="inlineStr"/>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="n">
-        <v>55893047.062</v>
+        <v>55895500.062</v>
       </c>
       <c r="H1501" t="inlineStr"/>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="n">
-        <v>57587918.416</v>
+        <v>57590370.416</v>
       </c>
       <c r="H1502" t="inlineStr"/>
     </row>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60129534.818</v>
+        <v>60131987.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33088,7 +33088,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59038355.841</v>
+        <v>59037854.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58336916.213</v>
+        <v>58339429.213</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58570208.727</v>
+        <v>58572666.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59657919.587</v>
+        <v>59660467.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58025381.8</v>
+        <v>58027858.8</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57255982.786</v>
+        <v>57258654.786</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33220,7 +33220,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56136065.11</v>
+        <v>56138560.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56448200.744</v>
+        <v>56450816.744</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33264,7 +33264,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55863429.876</v>
+        <v>55866507.876</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33286,7 +33286,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55586646.143</v>
+        <v>55589155.143</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55620380.479</v>
+        <v>55622819.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55670424.733</v>
+        <v>55672165.733</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33352,7 +33352,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55240472.15</v>
+        <v>55243088.15</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33374,7 +33374,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55285760.162</v>
+        <v>55288215.162</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
       </c>
       <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="n">
-        <v>54744555.928</v>
+        <v>54710168.928</v>
       </c>
       <c r="H1519" t="inlineStr"/>
     </row>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="n">
-        <v>55604268.663</v>
+        <v>55610780.663</v>
       </c>
       <c r="H1520" t="inlineStr"/>
     </row>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57356463.612</v>
+        <v>57361187.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60390554.02</v>
+        <v>60381541.102</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59181117.726</v>
+        <v>59183569.726</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58637414.442</v>
+        <v>58639867.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58664731.045</v>
+        <v>58667184.045</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59433583.058</v>
+        <v>59436036.058</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33588,7 +33588,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57840730.899</v>
+        <v>57843182.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57123080.668</v>
+        <v>57125533.668</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33632,7 +33632,7 @@
       </c>
       <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="n">
-        <v>56154766.566</v>
+        <v>56157219.566</v>
       </c>
       <c r="H1530" t="inlineStr"/>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="n">
-        <v>56041214.838</v>
+        <v>56043666.838</v>
       </c>
       <c r="H1531" t="inlineStr"/>
     </row>
@@ -33676,7 +33676,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55968261.807</v>
+        <v>55970714.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56236020.122</v>
+        <v>56238473.122</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55942031.807</v>
+        <v>55944483.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55084085.219</v>
+        <v>55086538.219</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="n">
-        <v>54532004.642</v>
+        <v>54534456.642</v>
       </c>
       <c r="H1536" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54593054.849</v>
+        <v>54594396.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54964416.638</v>
+        <v>54966869.638</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="n">
-        <v>56159241.153</v>
+        <v>56161693.153</v>
       </c>
       <c r="H1539" t="inlineStr"/>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="n">
-        <v>55836276.813</v>
+        <v>55838728.813</v>
       </c>
       <c r="H1540" t="inlineStr"/>
     </row>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="n">
-        <v>56011673.566</v>
+        <v>56014402.566</v>
       </c>
       <c r="H1541" t="inlineStr"/>
     </row>
@@ -33896,7 +33896,7 @@
       </c>
       <c r="F1542" t="inlineStr"/>
       <c r="G1542" t="n">
-        <v>57927002.958</v>
+        <v>57901206.373</v>
       </c>
       <c r="H1542" t="inlineStr"/>
     </row>
@@ -33920,9 +33920,11 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60635811.102</v>
-      </c>
-      <c r="H1543" t="inlineStr"/>
+        <v>60647344.573</v>
+      </c>
+      <c r="H1543" t="n">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="1544">
       <c r="A1544" s="1" t="n">
@@ -33942,7 +33944,7 @@
       </c>
       <c r="F1544" t="inlineStr"/>
       <c r="G1544" t="n">
-        <v>59372298.293</v>
+        <v>59359064.664</v>
       </c>
       <c r="H1544" t="inlineStr"/>
     </row>
@@ -33964,7 +33966,7 @@
       </c>
       <c r="F1545" t="inlineStr"/>
       <c r="G1545" t="n">
-        <v>58890732.38</v>
+        <v>58831280.705</v>
       </c>
       <c r="H1545" t="inlineStr"/>
     </row>
@@ -33986,7 +33988,7 @@
       </c>
       <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="n">
-        <v>58478470.921</v>
+        <v>58414529.232</v>
       </c>
       <c r="H1546" t="inlineStr"/>
     </row>
@@ -34007,15 +34009,21 @@
         <v>24.9375</v>
       </c>
       <c r="F1547" t="inlineStr"/>
-      <c r="G1547" t="inlineStr"/>
+      <c r="G1547" t="n">
+        <v>58205436.175</v>
+      </c>
       <c r="H1547" t="inlineStr"/>
     </row>
     <row r="1548">
       <c r="A1548" s="1" t="n">
         <v>46121</v>
       </c>
-      <c r="B1548" t="inlineStr"/>
-      <c r="C1548" t="inlineStr"/>
+      <c r="B1548" t="n">
+        <v>45154</v>
+      </c>
+      <c r="C1548" t="n">
+        <v>41291559</v>
+      </c>
       <c r="D1548" t="n">
         <v>1409.92</v>
       </c>
@@ -34023,22 +34031,126 @@
         <v>23.25</v>
       </c>
       <c r="F1548" t="inlineStr"/>
-      <c r="G1548" t="inlineStr"/>
+      <c r="G1548" t="n">
+        <v>57470966.852</v>
+      </c>
       <c r="H1548" t="inlineStr"/>
     </row>
     <row r="1549">
       <c r="A1549" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="B1549" t="inlineStr"/>
-      <c r="C1549" t="inlineStr"/>
+      <c r="B1549" t="n">
+        <v>45435</v>
+      </c>
+      <c r="C1549" t="n">
+        <v>41225945</v>
+      </c>
       <c r="D1549" t="n">
         <v>1399.42</v>
       </c>
-      <c r="E1549" t="inlineStr"/>
+      <c r="E1549" t="n">
+        <v>22.375</v>
+      </c>
       <c r="F1549" t="inlineStr"/>
-      <c r="G1549" t="inlineStr"/>
+      <c r="G1549" t="n">
+        <v>57037849.386</v>
+      </c>
       <c r="H1549" t="inlineStr"/>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B1550" t="n">
+        <v>45408</v>
+      </c>
+      <c r="C1550" t="n">
+        <v>40941598</v>
+      </c>
+      <c r="D1550" t="n">
+        <v>1387.78</v>
+      </c>
+      <c r="E1550" t="n">
+        <v>21.6875</v>
+      </c>
+      <c r="F1550" t="inlineStr"/>
+      <c r="G1550" t="n">
+        <v>55920941.501</v>
+      </c>
+      <c r="H1550" t="inlineStr"/>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B1551" t="n">
+        <v>45875</v>
+      </c>
+      <c r="C1551" t="n">
+        <v>40898167</v>
+      </c>
+      <c r="D1551" t="n">
+        <v>1389.01</v>
+      </c>
+      <c r="E1551" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F1551" t="inlineStr"/>
+      <c r="G1551" t="n">
+        <v>55721378.759</v>
+      </c>
+      <c r="H1551" t="inlineStr"/>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B1552" t="n">
+        <v>45622</v>
+      </c>
+      <c r="C1552" t="n">
+        <v>40308442</v>
+      </c>
+      <c r="D1552" t="n">
+        <v>1388.7</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="F1552" t="inlineStr"/>
+      <c r="G1552" t="inlineStr"/>
+      <c r="H1552" t="inlineStr"/>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B1553" t="inlineStr"/>
+      <c r="C1553" t="inlineStr"/>
+      <c r="D1553" t="n">
+        <v>1379.34</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>22.4375</v>
+      </c>
+      <c r="F1553" t="inlineStr"/>
+      <c r="G1553" t="inlineStr"/>
+      <c r="H1553" t="inlineStr"/>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B1554" t="inlineStr"/>
+      <c r="C1554" t="inlineStr"/>
+      <c r="D1554" t="n">
+        <v>1389.01</v>
+      </c>
+      <c r="E1554" t="inlineStr"/>
+      <c r="F1554" t="inlineStr"/>
+      <c r="G1554" t="inlineStr"/>
+      <c r="H1554" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1554"/>
+  <dimension ref="A1:H1559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28276,7 +28276,7 @@
       </c>
       <c r="F1286" t="inlineStr"/>
       <c r="G1286" t="n">
-        <v>45865271.451</v>
+        <v>45867431.451</v>
       </c>
       <c r="H1286" t="inlineStr"/>
     </row>
@@ -28542,7 +28542,7 @@
         <v>24.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>50399793.558</v>
+        <v>50383676.558</v>
       </c>
       <c r="H1298" t="n">
         <v>3.7</v>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="F1463" t="inlineStr"/>
       <c r="G1463" t="n">
-        <v>56171034.367</v>
+        <v>56171069.367</v>
       </c>
       <c r="H1463" t="inlineStr"/>
     </row>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="F1464" t="inlineStr"/>
       <c r="G1464" t="n">
-        <v>55040067.993</v>
+        <v>55040073.993</v>
       </c>
       <c r="H1464" t="inlineStr"/>
     </row>
@@ -32220,7 +32220,7 @@
       </c>
       <c r="F1465" t="inlineStr"/>
       <c r="G1465" t="n">
-        <v>55466342.785</v>
+        <v>55466348.785</v>
       </c>
       <c r="H1465" t="inlineStr"/>
     </row>
@@ -32242,7 +32242,7 @@
       </c>
       <c r="F1466" t="inlineStr"/>
       <c r="G1466" t="n">
-        <v>56346214.518</v>
+        <v>56346226.518</v>
       </c>
       <c r="H1466" t="inlineStr"/>
     </row>
@@ -32264,7 +32264,7 @@
       </c>
       <c r="F1467" t="inlineStr"/>
       <c r="G1467" t="n">
-        <v>55355946.095</v>
+        <v>55355955.095</v>
       </c>
       <c r="H1467" t="inlineStr"/>
     </row>
@@ -32286,7 +32286,7 @@
       </c>
       <c r="F1468" t="inlineStr"/>
       <c r="G1468" t="n">
-        <v>54689693.736</v>
+        <v>54689707.736</v>
       </c>
       <c r="H1468" t="inlineStr"/>
     </row>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="F1469" t="inlineStr"/>
       <c r="G1469" t="n">
-        <v>54565739.54</v>
+        <v>54565845.54</v>
       </c>
       <c r="H1469" t="inlineStr"/>
     </row>
@@ -32330,7 +32330,7 @@
       </c>
       <c r="F1470" t="inlineStr"/>
       <c r="G1470" t="n">
-        <v>55272312.612</v>
+        <v>55273378.612</v>
       </c>
       <c r="H1470" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
       </c>
       <c r="F1471" t="inlineStr"/>
       <c r="G1471" t="n">
-        <v>55087672.123</v>
+        <v>55087698.123</v>
       </c>
       <c r="H1471" t="inlineStr"/>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="F1472" t="inlineStr"/>
       <c r="G1472" t="n">
-        <v>56298633.956</v>
+        <v>56298646.956</v>
       </c>
       <c r="H1472" t="inlineStr"/>
     </row>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="F1473" t="inlineStr"/>
       <c r="G1473" t="n">
-        <v>56136793.885</v>
+        <v>56136930.885</v>
       </c>
       <c r="H1473" t="inlineStr"/>
     </row>
@@ -32418,7 +32418,7 @@
       </c>
       <c r="F1474" t="inlineStr"/>
       <c r="G1474" t="n">
-        <v>57312159.778</v>
+        <v>57312203.778</v>
       </c>
       <c r="H1474" t="inlineStr"/>
     </row>
@@ -32440,7 +32440,7 @@
       </c>
       <c r="F1475" t="inlineStr"/>
       <c r="G1475" t="n">
-        <v>58743801.611</v>
+        <v>58743818.611</v>
       </c>
       <c r="H1475" t="inlineStr"/>
     </row>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="F1476" t="inlineStr"/>
       <c r="G1476" t="n">
-        <v>59900847.332</v>
+        <v>59900884.332</v>
       </c>
       <c r="H1476" t="inlineStr"/>
     </row>
@@ -32484,7 +32484,7 @@
       </c>
       <c r="F1477" t="inlineStr"/>
       <c r="G1477" t="n">
-        <v>60284037.984</v>
+        <v>60284078.984</v>
       </c>
       <c r="H1477" t="inlineStr"/>
     </row>
@@ -32506,7 +32506,7 @@
       </c>
       <c r="F1478" t="inlineStr"/>
       <c r="G1478" t="n">
-        <v>60808869.024</v>
+        <v>60808926.024</v>
       </c>
       <c r="H1478" t="inlineStr"/>
     </row>
@@ -32528,7 +32528,7 @@
       </c>
       <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="n">
-        <v>60736112.044</v>
+        <v>60736131.044</v>
       </c>
       <c r="H1479" t="inlineStr"/>
     </row>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="F1480" t="inlineStr"/>
       <c r="G1480" t="n">
-        <v>62891128.767</v>
+        <v>62891143.767</v>
       </c>
       <c r="H1480" t="inlineStr"/>
     </row>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60131987.818</v>
+        <v>60132095.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60381541.102</v>
+        <v>60376122.102</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59183569.726</v>
+        <v>59184130.726</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58639867.442</v>
+        <v>58640428.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58667184.045</v>
+        <v>58667745.045</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59436036.058</v>
+        <v>59439155.058</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33588,7 +33588,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57843182.899</v>
+        <v>57843183.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57125533.668</v>
+        <v>57125534.668</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56238473.122</v>
+        <v>56240803.122</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55944483.807</v>
+        <v>55944484.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55086538.219</v>
+        <v>55086539.219</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54594396.849</v>
+        <v>54594397.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54966869.638</v>
+        <v>54966515.591</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="n">
-        <v>56161693.153</v>
+        <v>56161377.145</v>
       </c>
       <c r="H1539" t="inlineStr"/>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="n">
-        <v>55838728.813</v>
+        <v>55836890.824</v>
       </c>
       <c r="H1540" t="inlineStr"/>
     </row>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="n">
-        <v>56014402.566</v>
+        <v>56014258.906</v>
       </c>
       <c r="H1541" t="inlineStr"/>
     </row>
@@ -33896,7 +33896,7 @@
       </c>
       <c r="F1542" t="inlineStr"/>
       <c r="G1542" t="n">
-        <v>57901206.373</v>
+        <v>57901062.582</v>
       </c>
       <c r="H1542" t="inlineStr"/>
     </row>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60647344.573</v>
+        <v>60763497.517</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -33944,7 +33944,7 @@
       </c>
       <c r="F1544" t="inlineStr"/>
       <c r="G1544" t="n">
-        <v>59359064.664</v>
+        <v>59358755.198</v>
       </c>
       <c r="H1544" t="inlineStr"/>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="F1545" t="inlineStr"/>
       <c r="G1545" t="n">
-        <v>58831280.705</v>
+        <v>58816128.155</v>
       </c>
       <c r="H1545" t="inlineStr"/>
     </row>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="n">
-        <v>58414529.232</v>
+        <v>58414434.682</v>
       </c>
       <c r="H1546" t="inlineStr"/>
     </row>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="F1547" t="inlineStr"/>
       <c r="G1547" t="n">
-        <v>58205436.175</v>
+        <v>58153049.124</v>
       </c>
       <c r="H1547" t="inlineStr"/>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="F1548" t="inlineStr"/>
       <c r="G1548" t="n">
-        <v>57470966.852</v>
+        <v>57423894.389</v>
       </c>
       <c r="H1548" t="inlineStr"/>
     </row>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="n">
-        <v>57037849.386</v>
+        <v>56883367.286</v>
       </c>
       <c r="H1549" t="inlineStr"/>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="F1550" t="inlineStr"/>
       <c r="G1550" t="n">
-        <v>55920941.501</v>
+        <v>55894914.657</v>
       </c>
       <c r="H1550" t="inlineStr"/>
     </row>
@@ -34098,7 +34098,7 @@
       </c>
       <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="n">
-        <v>55721378.759</v>
+        <v>55688213.903</v>
       </c>
       <c r="H1551" t="inlineStr"/>
     </row>
@@ -34119,15 +34119,21 @@
         <v>22.125</v>
       </c>
       <c r="F1552" t="inlineStr"/>
-      <c r="G1552" t="inlineStr"/>
+      <c r="G1552" t="n">
+        <v>56245670.049</v>
+      </c>
       <c r="H1552" t="inlineStr"/>
     </row>
     <row r="1553">
       <c r="A1553" s="1" t="n">
         <v>46128</v>
       </c>
-      <c r="B1553" t="inlineStr"/>
-      <c r="C1553" t="inlineStr"/>
+      <c r="B1553" t="n">
+        <v>45629</v>
+      </c>
+      <c r="C1553" t="n">
+        <v>40553716</v>
+      </c>
       <c r="D1553" t="n">
         <v>1379.34</v>
       </c>
@@ -34135,22 +34141,126 @@
         <v>22.4375</v>
       </c>
       <c r="F1553" t="inlineStr"/>
-      <c r="G1553" t="inlineStr"/>
+      <c r="G1553" t="n">
+        <v>55502319.003</v>
+      </c>
       <c r="H1553" t="inlineStr"/>
     </row>
     <row r="1554">
       <c r="A1554" s="1" t="n">
         <v>46129</v>
       </c>
-      <c r="B1554" t="inlineStr"/>
-      <c r="C1554" t="inlineStr"/>
+      <c r="B1554" t="n">
+        <v>45793</v>
+      </c>
+      <c r="C1554" t="n">
+        <v>40105907</v>
+      </c>
       <c r="D1554" t="n">
         <v>1389.01</v>
       </c>
-      <c r="E1554" t="inlineStr"/>
+      <c r="E1554" t="n">
+        <v>22.375</v>
+      </c>
       <c r="F1554" t="inlineStr"/>
-      <c r="G1554" t="inlineStr"/>
+      <c r="G1554" t="n">
+        <v>55111844.271</v>
+      </c>
       <c r="H1554" t="inlineStr"/>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B1555" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C1555" t="n">
+        <v>40962136</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>1397.09</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>21.3125</v>
+      </c>
+      <c r="F1555" t="inlineStr"/>
+      <c r="G1555" t="n">
+        <v>55032861.315</v>
+      </c>
+      <c r="H1555" t="inlineStr"/>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B1556" t="n">
+        <v>45781</v>
+      </c>
+      <c r="C1556" t="n">
+        <v>40702673</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>1396.9</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>21.8125</v>
+      </c>
+      <c r="F1556" t="inlineStr"/>
+      <c r="G1556" t="n">
+        <v>54455300.129</v>
+      </c>
+      <c r="H1556" t="inlineStr"/>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B1557" t="n">
+        <v>45843</v>
+      </c>
+      <c r="C1557" t="n">
+        <v>40706598</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>1399.75</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1557" t="inlineStr"/>
+      <c r="G1557" t="inlineStr"/>
+      <c r="H1557" t="inlineStr"/>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B1558" t="inlineStr"/>
+      <c r="C1558" t="inlineStr"/>
+      <c r="D1558" t="n">
+        <v>1412.88</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1558" t="inlineStr"/>
+      <c r="G1558" t="inlineStr"/>
+      <c r="H1558" t="inlineStr"/>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B1559" t="inlineStr"/>
+      <c r="C1559" t="inlineStr"/>
+      <c r="D1559" t="n">
+        <v>1418.45</v>
+      </c>
+      <c r="E1559" t="inlineStr"/>
+      <c r="F1559" t="inlineStr"/>
+      <c r="G1559" t="inlineStr"/>
+      <c r="H1559" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1559"/>
+  <dimension ref="A1:H1563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28276,7 +28276,7 @@
       </c>
       <c r="F1286" t="inlineStr"/>
       <c r="G1286" t="n">
-        <v>45867431.451</v>
+        <v>45865271.348</v>
       </c>
       <c r="H1286" t="inlineStr"/>
     </row>
@@ -28542,7 +28542,7 @@
         <v>24.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>50383676.558</v>
+        <v>50399793.558</v>
       </c>
       <c r="H1298" t="n">
         <v>3.7</v>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60763497.517</v>
+        <v>60808038.977</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -33944,7 +33944,7 @@
       </c>
       <c r="F1544" t="inlineStr"/>
       <c r="G1544" t="n">
-        <v>59358755.198</v>
+        <v>59370744.198</v>
       </c>
       <c r="H1544" t="inlineStr"/>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="F1545" t="inlineStr"/>
       <c r="G1545" t="n">
-        <v>58816128.155</v>
+        <v>58839125.155</v>
       </c>
       <c r="H1545" t="inlineStr"/>
     </row>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="n">
-        <v>58414434.682</v>
+        <v>58452009.682</v>
       </c>
       <c r="H1546" t="inlineStr"/>
     </row>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="F1547" t="inlineStr"/>
       <c r="G1547" t="n">
-        <v>58153049.124</v>
+        <v>58165548.124</v>
       </c>
       <c r="H1547" t="inlineStr"/>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="F1548" t="inlineStr"/>
       <c r="G1548" t="n">
-        <v>57423894.389</v>
+        <v>57444490.389</v>
       </c>
       <c r="H1548" t="inlineStr"/>
     </row>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="n">
-        <v>56883367.286</v>
+        <v>56900664.286</v>
       </c>
       <c r="H1549" t="inlineStr"/>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="F1550" t="inlineStr"/>
       <c r="G1550" t="n">
-        <v>55894914.657</v>
+        <v>55910624.657</v>
       </c>
       <c r="H1550" t="inlineStr"/>
     </row>
@@ -34098,7 +34098,7 @@
       </c>
       <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="n">
-        <v>55688213.903</v>
+        <v>55711314.903</v>
       </c>
       <c r="H1551" t="inlineStr"/>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="F1552" t="inlineStr"/>
       <c r="G1552" t="n">
-        <v>56245670.049</v>
+        <v>56250720.687</v>
       </c>
       <c r="H1552" t="inlineStr"/>
     </row>
@@ -34142,7 +34142,7 @@
       </c>
       <c r="F1553" t="inlineStr"/>
       <c r="G1553" t="n">
-        <v>55502319.003</v>
+        <v>55510513.205</v>
       </c>
       <c r="H1553" t="inlineStr"/>
     </row>
@@ -34164,7 +34164,7 @@
       </c>
       <c r="F1554" t="inlineStr"/>
       <c r="G1554" t="n">
-        <v>55111844.271</v>
+        <v>55092305.834</v>
       </c>
       <c r="H1554" t="inlineStr"/>
     </row>
@@ -34186,7 +34186,7 @@
       </c>
       <c r="F1555" t="inlineStr"/>
       <c r="G1555" t="n">
-        <v>55032861.315</v>
+        <v>55048299.568</v>
       </c>
       <c r="H1555" t="inlineStr"/>
     </row>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="F1556" t="inlineStr"/>
       <c r="G1556" t="n">
-        <v>54455300.129</v>
+        <v>54459268.513</v>
       </c>
       <c r="H1556" t="inlineStr"/>
     </row>
@@ -34229,15 +34229,21 @@
         <v>22</v>
       </c>
       <c r="F1557" t="inlineStr"/>
-      <c r="G1557" t="inlineStr"/>
+      <c r="G1557" t="n">
+        <v>53870479.913</v>
+      </c>
       <c r="H1557" t="inlineStr"/>
     </row>
     <row r="1558">
       <c r="A1558" s="1" t="n">
         <v>46135</v>
       </c>
-      <c r="B1558" t="inlineStr"/>
-      <c r="C1558" t="inlineStr"/>
+      <c r="B1558" t="n">
+        <v>46130</v>
+      </c>
+      <c r="C1558" t="n">
+        <v>40372220</v>
+      </c>
       <c r="D1558" t="n">
         <v>1412.88</v>
       </c>
@@ -34245,22 +34251,104 @@
         <v>22</v>
       </c>
       <c r="F1558" t="inlineStr"/>
-      <c r="G1558" t="inlineStr"/>
+      <c r="G1558" t="n">
+        <v>54008568.169</v>
+      </c>
       <c r="H1558" t="inlineStr"/>
     </row>
     <row r="1559">
       <c r="A1559" s="1" t="n">
         <v>46136</v>
       </c>
-      <c r="B1559" t="inlineStr"/>
-      <c r="C1559" t="inlineStr"/>
+      <c r="B1559" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C1559" t="n">
+        <v>40052600</v>
+      </c>
       <c r="D1559" t="n">
         <v>1418.45</v>
       </c>
-      <c r="E1559" t="inlineStr"/>
+      <c r="E1559" t="n">
+        <v>21.3125</v>
+      </c>
       <c r="F1559" t="inlineStr"/>
-      <c r="G1559" t="inlineStr"/>
+      <c r="G1559" t="n">
+        <v>54427905.41</v>
+      </c>
       <c r="H1559" t="inlineStr"/>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B1560" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C1560" t="n">
+        <v>42283192</v>
+      </c>
+      <c r="D1560" t="n">
+        <v>1440.61</v>
+      </c>
+      <c r="E1560" t="n">
+        <v>20.375</v>
+      </c>
+      <c r="F1560" t="inlineStr"/>
+      <c r="G1560" t="n">
+        <v>55382574.306</v>
+      </c>
+      <c r="H1560" t="inlineStr"/>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B1561" t="n">
+        <v>45818</v>
+      </c>
+      <c r="C1561" t="n">
+        <v>41791914</v>
+      </c>
+      <c r="D1561" t="n">
+        <v>1435.68</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>21.625</v>
+      </c>
+      <c r="F1561" t="inlineStr"/>
+      <c r="G1561" t="inlineStr"/>
+      <c r="H1561" t="inlineStr"/>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B1562" t="inlineStr"/>
+      <c r="C1562" t="inlineStr"/>
+      <c r="D1562" t="n">
+        <v>1418.69</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1562" t="inlineStr"/>
+      <c r="G1562" t="inlineStr"/>
+      <c r="H1562" t="inlineStr"/>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B1563" t="inlineStr"/>
+      <c r="C1563" t="inlineStr"/>
+      <c r="D1563" t="n">
+        <v>1415.8</v>
+      </c>
+      <c r="E1563" t="inlineStr"/>
+      <c r="F1563" t="inlineStr"/>
+      <c r="G1563" t="inlineStr"/>
+      <c r="H1563" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1563"/>
+  <dimension ref="A1:H1568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="F1281" t="inlineStr"/>
       <c r="G1281" t="n">
-        <v>48135143.128</v>
+        <v>48130268.128</v>
       </c>
       <c r="H1281" t="inlineStr"/>
     </row>
@@ -28542,7 +28542,7 @@
         <v>24.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>50399793.558</v>
+        <v>50391335.558</v>
       </c>
       <c r="H1298" t="n">
         <v>3.7</v>
@@ -28566,7 +28566,7 @@
       </c>
       <c r="F1299" t="inlineStr"/>
       <c r="G1299" t="n">
-        <v>50025987.041</v>
+        <v>50017529.041</v>
       </c>
       <c r="H1299" t="inlineStr"/>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="F1300" t="inlineStr"/>
       <c r="G1300" t="n">
-        <v>49206105.253</v>
+        <v>49197647.253</v>
       </c>
       <c r="H1300" t="inlineStr"/>
     </row>
@@ -28610,7 +28610,7 @@
       </c>
       <c r="F1301" t="inlineStr"/>
       <c r="G1301" t="n">
-        <v>49530185.809</v>
+        <v>49563325.809</v>
       </c>
       <c r="H1301" t="inlineStr"/>
     </row>
@@ -28632,7 +28632,7 @@
       </c>
       <c r="F1302" t="inlineStr"/>
       <c r="G1302" t="n">
-        <v>49337656.324</v>
+        <v>49329199.324</v>
       </c>
       <c r="H1302" t="inlineStr"/>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="F1303" t="inlineStr"/>
       <c r="G1303" t="n">
-        <v>48597774.632</v>
+        <v>48589315.632</v>
       </c>
       <c r="H1303" t="inlineStr"/>
     </row>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="F1304" t="inlineStr"/>
       <c r="G1304" t="n">
-        <v>48587053.939</v>
+        <v>48455202.939</v>
       </c>
       <c r="H1304" t="inlineStr"/>
     </row>
@@ -28698,7 +28698,7 @@
       </c>
       <c r="F1305" t="inlineStr"/>
       <c r="G1305" t="n">
-        <v>48404060.49</v>
+        <v>48224820.49</v>
       </c>
       <c r="H1305" t="inlineStr"/>
     </row>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="F1306" t="inlineStr"/>
       <c r="G1306" t="n">
-        <v>48282632.393</v>
+        <v>48255420.393</v>
       </c>
       <c r="H1306" t="inlineStr"/>
     </row>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="F1307" t="inlineStr"/>
       <c r="G1307" t="n">
-        <v>48074692.613</v>
+        <v>48047482.613</v>
       </c>
       <c r="H1307" t="inlineStr"/>
     </row>
@@ -28764,7 +28764,7 @@
       </c>
       <c r="F1308" t="inlineStr"/>
       <c r="G1308" t="n">
-        <v>48094155.875</v>
+        <v>48085697.875</v>
       </c>
       <c r="H1308" t="inlineStr"/>
     </row>
@@ -28786,7 +28786,7 @@
       </c>
       <c r="F1309" t="inlineStr"/>
       <c r="G1309" t="n">
-        <v>46989402.386</v>
+        <v>46980943.386</v>
       </c>
       <c r="H1309" t="inlineStr"/>
     </row>
@@ -28808,7 +28808,7 @@
       </c>
       <c r="F1310" t="inlineStr"/>
       <c r="G1310" t="n">
-        <v>46587857.28</v>
+        <v>46579398.28</v>
       </c>
       <c r="H1310" t="inlineStr"/>
     </row>
@@ -28830,7 +28830,7 @@
       </c>
       <c r="F1311" t="inlineStr"/>
       <c r="G1311" t="n">
-        <v>46101504.74</v>
+        <v>46093046.74</v>
       </c>
       <c r="H1311" t="inlineStr"/>
     </row>
@@ -28852,7 +28852,7 @@
       </c>
       <c r="F1312" t="inlineStr"/>
       <c r="G1312" t="n">
-        <v>45475868.696</v>
+        <v>45467410.696</v>
       </c>
       <c r="H1312" t="inlineStr"/>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="F1313" t="inlineStr"/>
       <c r="G1313" t="n">
-        <v>45520427.554</v>
+        <v>45511969.554</v>
       </c>
       <c r="H1313" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
       </c>
       <c r="F1314" t="inlineStr"/>
       <c r="G1314" t="n">
-        <v>45634291.123</v>
+        <v>45625832.123</v>
       </c>
       <c r="H1314" t="inlineStr"/>
     </row>
@@ -28918,7 +28918,7 @@
       </c>
       <c r="F1315" t="inlineStr"/>
       <c r="G1315" t="n">
-        <v>47022597.258</v>
+        <v>47014138.258</v>
       </c>
       <c r="H1315" t="inlineStr"/>
     </row>
@@ -28940,7 +28940,7 @@
       </c>
       <c r="F1316" t="inlineStr"/>
       <c r="G1316" t="n">
-        <v>48548333.287</v>
+        <v>48539874.287</v>
       </c>
       <c r="H1316" t="inlineStr"/>
     </row>
@@ -28964,7 +28964,7 @@
         <v>26.3</v>
       </c>
       <c r="G1317" t="n">
-        <v>51151683.522</v>
+        <v>51143225.522</v>
       </c>
       <c r="H1317" t="n">
         <v>2.8</v>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="F1318" t="inlineStr"/>
       <c r="G1318" t="n">
-        <v>50598736.384</v>
+        <v>50590277.384</v>
       </c>
       <c r="H1318" t="inlineStr"/>
     </row>
@@ -29010,7 +29010,7 @@
       </c>
       <c r="F1319" t="inlineStr"/>
       <c r="G1319" t="n">
-        <v>50059603.371</v>
+        <v>50051145.371</v>
       </c>
       <c r="H1319" t="inlineStr"/>
     </row>
@@ -29032,7 +29032,7 @@
       </c>
       <c r="F1320" t="inlineStr"/>
       <c r="G1320" t="n">
-        <v>50539310.593</v>
+        <v>50530852.593</v>
       </c>
       <c r="H1320" t="inlineStr"/>
     </row>
@@ -29054,7 +29054,7 @@
       </c>
       <c r="F1321" t="inlineStr"/>
       <c r="G1321" t="n">
-        <v>49901869.095</v>
+        <v>49893410.095</v>
       </c>
       <c r="H1321" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="F1322" t="inlineStr"/>
       <c r="G1322" t="n">
-        <v>48799759.5</v>
+        <v>48791300.5</v>
       </c>
       <c r="H1322" t="inlineStr"/>
     </row>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="F1323" t="inlineStr"/>
       <c r="G1323" t="n">
-        <v>47622448.888</v>
+        <v>47613990.888</v>
       </c>
       <c r="H1323" t="inlineStr"/>
     </row>
@@ -29120,7 +29120,7 @@
       </c>
       <c r="F1324" t="inlineStr"/>
       <c r="G1324" t="n">
-        <v>47085491.957</v>
+        <v>47077032.957</v>
       </c>
       <c r="H1324" t="inlineStr"/>
     </row>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="F1325" t="inlineStr"/>
       <c r="G1325" t="n">
-        <v>47070895.466</v>
+        <v>47062437.466</v>
       </c>
       <c r="H1325" t="inlineStr"/>
     </row>
@@ -29164,7 +29164,7 @@
       </c>
       <c r="F1326" t="inlineStr"/>
       <c r="G1326" t="n">
-        <v>47331467.259</v>
+        <v>47323008.259</v>
       </c>
       <c r="H1326" t="inlineStr"/>
     </row>
@@ -29186,7 +29186,7 @@
       </c>
       <c r="F1327" t="inlineStr"/>
       <c r="G1327" t="n">
-        <v>46641548.658</v>
+        <v>46633090.658</v>
       </c>
       <c r="H1327" t="inlineStr"/>
     </row>
@@ -29208,7 +29208,7 @@
       </c>
       <c r="F1328" t="inlineStr"/>
       <c r="G1328" t="n">
-        <v>46272394.919</v>
+        <v>46263936.919</v>
       </c>
       <c r="H1328" t="inlineStr"/>
     </row>
@@ -29230,7 +29230,7 @@
       </c>
       <c r="F1329" t="inlineStr"/>
       <c r="G1329" t="n">
-        <v>45991893.839</v>
+        <v>45983434.839</v>
       </c>
       <c r="H1329" t="inlineStr"/>
     </row>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="F1330" t="inlineStr"/>
       <c r="G1330" t="n">
-        <v>46122077.497</v>
+        <v>46113618.497</v>
       </c>
       <c r="H1330" t="inlineStr"/>
     </row>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="F1331" t="inlineStr"/>
       <c r="G1331" t="n">
-        <v>46114923.925</v>
+        <v>46106465.925</v>
       </c>
       <c r="H1331" t="inlineStr"/>
     </row>
@@ -29296,7 +29296,7 @@
       </c>
       <c r="F1332" t="inlineStr"/>
       <c r="G1332" t="n">
-        <v>45977156.945</v>
+        <v>45968697.945</v>
       </c>
       <c r="H1332" t="inlineStr"/>
     </row>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="F1333" t="inlineStr"/>
       <c r="G1333" t="n">
-        <v>46252950.278</v>
+        <v>46244492.278</v>
       </c>
       <c r="H1333" t="inlineStr"/>
     </row>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="F1334" t="inlineStr"/>
       <c r="G1334" t="n">
-        <v>46650122.056</v>
+        <v>46641664.056</v>
       </c>
       <c r="H1334" t="inlineStr"/>
     </row>
@@ -29362,7 +29362,7 @@
       </c>
       <c r="F1335" t="inlineStr"/>
       <c r="G1335" t="n">
-        <v>47641172.807</v>
+        <v>47632714.807</v>
       </c>
       <c r="H1335" t="inlineStr"/>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="F1336" t="inlineStr"/>
       <c r="G1336" t="n">
-        <v>48900090.485</v>
+        <v>48891632.485</v>
       </c>
       <c r="H1336" t="inlineStr"/>
     </row>
@@ -29406,7 +29406,7 @@
       </c>
       <c r="F1337" t="inlineStr"/>
       <c r="G1337" t="n">
-        <v>51147551.335</v>
+        <v>51139093.335</v>
       </c>
       <c r="H1337" t="inlineStr"/>
     </row>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="F1339" t="inlineStr"/>
       <c r="G1339" t="n">
-        <v>50302142.099</v>
+        <v>50293684.099</v>
       </c>
       <c r="H1339" t="inlineStr"/>
     </row>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="F1340" t="inlineStr"/>
       <c r="G1340" t="n">
-        <v>50143754.2</v>
+        <v>50135297.2</v>
       </c>
       <c r="H1340" t="inlineStr"/>
     </row>
@@ -29488,7 +29488,7 @@
       </c>
       <c r="F1341" t="inlineStr"/>
       <c r="G1341" t="n">
-        <v>50671072.622</v>
+        <v>50662614.622</v>
       </c>
       <c r="H1341" t="inlineStr"/>
     </row>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="F1342" t="inlineStr"/>
       <c r="G1342" t="n">
-        <v>51353396.846</v>
+        <v>51344938.846</v>
       </c>
       <c r="H1342" t="inlineStr"/>
     </row>
@@ -29532,7 +29532,7 @@
       </c>
       <c r="F1343" t="inlineStr"/>
       <c r="G1343" t="n">
-        <v>49832034.676</v>
+        <v>49823576.676</v>
       </c>
       <c r="H1343" t="inlineStr"/>
     </row>
@@ -29554,7 +29554,7 @@
       </c>
       <c r="F1344" t="inlineStr"/>
       <c r="G1344" t="n">
-        <v>49555309.468</v>
+        <v>49546850.468</v>
       </c>
       <c r="H1344" t="inlineStr"/>
     </row>
@@ -29576,7 +29576,7 @@
       </c>
       <c r="F1345" t="inlineStr"/>
       <c r="G1345" t="n">
-        <v>48964071.358</v>
+        <v>48955613.358</v>
       </c>
       <c r="H1345" t="inlineStr"/>
     </row>
@@ -29598,7 +29598,7 @@
       </c>
       <c r="F1346" t="inlineStr"/>
       <c r="G1346" t="n">
-        <v>49435847.152</v>
+        <v>49427389.152</v>
       </c>
       <c r="H1346" t="inlineStr"/>
     </row>
@@ -29620,7 +29620,7 @@
       </c>
       <c r="F1347" t="inlineStr"/>
       <c r="G1347" t="n">
-        <v>49108213.486</v>
+        <v>49099754.486</v>
       </c>
       <c r="H1347" t="inlineStr"/>
     </row>
@@ -29642,7 +29642,7 @@
       </c>
       <c r="F1348" t="inlineStr"/>
       <c r="G1348" t="n">
-        <v>49170854.452</v>
+        <v>49162396.452</v>
       </c>
       <c r="H1348" t="inlineStr"/>
     </row>
@@ -29664,7 +29664,7 @@
       </c>
       <c r="F1349" t="inlineStr"/>
       <c r="G1349" t="n">
-        <v>49237224.726</v>
+        <v>49228766.726</v>
       </c>
       <c r="H1349" t="inlineStr"/>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="F1350" t="inlineStr"/>
       <c r="G1350" t="n">
-        <v>49636653.914</v>
+        <v>49628194.914</v>
       </c>
       <c r="H1350" t="inlineStr"/>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="F1351" t="inlineStr"/>
       <c r="G1351" t="n">
-        <v>49146668.391</v>
+        <v>49138210.391</v>
       </c>
       <c r="H1351" t="inlineStr"/>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="F1352" t="inlineStr"/>
       <c r="G1352" t="n">
-        <v>49730646.724</v>
+        <v>49722189.724</v>
       </c>
       <c r="H1352" t="inlineStr"/>
     </row>
@@ -29752,7 +29752,7 @@
       </c>
       <c r="F1353" t="inlineStr"/>
       <c r="G1353" t="n">
-        <v>50203187.696</v>
+        <v>50194728.696</v>
       </c>
       <c r="H1353" t="inlineStr"/>
     </row>
@@ -29774,7 +29774,7 @@
       </c>
       <c r="F1354" t="inlineStr"/>
       <c r="G1354" t="n">
-        <v>50616102.767</v>
+        <v>50607644.767</v>
       </c>
       <c r="H1354" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
       </c>
       <c r="F1355" t="inlineStr"/>
       <c r="G1355" t="n">
-        <v>52886535.995</v>
+        <v>52878077.995</v>
       </c>
       <c r="H1355" t="inlineStr"/>
     </row>
@@ -29818,7 +29818,7 @@
       </c>
       <c r="F1356" t="inlineStr"/>
       <c r="G1356" t="n">
-        <v>53939835.682</v>
+        <v>53931376.682</v>
       </c>
       <c r="H1356" t="inlineStr"/>
     </row>
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57870174.056</v>
+        <v>57861716.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="n">
-        <v>56690839.267</v>
+        <v>56682381.267</v>
       </c>
       <c r="H1358" t="inlineStr"/>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="F1359" t="inlineStr"/>
       <c r="G1359" t="n">
-        <v>56050753.372</v>
+        <v>56042294.372</v>
       </c>
       <c r="H1359" t="inlineStr"/>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="n">
-        <v>56609711.504</v>
+        <v>56601252.504</v>
       </c>
       <c r="H1360" t="inlineStr"/>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="n">
-        <v>56847580.839</v>
+        <v>56839121.839</v>
       </c>
       <c r="H1361" t="inlineStr"/>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="n">
-        <v>55528259.571</v>
+        <v>55519800.571</v>
       </c>
       <c r="H1362" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="n">
-        <v>55338261.556</v>
+        <v>55329802.556</v>
       </c>
       <c r="H1363" t="inlineStr"/>
     </row>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="n">
-        <v>54551736.68</v>
+        <v>54543278.68</v>
       </c>
       <c r="H1364" t="inlineStr"/>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="n">
-        <v>53973149.241</v>
+        <v>53964691.241</v>
       </c>
       <c r="H1365" t="inlineStr"/>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="n">
-        <v>53580553.918</v>
+        <v>53572094.918</v>
       </c>
       <c r="H1366" t="inlineStr"/>
     </row>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F1367" t="inlineStr"/>
       <c r="G1367" t="n">
-        <v>53714345.53</v>
+        <v>53705888.53</v>
       </c>
       <c r="H1367" t="inlineStr"/>
     </row>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="n">
-        <v>52810758.228</v>
+        <v>52802300.228</v>
       </c>
       <c r="H1368" t="inlineStr"/>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53029604.434</v>
+        <v>53021146.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30130,7 +30130,7 @@
       </c>
       <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="n">
-        <v>52811035.166</v>
+        <v>52802578.166</v>
       </c>
       <c r="H1370" t="inlineStr"/>
     </row>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="F1371" t="inlineStr"/>
       <c r="G1371" t="n">
-        <v>52600723.418</v>
+        <v>52592265.418</v>
       </c>
       <c r="H1371" t="inlineStr"/>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="n">
-        <v>52240705.099</v>
+        <v>52232247.099</v>
       </c>
       <c r="H1372" t="inlineStr"/>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="n">
-        <v>52336098.713</v>
+        <v>52327639.713</v>
       </c>
       <c r="H1373" t="inlineStr"/>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="n">
-        <v>52879495.596</v>
+        <v>52871036.596</v>
       </c>
       <c r="H1374" t="inlineStr"/>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="n">
-        <v>52230075.178</v>
+        <v>52221618.178</v>
       </c>
       <c r="H1375" t="inlineStr"/>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="n">
-        <v>52611451.503</v>
+        <v>52602993.503</v>
       </c>
       <c r="H1376" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="n">
-        <v>52830854.197</v>
+        <v>52822396.197</v>
       </c>
       <c r="H1377" t="inlineStr"/>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="n">
-        <v>54103765.568</v>
+        <v>54095307.568</v>
       </c>
       <c r="H1378" t="inlineStr"/>
     </row>
@@ -30330,7 +30330,7 @@
         <v>21.1</v>
       </c>
       <c r="G1379" t="n">
-        <v>56532206.897</v>
+        <v>56523749.897</v>
       </c>
       <c r="H1379" t="n">
         <v>1.9</v>
@@ -30354,7 +30354,7 @@
       </c>
       <c r="F1380" t="inlineStr"/>
       <c r="G1380" t="n">
-        <v>56842949.779</v>
+        <v>56834490.779</v>
       </c>
       <c r="H1380" t="inlineStr"/>
     </row>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="F1381" t="inlineStr"/>
       <c r="G1381" t="n">
-        <v>55283219.451</v>
+        <v>55274761.451</v>
       </c>
       <c r="H1381" t="inlineStr"/>
     </row>
@@ -30398,7 +30398,7 @@
       </c>
       <c r="F1382" t="inlineStr"/>
       <c r="G1382" t="n">
-        <v>55325106.742</v>
+        <v>55316647.742</v>
       </c>
       <c r="H1382" t="inlineStr"/>
     </row>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="F1383" t="inlineStr"/>
       <c r="G1383" t="n">
-        <v>55599872.888</v>
+        <v>55591414.888</v>
       </c>
       <c r="H1383" t="inlineStr"/>
     </row>
@@ -30442,7 +30442,7 @@
       </c>
       <c r="F1384" t="inlineStr"/>
       <c r="G1384" t="n">
-        <v>55081022.049</v>
+        <v>55072563.049</v>
       </c>
       <c r="H1384" t="inlineStr"/>
     </row>
@@ -30464,7 +30464,7 @@
       </c>
       <c r="F1385" t="inlineStr"/>
       <c r="G1385" t="n">
-        <v>53826659.218</v>
+        <v>53818201.218</v>
       </c>
       <c r="H1385" t="inlineStr"/>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="F1386" t="inlineStr"/>
       <c r="G1386" t="n">
-        <v>52853683.644</v>
+        <v>52845225.644</v>
       </c>
       <c r="H1386" t="inlineStr"/>
     </row>
@@ -30508,7 +30508,7 @@
       </c>
       <c r="F1387" t="inlineStr"/>
       <c r="G1387" t="n">
-        <v>52133693.57</v>
+        <v>52125234.57</v>
       </c>
       <c r="H1387" t="inlineStr"/>
     </row>
@@ -30530,7 +30530,7 @@
       </c>
       <c r="F1388" t="inlineStr"/>
       <c r="G1388" t="n">
-        <v>51906469.889</v>
+        <v>51898010.889</v>
       </c>
       <c r="H1388" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
       </c>
       <c r="F1389" t="inlineStr"/>
       <c r="G1389" t="n">
-        <v>51868256.679</v>
+        <v>51859797.679</v>
       </c>
       <c r="H1389" t="inlineStr"/>
     </row>
@@ -30574,7 +30574,7 @@
       </c>
       <c r="F1390" t="inlineStr"/>
       <c r="G1390" t="n">
-        <v>51761402.828</v>
+        <v>51752944.828</v>
       </c>
       <c r="H1390" t="inlineStr"/>
     </row>
@@ -30596,7 +30596,7 @@
       </c>
       <c r="F1391" t="inlineStr"/>
       <c r="G1391" t="n">
-        <v>51344112.283</v>
+        <v>51335654.283</v>
       </c>
       <c r="H1391" t="inlineStr"/>
     </row>
@@ -30618,7 +30618,7 @@
       </c>
       <c r="F1392" t="inlineStr"/>
       <c r="G1392" t="n">
-        <v>50740868.116</v>
+        <v>50732410.116</v>
       </c>
       <c r="H1392" t="inlineStr"/>
     </row>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="F1393" t="inlineStr"/>
       <c r="G1393" t="n">
-        <v>50592936.926</v>
+        <v>50584477.926</v>
       </c>
       <c r="H1393" t="inlineStr"/>
     </row>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="F1394" t="inlineStr"/>
       <c r="G1394" t="n">
-        <v>50248598.764</v>
+        <v>50240140.764</v>
       </c>
       <c r="H1394" t="inlineStr"/>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="F1395" t="inlineStr"/>
       <c r="G1395" t="n">
-        <v>50133603.563</v>
+        <v>50125144.563</v>
       </c>
       <c r="H1395" t="inlineStr"/>
     </row>
@@ -30706,7 +30706,7 @@
       </c>
       <c r="F1396" t="inlineStr"/>
       <c r="G1396" t="n">
-        <v>49666069.924</v>
+        <v>49657612.924</v>
       </c>
       <c r="H1396" t="inlineStr"/>
     </row>
@@ -30728,7 +30728,7 @@
       </c>
       <c r="F1397" t="inlineStr"/>
       <c r="G1397" t="n">
-        <v>51061598.556</v>
+        <v>51053140.556</v>
       </c>
       <c r="H1397" t="inlineStr"/>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="F1398" t="inlineStr"/>
       <c r="G1398" t="n">
-        <v>51934592.644</v>
+        <v>51926134.644</v>
       </c>
       <c r="H1398" t="inlineStr"/>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="F1399" t="inlineStr"/>
       <c r="G1399" t="n">
-        <v>54295505.622</v>
+        <v>54287047.622</v>
       </c>
       <c r="H1399" t="inlineStr"/>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="F1401" t="inlineStr"/>
       <c r="G1401" t="n">
-        <v>53411271.53</v>
+        <v>53402812.53</v>
       </c>
       <c r="H1401" t="inlineStr"/>
     </row>
@@ -30832,7 +30832,7 @@
       </c>
       <c r="F1402" t="inlineStr"/>
       <c r="G1402" t="n">
-        <v>52803828.855</v>
+        <v>52795369.855</v>
       </c>
       <c r="H1402" t="inlineStr"/>
     </row>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="F1403" t="inlineStr"/>
       <c r="G1403" t="n">
-        <v>53288409.593</v>
+        <v>53279951.593</v>
       </c>
       <c r="H1403" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
       </c>
       <c r="F1404" t="inlineStr"/>
       <c r="G1404" t="n">
-        <v>54227491.308</v>
+        <v>54219032.308</v>
       </c>
       <c r="H1404" t="inlineStr"/>
     </row>
@@ -30898,7 +30898,7 @@
       </c>
       <c r="F1405" t="inlineStr"/>
       <c r="G1405" t="n">
-        <v>53237806.494</v>
+        <v>53229348.494</v>
       </c>
       <c r="H1405" t="inlineStr"/>
     </row>
@@ -30920,7 +30920,7 @@
       </c>
       <c r="F1406" t="inlineStr"/>
       <c r="G1406" t="n">
-        <v>52670925.98</v>
+        <v>52662466.98</v>
       </c>
       <c r="H1406" t="inlineStr"/>
     </row>
@@ -30942,7 +30942,7 @@
       </c>
       <c r="F1407" t="inlineStr"/>
       <c r="G1407" t="n">
-        <v>51814468.704</v>
+        <v>51806010.704</v>
       </c>
       <c r="H1407" t="inlineStr"/>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="F1408" t="inlineStr"/>
       <c r="G1408" t="n">
-        <v>51822208.154</v>
+        <v>51813750.154</v>
       </c>
       <c r="H1408" t="inlineStr"/>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="F1409" t="inlineStr"/>
       <c r="G1409" t="n">
-        <v>51697231.007</v>
+        <v>51688773.007</v>
       </c>
       <c r="H1409" t="inlineStr"/>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="F1410" t="inlineStr"/>
       <c r="G1410" t="n">
-        <v>50972387.014</v>
+        <v>50963928.014</v>
       </c>
       <c r="H1410" t="inlineStr"/>
     </row>
@@ -31030,7 +31030,7 @@
       </c>
       <c r="F1411" t="inlineStr"/>
       <c r="G1411" t="n">
-        <v>51308434.064</v>
+        <v>51299976.064</v>
       </c>
       <c r="H1411" t="inlineStr"/>
     </row>
@@ -31052,7 +31052,7 @@
       </c>
       <c r="F1412" t="inlineStr"/>
       <c r="G1412" t="n">
-        <v>50254006.352</v>
+        <v>50245548.352</v>
       </c>
       <c r="H1412" t="inlineStr"/>
     </row>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="F1413" t="inlineStr"/>
       <c r="G1413" t="n">
-        <v>50406420.972</v>
+        <v>50397961.972</v>
       </c>
       <c r="H1413" t="inlineStr"/>
     </row>
@@ -31096,7 +31096,7 @@
       </c>
       <c r="F1414" t="inlineStr"/>
       <c r="G1414" t="n">
-        <v>50500571.477</v>
+        <v>50492113.477</v>
       </c>
       <c r="H1414" t="inlineStr"/>
     </row>
@@ -31118,7 +31118,7 @@
       </c>
       <c r="F1415" t="inlineStr"/>
       <c r="G1415" t="n">
-        <v>50439803.859</v>
+        <v>50431345.859</v>
       </c>
       <c r="H1415" t="inlineStr"/>
     </row>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="F1416" t="inlineStr"/>
       <c r="G1416" t="n">
-        <v>50481007.937</v>
+        <v>50472549.937</v>
       </c>
       <c r="H1416" t="inlineStr"/>
     </row>
@@ -31162,7 +31162,7 @@
       </c>
       <c r="F1417" t="inlineStr"/>
       <c r="G1417" t="n">
-        <v>50358553.92</v>
+        <v>50350094.92</v>
       </c>
       <c r="H1417" t="inlineStr"/>
     </row>
@@ -31184,7 +31184,7 @@
       </c>
       <c r="F1418" t="inlineStr"/>
       <c r="G1418" t="n">
-        <v>50633388.87</v>
+        <v>50624930.87</v>
       </c>
       <c r="H1418" t="inlineStr"/>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="F1419" t="inlineStr"/>
       <c r="G1419" t="n">
-        <v>51170146.993</v>
+        <v>51161688.993</v>
       </c>
       <c r="H1419" t="inlineStr"/>
     </row>
@@ -31228,7 +31228,7 @@
       </c>
       <c r="F1420" t="inlineStr"/>
       <c r="G1420" t="n">
-        <v>51149780.537</v>
+        <v>51141322.537</v>
       </c>
       <c r="H1420" t="inlineStr"/>
     </row>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="F1421" t="inlineStr"/>
       <c r="G1421" t="n">
-        <v>52962315.45</v>
+        <v>52953857.45</v>
       </c>
       <c r="H1421" t="inlineStr"/>
     </row>
@@ -31274,7 +31274,7 @@
         <v>21.9</v>
       </c>
       <c r="G1422" t="n">
-        <v>55421105.222</v>
+        <v>55412646.222</v>
       </c>
       <c r="H1422" t="n">
         <v>2.1</v>
@@ -31298,7 +31298,7 @@
       </c>
       <c r="F1423" t="inlineStr"/>
       <c r="G1423" t="n">
-        <v>55659699.331</v>
+        <v>55651241.331</v>
       </c>
       <c r="H1423" t="inlineStr"/>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="F1424" t="inlineStr"/>
       <c r="G1424" t="n">
-        <v>55721626.151</v>
+        <v>55713167.151</v>
       </c>
       <c r="H1424" t="inlineStr"/>
     </row>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="F1425" t="inlineStr"/>
       <c r="G1425" t="n">
-        <v>55987337.978</v>
+        <v>55978878.978</v>
       </c>
       <c r="H1425" t="inlineStr"/>
     </row>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="F1426" t="inlineStr"/>
       <c r="G1426" t="n">
-        <v>55759039.241</v>
+        <v>55750581.241</v>
       </c>
       <c r="H1426" t="inlineStr"/>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="F1427" t="inlineStr"/>
       <c r="G1427" t="n">
-        <v>54922215.217</v>
+        <v>54913757.217</v>
       </c>
       <c r="H1427" t="inlineStr"/>
     </row>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="F1428" t="inlineStr"/>
       <c r="G1428" t="n">
-        <v>54800519.24</v>
+        <v>54792060.24</v>
       </c>
       <c r="H1428" t="inlineStr"/>
     </row>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="F1429" t="inlineStr"/>
       <c r="G1429" t="n">
-        <v>54513647.576</v>
+        <v>54505188.576</v>
       </c>
       <c r="H1429" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="F1430" t="inlineStr"/>
       <c r="G1430" t="n">
-        <v>54525062.621</v>
+        <v>54516603.621</v>
       </c>
       <c r="H1430" t="inlineStr"/>
     </row>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="F1431" t="inlineStr"/>
       <c r="G1431" t="n">
-        <v>51993134.914</v>
+        <v>51984676.914</v>
       </c>
       <c r="H1431" t="inlineStr"/>
     </row>
@@ -31496,7 +31496,7 @@
       </c>
       <c r="F1432" t="inlineStr"/>
       <c r="G1432" t="n">
-        <v>52551957.382</v>
+        <v>52543499.382</v>
       </c>
       <c r="H1432" t="inlineStr"/>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="F1433" t="inlineStr"/>
       <c r="G1433" t="n">
-        <v>51756475.388</v>
+        <v>51748017.388</v>
       </c>
       <c r="H1433" t="inlineStr"/>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="F1434" t="inlineStr"/>
       <c r="G1434" t="n">
-        <v>50523927.623</v>
+        <v>50515468.623</v>
       </c>
       <c r="H1434" t="inlineStr"/>
     </row>
@@ -31562,7 +31562,7 @@
       </c>
       <c r="F1435" t="inlineStr"/>
       <c r="G1435" t="n">
-        <v>50569298.287</v>
+        <v>50560839.287</v>
       </c>
       <c r="H1435" t="inlineStr"/>
     </row>
@@ -31584,7 +31584,7 @@
       </c>
       <c r="F1436" t="inlineStr"/>
       <c r="G1436" t="n">
-        <v>50102876.307</v>
+        <v>50094418.307</v>
       </c>
       <c r="H1436" t="inlineStr"/>
     </row>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="F1437" t="inlineStr"/>
       <c r="G1437" t="n">
-        <v>50823224.53</v>
+        <v>50814766.53</v>
       </c>
       <c r="H1437" t="inlineStr"/>
     </row>
@@ -31628,7 +31628,7 @@
       </c>
       <c r="F1438" t="inlineStr"/>
       <c r="G1438" t="n">
-        <v>50067303.981</v>
+        <v>50058845.981</v>
       </c>
       <c r="H1438" t="inlineStr"/>
     </row>
@@ -31650,7 +31650,7 @@
       </c>
       <c r="F1439" t="inlineStr"/>
       <c r="G1439" t="n">
-        <v>49912789.76</v>
+        <v>49904330.76</v>
       </c>
       <c r="H1439" t="inlineStr"/>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="F1440" t="inlineStr"/>
       <c r="G1440" t="n">
-        <v>49828408.195</v>
+        <v>49819950.195</v>
       </c>
       <c r="H1440" t="inlineStr"/>
     </row>
@@ -31694,7 +31694,7 @@
       </c>
       <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="n">
-        <v>49571242.045</v>
+        <v>49562784.045</v>
       </c>
       <c r="H1441" t="inlineStr"/>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="F1442" t="inlineStr"/>
       <c r="G1442" t="n">
-        <v>50118935.504</v>
+        <v>50110477.504</v>
       </c>
       <c r="H1442" t="inlineStr"/>
     </row>
@@ -31738,7 +31738,7 @@
       </c>
       <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="n">
-        <v>51573617.942</v>
+        <v>51565158.942</v>
       </c>
       <c r="H1443" t="inlineStr"/>
     </row>
@@ -31762,7 +31762,7 @@
         <v>20.8</v>
       </c>
       <c r="G1444" t="n">
-        <v>53928320.608</v>
+        <v>53919863.608</v>
       </c>
       <c r="H1444" t="n">
         <v>2.3</v>
@@ -31786,7 +31786,7 @@
       </c>
       <c r="F1445" t="inlineStr"/>
       <c r="G1445" t="n">
-        <v>53500962.301</v>
+        <v>53492503.301</v>
       </c>
       <c r="H1445" t="inlineStr"/>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F1446" t="inlineStr"/>
       <c r="G1446" t="n">
-        <v>53073770.662</v>
+        <v>53065312.662</v>
       </c>
       <c r="H1446" t="inlineStr"/>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="F1447" t="inlineStr"/>
       <c r="G1447" t="n">
-        <v>53739993.632</v>
+        <v>53731535.632</v>
       </c>
       <c r="H1447" t="inlineStr"/>
     </row>
@@ -31852,7 +31852,7 @@
       </c>
       <c r="F1448" t="inlineStr"/>
       <c r="G1448" t="n">
-        <v>53006959.148</v>
+        <v>52998501.148</v>
       </c>
       <c r="H1448" t="inlineStr"/>
     </row>
@@ -31874,7 +31874,7 @@
       </c>
       <c r="F1449" t="inlineStr"/>
       <c r="G1449" t="n">
-        <v>51792799.271</v>
+        <v>51784340.271</v>
       </c>
       <c r="H1449" t="inlineStr"/>
     </row>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="F1450" t="inlineStr"/>
       <c r="G1450" t="n">
-        <v>50294060.976</v>
+        <v>50285602.976</v>
       </c>
       <c r="H1450" t="inlineStr"/>
     </row>
@@ -31918,7 +31918,7 @@
       </c>
       <c r="F1451" t="inlineStr"/>
       <c r="G1451" t="n">
-        <v>50854967.288</v>
+        <v>50846508.288</v>
       </c>
       <c r="H1451" t="inlineStr"/>
     </row>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="F1452" t="inlineStr"/>
       <c r="G1452" t="n">
-        <v>50585785.336</v>
+        <v>50577326.336</v>
       </c>
       <c r="H1452" t="inlineStr"/>
     </row>
@@ -31962,7 +31962,7 @@
       </c>
       <c r="F1453" t="inlineStr"/>
       <c r="G1453" t="n">
-        <v>50579961.135</v>
+        <v>50571502.135</v>
       </c>
       <c r="H1453" t="inlineStr"/>
     </row>
@@ -31984,7 +31984,7 @@
       </c>
       <c r="F1454" t="inlineStr"/>
       <c r="G1454" t="n">
-        <v>50394691.524</v>
+        <v>50386233.524</v>
       </c>
       <c r="H1454" t="inlineStr"/>
     </row>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="F1455" t="inlineStr"/>
       <c r="G1455" t="n">
-        <v>50232588.389</v>
+        <v>50224130.389</v>
       </c>
       <c r="H1455" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
       </c>
       <c r="F1456" t="inlineStr"/>
       <c r="G1456" t="n">
-        <v>50049249.804</v>
+        <v>50040791.804</v>
       </c>
       <c r="H1456" t="inlineStr"/>
     </row>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="F1457" t="inlineStr"/>
       <c r="G1457" t="n">
-        <v>50644753.035</v>
+        <v>50636294.035</v>
       </c>
       <c r="H1457" t="inlineStr"/>
     </row>
@@ -32072,7 +32072,7 @@
       </c>
       <c r="F1458" t="inlineStr"/>
       <c r="G1458" t="n">
-        <v>51439216.263</v>
+        <v>51430758.263</v>
       </c>
       <c r="H1458" t="inlineStr"/>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="F1459" t="inlineStr"/>
       <c r="G1459" t="n">
-        <v>51922788.288</v>
+        <v>51914331.288</v>
       </c>
       <c r="H1459" t="inlineStr"/>
     </row>
@@ -32116,7 +32116,7 @@
       </c>
       <c r="F1460" t="inlineStr"/>
       <c r="G1460" t="n">
-        <v>53305815.364</v>
+        <v>53297358.364</v>
       </c>
       <c r="H1460" t="inlineStr"/>
     </row>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="n">
-        <v>56168926.43</v>
+        <v>56137543.43</v>
       </c>
       <c r="H1461" t="inlineStr"/>
     </row>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="F1463" t="inlineStr"/>
       <c r="G1463" t="n">
-        <v>56171069.367</v>
+        <v>56139686.367</v>
       </c>
       <c r="H1463" t="inlineStr"/>
     </row>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="F1464" t="inlineStr"/>
       <c r="G1464" t="n">
-        <v>55040073.993</v>
+        <v>55008690.993</v>
       </c>
       <c r="H1464" t="inlineStr"/>
     </row>
@@ -32220,7 +32220,7 @@
       </c>
       <c r="F1465" t="inlineStr"/>
       <c r="G1465" t="n">
-        <v>55466348.785</v>
+        <v>55434965.785</v>
       </c>
       <c r="H1465" t="inlineStr"/>
     </row>
@@ -32242,7 +32242,7 @@
       </c>
       <c r="F1466" t="inlineStr"/>
       <c r="G1466" t="n">
-        <v>56346226.518</v>
+        <v>56314843.518</v>
       </c>
       <c r="H1466" t="inlineStr"/>
     </row>
@@ -32264,7 +32264,7 @@
       </c>
       <c r="F1467" t="inlineStr"/>
       <c r="G1467" t="n">
-        <v>55355955.095</v>
+        <v>55324573.095</v>
       </c>
       <c r="H1467" t="inlineStr"/>
     </row>
@@ -32286,7 +32286,7 @@
       </c>
       <c r="F1468" t="inlineStr"/>
       <c r="G1468" t="n">
-        <v>54689707.736</v>
+        <v>54658324.736</v>
       </c>
       <c r="H1468" t="inlineStr"/>
     </row>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="F1469" t="inlineStr"/>
       <c r="G1469" t="n">
-        <v>54565845.54</v>
+        <v>54534463.54</v>
       </c>
       <c r="H1469" t="inlineStr"/>
     </row>
@@ -32330,7 +32330,7 @@
       </c>
       <c r="F1470" t="inlineStr"/>
       <c r="G1470" t="n">
-        <v>55273378.612</v>
+        <v>55241995.612</v>
       </c>
       <c r="H1470" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
       </c>
       <c r="F1471" t="inlineStr"/>
       <c r="G1471" t="n">
-        <v>55087698.123</v>
+        <v>55056315.123</v>
       </c>
       <c r="H1471" t="inlineStr"/>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="F1472" t="inlineStr"/>
       <c r="G1472" t="n">
-        <v>56298646.956</v>
+        <v>56267264.956</v>
       </c>
       <c r="H1472" t="inlineStr"/>
     </row>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="F1473" t="inlineStr"/>
       <c r="G1473" t="n">
-        <v>56136930.885</v>
+        <v>56105547.885</v>
       </c>
       <c r="H1473" t="inlineStr"/>
     </row>
@@ -32418,7 +32418,7 @@
       </c>
       <c r="F1474" t="inlineStr"/>
       <c r="G1474" t="n">
-        <v>57312203.778</v>
+        <v>57280821.778</v>
       </c>
       <c r="H1474" t="inlineStr"/>
     </row>
@@ -32440,7 +32440,7 @@
       </c>
       <c r="F1475" t="inlineStr"/>
       <c r="G1475" t="n">
-        <v>58743818.611</v>
+        <v>58712436.611</v>
       </c>
       <c r="H1475" t="inlineStr"/>
     </row>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="F1476" t="inlineStr"/>
       <c r="G1476" t="n">
-        <v>59900884.332</v>
+        <v>59869501.332</v>
       </c>
       <c r="H1476" t="inlineStr"/>
     </row>
@@ -32484,7 +32484,7 @@
       </c>
       <c r="F1477" t="inlineStr"/>
       <c r="G1477" t="n">
-        <v>60284078.984</v>
+        <v>60252696.984</v>
       </c>
       <c r="H1477" t="inlineStr"/>
     </row>
@@ -32506,7 +32506,7 @@
       </c>
       <c r="F1478" t="inlineStr"/>
       <c r="G1478" t="n">
-        <v>60808926.024</v>
+        <v>60777543.024</v>
       </c>
       <c r="H1478" t="inlineStr"/>
     </row>
@@ -32528,7 +32528,7 @@
       </c>
       <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="n">
-        <v>60736131.044</v>
+        <v>60704748.044</v>
       </c>
       <c r="H1479" t="inlineStr"/>
     </row>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="F1480" t="inlineStr"/>
       <c r="G1480" t="n">
-        <v>62891143.767</v>
+        <v>62859760.767</v>
       </c>
       <c r="H1480" t="inlineStr"/>
     </row>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65285582.703</v>
+        <v>65254200.703</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -32610,7 +32610,7 @@
       </c>
       <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="n">
-        <v>64568116.281</v>
+        <v>64536734.281</v>
       </c>
       <c r="H1483" t="inlineStr"/>
     </row>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61856297.993</v>
+        <v>61824915.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61173985.519</v>
+        <v>61142602.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61709332.076</v>
+        <v>61677950.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32698,7 +32698,7 @@
       </c>
       <c r="F1487" t="inlineStr"/>
       <c r="G1487" t="n">
-        <v>60470218.004</v>
+        <v>60438835.004</v>
       </c>
       <c r="H1487" t="inlineStr"/>
     </row>
@@ -32720,7 +32720,7 @@
       </c>
       <c r="F1488" t="inlineStr"/>
       <c r="G1488" t="n">
-        <v>59516490.211</v>
+        <v>59485108.211</v>
       </c>
       <c r="H1488" t="inlineStr"/>
     </row>
@@ -32742,7 +32742,7 @@
       </c>
       <c r="F1489" t="inlineStr"/>
       <c r="G1489" t="n">
-        <v>57795000.381</v>
+        <v>57763617.381</v>
       </c>
       <c r="H1489" t="inlineStr"/>
     </row>
@@ -32764,7 +32764,7 @@
       </c>
       <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="n">
-        <v>57203686.101</v>
+        <v>57172304.101</v>
       </c>
       <c r="H1490" t="inlineStr"/>
     </row>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="n">
-        <v>57131635.244</v>
+        <v>57100253.244</v>
       </c>
       <c r="H1491" t="inlineStr"/>
     </row>
@@ -32808,7 +32808,7 @@
       </c>
       <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="n">
-        <v>57559010.399</v>
+        <v>57527627.399</v>
       </c>
       <c r="H1492" t="inlineStr"/>
     </row>
@@ -32830,7 +32830,7 @@
       </c>
       <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="n">
-        <v>56233995.088</v>
+        <v>56202613.088</v>
       </c>
       <c r="H1493" t="inlineStr"/>
     </row>
@@ -32852,7 +32852,7 @@
       </c>
       <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="n">
-        <v>55611083.47</v>
+        <v>55579701.47</v>
       </c>
       <c r="H1494" t="inlineStr"/>
     </row>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="n">
-        <v>55437531.492</v>
+        <v>55406149.492</v>
       </c>
       <c r="H1495" t="inlineStr"/>
     </row>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55266847.796</v>
+        <v>55235464.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="n">
-        <v>55029578.613</v>
+        <v>54998195.613</v>
       </c>
       <c r="H1497" t="inlineStr"/>
     </row>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="n">
-        <v>54730152.758</v>
+        <v>54698770.758</v>
       </c>
       <c r="H1498" t="inlineStr"/>
     </row>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54878596.349</v>
+        <v>54847213.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -32984,7 +32984,7 @@
       </c>
       <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="n">
-        <v>55139821.773</v>
+        <v>55108439.773</v>
       </c>
       <c r="H1500" t="inlineStr"/>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="n">
-        <v>55895500.062</v>
+        <v>55864117.062</v>
       </c>
       <c r="H1501" t="inlineStr"/>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="n">
-        <v>57590370.416</v>
+        <v>57558988.416</v>
       </c>
       <c r="H1502" t="inlineStr"/>
     </row>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60132095.818</v>
+        <v>60127059.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33088,7 +33088,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59037854.841</v>
+        <v>59032021.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58339429.213</v>
+        <v>58333595.213</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58572666.727</v>
+        <v>58566832.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59660467.587</v>
+        <v>59654634.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58027858.8</v>
+        <v>58022025.8</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57258654.786</v>
+        <v>57252820.786</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33220,7 +33220,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56138560.11</v>
+        <v>56132727.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56450816.744</v>
+        <v>56444984.744</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33264,7 +33264,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55866507.876</v>
+        <v>55860674.876</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33286,7 +33286,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55589155.143</v>
+        <v>55583322.143</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55622819.479</v>
+        <v>55616986.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55672165.733</v>
+        <v>55666332.733</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33352,7 +33352,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55243088.15</v>
+        <v>55237255.15</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33374,7 +33374,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55288215.162</v>
+        <v>55282382.162</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
       </c>
       <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="n">
-        <v>54710168.928</v>
+        <v>54704336.928</v>
       </c>
       <c r="H1519" t="inlineStr"/>
     </row>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="n">
-        <v>55610780.663</v>
+        <v>55604946.663</v>
       </c>
       <c r="H1520" t="inlineStr"/>
     </row>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57361187.612</v>
+        <v>57355353.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60376122.102</v>
+        <v>60364961.102</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59184130.726</v>
+        <v>59169263.726</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58640428.442</v>
+        <v>58625393.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58667745.045</v>
+        <v>58650299.045</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59439155.058</v>
+        <v>59428843.058</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33588,7 +33588,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57843183.899</v>
+        <v>57829613.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57125534.668</v>
+        <v>57120482.668</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33632,7 +33632,7 @@
       </c>
       <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="n">
-        <v>56157219.566</v>
+        <v>56146349.566</v>
       </c>
       <c r="H1530" t="inlineStr"/>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="n">
-        <v>56043666.838</v>
+        <v>56032703.838</v>
       </c>
       <c r="H1531" t="inlineStr"/>
     </row>
@@ -33676,7 +33676,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55970714.807</v>
+        <v>55959551.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56240803.122</v>
+        <v>56230150.122</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55944484.807</v>
+        <v>55935434.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55086539.219</v>
+        <v>55075712.219</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="n">
-        <v>54534456.642</v>
+        <v>54523399.642</v>
       </c>
       <c r="H1536" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54594397.849</v>
+        <v>54583252.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54966515.591</v>
+        <v>54955402.591</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="n">
-        <v>56161377.145</v>
+        <v>56151551.145</v>
       </c>
       <c r="H1539" t="inlineStr"/>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="n">
-        <v>55836890.824</v>
+        <v>55825762.824</v>
       </c>
       <c r="H1540" t="inlineStr"/>
     </row>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="n">
-        <v>56014258.906</v>
+        <v>56003116.906</v>
       </c>
       <c r="H1541" t="inlineStr"/>
     </row>
@@ -33896,7 +33896,7 @@
       </c>
       <c r="F1542" t="inlineStr"/>
       <c r="G1542" t="n">
-        <v>57901062.582</v>
+        <v>58224243.582</v>
       </c>
       <c r="H1542" t="inlineStr"/>
     </row>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60808038.977</v>
+        <v>60825764.977</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -33944,7 +33944,7 @@
       </c>
       <c r="F1544" t="inlineStr"/>
       <c r="G1544" t="n">
-        <v>59370744.198</v>
+        <v>59401698.307</v>
       </c>
       <c r="H1544" t="inlineStr"/>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="F1545" t="inlineStr"/>
       <c r="G1545" t="n">
-        <v>58839125.155</v>
+        <v>58871252.314</v>
       </c>
       <c r="H1545" t="inlineStr"/>
     </row>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="n">
-        <v>58452009.682</v>
+        <v>58484137.841</v>
       </c>
       <c r="H1546" t="inlineStr"/>
     </row>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="F1547" t="inlineStr"/>
       <c r="G1547" t="n">
-        <v>58165548.124</v>
+        <v>58197675.283</v>
       </c>
       <c r="H1547" t="inlineStr"/>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="F1548" t="inlineStr"/>
       <c r="G1548" t="n">
-        <v>57444490.389</v>
+        <v>57476618.548</v>
       </c>
       <c r="H1548" t="inlineStr"/>
     </row>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="n">
-        <v>56900664.286</v>
+        <v>56932791.445</v>
       </c>
       <c r="H1549" t="inlineStr"/>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="F1550" t="inlineStr"/>
       <c r="G1550" t="n">
-        <v>55910624.657</v>
+        <v>55942751.816</v>
       </c>
       <c r="H1550" t="inlineStr"/>
     </row>
@@ -34098,7 +34098,7 @@
       </c>
       <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="n">
-        <v>55711314.903</v>
+        <v>55743443.062</v>
       </c>
       <c r="H1551" t="inlineStr"/>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="F1552" t="inlineStr"/>
       <c r="G1552" t="n">
-        <v>56250720.687</v>
+        <v>56282847.846</v>
       </c>
       <c r="H1552" t="inlineStr"/>
     </row>
@@ -34142,7 +34142,7 @@
       </c>
       <c r="F1553" t="inlineStr"/>
       <c r="G1553" t="n">
-        <v>55510513.205</v>
+        <v>55510633.364</v>
       </c>
       <c r="H1553" t="inlineStr"/>
     </row>
@@ -34164,7 +34164,7 @@
       </c>
       <c r="F1554" t="inlineStr"/>
       <c r="G1554" t="n">
-        <v>55092305.834</v>
+        <v>55092424.993</v>
       </c>
       <c r="H1554" t="inlineStr"/>
     </row>
@@ -34186,7 +34186,7 @@
       </c>
       <c r="F1555" t="inlineStr"/>
       <c r="G1555" t="n">
-        <v>55048299.568</v>
+        <v>55048418.727</v>
       </c>
       <c r="H1555" t="inlineStr"/>
     </row>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="F1556" t="inlineStr"/>
       <c r="G1556" t="n">
-        <v>54459268.513</v>
+        <v>54449917.66</v>
       </c>
       <c r="H1556" t="inlineStr"/>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="F1557" t="inlineStr"/>
       <c r="G1557" t="n">
-        <v>53870479.913</v>
+        <v>53870535.922</v>
       </c>
       <c r="H1557" t="inlineStr"/>
     </row>
@@ -34252,7 +34252,7 @@
       </c>
       <c r="F1558" t="inlineStr"/>
       <c r="G1558" t="n">
-        <v>54008568.169</v>
+        <v>54000295.274</v>
       </c>
       <c r="H1558" t="inlineStr"/>
     </row>
@@ -34274,7 +34274,7 @@
       </c>
       <c r="F1559" t="inlineStr"/>
       <c r="G1559" t="n">
-        <v>54427905.41</v>
+        <v>54423761.634</v>
       </c>
       <c r="H1559" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
       </c>
       <c r="F1560" t="inlineStr"/>
       <c r="G1560" t="n">
-        <v>55382574.306</v>
+        <v>55403100.331</v>
       </c>
       <c r="H1560" t="inlineStr"/>
     </row>
@@ -34317,15 +34317,21 @@
         <v>21.625</v>
       </c>
       <c r="F1561" t="inlineStr"/>
-      <c r="G1561" t="inlineStr"/>
+      <c r="G1561" t="n">
+        <v>55803751.425</v>
+      </c>
       <c r="H1561" t="inlineStr"/>
     </row>
     <row r="1562">
       <c r="A1562" s="1" t="n">
         <v>46141</v>
       </c>
-      <c r="B1562" t="inlineStr"/>
-      <c r="C1562" t="inlineStr"/>
+      <c r="B1562" t="n">
+        <v>45207</v>
+      </c>
+      <c r="C1562" t="n">
+        <v>41994279</v>
+      </c>
       <c r="D1562" t="n">
         <v>1418.69</v>
       </c>
@@ -34333,22 +34339,128 @@
         <v>21</v>
       </c>
       <c r="F1562" t="inlineStr"/>
-      <c r="G1562" t="inlineStr"/>
+      <c r="G1562" t="n">
+        <v>59089246.861</v>
+      </c>
       <c r="H1562" t="inlineStr"/>
     </row>
     <row r="1563">
       <c r="A1563" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="B1563" t="inlineStr"/>
-      <c r="C1563" t="inlineStr"/>
+      <c r="B1563" t="n">
+        <v>44516</v>
+      </c>
+      <c r="C1563" t="n">
+        <v>42132457</v>
+      </c>
       <c r="D1563" t="n">
         <v>1415.8</v>
       </c>
-      <c r="E1563" t="inlineStr"/>
-      <c r="F1563" t="inlineStr"/>
-      <c r="G1563" t="inlineStr"/>
+      <c r="E1563" t="n">
+        <v>20.875</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G1563" t="n">
+        <v>62781439.944</v>
+      </c>
       <c r="H1563" t="inlineStr"/>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B1564" t="n">
+        <v>45657</v>
+      </c>
+      <c r="C1564" t="n">
+        <v>41845927</v>
+      </c>
+      <c r="D1564" t="n">
+        <v>1424.64</v>
+      </c>
+      <c r="E1564" t="n">
+        <v>21.4375</v>
+      </c>
+      <c r="F1564" t="inlineStr"/>
+      <c r="G1564" t="n">
+        <v>60478501.745</v>
+      </c>
+      <c r="H1564" t="inlineStr"/>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B1565" t="n">
+        <v>45906</v>
+      </c>
+      <c r="C1565" t="n">
+        <v>41285996</v>
+      </c>
+      <c r="D1565" t="n">
+        <v>1416.84</v>
+      </c>
+      <c r="E1565" t="n">
+        <v>22.3125</v>
+      </c>
+      <c r="F1565" t="inlineStr"/>
+      <c r="G1565" t="n">
+        <v>59841854.572</v>
+      </c>
+      <c r="H1565" t="inlineStr"/>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B1566" t="n">
+        <v>45678</v>
+      </c>
+      <c r="C1566" t="n">
+        <v>40768742</v>
+      </c>
+      <c r="D1566" t="n">
+        <v>1408.27</v>
+      </c>
+      <c r="E1566" t="n">
+        <v>20.9375</v>
+      </c>
+      <c r="F1566" t="inlineStr"/>
+      <c r="G1566" t="inlineStr"/>
+      <c r="H1566" t="inlineStr"/>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B1567" t="inlineStr"/>
+      <c r="C1567" t="inlineStr"/>
+      <c r="D1567" t="n">
+        <v>1417.62</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>21.375</v>
+      </c>
+      <c r="F1567" t="inlineStr"/>
+      <c r="G1567" t="inlineStr"/>
+      <c r="H1567" t="inlineStr"/>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B1568" t="inlineStr"/>
+      <c r="C1568" t="inlineStr"/>
+      <c r="D1568" t="n">
+        <v>1418.34</v>
+      </c>
+      <c r="E1568" t="inlineStr"/>
+      <c r="F1568" t="inlineStr"/>
+      <c r="G1568" t="inlineStr"/>
+      <c r="H1568" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1568"/>
+  <dimension ref="A1:H1573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27278,7 +27278,7 @@
       </c>
       <c r="F1241" t="inlineStr"/>
       <c r="G1241" t="n">
-        <v>47041621.424</v>
+        <v>47024027.424</v>
       </c>
       <c r="H1241" t="inlineStr"/>
     </row>
@@ -27300,7 +27300,7 @@
       </c>
       <c r="F1242" t="inlineStr"/>
       <c r="G1242" t="n">
-        <v>47228254.385</v>
+        <v>47210661.385</v>
       </c>
       <c r="H1242" t="inlineStr"/>
     </row>
@@ -27476,7 +27476,7 @@
       </c>
       <c r="F1250" t="inlineStr"/>
       <c r="G1250" t="n">
-        <v>44781155.692</v>
+        <v>44769130.692</v>
       </c>
       <c r="H1250" t="inlineStr"/>
     </row>
@@ -27498,7 +27498,7 @@
       </c>
       <c r="F1251" t="inlineStr"/>
       <c r="G1251" t="n">
-        <v>44341994.109</v>
+        <v>44329969.109</v>
       </c>
       <c r="H1251" t="inlineStr"/>
     </row>
@@ -27520,7 +27520,7 @@
       </c>
       <c r="F1252" t="inlineStr"/>
       <c r="G1252" t="n">
-        <v>43857508.764</v>
+        <v>43845482.764</v>
       </c>
       <c r="H1252" t="inlineStr"/>
     </row>
@@ -27986,7 +27986,7 @@
       </c>
       <c r="F1273" t="inlineStr"/>
       <c r="G1273" t="n">
-        <v>44057000.14</v>
+        <v>44044071.14</v>
       </c>
       <c r="H1273" t="inlineStr"/>
     </row>
@@ -28474,7 +28474,7 @@
       </c>
       <c r="F1295" t="inlineStr"/>
       <c r="G1295" t="n">
-        <v>46505241.702</v>
+        <v>46493805.702</v>
       </c>
       <c r="H1295" t="inlineStr"/>
     </row>
@@ -28964,7 +28964,7 @@
         <v>26.3</v>
       </c>
       <c r="G1317" t="n">
-        <v>51143225.522</v>
+        <v>51197359.522</v>
       </c>
       <c r="H1317" t="n">
         <v>2.8</v>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="F1318" t="inlineStr"/>
       <c r="G1318" t="n">
-        <v>50590277.384</v>
+        <v>50644412.384</v>
       </c>
       <c r="H1318" t="inlineStr"/>
     </row>
@@ -29010,7 +29010,7 @@
       </c>
       <c r="F1319" t="inlineStr"/>
       <c r="G1319" t="n">
-        <v>50051145.371</v>
+        <v>50105279.371</v>
       </c>
       <c r="H1319" t="inlineStr"/>
     </row>
@@ -29032,7 +29032,7 @@
       </c>
       <c r="F1320" t="inlineStr"/>
       <c r="G1320" t="n">
-        <v>50530852.593</v>
+        <v>50584987.593</v>
       </c>
       <c r="H1320" t="inlineStr"/>
     </row>
@@ -29054,7 +29054,7 @@
       </c>
       <c r="F1321" t="inlineStr"/>
       <c r="G1321" t="n">
-        <v>49893410.095</v>
+        <v>49947545.095</v>
       </c>
       <c r="H1321" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="F1322" t="inlineStr"/>
       <c r="G1322" t="n">
-        <v>48791300.5</v>
+        <v>48845435.5</v>
       </c>
       <c r="H1322" t="inlineStr"/>
     </row>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="F1323" t="inlineStr"/>
       <c r="G1323" t="n">
-        <v>47613990.888</v>
+        <v>47668125.888</v>
       </c>
       <c r="H1323" t="inlineStr"/>
     </row>
@@ -29120,7 +29120,7 @@
       </c>
       <c r="F1324" t="inlineStr"/>
       <c r="G1324" t="n">
-        <v>47077032.957</v>
+        <v>47131167.957</v>
       </c>
       <c r="H1324" t="inlineStr"/>
     </row>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="F1325" t="inlineStr"/>
       <c r="G1325" t="n">
-        <v>47062437.466</v>
+        <v>47116572.466</v>
       </c>
       <c r="H1325" t="inlineStr"/>
     </row>
@@ -29164,7 +29164,7 @@
       </c>
       <c r="F1326" t="inlineStr"/>
       <c r="G1326" t="n">
-        <v>47323008.259</v>
+        <v>47377142.259</v>
       </c>
       <c r="H1326" t="inlineStr"/>
     </row>
@@ -29186,7 +29186,7 @@
       </c>
       <c r="F1327" t="inlineStr"/>
       <c r="G1327" t="n">
-        <v>46633090.658</v>
+        <v>46687225.658</v>
       </c>
       <c r="H1327" t="inlineStr"/>
     </row>
@@ -29208,7 +29208,7 @@
       </c>
       <c r="F1328" t="inlineStr"/>
       <c r="G1328" t="n">
-        <v>46263936.919</v>
+        <v>46318071.919</v>
       </c>
       <c r="H1328" t="inlineStr"/>
     </row>
@@ -29230,7 +29230,7 @@
       </c>
       <c r="F1329" t="inlineStr"/>
       <c r="G1329" t="n">
-        <v>45983434.839</v>
+        <v>46037568.839</v>
       </c>
       <c r="H1329" t="inlineStr"/>
     </row>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="F1330" t="inlineStr"/>
       <c r="G1330" t="n">
-        <v>46113618.497</v>
+        <v>46167753.497</v>
       </c>
       <c r="H1330" t="inlineStr"/>
     </row>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="F1331" t="inlineStr"/>
       <c r="G1331" t="n">
-        <v>46106465.925</v>
+        <v>46160600.925</v>
       </c>
       <c r="H1331" t="inlineStr"/>
     </row>
@@ -29296,7 +29296,7 @@
       </c>
       <c r="F1332" t="inlineStr"/>
       <c r="G1332" t="n">
-        <v>45968697.945</v>
+        <v>46022832.945</v>
       </c>
       <c r="H1332" t="inlineStr"/>
     </row>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="F1333" t="inlineStr"/>
       <c r="G1333" t="n">
-        <v>46244492.278</v>
+        <v>46298626.278</v>
       </c>
       <c r="H1333" t="inlineStr"/>
     </row>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="F1334" t="inlineStr"/>
       <c r="G1334" t="n">
-        <v>46641664.056</v>
+        <v>46695799.056</v>
       </c>
       <c r="H1334" t="inlineStr"/>
     </row>
@@ -29362,7 +29362,7 @@
       </c>
       <c r="F1335" t="inlineStr"/>
       <c r="G1335" t="n">
-        <v>47632714.807</v>
+        <v>47686849.807</v>
       </c>
       <c r="H1335" t="inlineStr"/>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="F1336" t="inlineStr"/>
       <c r="G1336" t="n">
-        <v>48891632.485</v>
+        <v>48945767.485</v>
       </c>
       <c r="H1336" t="inlineStr"/>
     </row>
@@ -29406,7 +29406,7 @@
       </c>
       <c r="F1337" t="inlineStr"/>
       <c r="G1337" t="n">
-        <v>51139093.335</v>
+        <v>51097533.335</v>
       </c>
       <c r="H1337" t="inlineStr"/>
     </row>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="F1339" t="inlineStr"/>
       <c r="G1339" t="n">
-        <v>50293684.099</v>
+        <v>50252123.099</v>
       </c>
       <c r="H1339" t="inlineStr"/>
     </row>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="F1340" t="inlineStr"/>
       <c r="G1340" t="n">
-        <v>50135297.2</v>
+        <v>50093736.2</v>
       </c>
       <c r="H1340" t="inlineStr"/>
     </row>
@@ -29488,7 +29488,7 @@
       </c>
       <c r="F1341" t="inlineStr"/>
       <c r="G1341" t="n">
-        <v>50662614.622</v>
+        <v>50610246.622</v>
       </c>
       <c r="H1341" t="inlineStr"/>
     </row>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="F1342" t="inlineStr"/>
       <c r="G1342" t="n">
-        <v>51344938.846</v>
+        <v>51303378.846</v>
       </c>
       <c r="H1342" t="inlineStr"/>
     </row>
@@ -29532,7 +29532,7 @@
       </c>
       <c r="F1343" t="inlineStr"/>
       <c r="G1343" t="n">
-        <v>49823576.676</v>
+        <v>49776757.676</v>
       </c>
       <c r="H1343" t="inlineStr"/>
     </row>
@@ -29554,7 +29554,7 @@
       </c>
       <c r="F1344" t="inlineStr"/>
       <c r="G1344" t="n">
-        <v>49546850.468</v>
+        <v>49505290.468</v>
       </c>
       <c r="H1344" t="inlineStr"/>
     </row>
@@ -29576,7 +29576,7 @@
       </c>
       <c r="F1345" t="inlineStr"/>
       <c r="G1345" t="n">
-        <v>48955613.358</v>
+        <v>48914053.358</v>
       </c>
       <c r="H1345" t="inlineStr"/>
     </row>
@@ -29598,7 +29598,7 @@
       </c>
       <c r="F1346" t="inlineStr"/>
       <c r="G1346" t="n">
-        <v>49427389.152</v>
+        <v>49385829.152</v>
       </c>
       <c r="H1346" t="inlineStr"/>
     </row>
@@ -29620,7 +29620,7 @@
       </c>
       <c r="F1347" t="inlineStr"/>
       <c r="G1347" t="n">
-        <v>49099754.486</v>
+        <v>49058194.486</v>
       </c>
       <c r="H1347" t="inlineStr"/>
     </row>
@@ -29642,7 +29642,7 @@
       </c>
       <c r="F1348" t="inlineStr"/>
       <c r="G1348" t="n">
-        <v>49162396.452</v>
+        <v>49120836.452</v>
       </c>
       <c r="H1348" t="inlineStr"/>
     </row>
@@ -29664,7 +29664,7 @@
       </c>
       <c r="F1349" t="inlineStr"/>
       <c r="G1349" t="n">
-        <v>49228766.726</v>
+        <v>49187205.726</v>
       </c>
       <c r="H1349" t="inlineStr"/>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="F1350" t="inlineStr"/>
       <c r="G1350" t="n">
-        <v>49628194.914</v>
+        <v>49586634.914</v>
       </c>
       <c r="H1350" t="inlineStr"/>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="F1351" t="inlineStr"/>
       <c r="G1351" t="n">
-        <v>49138210.391</v>
+        <v>49096650.391</v>
       </c>
       <c r="H1351" t="inlineStr"/>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="F1352" t="inlineStr"/>
       <c r="G1352" t="n">
-        <v>49722189.724</v>
+        <v>49680629.724</v>
       </c>
       <c r="H1352" t="inlineStr"/>
     </row>
@@ -29752,7 +29752,7 @@
       </c>
       <c r="F1353" t="inlineStr"/>
       <c r="G1353" t="n">
-        <v>50194728.696</v>
+        <v>50153168.696</v>
       </c>
       <c r="H1353" t="inlineStr"/>
     </row>
@@ -29774,7 +29774,7 @@
       </c>
       <c r="F1354" t="inlineStr"/>
       <c r="G1354" t="n">
-        <v>50607644.767</v>
+        <v>50566084.767</v>
       </c>
       <c r="H1354" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
       </c>
       <c r="F1355" t="inlineStr"/>
       <c r="G1355" t="n">
-        <v>52878077.995</v>
+        <v>52836517.995</v>
       </c>
       <c r="H1355" t="inlineStr"/>
     </row>
@@ -29818,7 +29818,7 @@
       </c>
       <c r="F1356" t="inlineStr"/>
       <c r="G1356" t="n">
-        <v>53931376.682</v>
+        <v>53889816.682</v>
       </c>
       <c r="H1356" t="inlineStr"/>
     </row>
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57861716.056</v>
+        <v>57841431.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="n">
-        <v>56682381.267</v>
+        <v>56662097.267</v>
       </c>
       <c r="H1358" t="inlineStr"/>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="F1359" t="inlineStr"/>
       <c r="G1359" t="n">
-        <v>56042294.372</v>
+        <v>56022010.372</v>
       </c>
       <c r="H1359" t="inlineStr"/>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="n">
-        <v>56601252.504</v>
+        <v>56580968.504</v>
       </c>
       <c r="H1360" t="inlineStr"/>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="n">
-        <v>56839121.839</v>
+        <v>56818837.839</v>
       </c>
       <c r="H1361" t="inlineStr"/>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="n">
-        <v>55519800.571</v>
+        <v>55499516.571</v>
       </c>
       <c r="H1362" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="n">
-        <v>55329802.556</v>
+        <v>55309518.556</v>
       </c>
       <c r="H1363" t="inlineStr"/>
     </row>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="n">
-        <v>54543278.68</v>
+        <v>54522994.68</v>
       </c>
       <c r="H1364" t="inlineStr"/>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="n">
-        <v>53964691.241</v>
+        <v>53944407.241</v>
       </c>
       <c r="H1365" t="inlineStr"/>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="n">
-        <v>53572094.918</v>
+        <v>53551810.918</v>
       </c>
       <c r="H1366" t="inlineStr"/>
     </row>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F1367" t="inlineStr"/>
       <c r="G1367" t="n">
-        <v>53705888.53</v>
+        <v>53685603.53</v>
       </c>
       <c r="H1367" t="inlineStr"/>
     </row>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="n">
-        <v>52802300.228</v>
+        <v>52771726.228</v>
       </c>
       <c r="H1368" t="inlineStr"/>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53021146.434</v>
+        <v>53000861.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30130,7 +30130,7 @@
       </c>
       <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="n">
-        <v>52802578.166</v>
+        <v>52782293.166</v>
       </c>
       <c r="H1370" t="inlineStr"/>
     </row>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="F1371" t="inlineStr"/>
       <c r="G1371" t="n">
-        <v>52592265.418</v>
+        <v>52571981.418</v>
       </c>
       <c r="H1371" t="inlineStr"/>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="n">
-        <v>52232247.099</v>
+        <v>52211962.099</v>
       </c>
       <c r="H1372" t="inlineStr"/>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="n">
-        <v>52327639.713</v>
+        <v>52307355.713</v>
       </c>
       <c r="H1373" t="inlineStr"/>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="n">
-        <v>52871036.596</v>
+        <v>52850752.596</v>
       </c>
       <c r="H1374" t="inlineStr"/>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="n">
-        <v>52221618.178</v>
+        <v>52201333.178</v>
       </c>
       <c r="H1375" t="inlineStr"/>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="n">
-        <v>52602993.503</v>
+        <v>52582708.503</v>
       </c>
       <c r="H1376" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="n">
-        <v>52822396.197</v>
+        <v>52802111.197</v>
       </c>
       <c r="H1377" t="inlineStr"/>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="n">
-        <v>54095307.568</v>
+        <v>54075022.568</v>
       </c>
       <c r="H1378" t="inlineStr"/>
     </row>
@@ -30330,7 +30330,7 @@
         <v>21.1</v>
       </c>
       <c r="G1379" t="n">
-        <v>56523749.897</v>
+        <v>56492211.897</v>
       </c>
       <c r="H1379" t="n">
         <v>1.9</v>
@@ -30354,7 +30354,7 @@
       </c>
       <c r="F1380" t="inlineStr"/>
       <c r="G1380" t="n">
-        <v>56834490.779</v>
+        <v>56802952.779</v>
       </c>
       <c r="H1380" t="inlineStr"/>
     </row>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="F1381" t="inlineStr"/>
       <c r="G1381" t="n">
-        <v>55274761.451</v>
+        <v>55243223.451</v>
       </c>
       <c r="H1381" t="inlineStr"/>
     </row>
@@ -30398,7 +30398,7 @@
       </c>
       <c r="F1382" t="inlineStr"/>
       <c r="G1382" t="n">
-        <v>55316647.742</v>
+        <v>55285109.742</v>
       </c>
       <c r="H1382" t="inlineStr"/>
     </row>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="F1383" t="inlineStr"/>
       <c r="G1383" t="n">
-        <v>55591414.888</v>
+        <v>55559877.888</v>
       </c>
       <c r="H1383" t="inlineStr"/>
     </row>
@@ -30442,7 +30442,7 @@
       </c>
       <c r="F1384" t="inlineStr"/>
       <c r="G1384" t="n">
-        <v>55072563.049</v>
+        <v>55041025.049</v>
       </c>
       <c r="H1384" t="inlineStr"/>
     </row>
@@ -30464,7 +30464,7 @@
       </c>
       <c r="F1385" t="inlineStr"/>
       <c r="G1385" t="n">
-        <v>53818201.218</v>
+        <v>53786664.218</v>
       </c>
       <c r="H1385" t="inlineStr"/>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="F1386" t="inlineStr"/>
       <c r="G1386" t="n">
-        <v>52845225.644</v>
+        <v>52813688.644</v>
       </c>
       <c r="H1386" t="inlineStr"/>
     </row>
@@ -30508,7 +30508,7 @@
       </c>
       <c r="F1387" t="inlineStr"/>
       <c r="G1387" t="n">
-        <v>52125234.57</v>
+        <v>52093697.57</v>
       </c>
       <c r="H1387" t="inlineStr"/>
     </row>
@@ -30530,7 +30530,7 @@
       </c>
       <c r="F1388" t="inlineStr"/>
       <c r="G1388" t="n">
-        <v>51898010.889</v>
+        <v>51866473.889</v>
       </c>
       <c r="H1388" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
       </c>
       <c r="F1389" t="inlineStr"/>
       <c r="G1389" t="n">
-        <v>51859797.679</v>
+        <v>51828260.679</v>
       </c>
       <c r="H1389" t="inlineStr"/>
     </row>
@@ -30574,7 +30574,7 @@
       </c>
       <c r="F1390" t="inlineStr"/>
       <c r="G1390" t="n">
-        <v>51752944.828</v>
+        <v>51721406.828</v>
       </c>
       <c r="H1390" t="inlineStr"/>
     </row>
@@ -30596,7 +30596,7 @@
       </c>
       <c r="F1391" t="inlineStr"/>
       <c r="G1391" t="n">
-        <v>51335654.283</v>
+        <v>51304117.283</v>
       </c>
       <c r="H1391" t="inlineStr"/>
     </row>
@@ -30618,7 +30618,7 @@
       </c>
       <c r="F1392" t="inlineStr"/>
       <c r="G1392" t="n">
-        <v>50732410.116</v>
+        <v>50700872.116</v>
       </c>
       <c r="H1392" t="inlineStr"/>
     </row>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="F1393" t="inlineStr"/>
       <c r="G1393" t="n">
-        <v>50584477.926</v>
+        <v>50552940.926</v>
       </c>
       <c r="H1393" t="inlineStr"/>
     </row>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="F1394" t="inlineStr"/>
       <c r="G1394" t="n">
-        <v>50240140.764</v>
+        <v>50208603.764</v>
       </c>
       <c r="H1394" t="inlineStr"/>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="F1395" t="inlineStr"/>
       <c r="G1395" t="n">
-        <v>50125144.563</v>
+        <v>50093606.563</v>
       </c>
       <c r="H1395" t="inlineStr"/>
     </row>
@@ -30706,7 +30706,7 @@
       </c>
       <c r="F1396" t="inlineStr"/>
       <c r="G1396" t="n">
-        <v>49657612.924</v>
+        <v>49626074.924</v>
       </c>
       <c r="H1396" t="inlineStr"/>
     </row>
@@ -30728,7 +30728,7 @@
       </c>
       <c r="F1397" t="inlineStr"/>
       <c r="G1397" t="n">
-        <v>51053140.556</v>
+        <v>51021602.556</v>
       </c>
       <c r="H1397" t="inlineStr"/>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="F1398" t="inlineStr"/>
       <c r="G1398" t="n">
-        <v>51926134.644</v>
+        <v>51894596.644</v>
       </c>
       <c r="H1398" t="inlineStr"/>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="F1399" t="inlineStr"/>
       <c r="G1399" t="n">
-        <v>54287047.622</v>
+        <v>54245702.622</v>
       </c>
       <c r="H1399" t="inlineStr"/>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="F1401" t="inlineStr"/>
       <c r="G1401" t="n">
-        <v>53402812.53</v>
+        <v>53361468.53</v>
       </c>
       <c r="H1401" t="inlineStr"/>
     </row>
@@ -30832,7 +30832,7 @@
       </c>
       <c r="F1402" t="inlineStr"/>
       <c r="G1402" t="n">
-        <v>52795369.855</v>
+        <v>52754025.855</v>
       </c>
       <c r="H1402" t="inlineStr"/>
     </row>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="F1403" t="inlineStr"/>
       <c r="G1403" t="n">
-        <v>53279951.593</v>
+        <v>53238606.593</v>
       </c>
       <c r="H1403" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
       </c>
       <c r="F1404" t="inlineStr"/>
       <c r="G1404" t="n">
-        <v>54219032.308</v>
+        <v>54177688.308</v>
       </c>
       <c r="H1404" t="inlineStr"/>
     </row>
@@ -30898,7 +30898,7 @@
       </c>
       <c r="F1405" t="inlineStr"/>
       <c r="G1405" t="n">
-        <v>53229348.494</v>
+        <v>53188004.494</v>
       </c>
       <c r="H1405" t="inlineStr"/>
     </row>
@@ -30920,7 +30920,7 @@
       </c>
       <c r="F1406" t="inlineStr"/>
       <c r="G1406" t="n">
-        <v>52662466.98</v>
+        <v>52621122.98</v>
       </c>
       <c r="H1406" t="inlineStr"/>
     </row>
@@ -30942,7 +30942,7 @@
       </c>
       <c r="F1407" t="inlineStr"/>
       <c r="G1407" t="n">
-        <v>51806010.704</v>
+        <v>51764665.704</v>
       </c>
       <c r="H1407" t="inlineStr"/>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="F1408" t="inlineStr"/>
       <c r="G1408" t="n">
-        <v>51813750.154</v>
+        <v>51772405.154</v>
       </c>
       <c r="H1408" t="inlineStr"/>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="F1409" t="inlineStr"/>
       <c r="G1409" t="n">
-        <v>51688773.007</v>
+        <v>51647428.007</v>
       </c>
       <c r="H1409" t="inlineStr"/>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="F1410" t="inlineStr"/>
       <c r="G1410" t="n">
-        <v>50963928.014</v>
+        <v>50922584.014</v>
       </c>
       <c r="H1410" t="inlineStr"/>
     </row>
@@ -31030,7 +31030,7 @@
       </c>
       <c r="F1411" t="inlineStr"/>
       <c r="G1411" t="n">
-        <v>51299976.064</v>
+        <v>51258631.064</v>
       </c>
       <c r="H1411" t="inlineStr"/>
     </row>
@@ -31052,7 +31052,7 @@
       </c>
       <c r="F1412" t="inlineStr"/>
       <c r="G1412" t="n">
-        <v>50245548.352</v>
+        <v>50204204.352</v>
       </c>
       <c r="H1412" t="inlineStr"/>
     </row>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="F1413" t="inlineStr"/>
       <c r="G1413" t="n">
-        <v>50397961.972</v>
+        <v>50356617.972</v>
       </c>
       <c r="H1413" t="inlineStr"/>
     </row>
@@ -31096,7 +31096,7 @@
       </c>
       <c r="F1414" t="inlineStr"/>
       <c r="G1414" t="n">
-        <v>50492113.477</v>
+        <v>50450768.477</v>
       </c>
       <c r="H1414" t="inlineStr"/>
     </row>
@@ -31118,7 +31118,7 @@
       </c>
       <c r="F1415" t="inlineStr"/>
       <c r="G1415" t="n">
-        <v>50431345.859</v>
+        <v>50390000.859</v>
       </c>
       <c r="H1415" t="inlineStr"/>
     </row>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="F1416" t="inlineStr"/>
       <c r="G1416" t="n">
-        <v>50472549.937</v>
+        <v>50431205.937</v>
       </c>
       <c r="H1416" t="inlineStr"/>
     </row>
@@ -31162,7 +31162,7 @@
       </c>
       <c r="F1417" t="inlineStr"/>
       <c r="G1417" t="n">
-        <v>50350094.92</v>
+        <v>50308750.92</v>
       </c>
       <c r="H1417" t="inlineStr"/>
     </row>
@@ -31184,7 +31184,7 @@
       </c>
       <c r="F1418" t="inlineStr"/>
       <c r="G1418" t="n">
-        <v>50624930.87</v>
+        <v>50583585.87</v>
       </c>
       <c r="H1418" t="inlineStr"/>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="F1419" t="inlineStr"/>
       <c r="G1419" t="n">
-        <v>51161688.993</v>
+        <v>51120343.993</v>
       </c>
       <c r="H1419" t="inlineStr"/>
     </row>
@@ -31228,7 +31228,7 @@
       </c>
       <c r="F1420" t="inlineStr"/>
       <c r="G1420" t="n">
-        <v>51141322.537</v>
+        <v>51099977.537</v>
       </c>
       <c r="H1420" t="inlineStr"/>
     </row>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="F1421" t="inlineStr"/>
       <c r="G1421" t="n">
-        <v>52953857.45</v>
+        <v>52912512.45</v>
       </c>
       <c r="H1421" t="inlineStr"/>
     </row>
@@ -31274,7 +31274,7 @@
         <v>21.9</v>
       </c>
       <c r="G1422" t="n">
-        <v>55412646.222</v>
+        <v>55368558.222</v>
       </c>
       <c r="H1422" t="n">
         <v>2.1</v>
@@ -31298,7 +31298,7 @@
       </c>
       <c r="F1423" t="inlineStr"/>
       <c r="G1423" t="n">
-        <v>55651241.331</v>
+        <v>55607152.331</v>
       </c>
       <c r="H1423" t="inlineStr"/>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="F1424" t="inlineStr"/>
       <c r="G1424" t="n">
-        <v>55713167.151</v>
+        <v>55669078.151</v>
       </c>
       <c r="H1424" t="inlineStr"/>
     </row>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="F1425" t="inlineStr"/>
       <c r="G1425" t="n">
-        <v>55978878.978</v>
+        <v>55934789.978</v>
       </c>
       <c r="H1425" t="inlineStr"/>
     </row>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="F1426" t="inlineStr"/>
       <c r="G1426" t="n">
-        <v>55750581.241</v>
+        <v>55706492.241</v>
       </c>
       <c r="H1426" t="inlineStr"/>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="F1427" t="inlineStr"/>
       <c r="G1427" t="n">
-        <v>54913757.217</v>
+        <v>54869668.217</v>
       </c>
       <c r="H1427" t="inlineStr"/>
     </row>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="F1428" t="inlineStr"/>
       <c r="G1428" t="n">
-        <v>54792060.24</v>
+        <v>54747971.24</v>
       </c>
       <c r="H1428" t="inlineStr"/>
     </row>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="F1429" t="inlineStr"/>
       <c r="G1429" t="n">
-        <v>54505188.576</v>
+        <v>54461099.576</v>
       </c>
       <c r="H1429" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="F1430" t="inlineStr"/>
       <c r="G1430" t="n">
-        <v>54516603.621</v>
+        <v>54472514.621</v>
       </c>
       <c r="H1430" t="inlineStr"/>
     </row>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="F1431" t="inlineStr"/>
       <c r="G1431" t="n">
-        <v>51984676.914</v>
+        <v>51940587.914</v>
       </c>
       <c r="H1431" t="inlineStr"/>
     </row>
@@ -31496,7 +31496,7 @@
       </c>
       <c r="F1432" t="inlineStr"/>
       <c r="G1432" t="n">
-        <v>52543499.382</v>
+        <v>52499410.382</v>
       </c>
       <c r="H1432" t="inlineStr"/>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="F1433" t="inlineStr"/>
       <c r="G1433" t="n">
-        <v>51748017.388</v>
+        <v>51703928.388</v>
       </c>
       <c r="H1433" t="inlineStr"/>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="F1434" t="inlineStr"/>
       <c r="G1434" t="n">
-        <v>50515468.623</v>
+        <v>50471380.623</v>
       </c>
       <c r="H1434" t="inlineStr"/>
     </row>
@@ -31562,7 +31562,7 @@
       </c>
       <c r="F1435" t="inlineStr"/>
       <c r="G1435" t="n">
-        <v>50560839.287</v>
+        <v>50516750.287</v>
       </c>
       <c r="H1435" t="inlineStr"/>
     </row>
@@ -31584,7 +31584,7 @@
       </c>
       <c r="F1436" t="inlineStr"/>
       <c r="G1436" t="n">
-        <v>50094418.307</v>
+        <v>50050329.307</v>
       </c>
       <c r="H1436" t="inlineStr"/>
     </row>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="F1437" t="inlineStr"/>
       <c r="G1437" t="n">
-        <v>50814766.53</v>
+        <v>50770677.53</v>
       </c>
       <c r="H1437" t="inlineStr"/>
     </row>
@@ -31628,7 +31628,7 @@
       </c>
       <c r="F1438" t="inlineStr"/>
       <c r="G1438" t="n">
-        <v>50058845.981</v>
+        <v>50014756.981</v>
       </c>
       <c r="H1438" t="inlineStr"/>
     </row>
@@ -31650,7 +31650,7 @@
       </c>
       <c r="F1439" t="inlineStr"/>
       <c r="G1439" t="n">
-        <v>49904330.76</v>
+        <v>49860241.76</v>
       </c>
       <c r="H1439" t="inlineStr"/>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="F1440" t="inlineStr"/>
       <c r="G1440" t="n">
-        <v>49819950.195</v>
+        <v>49775861.195</v>
       </c>
       <c r="H1440" t="inlineStr"/>
     </row>
@@ -31694,7 +31694,7 @@
       </c>
       <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="n">
-        <v>49562784.045</v>
+        <v>49518695.045</v>
       </c>
       <c r="H1441" t="inlineStr"/>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="F1442" t="inlineStr"/>
       <c r="G1442" t="n">
-        <v>50110477.504</v>
+        <v>50066388.504</v>
       </c>
       <c r="H1442" t="inlineStr"/>
     </row>
@@ -31738,7 +31738,7 @@
       </c>
       <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="n">
-        <v>51565158.942</v>
+        <v>51521069.942</v>
       </c>
       <c r="H1443" t="inlineStr"/>
     </row>
@@ -31762,7 +31762,7 @@
         <v>20.8</v>
       </c>
       <c r="G1444" t="n">
-        <v>53919863.608</v>
+        <v>53881677.608</v>
       </c>
       <c r="H1444" t="n">
         <v>2.3</v>
@@ -31786,7 +31786,7 @@
       </c>
       <c r="F1445" t="inlineStr"/>
       <c r="G1445" t="n">
-        <v>53492503.301</v>
+        <v>53454317.301</v>
       </c>
       <c r="H1445" t="inlineStr"/>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F1446" t="inlineStr"/>
       <c r="G1446" t="n">
-        <v>53065312.662</v>
+        <v>53027126.662</v>
       </c>
       <c r="H1446" t="inlineStr"/>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="F1447" t="inlineStr"/>
       <c r="G1447" t="n">
-        <v>53731535.632</v>
+        <v>53693349.632</v>
       </c>
       <c r="H1447" t="inlineStr"/>
     </row>
@@ -31852,7 +31852,7 @@
       </c>
       <c r="F1448" t="inlineStr"/>
       <c r="G1448" t="n">
-        <v>52998501.148</v>
+        <v>52960315.148</v>
       </c>
       <c r="H1448" t="inlineStr"/>
     </row>
@@ -31874,7 +31874,7 @@
       </c>
       <c r="F1449" t="inlineStr"/>
       <c r="G1449" t="n">
-        <v>51784340.271</v>
+        <v>51746155.271</v>
       </c>
       <c r="H1449" t="inlineStr"/>
     </row>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="F1450" t="inlineStr"/>
       <c r="G1450" t="n">
-        <v>50285602.976</v>
+        <v>50247416.976</v>
       </c>
       <c r="H1450" t="inlineStr"/>
     </row>
@@ -31918,7 +31918,7 @@
       </c>
       <c r="F1451" t="inlineStr"/>
       <c r="G1451" t="n">
-        <v>50846508.288</v>
+        <v>50808322.288</v>
       </c>
       <c r="H1451" t="inlineStr"/>
     </row>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="F1452" t="inlineStr"/>
       <c r="G1452" t="n">
-        <v>50577326.336</v>
+        <v>50539140.336</v>
       </c>
       <c r="H1452" t="inlineStr"/>
     </row>
@@ -31962,7 +31962,7 @@
       </c>
       <c r="F1453" t="inlineStr"/>
       <c r="G1453" t="n">
-        <v>50571502.135</v>
+        <v>50533316.135</v>
       </c>
       <c r="H1453" t="inlineStr"/>
     </row>
@@ -31984,7 +31984,7 @@
       </c>
       <c r="F1454" t="inlineStr"/>
       <c r="G1454" t="n">
-        <v>50386233.524</v>
+        <v>50348047.524</v>
       </c>
       <c r="H1454" t="inlineStr"/>
     </row>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="F1455" t="inlineStr"/>
       <c r="G1455" t="n">
-        <v>50224130.389</v>
+        <v>50185945.389</v>
       </c>
       <c r="H1455" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
       </c>
       <c r="F1456" t="inlineStr"/>
       <c r="G1456" t="n">
-        <v>50040791.804</v>
+        <v>50002605.804</v>
       </c>
       <c r="H1456" t="inlineStr"/>
     </row>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="F1457" t="inlineStr"/>
       <c r="G1457" t="n">
-        <v>50636294.035</v>
+        <v>50598109.035</v>
       </c>
       <c r="H1457" t="inlineStr"/>
     </row>
@@ -32072,7 +32072,7 @@
       </c>
       <c r="F1458" t="inlineStr"/>
       <c r="G1458" t="n">
-        <v>51430758.263</v>
+        <v>51392573.263</v>
       </c>
       <c r="H1458" t="inlineStr"/>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="F1459" t="inlineStr"/>
       <c r="G1459" t="n">
-        <v>51914331.288</v>
+        <v>51876145.288</v>
       </c>
       <c r="H1459" t="inlineStr"/>
     </row>
@@ -32116,7 +32116,7 @@
       </c>
       <c r="F1460" t="inlineStr"/>
       <c r="G1460" t="n">
-        <v>53297358.364</v>
+        <v>53259172.364</v>
       </c>
       <c r="H1460" t="inlineStr"/>
     </row>
@@ -32808,7 +32808,7 @@
       </c>
       <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="n">
-        <v>57527627.399</v>
+        <v>57528237.399</v>
       </c>
       <c r="H1492" t="inlineStr"/>
     </row>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54847213.349</v>
+        <v>54854000.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55616986.479</v>
+        <v>55615431.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57355353.612</v>
+        <v>57359991.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60364961.102</v>
+        <v>60360233.102</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59169263.726</v>
+        <v>59166078.726</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58625393.442</v>
+        <v>58622142.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59428843.058</v>
+        <v>59428853.107</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33676,7 +33676,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55959551.807</v>
+        <v>55920479.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56230150.122</v>
+        <v>56209278.122</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55935434.807</v>
+        <v>55925719.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55075712.219</v>
+        <v>55075837.219</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="n">
-        <v>54523399.642</v>
+        <v>54526532.642</v>
       </c>
       <c r="H1536" t="inlineStr"/>
     </row>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60825764.977</v>
+        <v>60835690.977</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="n">
-        <v>58484137.841</v>
+        <v>58484690.356</v>
       </c>
       <c r="H1546" t="inlineStr"/>
     </row>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="F1547" t="inlineStr"/>
       <c r="G1547" t="n">
-        <v>58197675.283</v>
+        <v>58197953.536</v>
       </c>
       <c r="H1547" t="inlineStr"/>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="F1548" t="inlineStr"/>
       <c r="G1548" t="n">
-        <v>57476618.548</v>
+        <v>57476776.632</v>
       </c>
       <c r="H1548" t="inlineStr"/>
     </row>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="n">
-        <v>56932791.445</v>
+        <v>56932950.529</v>
       </c>
       <c r="H1549" t="inlineStr"/>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="F1550" t="inlineStr"/>
       <c r="G1550" t="n">
-        <v>55942751.816</v>
+        <v>55935247.207</v>
       </c>
       <c r="H1550" t="inlineStr"/>
     </row>
@@ -34098,7 +34098,7 @@
       </c>
       <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="n">
-        <v>55743443.062</v>
+        <v>55746722.146</v>
       </c>
       <c r="H1551" t="inlineStr"/>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="F1552" t="inlineStr"/>
       <c r="G1552" t="n">
-        <v>56282847.846</v>
+        <v>56286126.93</v>
       </c>
       <c r="H1552" t="inlineStr"/>
     </row>
@@ -34142,7 +34142,7 @@
       </c>
       <c r="F1553" t="inlineStr"/>
       <c r="G1553" t="n">
-        <v>55510633.364</v>
+        <v>55513912.448</v>
       </c>
       <c r="H1553" t="inlineStr"/>
     </row>
@@ -34164,7 +34164,7 @@
       </c>
       <c r="F1554" t="inlineStr"/>
       <c r="G1554" t="n">
-        <v>55092424.993</v>
+        <v>55095704.077</v>
       </c>
       <c r="H1554" t="inlineStr"/>
     </row>
@@ -34186,7 +34186,7 @@
       </c>
       <c r="F1555" t="inlineStr"/>
       <c r="G1555" t="n">
-        <v>55048418.727</v>
+        <v>55051697.811</v>
       </c>
       <c r="H1555" t="inlineStr"/>
     </row>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="F1556" t="inlineStr"/>
       <c r="G1556" t="n">
-        <v>54449917.66</v>
+        <v>54453196.744</v>
       </c>
       <c r="H1556" t="inlineStr"/>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="F1557" t="inlineStr"/>
       <c r="G1557" t="n">
-        <v>53870535.922</v>
+        <v>53873815.006</v>
       </c>
       <c r="H1557" t="inlineStr"/>
     </row>
@@ -34252,7 +34252,7 @@
       </c>
       <c r="F1558" t="inlineStr"/>
       <c r="G1558" t="n">
-        <v>54000295.274</v>
+        <v>54003574.358</v>
       </c>
       <c r="H1558" t="inlineStr"/>
     </row>
@@ -34274,7 +34274,7 @@
       </c>
       <c r="F1559" t="inlineStr"/>
       <c r="G1559" t="n">
-        <v>54423761.634</v>
+        <v>54427040.718</v>
       </c>
       <c r="H1559" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
       </c>
       <c r="F1560" t="inlineStr"/>
       <c r="G1560" t="n">
-        <v>55403100.331</v>
+        <v>55399054.415</v>
       </c>
       <c r="H1560" t="inlineStr"/>
     </row>
@@ -34318,7 +34318,7 @@
       </c>
       <c r="F1561" t="inlineStr"/>
       <c r="G1561" t="n">
-        <v>55803751.425</v>
+        <v>55806190.509</v>
       </c>
       <c r="H1561" t="inlineStr"/>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="F1562" t="inlineStr"/>
       <c r="G1562" t="n">
-        <v>59089246.861</v>
+        <v>58982974.598</v>
       </c>
       <c r="H1562" t="inlineStr"/>
     </row>
@@ -34364,9 +34364,11 @@
         <v>24.2</v>
       </c>
       <c r="G1563" t="n">
-        <v>62781439.944</v>
-      </c>
-      <c r="H1563" t="inlineStr"/>
+        <v>62789430.647</v>
+      </c>
+      <c r="H1563" t="n">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="1564">
       <c r="A1564" s="1" t="n">
@@ -34386,7 +34388,7 @@
       </c>
       <c r="F1564" t="inlineStr"/>
       <c r="G1564" t="n">
-        <v>60478501.745</v>
+        <v>60734689.957</v>
       </c>
       <c r="H1564" t="inlineStr"/>
     </row>
@@ -34408,7 +34410,7 @@
       </c>
       <c r="F1565" t="inlineStr"/>
       <c r="G1565" t="n">
-        <v>59841854.572</v>
+        <v>59796477.279</v>
       </c>
       <c r="H1565" t="inlineStr"/>
     </row>
@@ -34429,15 +34431,21 @@
         <v>20.9375</v>
       </c>
       <c r="F1566" t="inlineStr"/>
-      <c r="G1566" t="inlineStr"/>
+      <c r="G1566" t="n">
+        <v>60660651.741</v>
+      </c>
       <c r="H1566" t="inlineStr"/>
     </row>
     <row r="1567">
       <c r="A1567" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="B1567" t="inlineStr"/>
-      <c r="C1567" t="inlineStr"/>
+      <c r="B1567" t="n">
+        <v>45953</v>
+      </c>
+      <c r="C1567" t="n">
+        <v>41186004</v>
+      </c>
       <c r="D1567" t="n">
         <v>1417.62</v>
       </c>
@@ -34445,22 +34453,126 @@
         <v>21.375</v>
       </c>
       <c r="F1567" t="inlineStr"/>
-      <c r="G1567" t="inlineStr"/>
+      <c r="G1567" t="n">
+        <v>60752303.074</v>
+      </c>
       <c r="H1567" t="inlineStr"/>
     </row>
     <row r="1568">
       <c r="A1568" s="1" t="n">
         <v>46150</v>
       </c>
-      <c r="B1568" t="inlineStr"/>
-      <c r="C1568" t="inlineStr"/>
+      <c r="B1568" t="n">
+        <v>46061</v>
+      </c>
+      <c r="C1568" t="n">
+        <v>40710852</v>
+      </c>
       <c r="D1568" t="n">
         <v>1418.34</v>
       </c>
-      <c r="E1568" t="inlineStr"/>
+      <c r="E1568" t="n">
+        <v>20.875</v>
+      </c>
       <c r="F1568" t="inlineStr"/>
-      <c r="G1568" t="inlineStr"/>
+      <c r="G1568" t="n">
+        <v>58977513.233</v>
+      </c>
       <c r="H1568" t="inlineStr"/>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B1569" t="n">
+        <v>46144</v>
+      </c>
+      <c r="C1569" t="n">
+        <v>41639647</v>
+      </c>
+      <c r="D1569" t="n">
+        <v>1417.11</v>
+      </c>
+      <c r="E1569" t="n">
+        <v>20.875</v>
+      </c>
+      <c r="F1569" t="inlineStr"/>
+      <c r="G1569" t="n">
+        <v>58175977.865</v>
+      </c>
+      <c r="H1569" t="inlineStr"/>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B1570" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C1570" t="n">
+        <v>40570598</v>
+      </c>
+      <c r="D1570" t="n">
+        <v>1408.67</v>
+      </c>
+      <c r="E1570" t="n">
+        <v>21.5625</v>
+      </c>
+      <c r="F1570" t="inlineStr"/>
+      <c r="G1570" t="n">
+        <v>57676758.653</v>
+      </c>
+      <c r="H1570" t="inlineStr"/>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B1571" t="n">
+        <v>46534</v>
+      </c>
+      <c r="C1571" t="n">
+        <v>41228855</v>
+      </c>
+      <c r="D1571" t="n">
+        <v>1412.45</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="F1571" t="inlineStr"/>
+      <c r="G1571" t="inlineStr"/>
+      <c r="H1571" t="inlineStr"/>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B1572" t="inlineStr"/>
+      <c r="C1572" t="inlineStr"/>
+      <c r="D1572" t="n">
+        <v>1414.07</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="F1572" t="inlineStr"/>
+      <c r="G1572" t="inlineStr"/>
+      <c r="H1572" t="inlineStr"/>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B1573" t="inlineStr"/>
+      <c r="C1573" t="inlineStr"/>
+      <c r="D1573" t="n">
+        <v>1418.57</v>
+      </c>
+      <c r="E1573" t="inlineStr"/>
+      <c r="F1573" t="inlineStr"/>
+      <c r="G1573" t="inlineStr"/>
+      <c r="H1573" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1573"/>
+  <dimension ref="A1:H1574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="F1281" t="inlineStr"/>
       <c r="G1281" t="n">
-        <v>48130268.128</v>
+        <v>48115207.128</v>
       </c>
       <c r="H1281" t="inlineStr"/>
     </row>
@@ -28188,7 +28188,7 @@
       </c>
       <c r="F1282" t="inlineStr"/>
       <c r="G1282" t="n">
-        <v>48342370.475</v>
+        <v>48328769.475</v>
       </c>
       <c r="H1282" t="inlineStr"/>
     </row>
@@ -28210,7 +28210,7 @@
       </c>
       <c r="F1283" t="inlineStr"/>
       <c r="G1283" t="n">
-        <v>48348228.734</v>
+        <v>48336198.734</v>
       </c>
       <c r="H1283" t="inlineStr"/>
     </row>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="F1284" t="inlineStr"/>
       <c r="G1284" t="n">
-        <v>46582422.614</v>
+        <v>46569989.614</v>
       </c>
       <c r="H1284" t="inlineStr"/>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="F1285" t="inlineStr"/>
       <c r="G1285" t="n">
-        <v>46033437.384</v>
+        <v>46020323.384</v>
       </c>
       <c r="H1285" t="inlineStr"/>
     </row>
@@ -28276,7 +28276,7 @@
       </c>
       <c r="F1286" t="inlineStr"/>
       <c r="G1286" t="n">
-        <v>45865271.348</v>
+        <v>45853774.348</v>
       </c>
       <c r="H1286" t="inlineStr"/>
     </row>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="F1287" t="inlineStr"/>
       <c r="G1287" t="n">
-        <v>46144803.268</v>
+        <v>46136403.268</v>
       </c>
       <c r="H1287" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
       </c>
       <c r="F1288" t="inlineStr"/>
       <c r="G1288" t="n">
-        <v>46154533.624</v>
+        <v>46150853.624</v>
       </c>
       <c r="H1288" t="inlineStr"/>
     </row>
@@ -28342,7 +28342,7 @@
       </c>
       <c r="F1289" t="inlineStr"/>
       <c r="G1289" t="n">
-        <v>45438707.744</v>
+        <v>45440043.744</v>
       </c>
       <c r="H1289" t="inlineStr"/>
     </row>
@@ -28364,7 +28364,7 @@
       </c>
       <c r="F1290" t="inlineStr"/>
       <c r="G1290" t="n">
-        <v>45460947.72</v>
+        <v>45462223.72</v>
       </c>
       <c r="H1290" t="inlineStr"/>
     </row>
@@ -28386,7 +28386,7 @@
       </c>
       <c r="F1291" t="inlineStr"/>
       <c r="G1291" t="n">
-        <v>45750566.502</v>
+        <v>45753992.502</v>
       </c>
       <c r="H1291" t="inlineStr"/>
     </row>
@@ -28408,7 +28408,7 @@
       </c>
       <c r="F1292" t="inlineStr"/>
       <c r="G1292" t="n">
-        <v>45680818.131</v>
+        <v>45684933.131</v>
       </c>
       <c r="H1292" t="inlineStr"/>
     </row>
@@ -28430,7 +28430,7 @@
       </c>
       <c r="F1293" t="inlineStr"/>
       <c r="G1293" t="n">
-        <v>45881315.473</v>
+        <v>45885958.473</v>
       </c>
       <c r="H1293" t="inlineStr"/>
     </row>
@@ -28452,7 +28452,7 @@
       </c>
       <c r="F1294" t="inlineStr"/>
       <c r="G1294" t="n">
-        <v>46103027.998</v>
+        <v>46106105.998</v>
       </c>
       <c r="H1294" t="inlineStr"/>
     </row>
@@ -28474,7 +28474,7 @@
       </c>
       <c r="F1295" t="inlineStr"/>
       <c r="G1295" t="n">
-        <v>46493805.702</v>
+        <v>46492305.702</v>
       </c>
       <c r="H1295" t="inlineStr"/>
     </row>
@@ -28496,7 +28496,7 @@
       </c>
       <c r="F1296" t="inlineStr"/>
       <c r="G1296" t="n">
-        <v>46839500.161</v>
+        <v>46832116.161</v>
       </c>
       <c r="H1296" t="inlineStr"/>
     </row>
@@ -28518,7 +28518,7 @@
       </c>
       <c r="F1297" t="inlineStr"/>
       <c r="G1297" t="n">
-        <v>47962559.473</v>
+        <v>47958273.473</v>
       </c>
       <c r="H1297" t="inlineStr"/>
     </row>
@@ -28542,7 +28542,7 @@
         <v>24.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>50391335.558</v>
+        <v>50400113.558</v>
       </c>
       <c r="H1298" t="n">
         <v>3.7</v>
@@ -28566,7 +28566,7 @@
       </c>
       <c r="F1299" t="inlineStr"/>
       <c r="G1299" t="n">
-        <v>50017529.041</v>
+        <v>50026308.041</v>
       </c>
       <c r="H1299" t="inlineStr"/>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="F1300" t="inlineStr"/>
       <c r="G1300" t="n">
-        <v>49197647.253</v>
+        <v>49206426.253</v>
       </c>
       <c r="H1300" t="inlineStr"/>
     </row>
@@ -28610,7 +28610,7 @@
       </c>
       <c r="F1301" t="inlineStr"/>
       <c r="G1301" t="n">
-        <v>49563325.809</v>
+        <v>49572104.809</v>
       </c>
       <c r="H1301" t="inlineStr"/>
     </row>
@@ -28632,7 +28632,7 @@
       </c>
       <c r="F1302" t="inlineStr"/>
       <c r="G1302" t="n">
-        <v>49329199.324</v>
+        <v>49337978.324</v>
       </c>
       <c r="H1302" t="inlineStr"/>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="F1303" t="inlineStr"/>
       <c r="G1303" t="n">
-        <v>48589315.632</v>
+        <v>48598094.632</v>
       </c>
       <c r="H1303" t="inlineStr"/>
     </row>
@@ -28676,7 +28676,7 @@
       </c>
       <c r="F1304" t="inlineStr"/>
       <c r="G1304" t="n">
-        <v>48455202.939</v>
+        <v>48463981.939</v>
       </c>
       <c r="H1304" t="inlineStr"/>
     </row>
@@ -28698,7 +28698,7 @@
       </c>
       <c r="F1305" t="inlineStr"/>
       <c r="G1305" t="n">
-        <v>48224820.49</v>
+        <v>48233599.49</v>
       </c>
       <c r="H1305" t="inlineStr"/>
     </row>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="F1306" t="inlineStr"/>
       <c r="G1306" t="n">
-        <v>48255420.393</v>
+        <v>48264199.393</v>
       </c>
       <c r="H1306" t="inlineStr"/>
     </row>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="F1307" t="inlineStr"/>
       <c r="G1307" t="n">
-        <v>48047482.613</v>
+        <v>48056261.613</v>
       </c>
       <c r="H1307" t="inlineStr"/>
     </row>
@@ -28764,7 +28764,7 @@
       </c>
       <c r="F1308" t="inlineStr"/>
       <c r="G1308" t="n">
-        <v>48085697.875</v>
+        <v>48094476.875</v>
       </c>
       <c r="H1308" t="inlineStr"/>
     </row>
@@ -28786,7 +28786,7 @@
       </c>
       <c r="F1309" t="inlineStr"/>
       <c r="G1309" t="n">
-        <v>46980943.386</v>
+        <v>46989722.386</v>
       </c>
       <c r="H1309" t="inlineStr"/>
     </row>
@@ -28808,7 +28808,7 @@
       </c>
       <c r="F1310" t="inlineStr"/>
       <c r="G1310" t="n">
-        <v>46579398.28</v>
+        <v>46588177.28</v>
       </c>
       <c r="H1310" t="inlineStr"/>
     </row>
@@ -28830,7 +28830,7 @@
       </c>
       <c r="F1311" t="inlineStr"/>
       <c r="G1311" t="n">
-        <v>46093046.74</v>
+        <v>46101824.74</v>
       </c>
       <c r="H1311" t="inlineStr"/>
     </row>
@@ -28852,7 +28852,7 @@
       </c>
       <c r="F1312" t="inlineStr"/>
       <c r="G1312" t="n">
-        <v>45467410.696</v>
+        <v>45476189.696</v>
       </c>
       <c r="H1312" t="inlineStr"/>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="F1313" t="inlineStr"/>
       <c r="G1313" t="n">
-        <v>45511969.554</v>
+        <v>45520748.554</v>
       </c>
       <c r="H1313" t="inlineStr"/>
     </row>
@@ -28896,7 +28896,7 @@
       </c>
       <c r="F1314" t="inlineStr"/>
       <c r="G1314" t="n">
-        <v>45625832.123</v>
+        <v>45634611.123</v>
       </c>
       <c r="H1314" t="inlineStr"/>
     </row>
@@ -28918,7 +28918,7 @@
       </c>
       <c r="F1315" t="inlineStr"/>
       <c r="G1315" t="n">
-        <v>47014138.258</v>
+        <v>47022917.258</v>
       </c>
       <c r="H1315" t="inlineStr"/>
     </row>
@@ -28940,7 +28940,7 @@
       </c>
       <c r="F1316" t="inlineStr"/>
       <c r="G1316" t="n">
-        <v>48539874.287</v>
+        <v>48548653.287</v>
       </c>
       <c r="H1316" t="inlineStr"/>
     </row>
@@ -28964,7 +28964,7 @@
         <v>26.3</v>
       </c>
       <c r="G1317" t="n">
-        <v>51197359.522</v>
+        <v>51201565.522</v>
       </c>
       <c r="H1317" t="n">
         <v>2.8</v>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="F1318" t="inlineStr"/>
       <c r="G1318" t="n">
-        <v>50644412.384</v>
+        <v>50648619.384</v>
       </c>
       <c r="H1318" t="inlineStr"/>
     </row>
@@ -29010,7 +29010,7 @@
       </c>
       <c r="F1319" t="inlineStr"/>
       <c r="G1319" t="n">
-        <v>50105279.371</v>
+        <v>50109486.371</v>
       </c>
       <c r="H1319" t="inlineStr"/>
     </row>
@@ -29032,7 +29032,7 @@
       </c>
       <c r="F1320" t="inlineStr"/>
       <c r="G1320" t="n">
-        <v>50584987.593</v>
+        <v>50589193.593</v>
       </c>
       <c r="H1320" t="inlineStr"/>
     </row>
@@ -29054,7 +29054,7 @@
       </c>
       <c r="F1321" t="inlineStr"/>
       <c r="G1321" t="n">
-        <v>49947545.095</v>
+        <v>49951751.095</v>
       </c>
       <c r="H1321" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="F1322" t="inlineStr"/>
       <c r="G1322" t="n">
-        <v>48845435.5</v>
+        <v>48849641.5</v>
       </c>
       <c r="H1322" t="inlineStr"/>
     </row>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="F1323" t="inlineStr"/>
       <c r="G1323" t="n">
-        <v>47668125.888</v>
+        <v>47672331.888</v>
       </c>
       <c r="H1323" t="inlineStr"/>
     </row>
@@ -29120,7 +29120,7 @@
       </c>
       <c r="F1324" t="inlineStr"/>
       <c r="G1324" t="n">
-        <v>47131167.957</v>
+        <v>47135373.957</v>
       </c>
       <c r="H1324" t="inlineStr"/>
     </row>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="F1325" t="inlineStr"/>
       <c r="G1325" t="n">
-        <v>47116572.466</v>
+        <v>47120778.466</v>
       </c>
       <c r="H1325" t="inlineStr"/>
     </row>
@@ -29164,7 +29164,7 @@
       </c>
       <c r="F1326" t="inlineStr"/>
       <c r="G1326" t="n">
-        <v>47377142.259</v>
+        <v>47381348.259</v>
       </c>
       <c r="H1326" t="inlineStr"/>
     </row>
@@ -29186,7 +29186,7 @@
       </c>
       <c r="F1327" t="inlineStr"/>
       <c r="G1327" t="n">
-        <v>46687225.658</v>
+        <v>46691432.658</v>
       </c>
       <c r="H1327" t="inlineStr"/>
     </row>
@@ -29208,7 +29208,7 @@
       </c>
       <c r="F1328" t="inlineStr"/>
       <c r="G1328" t="n">
-        <v>46318071.919</v>
+        <v>46322277.919</v>
       </c>
       <c r="H1328" t="inlineStr"/>
     </row>
@@ -29230,7 +29230,7 @@
       </c>
       <c r="F1329" t="inlineStr"/>
       <c r="G1329" t="n">
-        <v>46037568.839</v>
+        <v>46041774.839</v>
       </c>
       <c r="H1329" t="inlineStr"/>
     </row>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="F1330" t="inlineStr"/>
       <c r="G1330" t="n">
-        <v>46167753.497</v>
+        <v>46171959.497</v>
       </c>
       <c r="H1330" t="inlineStr"/>
     </row>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="F1331" t="inlineStr"/>
       <c r="G1331" t="n">
-        <v>46160600.925</v>
+        <v>46164806.925</v>
       </c>
       <c r="H1331" t="inlineStr"/>
     </row>
@@ -29296,7 +29296,7 @@
       </c>
       <c r="F1332" t="inlineStr"/>
       <c r="G1332" t="n">
-        <v>46022832.945</v>
+        <v>46027039.945</v>
       </c>
       <c r="H1332" t="inlineStr"/>
     </row>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="F1333" t="inlineStr"/>
       <c r="G1333" t="n">
-        <v>46298626.278</v>
+        <v>46302832.278</v>
       </c>
       <c r="H1333" t="inlineStr"/>
     </row>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="F1334" t="inlineStr"/>
       <c r="G1334" t="n">
-        <v>46695799.056</v>
+        <v>46700006.056</v>
       </c>
       <c r="H1334" t="inlineStr"/>
     </row>
@@ -29362,7 +29362,7 @@
       </c>
       <c r="F1335" t="inlineStr"/>
       <c r="G1335" t="n">
-        <v>47686849.807</v>
+        <v>47691055.807</v>
       </c>
       <c r="H1335" t="inlineStr"/>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="F1336" t="inlineStr"/>
       <c r="G1336" t="n">
-        <v>48945767.485</v>
+        <v>48949973.485</v>
       </c>
       <c r="H1336" t="inlineStr"/>
     </row>
@@ -29406,7 +29406,7 @@
       </c>
       <c r="F1337" t="inlineStr"/>
       <c r="G1337" t="n">
-        <v>51097533.335</v>
+        <v>51108699.335</v>
       </c>
       <c r="H1337" t="inlineStr"/>
     </row>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="F1339" t="inlineStr"/>
       <c r="G1339" t="n">
-        <v>50252123.099</v>
+        <v>50263288.099</v>
       </c>
       <c r="H1339" t="inlineStr"/>
     </row>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="F1340" t="inlineStr"/>
       <c r="G1340" t="n">
-        <v>50093736.2</v>
+        <v>50104901.2</v>
       </c>
       <c r="H1340" t="inlineStr"/>
     </row>
@@ -29488,7 +29488,7 @@
       </c>
       <c r="F1341" t="inlineStr"/>
       <c r="G1341" t="n">
-        <v>50610246.622</v>
+        <v>50621412.622</v>
       </c>
       <c r="H1341" t="inlineStr"/>
     </row>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="F1342" t="inlineStr"/>
       <c r="G1342" t="n">
-        <v>51303378.846</v>
+        <v>51314544.846</v>
       </c>
       <c r="H1342" t="inlineStr"/>
     </row>
@@ -29532,7 +29532,7 @@
       </c>
       <c r="F1343" t="inlineStr"/>
       <c r="G1343" t="n">
-        <v>49776757.676</v>
+        <v>49787923.676</v>
       </c>
       <c r="H1343" t="inlineStr"/>
     </row>
@@ -29554,7 +29554,7 @@
       </c>
       <c r="F1344" t="inlineStr"/>
       <c r="G1344" t="n">
-        <v>49505290.468</v>
+        <v>49516455.468</v>
       </c>
       <c r="H1344" t="inlineStr"/>
     </row>
@@ -29576,7 +29576,7 @@
       </c>
       <c r="F1345" t="inlineStr"/>
       <c r="G1345" t="n">
-        <v>48914053.358</v>
+        <v>48925218.358</v>
       </c>
       <c r="H1345" t="inlineStr"/>
     </row>
@@ -29598,7 +29598,7 @@
       </c>
       <c r="F1346" t="inlineStr"/>
       <c r="G1346" t="n">
-        <v>49385829.152</v>
+        <v>49396994.152</v>
       </c>
       <c r="H1346" t="inlineStr"/>
     </row>
@@ -29620,7 +29620,7 @@
       </c>
       <c r="F1347" t="inlineStr"/>
       <c r="G1347" t="n">
-        <v>49058194.486</v>
+        <v>49069360.486</v>
       </c>
       <c r="H1347" t="inlineStr"/>
     </row>
@@ -29642,7 +29642,7 @@
       </c>
       <c r="F1348" t="inlineStr"/>
       <c r="G1348" t="n">
-        <v>49120836.452</v>
+        <v>49132002.452</v>
       </c>
       <c r="H1348" t="inlineStr"/>
     </row>
@@ -29664,7 +29664,7 @@
       </c>
       <c r="F1349" t="inlineStr"/>
       <c r="G1349" t="n">
-        <v>49187205.726</v>
+        <v>49198371.726</v>
       </c>
       <c r="H1349" t="inlineStr"/>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="F1350" t="inlineStr"/>
       <c r="G1350" t="n">
-        <v>49586634.914</v>
+        <v>49597800.914</v>
       </c>
       <c r="H1350" t="inlineStr"/>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="F1351" t="inlineStr"/>
       <c r="G1351" t="n">
-        <v>49096650.391</v>
+        <v>49107815.391</v>
       </c>
       <c r="H1351" t="inlineStr"/>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="F1352" t="inlineStr"/>
       <c r="G1352" t="n">
-        <v>49680629.724</v>
+        <v>49691795.724</v>
       </c>
       <c r="H1352" t="inlineStr"/>
     </row>
@@ -29752,7 +29752,7 @@
       </c>
       <c r="F1353" t="inlineStr"/>
       <c r="G1353" t="n">
-        <v>50153168.696</v>
+        <v>50164334.696</v>
       </c>
       <c r="H1353" t="inlineStr"/>
     </row>
@@ -29774,7 +29774,7 @@
       </c>
       <c r="F1354" t="inlineStr"/>
       <c r="G1354" t="n">
-        <v>50566084.767</v>
+        <v>50577249.767</v>
       </c>
       <c r="H1354" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
       </c>
       <c r="F1355" t="inlineStr"/>
       <c r="G1355" t="n">
-        <v>52836517.995</v>
+        <v>52847683.995</v>
       </c>
       <c r="H1355" t="inlineStr"/>
     </row>
@@ -29818,7 +29818,7 @@
       </c>
       <c r="F1356" t="inlineStr"/>
       <c r="G1356" t="n">
-        <v>53889816.682</v>
+        <v>53900981.682</v>
       </c>
       <c r="H1356" t="inlineStr"/>
     </row>
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57841431.056</v>
+        <v>57852597.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="n">
-        <v>56662097.267</v>
+        <v>56673262.267</v>
       </c>
       <c r="H1358" t="inlineStr"/>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="F1359" t="inlineStr"/>
       <c r="G1359" t="n">
-        <v>56022010.372</v>
+        <v>56033175.372</v>
       </c>
       <c r="H1359" t="inlineStr"/>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="n">
-        <v>56580968.504</v>
+        <v>56592133.504</v>
       </c>
       <c r="H1360" t="inlineStr"/>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="n">
-        <v>56818837.839</v>
+        <v>56830002.839</v>
       </c>
       <c r="H1361" t="inlineStr"/>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="n">
-        <v>55499516.571</v>
+        <v>55510681.571</v>
       </c>
       <c r="H1362" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="n">
-        <v>55309518.556</v>
+        <v>55320684.556</v>
       </c>
       <c r="H1363" t="inlineStr"/>
     </row>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="n">
-        <v>54522994.68</v>
+        <v>54534159.68</v>
       </c>
       <c r="H1364" t="inlineStr"/>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="n">
-        <v>53944407.241</v>
+        <v>53955572.241</v>
       </c>
       <c r="H1365" t="inlineStr"/>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="n">
-        <v>53551810.918</v>
+        <v>53562975.918</v>
       </c>
       <c r="H1366" t="inlineStr"/>
     </row>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F1367" t="inlineStr"/>
       <c r="G1367" t="n">
-        <v>53685603.53</v>
+        <v>53696769.53</v>
       </c>
       <c r="H1367" t="inlineStr"/>
     </row>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="n">
-        <v>52771726.228</v>
+        <v>52782892.228</v>
       </c>
       <c r="H1368" t="inlineStr"/>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53000861.434</v>
+        <v>53012026.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30130,7 +30130,7 @@
       </c>
       <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="n">
-        <v>52782293.166</v>
+        <v>52793458.166</v>
       </c>
       <c r="H1370" t="inlineStr"/>
     </row>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="F1371" t="inlineStr"/>
       <c r="G1371" t="n">
-        <v>52571981.418</v>
+        <v>52583147.418</v>
       </c>
       <c r="H1371" t="inlineStr"/>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="n">
-        <v>52211962.099</v>
+        <v>52223128.099</v>
       </c>
       <c r="H1372" t="inlineStr"/>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="n">
-        <v>52307355.713</v>
+        <v>52318520.713</v>
       </c>
       <c r="H1373" t="inlineStr"/>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="n">
-        <v>52850752.596</v>
+        <v>52861917.596</v>
       </c>
       <c r="H1374" t="inlineStr"/>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="n">
-        <v>52201333.178</v>
+        <v>52212499.178</v>
       </c>
       <c r="H1375" t="inlineStr"/>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="n">
-        <v>52582708.503</v>
+        <v>52593873.503</v>
       </c>
       <c r="H1376" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="n">
-        <v>52802111.197</v>
+        <v>52813277.197</v>
       </c>
       <c r="H1377" t="inlineStr"/>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="n">
-        <v>54075022.568</v>
+        <v>54086188.568</v>
       </c>
       <c r="H1378" t="inlineStr"/>
     </row>
@@ -30330,7 +30330,7 @@
         <v>21.1</v>
       </c>
       <c r="G1379" t="n">
-        <v>56492211.897</v>
+        <v>56498456.897</v>
       </c>
       <c r="H1379" t="n">
         <v>1.9</v>
@@ -30354,7 +30354,7 @@
       </c>
       <c r="F1380" t="inlineStr"/>
       <c r="G1380" t="n">
-        <v>56802952.779</v>
+        <v>56809196.779</v>
       </c>
       <c r="H1380" t="inlineStr"/>
     </row>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="F1381" t="inlineStr"/>
       <c r="G1381" t="n">
-        <v>55243223.451</v>
+        <v>55249467.451</v>
       </c>
       <c r="H1381" t="inlineStr"/>
     </row>
@@ -30398,7 +30398,7 @@
       </c>
       <c r="F1382" t="inlineStr"/>
       <c r="G1382" t="n">
-        <v>55285109.742</v>
+        <v>55291353.742</v>
       </c>
       <c r="H1382" t="inlineStr"/>
     </row>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="F1383" t="inlineStr"/>
       <c r="G1383" t="n">
-        <v>55559877.888</v>
+        <v>55566121.888</v>
       </c>
       <c r="H1383" t="inlineStr"/>
     </row>
@@ -30442,7 +30442,7 @@
       </c>
       <c r="F1384" t="inlineStr"/>
       <c r="G1384" t="n">
-        <v>55041025.049</v>
+        <v>55047269.049</v>
       </c>
       <c r="H1384" t="inlineStr"/>
     </row>
@@ -30464,7 +30464,7 @@
       </c>
       <c r="F1385" t="inlineStr"/>
       <c r="G1385" t="n">
-        <v>53786664.218</v>
+        <v>53792908.218</v>
       </c>
       <c r="H1385" t="inlineStr"/>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="F1386" t="inlineStr"/>
       <c r="G1386" t="n">
-        <v>52813688.644</v>
+        <v>52819932.644</v>
       </c>
       <c r="H1386" t="inlineStr"/>
     </row>
@@ -30508,7 +30508,7 @@
       </c>
       <c r="F1387" t="inlineStr"/>
       <c r="G1387" t="n">
-        <v>52093697.57</v>
+        <v>52099941.57</v>
       </c>
       <c r="H1387" t="inlineStr"/>
     </row>
@@ -30530,7 +30530,7 @@
       </c>
       <c r="F1388" t="inlineStr"/>
       <c r="G1388" t="n">
-        <v>51866473.889</v>
+        <v>51872717.889</v>
       </c>
       <c r="H1388" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
       </c>
       <c r="F1389" t="inlineStr"/>
       <c r="G1389" t="n">
-        <v>51828260.679</v>
+        <v>51834504.679</v>
       </c>
       <c r="H1389" t="inlineStr"/>
     </row>
@@ -30574,7 +30574,7 @@
       </c>
       <c r="F1390" t="inlineStr"/>
       <c r="G1390" t="n">
-        <v>51721406.828</v>
+        <v>51727650.828</v>
       </c>
       <c r="H1390" t="inlineStr"/>
     </row>
@@ -30596,7 +30596,7 @@
       </c>
       <c r="F1391" t="inlineStr"/>
       <c r="G1391" t="n">
-        <v>51304117.283</v>
+        <v>51310361.283</v>
       </c>
       <c r="H1391" t="inlineStr"/>
     </row>
@@ -30618,7 +30618,7 @@
       </c>
       <c r="F1392" t="inlineStr"/>
       <c r="G1392" t="n">
-        <v>50700872.116</v>
+        <v>50707116.116</v>
       </c>
       <c r="H1392" t="inlineStr"/>
     </row>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="F1393" t="inlineStr"/>
       <c r="G1393" t="n">
-        <v>50552940.926</v>
+        <v>50559184.926</v>
       </c>
       <c r="H1393" t="inlineStr"/>
     </row>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="F1394" t="inlineStr"/>
       <c r="G1394" t="n">
-        <v>50208603.764</v>
+        <v>50214847.764</v>
       </c>
       <c r="H1394" t="inlineStr"/>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="F1395" t="inlineStr"/>
       <c r="G1395" t="n">
-        <v>50093606.563</v>
+        <v>50099850.563</v>
       </c>
       <c r="H1395" t="inlineStr"/>
     </row>
@@ -30706,7 +30706,7 @@
       </c>
       <c r="F1396" t="inlineStr"/>
       <c r="G1396" t="n">
-        <v>49626074.924</v>
+        <v>49632318.924</v>
       </c>
       <c r="H1396" t="inlineStr"/>
     </row>
@@ -30728,7 +30728,7 @@
       </c>
       <c r="F1397" t="inlineStr"/>
       <c r="G1397" t="n">
-        <v>51021602.556</v>
+        <v>51027847.556</v>
       </c>
       <c r="H1397" t="inlineStr"/>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="F1398" t="inlineStr"/>
       <c r="G1398" t="n">
-        <v>51894596.644</v>
+        <v>51900840.644</v>
       </c>
       <c r="H1398" t="inlineStr"/>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="F1399" t="inlineStr"/>
       <c r="G1399" t="n">
-        <v>54245702.622</v>
+        <v>54258199.622</v>
       </c>
       <c r="H1399" t="inlineStr"/>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="F1401" t="inlineStr"/>
       <c r="G1401" t="n">
-        <v>53361468.53</v>
+        <v>53373965.53</v>
       </c>
       <c r="H1401" t="inlineStr"/>
     </row>
@@ -30832,7 +30832,7 @@
       </c>
       <c r="F1402" t="inlineStr"/>
       <c r="G1402" t="n">
-        <v>52754025.855</v>
+        <v>52766522.855</v>
       </c>
       <c r="H1402" t="inlineStr"/>
     </row>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="F1403" t="inlineStr"/>
       <c r="G1403" t="n">
-        <v>53238606.593</v>
+        <v>53251103.593</v>
       </c>
       <c r="H1403" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
       </c>
       <c r="F1404" t="inlineStr"/>
       <c r="G1404" t="n">
-        <v>54177688.308</v>
+        <v>54190186.308</v>
       </c>
       <c r="H1404" t="inlineStr"/>
     </row>
@@ -30898,7 +30898,7 @@
       </c>
       <c r="F1405" t="inlineStr"/>
       <c r="G1405" t="n">
-        <v>53188004.494</v>
+        <v>53200502.494</v>
       </c>
       <c r="H1405" t="inlineStr"/>
     </row>
@@ -30920,7 +30920,7 @@
       </c>
       <c r="F1406" t="inlineStr"/>
       <c r="G1406" t="n">
-        <v>52621122.98</v>
+        <v>52633619.98</v>
       </c>
       <c r="H1406" t="inlineStr"/>
     </row>
@@ -30942,7 +30942,7 @@
       </c>
       <c r="F1407" t="inlineStr"/>
       <c r="G1407" t="n">
-        <v>51764665.704</v>
+        <v>51777162.704</v>
       </c>
       <c r="H1407" t="inlineStr"/>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="F1408" t="inlineStr"/>
       <c r="G1408" t="n">
-        <v>51772405.154</v>
+        <v>51784902.154</v>
       </c>
       <c r="H1408" t="inlineStr"/>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="F1409" t="inlineStr"/>
       <c r="G1409" t="n">
-        <v>51647428.007</v>
+        <v>51659925.007</v>
       </c>
       <c r="H1409" t="inlineStr"/>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="F1410" t="inlineStr"/>
       <c r="G1410" t="n">
-        <v>50922584.014</v>
+        <v>50935081.014</v>
       </c>
       <c r="H1410" t="inlineStr"/>
     </row>
@@ -31030,7 +31030,7 @@
       </c>
       <c r="F1411" t="inlineStr"/>
       <c r="G1411" t="n">
-        <v>51258631.064</v>
+        <v>51271129.064</v>
       </c>
       <c r="H1411" t="inlineStr"/>
     </row>
@@ -31052,7 +31052,7 @@
       </c>
       <c r="F1412" t="inlineStr"/>
       <c r="G1412" t="n">
-        <v>50204204.352</v>
+        <v>50216701.352</v>
       </c>
       <c r="H1412" t="inlineStr"/>
     </row>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="F1413" t="inlineStr"/>
       <c r="G1413" t="n">
-        <v>50356617.972</v>
+        <v>50369114.972</v>
       </c>
       <c r="H1413" t="inlineStr"/>
     </row>
@@ -31096,7 +31096,7 @@
       </c>
       <c r="F1414" t="inlineStr"/>
       <c r="G1414" t="n">
-        <v>50450768.477</v>
+        <v>50463265.477</v>
       </c>
       <c r="H1414" t="inlineStr"/>
     </row>
@@ -31118,7 +31118,7 @@
       </c>
       <c r="F1415" t="inlineStr"/>
       <c r="G1415" t="n">
-        <v>50390000.859</v>
+        <v>50402497.859</v>
       </c>
       <c r="H1415" t="inlineStr"/>
     </row>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="F1416" t="inlineStr"/>
       <c r="G1416" t="n">
-        <v>50431205.937</v>
+        <v>50443702.937</v>
       </c>
       <c r="H1416" t="inlineStr"/>
     </row>
@@ -31162,7 +31162,7 @@
       </c>
       <c r="F1417" t="inlineStr"/>
       <c r="G1417" t="n">
-        <v>50308750.92</v>
+        <v>50321247.92</v>
       </c>
       <c r="H1417" t="inlineStr"/>
     </row>
@@ -31184,7 +31184,7 @@
       </c>
       <c r="F1418" t="inlineStr"/>
       <c r="G1418" t="n">
-        <v>50583585.87</v>
+        <v>50577394.87</v>
       </c>
       <c r="H1418" t="inlineStr"/>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="F1419" t="inlineStr"/>
       <c r="G1419" t="n">
-        <v>51120343.993</v>
+        <v>51114151.993</v>
       </c>
       <c r="H1419" t="inlineStr"/>
     </row>
@@ -31228,7 +31228,7 @@
       </c>
       <c r="F1420" t="inlineStr"/>
       <c r="G1420" t="n">
-        <v>51099977.537</v>
+        <v>51112474.537</v>
       </c>
       <c r="H1420" t="inlineStr"/>
     </row>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="F1421" t="inlineStr"/>
       <c r="G1421" t="n">
-        <v>52912512.45</v>
+        <v>52908295.45</v>
       </c>
       <c r="H1421" t="inlineStr"/>
     </row>
@@ -31274,7 +31274,7 @@
         <v>21.9</v>
       </c>
       <c r="G1422" t="n">
-        <v>55368558.222</v>
+        <v>55345804.222</v>
       </c>
       <c r="H1422" t="n">
         <v>2.1</v>
@@ -31298,7 +31298,7 @@
       </c>
       <c r="F1423" t="inlineStr"/>
       <c r="G1423" t="n">
-        <v>55607152.331</v>
+        <v>55584399.331</v>
       </c>
       <c r="H1423" t="inlineStr"/>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="F1424" t="inlineStr"/>
       <c r="G1424" t="n">
-        <v>55669078.151</v>
+        <v>55646325.151</v>
       </c>
       <c r="H1424" t="inlineStr"/>
     </row>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="F1425" t="inlineStr"/>
       <c r="G1425" t="n">
-        <v>55934789.978</v>
+        <v>55912037.978</v>
       </c>
       <c r="H1425" t="inlineStr"/>
     </row>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="F1426" t="inlineStr"/>
       <c r="G1426" t="n">
-        <v>55706492.241</v>
+        <v>55683740.241</v>
       </c>
       <c r="H1426" t="inlineStr"/>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="F1427" t="inlineStr"/>
       <c r="G1427" t="n">
-        <v>54869668.217</v>
+        <v>54846916.217</v>
       </c>
       <c r="H1427" t="inlineStr"/>
     </row>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="F1428" t="inlineStr"/>
       <c r="G1428" t="n">
-        <v>54747971.24</v>
+        <v>54725217.24</v>
       </c>
       <c r="H1428" t="inlineStr"/>
     </row>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="F1429" t="inlineStr"/>
       <c r="G1429" t="n">
-        <v>54461099.576</v>
+        <v>54438345.576</v>
       </c>
       <c r="H1429" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="F1430" t="inlineStr"/>
       <c r="G1430" t="n">
-        <v>54472514.621</v>
+        <v>54449761.621</v>
       </c>
       <c r="H1430" t="inlineStr"/>
     </row>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="F1431" t="inlineStr"/>
       <c r="G1431" t="n">
-        <v>51940587.914</v>
+        <v>51917834.914</v>
       </c>
       <c r="H1431" t="inlineStr"/>
     </row>
@@ -31496,7 +31496,7 @@
       </c>
       <c r="F1432" t="inlineStr"/>
       <c r="G1432" t="n">
-        <v>52499410.382</v>
+        <v>52476658.382</v>
       </c>
       <c r="H1432" t="inlineStr"/>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="F1433" t="inlineStr"/>
       <c r="G1433" t="n">
-        <v>51703928.388</v>
+        <v>51681176.388</v>
       </c>
       <c r="H1433" t="inlineStr"/>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="F1434" t="inlineStr"/>
       <c r="G1434" t="n">
-        <v>50471380.623</v>
+        <v>50448626.623</v>
       </c>
       <c r="H1434" t="inlineStr"/>
     </row>
@@ -31562,7 +31562,7 @@
       </c>
       <c r="F1435" t="inlineStr"/>
       <c r="G1435" t="n">
-        <v>50516750.287</v>
+        <v>50493998.287</v>
       </c>
       <c r="H1435" t="inlineStr"/>
     </row>
@@ -31584,7 +31584,7 @@
       </c>
       <c r="F1436" t="inlineStr"/>
       <c r="G1436" t="n">
-        <v>50050329.307</v>
+        <v>50027576.307</v>
       </c>
       <c r="H1436" t="inlineStr"/>
     </row>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="F1437" t="inlineStr"/>
       <c r="G1437" t="n">
-        <v>50770677.53</v>
+        <v>50747924.53</v>
       </c>
       <c r="H1437" t="inlineStr"/>
     </row>
@@ -31628,7 +31628,7 @@
       </c>
       <c r="F1438" t="inlineStr"/>
       <c r="G1438" t="n">
-        <v>50014756.981</v>
+        <v>49992003.981</v>
       </c>
       <c r="H1438" t="inlineStr"/>
     </row>
@@ -31650,7 +31650,7 @@
       </c>
       <c r="F1439" t="inlineStr"/>
       <c r="G1439" t="n">
-        <v>49860241.76</v>
+        <v>49837487.76</v>
       </c>
       <c r="H1439" t="inlineStr"/>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="F1440" t="inlineStr"/>
       <c r="G1440" t="n">
-        <v>49775861.195</v>
+        <v>49753107.195</v>
       </c>
       <c r="H1440" t="inlineStr"/>
     </row>
@@ -31694,7 +31694,7 @@
       </c>
       <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="n">
-        <v>49518695.045</v>
+        <v>49495942.045</v>
       </c>
       <c r="H1441" t="inlineStr"/>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="F1442" t="inlineStr"/>
       <c r="G1442" t="n">
-        <v>50066388.504</v>
+        <v>50043634.504</v>
       </c>
       <c r="H1442" t="inlineStr"/>
     </row>
@@ -31738,7 +31738,7 @@
       </c>
       <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="n">
-        <v>51521069.942</v>
+        <v>51498315.942</v>
       </c>
       <c r="H1443" t="inlineStr"/>
     </row>
@@ -31762,7 +31762,7 @@
         <v>20.8</v>
       </c>
       <c r="G1444" t="n">
-        <v>53881677.608</v>
+        <v>53885494.608</v>
       </c>
       <c r="H1444" t="n">
         <v>2.3</v>
@@ -31786,7 +31786,7 @@
       </c>
       <c r="F1445" t="inlineStr"/>
       <c r="G1445" t="n">
-        <v>53454317.301</v>
+        <v>53458135.301</v>
       </c>
       <c r="H1445" t="inlineStr"/>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F1446" t="inlineStr"/>
       <c r="G1446" t="n">
-        <v>53027126.662</v>
+        <v>53030944.662</v>
       </c>
       <c r="H1446" t="inlineStr"/>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="F1447" t="inlineStr"/>
       <c r="G1447" t="n">
-        <v>53693349.632</v>
+        <v>53697167.632</v>
       </c>
       <c r="H1447" t="inlineStr"/>
     </row>
@@ -31852,7 +31852,7 @@
       </c>
       <c r="F1448" t="inlineStr"/>
       <c r="G1448" t="n">
-        <v>52960315.148</v>
+        <v>52964132.148</v>
       </c>
       <c r="H1448" t="inlineStr"/>
     </row>
@@ -31874,7 +31874,7 @@
       </c>
       <c r="F1449" t="inlineStr"/>
       <c r="G1449" t="n">
-        <v>51746155.271</v>
+        <v>51749972.271</v>
       </c>
       <c r="H1449" t="inlineStr"/>
     </row>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="F1450" t="inlineStr"/>
       <c r="G1450" t="n">
-        <v>50247416.976</v>
+        <v>50251234.976</v>
       </c>
       <c r="H1450" t="inlineStr"/>
     </row>
@@ -31918,7 +31918,7 @@
       </c>
       <c r="F1451" t="inlineStr"/>
       <c r="G1451" t="n">
-        <v>50808322.288</v>
+        <v>50812140.288</v>
       </c>
       <c r="H1451" t="inlineStr"/>
     </row>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="F1452" t="inlineStr"/>
       <c r="G1452" t="n">
-        <v>50539140.336</v>
+        <v>50542959.336</v>
       </c>
       <c r="H1452" t="inlineStr"/>
     </row>
@@ -31962,7 +31962,7 @@
       </c>
       <c r="F1453" t="inlineStr"/>
       <c r="G1453" t="n">
-        <v>50533316.135</v>
+        <v>50537135.135</v>
       </c>
       <c r="H1453" t="inlineStr"/>
     </row>
@@ -31984,7 +31984,7 @@
       </c>
       <c r="F1454" t="inlineStr"/>
       <c r="G1454" t="n">
-        <v>50348047.524</v>
+        <v>50351866.524</v>
       </c>
       <c r="H1454" t="inlineStr"/>
     </row>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="F1455" t="inlineStr"/>
       <c r="G1455" t="n">
-        <v>50185945.389</v>
+        <v>50189762.389</v>
       </c>
       <c r="H1455" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
       </c>
       <c r="F1456" t="inlineStr"/>
       <c r="G1456" t="n">
-        <v>50002605.804</v>
+        <v>50006424.804</v>
       </c>
       <c r="H1456" t="inlineStr"/>
     </row>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="F1457" t="inlineStr"/>
       <c r="G1457" t="n">
-        <v>50598109.035</v>
+        <v>50601927.035</v>
       </c>
       <c r="H1457" t="inlineStr"/>
     </row>
@@ -32072,7 +32072,7 @@
       </c>
       <c r="F1458" t="inlineStr"/>
       <c r="G1458" t="n">
-        <v>51392573.263</v>
+        <v>51396389.263</v>
       </c>
       <c r="H1458" t="inlineStr"/>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="F1459" t="inlineStr"/>
       <c r="G1459" t="n">
-        <v>51876145.288</v>
+        <v>51879962.288</v>
       </c>
       <c r="H1459" t="inlineStr"/>
     </row>
@@ -32116,7 +32116,7 @@
       </c>
       <c r="F1460" t="inlineStr"/>
       <c r="G1460" t="n">
-        <v>53259172.364</v>
+        <v>53262990.364</v>
       </c>
       <c r="H1460" t="inlineStr"/>
     </row>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="n">
-        <v>56137543.43</v>
+        <v>56141362.43</v>
       </c>
       <c r="H1461" t="inlineStr"/>
     </row>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="F1463" t="inlineStr"/>
       <c r="G1463" t="n">
-        <v>56139686.367</v>
+        <v>56143504.367</v>
       </c>
       <c r="H1463" t="inlineStr"/>
     </row>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="F1464" t="inlineStr"/>
       <c r="G1464" t="n">
-        <v>55008690.993</v>
+        <v>55012509.993</v>
       </c>
       <c r="H1464" t="inlineStr"/>
     </row>
@@ -32220,7 +32220,7 @@
       </c>
       <c r="F1465" t="inlineStr"/>
       <c r="G1465" t="n">
-        <v>55434965.785</v>
+        <v>55438783.785</v>
       </c>
       <c r="H1465" t="inlineStr"/>
     </row>
@@ -32242,7 +32242,7 @@
       </c>
       <c r="F1466" t="inlineStr"/>
       <c r="G1466" t="n">
-        <v>56314843.518</v>
+        <v>56318661.518</v>
       </c>
       <c r="H1466" t="inlineStr"/>
     </row>
@@ -32264,7 +32264,7 @@
       </c>
       <c r="F1467" t="inlineStr"/>
       <c r="G1467" t="n">
-        <v>55324573.095</v>
+        <v>55328392.095</v>
       </c>
       <c r="H1467" t="inlineStr"/>
     </row>
@@ -32286,7 +32286,7 @@
       </c>
       <c r="F1468" t="inlineStr"/>
       <c r="G1468" t="n">
-        <v>54658324.736</v>
+        <v>54678857.736</v>
       </c>
       <c r="H1468" t="inlineStr"/>
     </row>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="F1469" t="inlineStr"/>
       <c r="G1469" t="n">
-        <v>54534463.54</v>
+        <v>54554995.54</v>
       </c>
       <c r="H1469" t="inlineStr"/>
     </row>
@@ -32330,7 +32330,7 @@
       </c>
       <c r="F1470" t="inlineStr"/>
       <c r="G1470" t="n">
-        <v>55241995.612</v>
+        <v>55262528.612</v>
       </c>
       <c r="H1470" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
       </c>
       <c r="F1471" t="inlineStr"/>
       <c r="G1471" t="n">
-        <v>55056315.123</v>
+        <v>55076848.123</v>
       </c>
       <c r="H1471" t="inlineStr"/>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="F1472" t="inlineStr"/>
       <c r="G1472" t="n">
-        <v>56267264.956</v>
+        <v>56287797.956</v>
       </c>
       <c r="H1472" t="inlineStr"/>
     </row>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="F1473" t="inlineStr"/>
       <c r="G1473" t="n">
-        <v>56105547.885</v>
+        <v>56126079.885</v>
       </c>
       <c r="H1473" t="inlineStr"/>
     </row>
@@ -32418,7 +32418,7 @@
       </c>
       <c r="F1474" t="inlineStr"/>
       <c r="G1474" t="n">
-        <v>57280821.778</v>
+        <v>57301353.778</v>
       </c>
       <c r="H1474" t="inlineStr"/>
     </row>
@@ -32440,7 +32440,7 @@
       </c>
       <c r="F1475" t="inlineStr"/>
       <c r="G1475" t="n">
-        <v>58712436.611</v>
+        <v>58732968.611</v>
       </c>
       <c r="H1475" t="inlineStr"/>
     </row>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="F1476" t="inlineStr"/>
       <c r="G1476" t="n">
-        <v>59869501.332</v>
+        <v>59890034.332</v>
       </c>
       <c r="H1476" t="inlineStr"/>
     </row>
@@ -32484,7 +32484,7 @@
       </c>
       <c r="F1477" t="inlineStr"/>
       <c r="G1477" t="n">
-        <v>60252696.984</v>
+        <v>60273228.984</v>
       </c>
       <c r="H1477" t="inlineStr"/>
     </row>
@@ -32506,7 +32506,7 @@
       </c>
       <c r="F1478" t="inlineStr"/>
       <c r="G1478" t="n">
-        <v>60777543.024</v>
+        <v>60798076.024</v>
       </c>
       <c r="H1478" t="inlineStr"/>
     </row>
@@ -32528,7 +32528,7 @@
       </c>
       <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="n">
-        <v>60704748.044</v>
+        <v>60725280.044</v>
       </c>
       <c r="H1479" t="inlineStr"/>
     </row>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="F1480" t="inlineStr"/>
       <c r="G1480" t="n">
-        <v>62859760.767</v>
+        <v>62880292.767</v>
       </c>
       <c r="H1480" t="inlineStr"/>
     </row>
@@ -32559,7 +32559,7 @@
         <v>46021</v>
       </c>
       <c r="B1481" t="n">
-        <v>41167</v>
+        <v>41095</v>
       </c>
       <c r="C1481" t="n">
         <v>42956965</v>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65254200.703</v>
+        <v>65326084.703</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -32610,7 +32610,7 @@
       </c>
       <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="n">
-        <v>64536734.281</v>
+        <v>64608617.281</v>
       </c>
       <c r="H1483" t="inlineStr"/>
     </row>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61824915.993</v>
+        <v>61896799.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61142602.519</v>
+        <v>61214486.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61677950.076</v>
+        <v>61749834.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32698,7 +32698,7 @@
       </c>
       <c r="F1487" t="inlineStr"/>
       <c r="G1487" t="n">
-        <v>60438835.004</v>
+        <v>60510718.004</v>
       </c>
       <c r="H1487" t="inlineStr"/>
     </row>
@@ -32720,7 +32720,7 @@
       </c>
       <c r="F1488" t="inlineStr"/>
       <c r="G1488" t="n">
-        <v>59485108.211</v>
+        <v>59556992.211</v>
       </c>
       <c r="H1488" t="inlineStr"/>
     </row>
@@ -32742,7 +32742,7 @@
       </c>
       <c r="F1489" t="inlineStr"/>
       <c r="G1489" t="n">
-        <v>57763617.381</v>
+        <v>57835501.381</v>
       </c>
       <c r="H1489" t="inlineStr"/>
     </row>
@@ -32764,7 +32764,7 @@
       </c>
       <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="n">
-        <v>57172304.101</v>
+        <v>57244186.101</v>
       </c>
       <c r="H1490" t="inlineStr"/>
     </row>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="n">
-        <v>57100253.244</v>
+        <v>57172137.244</v>
       </c>
       <c r="H1491" t="inlineStr"/>
     </row>
@@ -32808,7 +32808,7 @@
       </c>
       <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="n">
-        <v>57528237.399</v>
+        <v>57600120.399</v>
       </c>
       <c r="H1492" t="inlineStr"/>
     </row>
@@ -32830,7 +32830,7 @@
       </c>
       <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="n">
-        <v>56202613.088</v>
+        <v>56274497.088</v>
       </c>
       <c r="H1493" t="inlineStr"/>
     </row>
@@ -32852,7 +32852,7 @@
       </c>
       <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="n">
-        <v>55579701.47</v>
+        <v>55651584.47</v>
       </c>
       <c r="H1494" t="inlineStr"/>
     </row>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="n">
-        <v>55406149.492</v>
+        <v>55478033.492</v>
       </c>
       <c r="H1495" t="inlineStr"/>
     </row>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55235464.796</v>
+        <v>55307347.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="n">
-        <v>54998195.613</v>
+        <v>55070080.613</v>
       </c>
       <c r="H1497" t="inlineStr"/>
     </row>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="n">
-        <v>54698770.758</v>
+        <v>54770654.758</v>
       </c>
       <c r="H1498" t="inlineStr"/>
     </row>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54854000.349</v>
+        <v>54925883.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -32984,7 +32984,7 @@
       </c>
       <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="n">
-        <v>55108439.773</v>
+        <v>55180322.773</v>
       </c>
       <c r="H1500" t="inlineStr"/>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="n">
-        <v>55864117.062</v>
+        <v>55936001.062</v>
       </c>
       <c r="H1501" t="inlineStr"/>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="n">
-        <v>57558988.416</v>
+        <v>57630872.416</v>
       </c>
       <c r="H1502" t="inlineStr"/>
     </row>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60127059.818</v>
+        <v>60140783.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33088,7 +33088,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59032021.841</v>
+        <v>59045746.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58333595.213</v>
+        <v>58347319.213</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58566832.727</v>
+        <v>58580557.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59654634.587</v>
+        <v>59668358.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58022025.8</v>
+        <v>58035749.8</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57252820.786</v>
+        <v>57266544.786</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33220,7 +33220,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56132727.11</v>
+        <v>56146451.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56444984.744</v>
+        <v>56458709.744</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33264,7 +33264,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55860674.876</v>
+        <v>55874398.876</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33286,7 +33286,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55583322.143</v>
+        <v>55597047.143</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55615431.479</v>
+        <v>55629155.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55666332.733</v>
+        <v>55680056.733</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33352,7 +33352,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55237255.15</v>
+        <v>55250979.15</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33374,7 +33374,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55282382.162</v>
+        <v>55296106.162</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
       </c>
       <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="n">
-        <v>54704336.928</v>
+        <v>54718060.928</v>
       </c>
       <c r="H1519" t="inlineStr"/>
     </row>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="n">
-        <v>55604946.663</v>
+        <v>55618670.663</v>
       </c>
       <c r="H1520" t="inlineStr"/>
     </row>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57359991.612</v>
+        <v>57373715.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60360233.102</v>
+        <v>60378787.102</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59166078.726</v>
+        <v>59184632.726</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58622142.442</v>
+        <v>58640696.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58650299.045</v>
+        <v>58668853.045</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59428853.107</v>
+        <v>59447406.107</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33588,7 +33588,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57829613.899</v>
+        <v>57848167.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57120482.668</v>
+        <v>57139035.668</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33632,7 +33632,7 @@
       </c>
       <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="n">
-        <v>56146349.566</v>
+        <v>56164902.566</v>
       </c>
       <c r="H1530" t="inlineStr"/>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="n">
-        <v>56032703.838</v>
+        <v>56051257.838</v>
       </c>
       <c r="H1531" t="inlineStr"/>
     </row>
@@ -33676,7 +33676,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55920479.807</v>
+        <v>55939032.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56209278.122</v>
+        <v>56227831.122</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55925719.807</v>
+        <v>55944273.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55075837.219</v>
+        <v>55094390.219</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="n">
-        <v>54526532.642</v>
+        <v>54545086.642</v>
       </c>
       <c r="H1536" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54583252.849</v>
+        <v>54601805.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54955402.591</v>
+        <v>54973955.591</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="n">
-        <v>56151551.145</v>
+        <v>56170105.145</v>
       </c>
       <c r="H1539" t="inlineStr"/>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="n">
-        <v>55825762.824</v>
+        <v>55844316.824</v>
       </c>
       <c r="H1540" t="inlineStr"/>
     </row>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="n">
-        <v>56003116.906</v>
+        <v>56021670.906</v>
       </c>
       <c r="H1541" t="inlineStr"/>
     </row>
@@ -33896,7 +33896,7 @@
       </c>
       <c r="F1542" t="inlineStr"/>
       <c r="G1542" t="n">
-        <v>58224243.582</v>
+        <v>58242796.582</v>
       </c>
       <c r="H1542" t="inlineStr"/>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="F1565" t="inlineStr"/>
       <c r="G1565" t="n">
-        <v>59796477.279</v>
+        <v>60129263.279</v>
       </c>
       <c r="H1565" t="inlineStr"/>
     </row>
@@ -34432,7 +34432,7 @@
       </c>
       <c r="F1566" t="inlineStr"/>
       <c r="G1566" t="n">
-        <v>60660651.741</v>
+        <v>60048913.918</v>
       </c>
       <c r="H1566" t="inlineStr"/>
     </row>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="F1567" t="inlineStr"/>
       <c r="G1567" t="n">
-        <v>60752303.074</v>
+        <v>60760212.379</v>
       </c>
       <c r="H1567" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
       </c>
       <c r="F1568" t="inlineStr"/>
       <c r="G1568" t="n">
-        <v>58977513.233</v>
+        <v>58972403.37</v>
       </c>
       <c r="H1568" t="inlineStr"/>
     </row>
@@ -34498,7 +34498,7 @@
       </c>
       <c r="F1569" t="inlineStr"/>
       <c r="G1569" t="n">
-        <v>58175977.865</v>
+        <v>58204242.865</v>
       </c>
       <c r="H1569" t="inlineStr"/>
     </row>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="n">
-        <v>57676758.653</v>
+        <v>57715092.653</v>
       </c>
       <c r="H1570" t="inlineStr"/>
     </row>
@@ -34541,15 +34541,21 @@
         <v>20.25</v>
       </c>
       <c r="F1571" t="inlineStr"/>
-      <c r="G1571" t="inlineStr"/>
+      <c r="G1571" t="n">
+        <v>57652407.262</v>
+      </c>
       <c r="H1571" t="inlineStr"/>
     </row>
     <row r="1572">
       <c r="A1572" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="B1572" t="inlineStr"/>
-      <c r="C1572" t="inlineStr"/>
+      <c r="B1572" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C1572" t="n">
+        <v>41730096</v>
+      </c>
       <c r="D1572" t="n">
         <v>1414.07</v>
       </c>
@@ -34569,10 +34575,26 @@
       <c r="D1573" t="n">
         <v>1418.57</v>
       </c>
-      <c r="E1573" t="inlineStr"/>
+      <c r="E1573" t="n">
+        <v>21.125</v>
+      </c>
       <c r="F1573" t="inlineStr"/>
       <c r="G1573" t="inlineStr"/>
       <c r="H1573" t="inlineStr"/>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B1574" t="inlineStr"/>
+      <c r="C1574" t="inlineStr"/>
+      <c r="D1574" t="n">
+        <v>1416.31</v>
+      </c>
+      <c r="E1574" t="inlineStr"/>
+      <c r="F1574" t="inlineStr"/>
+      <c r="G1574" t="inlineStr"/>
+      <c r="H1574" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1574"/>
+  <dimension ref="A1:H1578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.48</v>
+        <v>108.29</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.61</v>
+        <v>108.48</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.63</v>
+        <v>108.61</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.72</v>
+        <v>108.63</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.86</v>
+        <v>108.72</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.96</v>
+        <v>108.86</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.97</v>
+        <v>108.96</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>109.05</v>
+        <v>108.97</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.11</v>
+        <v>109.05</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.21</v>
+        <v>109.11</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.46</v>
+        <v>109.21</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.64</v>
+        <v>109.46</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.67</v>
+        <v>109.64</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.71</v>
+        <v>109.67</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.79</v>
+        <v>109.71</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>110.08</v>
+        <v>109.79</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.11</v>
+        <v>110.08</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.15</v>
+        <v>110.11</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.5</v>
+        <v>110.15</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.68</v>
+        <v>110.5</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.71</v>
+        <v>110.68</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.92</v>
+        <v>110.75</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>111.37</v>
+        <v>110.92</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.46</v>
+        <v>111.37</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.49</v>
+        <v>111.46</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.52</v>
+        <v>111.49</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.59</v>
+        <v>111.52</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.67</v>
+        <v>111.59</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>112.01</v>
+        <v>111.67</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.17</v>
+        <v>112.01</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.21</v>
+        <v>112.17</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.24</v>
+        <v>112.21</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.48</v>
+        <v>112.24</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.71</v>
+        <v>112.48</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.8</v>
+        <v>112.71</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.83</v>
+        <v>112.8</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.89</v>
+        <v>112.83</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.95</v>
+        <v>112.89</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="F1307" t="inlineStr"/>
       <c r="G1307" t="n">
-        <v>48056261.613</v>
+        <v>48055823.613</v>
       </c>
       <c r="H1307" t="inlineStr"/>
     </row>
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57852597.056</v>
+        <v>57849024.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="n">
-        <v>56673262.267</v>
+        <v>56669690.267</v>
       </c>
       <c r="H1358" t="inlineStr"/>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="F1359" t="inlineStr"/>
       <c r="G1359" t="n">
-        <v>56033175.372</v>
+        <v>56029603.372</v>
       </c>
       <c r="H1359" t="inlineStr"/>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="n">
-        <v>56592133.504</v>
+        <v>56588561.504</v>
       </c>
       <c r="H1360" t="inlineStr"/>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="n">
-        <v>56830002.839</v>
+        <v>56826429.839</v>
       </c>
       <c r="H1361" t="inlineStr"/>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="n">
-        <v>55510681.571</v>
+        <v>55507108.571</v>
       </c>
       <c r="H1362" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="n">
-        <v>55320684.556</v>
+        <v>55317111.556</v>
       </c>
       <c r="H1363" t="inlineStr"/>
     </row>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="n">
-        <v>54534159.68</v>
+        <v>54530587.68</v>
       </c>
       <c r="H1364" t="inlineStr"/>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="n">
-        <v>53955572.241</v>
+        <v>53951999.241</v>
       </c>
       <c r="H1365" t="inlineStr"/>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="n">
-        <v>53562975.918</v>
+        <v>53559403.918</v>
       </c>
       <c r="H1366" t="inlineStr"/>
     </row>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F1367" t="inlineStr"/>
       <c r="G1367" t="n">
-        <v>53696769.53</v>
+        <v>53693196.53</v>
       </c>
       <c r="H1367" t="inlineStr"/>
     </row>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="n">
-        <v>52782892.228</v>
+        <v>52779319.228</v>
       </c>
       <c r="H1368" t="inlineStr"/>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53012026.434</v>
+        <v>53008454.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30130,7 +30130,7 @@
       </c>
       <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="n">
-        <v>52793458.166</v>
+        <v>52789885.166</v>
       </c>
       <c r="H1370" t="inlineStr"/>
     </row>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="F1371" t="inlineStr"/>
       <c r="G1371" t="n">
-        <v>52583147.418</v>
+        <v>52579574.418</v>
       </c>
       <c r="H1371" t="inlineStr"/>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="n">
-        <v>52223128.099</v>
+        <v>52219555.099</v>
       </c>
       <c r="H1372" t="inlineStr"/>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="n">
-        <v>52318520.713</v>
+        <v>52314947.713</v>
       </c>
       <c r="H1373" t="inlineStr"/>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="n">
-        <v>52861917.596</v>
+        <v>52858345.596</v>
       </c>
       <c r="H1374" t="inlineStr"/>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="n">
-        <v>52212499.178</v>
+        <v>52208926.178</v>
       </c>
       <c r="H1375" t="inlineStr"/>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="n">
-        <v>52593873.503</v>
+        <v>52590301.503</v>
       </c>
       <c r="H1376" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="n">
-        <v>52813277.197</v>
+        <v>52809704.197</v>
       </c>
       <c r="H1377" t="inlineStr"/>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="n">
-        <v>54086188.568</v>
+        <v>54082615.568</v>
       </c>
       <c r="H1378" t="inlineStr"/>
     </row>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="F1450" t="inlineStr"/>
       <c r="G1450" t="n">
-        <v>50251234.976</v>
+        <v>50251414.976</v>
       </c>
       <c r="H1450" t="inlineStr"/>
     </row>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="n">
-        <v>56141362.43</v>
+        <v>56142263.43</v>
       </c>
       <c r="H1461" t="inlineStr"/>
     </row>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="F1463" t="inlineStr"/>
       <c r="G1463" t="n">
-        <v>56143504.367</v>
+        <v>56164903.367</v>
       </c>
       <c r="H1463" t="inlineStr"/>
     </row>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="F1464" t="inlineStr"/>
       <c r="G1464" t="n">
-        <v>55012509.993</v>
+        <v>55033908.993</v>
       </c>
       <c r="H1464" t="inlineStr"/>
     </row>
@@ -32220,7 +32220,7 @@
       </c>
       <c r="F1465" t="inlineStr"/>
       <c r="G1465" t="n">
-        <v>55438783.785</v>
+        <v>55457251.785</v>
       </c>
       <c r="H1465" t="inlineStr"/>
     </row>
@@ -32242,7 +32242,7 @@
       </c>
       <c r="F1466" t="inlineStr"/>
       <c r="G1466" t="n">
-        <v>56318661.518</v>
+        <v>56337129.518</v>
       </c>
       <c r="H1466" t="inlineStr"/>
     </row>
@@ -32264,7 +32264,7 @@
       </c>
       <c r="F1467" t="inlineStr"/>
       <c r="G1467" t="n">
-        <v>55328392.095</v>
+        <v>55346859.095</v>
       </c>
       <c r="H1467" t="inlineStr"/>
     </row>
@@ -32286,7 +32286,7 @@
       </c>
       <c r="F1468" t="inlineStr"/>
       <c r="G1468" t="n">
-        <v>54678857.736</v>
+        <v>54679758.736</v>
       </c>
       <c r="H1468" t="inlineStr"/>
     </row>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="F1469" t="inlineStr"/>
       <c r="G1469" t="n">
-        <v>54554995.54</v>
+        <v>54555897.54</v>
       </c>
       <c r="H1469" t="inlineStr"/>
     </row>
@@ -32330,7 +32330,7 @@
       </c>
       <c r="F1470" t="inlineStr"/>
       <c r="G1470" t="n">
-        <v>55262528.612</v>
+        <v>55263429.612</v>
       </c>
       <c r="H1470" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
       </c>
       <c r="F1471" t="inlineStr"/>
       <c r="G1471" t="n">
-        <v>55076848.123</v>
+        <v>55077749.123</v>
       </c>
       <c r="H1471" t="inlineStr"/>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="F1472" t="inlineStr"/>
       <c r="G1472" t="n">
-        <v>56287797.956</v>
+        <v>56288698.956</v>
       </c>
       <c r="H1472" t="inlineStr"/>
     </row>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="F1473" t="inlineStr"/>
       <c r="G1473" t="n">
-        <v>56126079.885</v>
+        <v>56126981.885</v>
       </c>
       <c r="H1473" t="inlineStr"/>
     </row>
@@ -32418,7 +32418,7 @@
       </c>
       <c r="F1474" t="inlineStr"/>
       <c r="G1474" t="n">
-        <v>57301353.778</v>
+        <v>57302255.778</v>
       </c>
       <c r="H1474" t="inlineStr"/>
     </row>
@@ -32440,7 +32440,7 @@
       </c>
       <c r="F1475" t="inlineStr"/>
       <c r="G1475" t="n">
-        <v>58732968.611</v>
+        <v>58733870.611</v>
       </c>
       <c r="H1475" t="inlineStr"/>
     </row>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="F1476" t="inlineStr"/>
       <c r="G1476" t="n">
-        <v>59890034.332</v>
+        <v>59890935.332</v>
       </c>
       <c r="H1476" t="inlineStr"/>
     </row>
@@ -32484,7 +32484,7 @@
       </c>
       <c r="F1477" t="inlineStr"/>
       <c r="G1477" t="n">
-        <v>60273228.984</v>
+        <v>60274130.984</v>
       </c>
       <c r="H1477" t="inlineStr"/>
     </row>
@@ -32506,7 +32506,7 @@
       </c>
       <c r="F1478" t="inlineStr"/>
       <c r="G1478" t="n">
-        <v>60798076.024</v>
+        <v>60798977.024</v>
       </c>
       <c r="H1478" t="inlineStr"/>
     </row>
@@ -32528,7 +32528,7 @@
       </c>
       <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="n">
-        <v>60725280.044</v>
+        <v>60726182.044</v>
       </c>
       <c r="H1479" t="inlineStr"/>
     </row>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="F1480" t="inlineStr"/>
       <c r="G1480" t="n">
-        <v>62880292.767</v>
+        <v>62881194.767</v>
       </c>
       <c r="H1480" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54601805.849</v>
+        <v>54500508.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54973955.591</v>
+        <v>54973662.591</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="n">
-        <v>56170105.145</v>
+        <v>56102392.145</v>
       </c>
       <c r="H1539" t="inlineStr"/>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="n">
-        <v>55844316.824</v>
+        <v>55839968.824</v>
       </c>
       <c r="H1540" t="inlineStr"/>
     </row>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="n">
-        <v>56021670.906</v>
+        <v>55927616.906</v>
       </c>
       <c r="H1541" t="inlineStr"/>
     </row>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60835690.977</v>
+        <v>60835773.977</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="n">
-        <v>56932950.529</v>
+        <v>56932829.446</v>
       </c>
       <c r="H1549" t="inlineStr"/>
     </row>
@@ -34098,7 +34098,7 @@
       </c>
       <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="n">
-        <v>55746722.146</v>
+        <v>55746749.443</v>
       </c>
       <c r="H1551" t="inlineStr"/>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="F1552" t="inlineStr"/>
       <c r="G1552" t="n">
-        <v>56286126.93</v>
+        <v>56286154.227</v>
       </c>
       <c r="H1552" t="inlineStr"/>
     </row>
@@ -34142,7 +34142,7 @@
       </c>
       <c r="F1553" t="inlineStr"/>
       <c r="G1553" t="n">
-        <v>55513912.448</v>
+        <v>55513939.745</v>
       </c>
       <c r="H1553" t="inlineStr"/>
     </row>
@@ -34164,7 +34164,7 @@
       </c>
       <c r="F1554" t="inlineStr"/>
       <c r="G1554" t="n">
-        <v>55095704.077</v>
+        <v>55095731.374</v>
       </c>
       <c r="H1554" t="inlineStr"/>
     </row>
@@ -34186,7 +34186,7 @@
       </c>
       <c r="F1555" t="inlineStr"/>
       <c r="G1555" t="n">
-        <v>55051697.811</v>
+        <v>55051725.108</v>
       </c>
       <c r="H1555" t="inlineStr"/>
     </row>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="F1556" t="inlineStr"/>
       <c r="G1556" t="n">
-        <v>54453196.744</v>
+        <v>54453224.041</v>
       </c>
       <c r="H1556" t="inlineStr"/>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="F1557" t="inlineStr"/>
       <c r="G1557" t="n">
-        <v>53873815.006</v>
+        <v>53873842.303</v>
       </c>
       <c r="H1557" t="inlineStr"/>
     </row>
@@ -34252,7 +34252,7 @@
       </c>
       <c r="F1558" t="inlineStr"/>
       <c r="G1558" t="n">
-        <v>54003574.358</v>
+        <v>54003601.655</v>
       </c>
       <c r="H1558" t="inlineStr"/>
     </row>
@@ -34274,7 +34274,7 @@
       </c>
       <c r="F1559" t="inlineStr"/>
       <c r="G1559" t="n">
-        <v>54427040.718</v>
+        <v>54427068.015</v>
       </c>
       <c r="H1559" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
       </c>
       <c r="F1560" t="inlineStr"/>
       <c r="G1560" t="n">
-        <v>55399054.415</v>
+        <v>55399081.712</v>
       </c>
       <c r="H1560" t="inlineStr"/>
     </row>
@@ -34318,7 +34318,7 @@
       </c>
       <c r="F1561" t="inlineStr"/>
       <c r="G1561" t="n">
-        <v>55806190.509</v>
+        <v>55806217.806</v>
       </c>
       <c r="H1561" t="inlineStr"/>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="F1562" t="inlineStr"/>
       <c r="G1562" t="n">
-        <v>58982974.598</v>
+        <v>58983001.895</v>
       </c>
       <c r="H1562" t="inlineStr"/>
     </row>
@@ -34364,7 +34364,7 @@
         <v>24.2</v>
       </c>
       <c r="G1563" t="n">
-        <v>62789430.647</v>
+        <v>62801770.695</v>
       </c>
       <c r="H1563" t="n">
         <v>2.6</v>
@@ -34388,7 +34388,7 @@
       </c>
       <c r="F1564" t="inlineStr"/>
       <c r="G1564" t="n">
-        <v>60734689.957</v>
+        <v>60730367.375</v>
       </c>
       <c r="H1564" t="inlineStr"/>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="F1565" t="inlineStr"/>
       <c r="G1565" t="n">
-        <v>60129263.279</v>
+        <v>60124939.697</v>
       </c>
       <c r="H1565" t="inlineStr"/>
     </row>
@@ -34432,7 +34432,7 @@
       </c>
       <c r="F1566" t="inlineStr"/>
       <c r="G1566" t="n">
-        <v>60048913.918</v>
+        <v>60065761.336</v>
       </c>
       <c r="H1566" t="inlineStr"/>
     </row>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="F1567" t="inlineStr"/>
       <c r="G1567" t="n">
-        <v>60760212.379</v>
+        <v>60734860.337</v>
       </c>
       <c r="H1567" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
       </c>
       <c r="F1568" t="inlineStr"/>
       <c r="G1568" t="n">
-        <v>58972403.37</v>
+        <v>59028553.546</v>
       </c>
       <c r="H1568" t="inlineStr"/>
     </row>
@@ -34498,7 +34498,7 @@
       </c>
       <c r="F1569" t="inlineStr"/>
       <c r="G1569" t="n">
-        <v>58204242.865</v>
+        <v>58186051.826</v>
       </c>
       <c r="H1569" t="inlineStr"/>
     </row>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="n">
-        <v>57715092.653</v>
+        <v>57654756.557</v>
       </c>
       <c r="H1570" t="inlineStr"/>
     </row>
@@ -34542,7 +34542,7 @@
       </c>
       <c r="F1571" t="inlineStr"/>
       <c r="G1571" t="n">
-        <v>57652407.262</v>
+        <v>57649493.53</v>
       </c>
       <c r="H1571" t="inlineStr"/>
     </row>
@@ -34563,15 +34563,21 @@
         <v>21.25</v>
       </c>
       <c r="F1572" t="inlineStr"/>
-      <c r="G1572" t="inlineStr"/>
+      <c r="G1572" t="n">
+        <v>57830265.248</v>
+      </c>
       <c r="H1572" t="inlineStr"/>
     </row>
     <row r="1573">
       <c r="A1573" s="1" t="n">
         <v>46157</v>
       </c>
-      <c r="B1573" t="inlineStr"/>
-      <c r="C1573" t="inlineStr"/>
+      <c r="B1573" t="n">
+        <v>46062</v>
+      </c>
+      <c r="C1573" t="n">
+        <v>41637331</v>
+      </c>
       <c r="D1573" t="n">
         <v>1418.57</v>
       </c>
@@ -34579,22 +34585,104 @@
         <v>21.125</v>
       </c>
       <c r="F1573" t="inlineStr"/>
-      <c r="G1573" t="inlineStr"/>
+      <c r="G1573" t="n">
+        <v>58036352.383</v>
+      </c>
       <c r="H1573" t="inlineStr"/>
     </row>
     <row r="1574">
       <c r="A1574" s="1" t="n">
         <v>46160</v>
       </c>
-      <c r="B1574" t="inlineStr"/>
-      <c r="C1574" t="inlineStr"/>
+      <c r="B1574" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C1574" t="n">
+        <v>41006735</v>
+      </c>
       <c r="D1574" t="n">
         <v>1416.31</v>
       </c>
-      <c r="E1574" t="inlineStr"/>
+      <c r="E1574" t="n">
+        <v>21.5</v>
+      </c>
       <c r="F1574" t="inlineStr"/>
-      <c r="G1574" t="inlineStr"/>
+      <c r="G1574" t="n">
+        <v>56599346.634</v>
+      </c>
       <c r="H1574" t="inlineStr"/>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B1575" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C1575" t="n">
+        <v>41284793</v>
+      </c>
+      <c r="D1575" t="n">
+        <v>1418.66</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1575" t="inlineStr"/>
+      <c r="G1575" t="n">
+        <v>56498947.538</v>
+      </c>
+      <c r="H1575" t="inlineStr"/>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B1576" t="n">
+        <v>46585</v>
+      </c>
+      <c r="C1576" t="n">
+        <v>40990233</v>
+      </c>
+      <c r="D1576" t="n">
+        <v>1420.88</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="F1576" t="inlineStr"/>
+      <c r="G1576" t="inlineStr"/>
+      <c r="H1576" t="inlineStr"/>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B1577" t="inlineStr"/>
+      <c r="C1577" t="inlineStr"/>
+      <c r="D1577" t="n">
+        <v>1411.66</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1577" t="inlineStr"/>
+      <c r="G1577" t="inlineStr"/>
+      <c r="H1577" t="inlineStr"/>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B1578" t="inlineStr"/>
+      <c r="C1578" t="inlineStr"/>
+      <c r="D1578" t="n">
+        <v>1419.74</v>
+      </c>
+      <c r="E1578" t="inlineStr"/>
+      <c r="F1578" t="inlineStr"/>
+      <c r="G1578" t="inlineStr"/>
+      <c r="H1578" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1578"/>
+  <dimension ref="A1:H1582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28964,7 +28964,7 @@
         <v>26.3</v>
       </c>
       <c r="G1317" t="n">
-        <v>51201565.522</v>
+        <v>51202643.522</v>
       </c>
       <c r="H1317" t="n">
         <v>2.8</v>
@@ -33088,7 +33088,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59045746.841</v>
+        <v>59044753.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58347319.213</v>
+        <v>58347447.213</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58580557.727</v>
+        <v>58573801.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59668358.587</v>
+        <v>59670261.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58035749.8</v>
+        <v>58037015.8</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57266544.786</v>
+        <v>57269578.786</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33220,7 +33220,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56146451.11</v>
+        <v>56151360.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56458709.744</v>
+        <v>56465283.744</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33264,7 +33264,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55874398.876</v>
+        <v>55882847.876</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33286,7 +33286,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55597047.143</v>
+        <v>55601466.143</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55629155.479</v>
+        <v>55635513.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55680056.733</v>
+        <v>55686435.733</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33352,7 +33352,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55250979.15</v>
+        <v>55258365.15</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33374,7 +33374,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55296106.162</v>
+        <v>55302210.162</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
       </c>
       <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="n">
-        <v>54718060.928</v>
+        <v>54724945.928</v>
       </c>
       <c r="H1519" t="inlineStr"/>
     </row>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="n">
-        <v>55618670.663</v>
+        <v>55626110.663</v>
       </c>
       <c r="H1520" t="inlineStr"/>
     </row>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57373715.612</v>
+        <v>57381756.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59184632.726</v>
+        <v>59177586.726</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58640696.442</v>
+        <v>58635329.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58668853.045</v>
+        <v>58664487.045</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59447406.107</v>
+        <v>59444514.107</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33588,7 +33588,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57848167.899</v>
+        <v>57845125.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57139035.668</v>
+        <v>57137889.668</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33632,7 +33632,7 @@
       </c>
       <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="n">
-        <v>56164902.566</v>
+        <v>56165900.566</v>
       </c>
       <c r="H1530" t="inlineStr"/>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="n">
-        <v>56051257.838</v>
+        <v>56053379.838</v>
       </c>
       <c r="H1531" t="inlineStr"/>
     </row>
@@ -33676,7 +33676,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55939032.807</v>
+        <v>55943253.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56227831.122</v>
+        <v>56231284.122</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55944273.807</v>
+        <v>55949091.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55094390.219</v>
+        <v>55099221.219</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="n">
-        <v>54545086.642</v>
+        <v>54550621.642</v>
       </c>
       <c r="H1536" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54500508.849</v>
+        <v>54505271.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54973662.591</v>
+        <v>54979263.591</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="n">
-        <v>56102392.145</v>
+        <v>56106413.145</v>
       </c>
       <c r="H1539" t="inlineStr"/>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="n">
-        <v>55839968.824</v>
+        <v>55843403.824</v>
       </c>
       <c r="H1540" t="inlineStr"/>
     </row>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="n">
-        <v>55927616.906</v>
+        <v>55925793.906</v>
       </c>
       <c r="H1541" t="inlineStr"/>
     </row>
@@ -33896,7 +33896,7 @@
       </c>
       <c r="F1542" t="inlineStr"/>
       <c r="G1542" t="n">
-        <v>58242796.582</v>
+        <v>58239848.582</v>
       </c>
       <c r="H1542" t="inlineStr"/>
     </row>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60835773.977</v>
+        <v>60849791.977</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -33944,7 +33944,7 @@
       </c>
       <c r="F1544" t="inlineStr"/>
       <c r="G1544" t="n">
-        <v>59401698.307</v>
+        <v>59401747.307</v>
       </c>
       <c r="H1544" t="inlineStr"/>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="F1545" t="inlineStr"/>
       <c r="G1545" t="n">
-        <v>58871252.314</v>
+        <v>58874426.314</v>
       </c>
       <c r="H1545" t="inlineStr"/>
     </row>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="n">
-        <v>58484690.356</v>
+        <v>58487054.356</v>
       </c>
       <c r="H1546" t="inlineStr"/>
     </row>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="F1547" t="inlineStr"/>
       <c r="G1547" t="n">
-        <v>58197953.536</v>
+        <v>58201446.536</v>
       </c>
       <c r="H1547" t="inlineStr"/>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="F1548" t="inlineStr"/>
       <c r="G1548" t="n">
-        <v>57476776.632</v>
+        <v>57481345.632</v>
       </c>
       <c r="H1548" t="inlineStr"/>
     </row>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="n">
-        <v>56932829.446</v>
+        <v>56939139.446</v>
       </c>
       <c r="H1549" t="inlineStr"/>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="F1550" t="inlineStr"/>
       <c r="G1550" t="n">
-        <v>55935247.207</v>
+        <v>55945330.207</v>
       </c>
       <c r="H1550" t="inlineStr"/>
     </row>
@@ -34098,7 +34098,7 @@
       </c>
       <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="n">
-        <v>55746749.443</v>
+        <v>55757380.443</v>
       </c>
       <c r="H1551" t="inlineStr"/>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="F1552" t="inlineStr"/>
       <c r="G1552" t="n">
-        <v>56286154.227</v>
+        <v>56293938.934</v>
       </c>
       <c r="H1552" t="inlineStr"/>
     </row>
@@ -34142,7 +34142,7 @@
       </c>
       <c r="F1553" t="inlineStr"/>
       <c r="G1553" t="n">
-        <v>55513939.745</v>
+        <v>55510660.762</v>
       </c>
       <c r="H1553" t="inlineStr"/>
     </row>
@@ -34164,7 +34164,7 @@
       </c>
       <c r="F1554" t="inlineStr"/>
       <c r="G1554" t="n">
-        <v>55095731.374</v>
+        <v>55092484.13</v>
       </c>
       <c r="H1554" t="inlineStr"/>
     </row>
@@ -34186,7 +34186,7 @@
       </c>
       <c r="F1555" t="inlineStr"/>
       <c r="G1555" t="n">
-        <v>55051725.108</v>
+        <v>55048487.313</v>
       </c>
       <c r="H1555" t="inlineStr"/>
     </row>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="F1556" t="inlineStr"/>
       <c r="G1556" t="n">
-        <v>54453224.041</v>
+        <v>54449986.246</v>
       </c>
       <c r="H1556" t="inlineStr"/>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="F1557" t="inlineStr"/>
       <c r="G1557" t="n">
-        <v>53873842.303</v>
+        <v>53870197.057</v>
       </c>
       <c r="H1557" t="inlineStr"/>
     </row>
@@ -34252,7 +34252,7 @@
       </c>
       <c r="F1558" t="inlineStr"/>
       <c r="G1558" t="n">
-        <v>54003601.655</v>
+        <v>53999813.573</v>
       </c>
       <c r="H1558" t="inlineStr"/>
     </row>
@@ -34274,7 +34274,7 @@
       </c>
       <c r="F1559" t="inlineStr"/>
       <c r="G1559" t="n">
-        <v>54427068.015</v>
+        <v>54422905.933</v>
       </c>
       <c r="H1559" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
       </c>
       <c r="F1560" t="inlineStr"/>
       <c r="G1560" t="n">
-        <v>55399081.712</v>
+        <v>55395293.63</v>
       </c>
       <c r="H1560" t="inlineStr"/>
     </row>
@@ -34318,7 +34318,7 @@
       </c>
       <c r="F1561" t="inlineStr"/>
       <c r="G1561" t="n">
-        <v>55806217.806</v>
+        <v>55802429.724</v>
       </c>
       <c r="H1561" t="inlineStr"/>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="F1562" t="inlineStr"/>
       <c r="G1562" t="n">
-        <v>58983001.895</v>
+        <v>58979213.813</v>
       </c>
       <c r="H1562" t="inlineStr"/>
     </row>
@@ -34364,7 +34364,7 @@
         <v>24.2</v>
       </c>
       <c r="G1563" t="n">
-        <v>62801770.695</v>
+        <v>63099801.838</v>
       </c>
       <c r="H1563" t="n">
         <v>2.6</v>
@@ -34388,7 +34388,7 @@
       </c>
       <c r="F1564" t="inlineStr"/>
       <c r="G1564" t="n">
-        <v>60730367.375</v>
+        <v>60730388.375</v>
       </c>
       <c r="H1564" t="inlineStr"/>
     </row>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="n">
-        <v>57654756.557</v>
+        <v>57620466.557</v>
       </c>
       <c r="H1570" t="inlineStr"/>
     </row>
@@ -34542,7 +34542,7 @@
       </c>
       <c r="F1571" t="inlineStr"/>
       <c r="G1571" t="n">
-        <v>57649493.53</v>
+        <v>57626042.9</v>
       </c>
       <c r="H1571" t="inlineStr"/>
     </row>
@@ -34564,7 +34564,7 @@
       </c>
       <c r="F1572" t="inlineStr"/>
       <c r="G1572" t="n">
-        <v>57830265.248</v>
+        <v>57692353.026</v>
       </c>
       <c r="H1572" t="inlineStr"/>
     </row>
@@ -34586,7 +34586,7 @@
       </c>
       <c r="F1573" t="inlineStr"/>
       <c r="G1573" t="n">
-        <v>58036352.383</v>
+        <v>58024078.6</v>
       </c>
       <c r="H1573" t="inlineStr"/>
     </row>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="F1574" t="inlineStr"/>
       <c r="G1574" t="n">
-        <v>56599346.634</v>
+        <v>56576697.718</v>
       </c>
       <c r="H1574" t="inlineStr"/>
     </row>
@@ -34630,7 +34630,7 @@
       </c>
       <c r="F1575" t="inlineStr"/>
       <c r="G1575" t="n">
-        <v>56498947.538</v>
+        <v>56526932.314</v>
       </c>
       <c r="H1575" t="inlineStr"/>
     </row>
@@ -34651,15 +34651,21 @@
         <v>21.25</v>
       </c>
       <c r="F1576" t="inlineStr"/>
-      <c r="G1576" t="inlineStr"/>
+      <c r="G1576" t="n">
+        <v>56548304.885</v>
+      </c>
       <c r="H1576" t="inlineStr"/>
     </row>
     <row r="1577">
       <c r="A1577" s="1" t="n">
         <v>46163</v>
       </c>
-      <c r="B1577" t="inlineStr"/>
-      <c r="C1577" t="inlineStr"/>
+      <c r="B1577" t="n">
+        <v>46748</v>
+      </c>
+      <c r="C1577" t="n">
+        <v>41162596</v>
+      </c>
       <c r="D1577" t="n">
         <v>1411.66</v>
       </c>
@@ -34667,22 +34673,104 @@
         <v>22</v>
       </c>
       <c r="F1577" t="inlineStr"/>
-      <c r="G1577" t="inlineStr"/>
+      <c r="G1577" t="n">
+        <v>56660288.304</v>
+      </c>
       <c r="H1577" t="inlineStr"/>
     </row>
     <row r="1578">
       <c r="A1578" s="1" t="n">
         <v>46164</v>
       </c>
-      <c r="B1578" t="inlineStr"/>
-      <c r="C1578" t="inlineStr"/>
+      <c r="B1578" t="n">
+        <v>46806</v>
+      </c>
+      <c r="C1578" t="n">
+        <v>40812053</v>
+      </c>
       <c r="D1578" t="n">
         <v>1419.74</v>
       </c>
-      <c r="E1578" t="inlineStr"/>
+      <c r="E1578" t="n">
+        <v>22</v>
+      </c>
       <c r="F1578" t="inlineStr"/>
-      <c r="G1578" t="inlineStr"/>
+      <c r="G1578" t="n">
+        <v>56391024.468</v>
+      </c>
       <c r="H1578" t="inlineStr"/>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B1579" t="n">
+        <v>47909</v>
+      </c>
+      <c r="C1579" t="n">
+        <v>41837112</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>1428.9</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>21.5625</v>
+      </c>
+      <c r="F1579" t="inlineStr"/>
+      <c r="G1579" t="n">
+        <v>56999460.078</v>
+      </c>
+      <c r="H1579" t="inlineStr"/>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B1580" t="n">
+        <v>47874</v>
+      </c>
+      <c r="C1580" t="n">
+        <v>41922477</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>1429.9</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>20.6875</v>
+      </c>
+      <c r="F1580" t="inlineStr"/>
+      <c r="G1580" t="inlineStr"/>
+      <c r="H1580" t="inlineStr"/>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B1581" t="inlineStr"/>
+      <c r="C1581" t="inlineStr"/>
+      <c r="D1581" t="n">
+        <v>1430.45</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>21.9375</v>
+      </c>
+      <c r="F1581" t="inlineStr"/>
+      <c r="G1581" t="inlineStr"/>
+      <c r="H1581" t="inlineStr"/>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B1582" t="inlineStr"/>
+      <c r="C1582" t="inlineStr"/>
+      <c r="D1582" t="n">
+        <v>1431.57</v>
+      </c>
+      <c r="E1582" t="inlineStr"/>
+      <c r="F1582" t="inlineStr"/>
+      <c r="G1582" t="inlineStr"/>
+      <c r="H1582" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1582"/>
+  <dimension ref="A1:H1588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28964,7 +28964,7 @@
         <v>26.3</v>
       </c>
       <c r="G1317" t="n">
-        <v>51202643.522</v>
+        <v>51201565.522</v>
       </c>
       <c r="H1317" t="n">
         <v>2.8</v>
@@ -32610,7 +32610,7 @@
       </c>
       <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="n">
-        <v>64608617.281</v>
+        <v>64612279.281</v>
       </c>
       <c r="H1483" t="inlineStr"/>
     </row>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61896799.993</v>
+        <v>61896822.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61214486.519</v>
+        <v>61214488.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61749834.076</v>
+        <v>61746796.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32698,7 +32698,7 @@
       </c>
       <c r="F1487" t="inlineStr"/>
       <c r="G1487" t="n">
-        <v>60510718.004</v>
+        <v>60510736.004</v>
       </c>
       <c r="H1487" t="inlineStr"/>
     </row>
@@ -32720,7 +32720,7 @@
       </c>
       <c r="F1488" t="inlineStr"/>
       <c r="G1488" t="n">
-        <v>59556992.211</v>
+        <v>59557006.211</v>
       </c>
       <c r="H1488" t="inlineStr"/>
     </row>
@@ -32742,7 +32742,7 @@
       </c>
       <c r="F1489" t="inlineStr"/>
       <c r="G1489" t="n">
-        <v>57835501.381</v>
+        <v>57835851.381</v>
       </c>
       <c r="H1489" t="inlineStr"/>
     </row>
@@ -32764,7 +32764,7 @@
       </c>
       <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="n">
-        <v>57244186.101</v>
+        <v>57244504.101</v>
       </c>
       <c r="H1490" t="inlineStr"/>
     </row>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="n">
-        <v>57172137.244</v>
+        <v>57172449.244</v>
       </c>
       <c r="H1491" t="inlineStr"/>
     </row>
@@ -32808,7 +32808,7 @@
       </c>
       <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="n">
-        <v>57600120.399</v>
+        <v>57600421.399</v>
       </c>
       <c r="H1492" t="inlineStr"/>
     </row>
@@ -32830,7 +32830,7 @@
       </c>
       <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="n">
-        <v>56274497.088</v>
+        <v>56274804.088</v>
       </c>
       <c r="H1493" t="inlineStr"/>
     </row>
@@ -32852,7 +32852,7 @@
       </c>
       <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="n">
-        <v>55651584.47</v>
+        <v>55651580.47</v>
       </c>
       <c r="H1494" t="inlineStr"/>
     </row>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="n">
-        <v>55478033.492</v>
+        <v>55478031.492</v>
       </c>
       <c r="H1495" t="inlineStr"/>
     </row>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55307347.796</v>
+        <v>55307343.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="n">
-        <v>55070080.613</v>
+        <v>55070076.613</v>
       </c>
       <c r="H1497" t="inlineStr"/>
     </row>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="n">
-        <v>54770654.758</v>
+        <v>54770646.758</v>
       </c>
       <c r="H1498" t="inlineStr"/>
     </row>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54925883.349</v>
+        <v>54925875.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -32984,7 +32984,7 @@
       </c>
       <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="n">
-        <v>55180322.773</v>
+        <v>55180316.773</v>
       </c>
       <c r="H1500" t="inlineStr"/>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="n">
-        <v>55936001.062</v>
+        <v>55935996.062</v>
       </c>
       <c r="H1501" t="inlineStr"/>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="n">
-        <v>57630872.416</v>
+        <v>57630894.416</v>
       </c>
       <c r="H1502" t="inlineStr"/>
     </row>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60378787.102</v>
+        <v>60377527.102</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60849791.977</v>
+        <v>60848675.977</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -34274,7 +34274,7 @@
       </c>
       <c r="F1559" t="inlineStr"/>
       <c r="G1559" t="n">
-        <v>54422905.933</v>
+        <v>54422383.702</v>
       </c>
       <c r="H1559" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
       </c>
       <c r="F1560" t="inlineStr"/>
       <c r="G1560" t="n">
-        <v>55395293.63</v>
+        <v>55394850.514</v>
       </c>
       <c r="H1560" t="inlineStr"/>
     </row>
@@ -34318,7 +34318,7 @@
       </c>
       <c r="F1561" t="inlineStr"/>
       <c r="G1561" t="n">
-        <v>55802429.724</v>
+        <v>55801821.608</v>
       </c>
       <c r="H1561" t="inlineStr"/>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="F1562" t="inlineStr"/>
       <c r="G1562" t="n">
-        <v>58979213.813</v>
+        <v>58993120.116</v>
       </c>
       <c r="H1562" t="inlineStr"/>
     </row>
@@ -34364,7 +34364,7 @@
         <v>24.2</v>
       </c>
       <c r="G1563" t="n">
-        <v>63099801.838</v>
+        <v>63101673.437</v>
       </c>
       <c r="H1563" t="n">
         <v>2.6</v>
@@ -34388,7 +34388,7 @@
       </c>
       <c r="F1564" t="inlineStr"/>
       <c r="G1564" t="n">
-        <v>60730388.375</v>
+        <v>60730926.828</v>
       </c>
       <c r="H1564" t="inlineStr"/>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="F1565" t="inlineStr"/>
       <c r="G1565" t="n">
-        <v>60124939.697</v>
+        <v>60125037.987</v>
       </c>
       <c r="H1565" t="inlineStr"/>
     </row>
@@ -34432,7 +34432,7 @@
       </c>
       <c r="F1566" t="inlineStr"/>
       <c r="G1566" t="n">
-        <v>60065761.336</v>
+        <v>60065858.626</v>
       </c>
       <c r="H1566" t="inlineStr"/>
     </row>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="F1567" t="inlineStr"/>
       <c r="G1567" t="n">
-        <v>60734860.337</v>
+        <v>60734957.627</v>
       </c>
       <c r="H1567" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
       </c>
       <c r="F1568" t="inlineStr"/>
       <c r="G1568" t="n">
-        <v>59028553.546</v>
+        <v>59028650.836</v>
       </c>
       <c r="H1568" t="inlineStr"/>
     </row>
@@ -34498,7 +34498,7 @@
       </c>
       <c r="F1569" t="inlineStr"/>
       <c r="G1569" t="n">
-        <v>58186051.826</v>
+        <v>58186149.116</v>
       </c>
       <c r="H1569" t="inlineStr"/>
     </row>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="n">
-        <v>57620466.557</v>
+        <v>57620563.847</v>
       </c>
       <c r="H1570" t="inlineStr"/>
     </row>
@@ -34542,7 +34542,7 @@
       </c>
       <c r="F1571" t="inlineStr"/>
       <c r="G1571" t="n">
-        <v>57626042.9</v>
+        <v>57626140.19</v>
       </c>
       <c r="H1571" t="inlineStr"/>
     </row>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="F1574" t="inlineStr"/>
       <c r="G1574" t="n">
-        <v>56576697.718</v>
+        <v>56575494.718</v>
       </c>
       <c r="H1574" t="inlineStr"/>
     </row>
@@ -34630,7 +34630,7 @@
       </c>
       <c r="F1575" t="inlineStr"/>
       <c r="G1575" t="n">
-        <v>56526932.314</v>
+        <v>56516777.683</v>
       </c>
       <c r="H1575" t="inlineStr"/>
     </row>
@@ -34652,7 +34652,7 @@
       </c>
       <c r="F1576" t="inlineStr"/>
       <c r="G1576" t="n">
-        <v>56548304.885</v>
+        <v>56520085.473</v>
       </c>
       <c r="H1576" t="inlineStr"/>
     </row>
@@ -34674,7 +34674,7 @@
       </c>
       <c r="F1577" t="inlineStr"/>
       <c r="G1577" t="n">
-        <v>56660288.304</v>
+        <v>56614291.751</v>
       </c>
       <c r="H1577" t="inlineStr"/>
     </row>
@@ -34696,7 +34696,7 @@
       </c>
       <c r="F1578" t="inlineStr"/>
       <c r="G1578" t="n">
-        <v>56391024.468</v>
+        <v>56497098.527</v>
       </c>
       <c r="H1578" t="inlineStr"/>
     </row>
@@ -34718,7 +34718,7 @@
       </c>
       <c r="F1579" t="inlineStr"/>
       <c r="G1579" t="n">
-        <v>56999460.078</v>
+        <v>57014645.328</v>
       </c>
       <c r="H1579" t="inlineStr"/>
     </row>
@@ -34739,15 +34739,21 @@
         <v>20.6875</v>
       </c>
       <c r="F1580" t="inlineStr"/>
-      <c r="G1580" t="inlineStr"/>
+      <c r="G1580" t="n">
+        <v>57904727.253</v>
+      </c>
       <c r="H1580" t="inlineStr"/>
     </row>
     <row r="1581">
       <c r="A1581" s="1" t="n">
         <v>46170</v>
       </c>
-      <c r="B1581" t="inlineStr"/>
-      <c r="C1581" t="inlineStr"/>
+      <c r="B1581" t="n">
+        <v>48113</v>
+      </c>
+      <c r="C1581" t="n">
+        <v>42303192</v>
+      </c>
       <c r="D1581" t="n">
         <v>1430.45</v>
       </c>
@@ -34755,22 +34761,140 @@
         <v>21.9375</v>
       </c>
       <c r="F1581" t="inlineStr"/>
-      <c r="G1581" t="inlineStr"/>
+      <c r="G1581" t="n">
+        <v>59936655.953</v>
+      </c>
       <c r="H1581" t="inlineStr"/>
     </row>
     <row r="1582">
       <c r="A1582" s="1" t="n">
         <v>46171</v>
       </c>
-      <c r="B1582" t="inlineStr"/>
-      <c r="C1582" t="inlineStr"/>
+      <c r="B1582" t="n">
+        <v>48193</v>
+      </c>
+      <c r="C1582" t="n">
+        <v>41975464</v>
+      </c>
       <c r="D1582" t="n">
         <v>1431.57</v>
       </c>
-      <c r="E1582" t="inlineStr"/>
+      <c r="E1582" t="n">
+        <v>20.625</v>
+      </c>
       <c r="F1582" t="inlineStr"/>
-      <c r="G1582" t="inlineStr"/>
+      <c r="G1582" t="n">
+        <v>63046049.566</v>
+      </c>
       <c r="H1582" t="inlineStr"/>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B1583" t="inlineStr"/>
+      <c r="C1583" t="inlineStr"/>
+      <c r="D1583" t="inlineStr"/>
+      <c r="E1583" t="inlineStr"/>
+      <c r="F1583" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G1583" t="inlineStr"/>
+      <c r="H1583" t="inlineStr"/>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B1584" t="n">
+        <v>48362</v>
+      </c>
+      <c r="C1584" t="n">
+        <v>43177866</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>1444.58</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>20.8125</v>
+      </c>
+      <c r="F1584" t="inlineStr"/>
+      <c r="G1584" t="n">
+        <v>62058011.211</v>
+      </c>
+      <c r="H1584" t="inlineStr"/>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B1585" t="n">
+        <v>48430</v>
+      </c>
+      <c r="C1585" t="n">
+        <v>42960824</v>
+      </c>
+      <c r="D1585" t="n">
+        <v>1448.79</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>21.6875</v>
+      </c>
+      <c r="F1585" t="inlineStr"/>
+      <c r="G1585" t="n">
+        <v>62126067.903</v>
+      </c>
+      <c r="H1585" t="inlineStr"/>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B1586" t="n">
+        <v>48414</v>
+      </c>
+      <c r="C1586" t="n">
+        <v>42215553</v>
+      </c>
+      <c r="D1586" t="n">
+        <v>1459.69</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1586" t="inlineStr"/>
+      <c r="G1586" t="inlineStr"/>
+      <c r="H1586" t="inlineStr"/>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B1587" t="inlineStr"/>
+      <c r="C1587" t="inlineStr"/>
+      <c r="D1587" t="n">
+        <v>1458.02</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>21.0625</v>
+      </c>
+      <c r="F1587" t="inlineStr"/>
+      <c r="G1587" t="inlineStr"/>
+      <c r="H1587" t="inlineStr"/>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B1588" t="inlineStr"/>
+      <c r="C1588" t="inlineStr"/>
+      <c r="D1588" t="n">
+        <v>1462.88</v>
+      </c>
+      <c r="E1588" t="inlineStr"/>
+      <c r="F1588" t="inlineStr"/>
+      <c r="G1588" t="inlineStr"/>
+      <c r="H1588" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1588"/>
+  <dimension ref="A1:H1593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Variación mensual del índice de precios al consumidor</t>
+          <t>Inflación mensual.</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.29</v>
+        <v>108.48</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.48</v>
+        <v>108.61</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.61</v>
+        <v>108.63</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.63</v>
+        <v>108.72</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.72</v>
+        <v>108.86</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.86</v>
+        <v>108.96</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.96</v>
+        <v>108.97</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>108.97</v>
+        <v>109.05</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.05</v>
+        <v>109.11</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.11</v>
+        <v>109.21</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.21</v>
+        <v>109.46</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.46</v>
+        <v>109.64</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.64</v>
+        <v>109.67</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.67</v>
+        <v>109.71</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.71</v>
+        <v>109.79</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>109.79</v>
+        <v>110.08</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.08</v>
+        <v>110.11</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.11</v>
+        <v>110.15</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.15</v>
+        <v>110.5</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.5</v>
+        <v>110.68</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.68</v>
+        <v>110.71</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.71</v>
+        <v>110.75</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.75</v>
+        <v>110.92</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>110.92</v>
+        <v>111.37</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.37</v>
+        <v>111.46</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.46</v>
+        <v>111.49</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.49</v>
+        <v>111.52</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.52</v>
+        <v>111.59</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.59</v>
+        <v>111.67</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>111.67</v>
+        <v>112.01</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.01</v>
+        <v>112.17</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.17</v>
+        <v>112.21</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.21</v>
+        <v>112.24</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.24</v>
+        <v>112.48</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.48</v>
+        <v>112.71</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.71</v>
+        <v>112.8</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.8</v>
+        <v>112.83</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.83</v>
+        <v>112.89</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.89</v>
+        <v>112.95</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58635329.442</v>
+        <v>58635334.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58664487.045</v>
+        <v>58664488.045</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59444514.107</v>
+        <v>59444502.107</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33588,7 +33588,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57845125.899</v>
+        <v>57845133.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57137889.668</v>
+        <v>57137896.668</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33632,7 +33632,7 @@
       </c>
       <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="n">
-        <v>56165900.566</v>
+        <v>56165913.566</v>
       </c>
       <c r="H1530" t="inlineStr"/>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="n">
-        <v>56053379.838</v>
+        <v>56053389.838</v>
       </c>
       <c r="H1531" t="inlineStr"/>
     </row>
@@ -33676,7 +33676,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55943253.807</v>
+        <v>55943263.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56231284.122</v>
+        <v>56231299.122</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55949091.807</v>
+        <v>55949101.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55099221.219</v>
+        <v>55099236.219</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="n">
-        <v>54550621.642</v>
+        <v>54550632.642</v>
       </c>
       <c r="H1536" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54505271.849</v>
+        <v>54505274.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54979263.591</v>
+        <v>54979265.591</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="n">
-        <v>56106413.145</v>
+        <v>56106414.145</v>
       </c>
       <c r="H1539" t="inlineStr"/>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="n">
-        <v>55843403.824</v>
+        <v>55843411.824</v>
       </c>
       <c r="H1540" t="inlineStr"/>
     </row>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="n">
-        <v>55925793.906</v>
+        <v>55925797.906</v>
       </c>
       <c r="H1541" t="inlineStr"/>
     </row>
@@ -33896,7 +33896,7 @@
       </c>
       <c r="F1542" t="inlineStr"/>
       <c r="G1542" t="n">
-        <v>58239848.582</v>
+        <v>58239872.582</v>
       </c>
       <c r="H1542" t="inlineStr"/>
     </row>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60848675.977</v>
+        <v>60853987.977</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -33944,7 +33944,7 @@
       </c>
       <c r="F1544" t="inlineStr"/>
       <c r="G1544" t="n">
-        <v>59401747.307</v>
+        <v>59401779.307</v>
       </c>
       <c r="H1544" t="inlineStr"/>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="F1545" t="inlineStr"/>
       <c r="G1545" t="n">
-        <v>58874426.314</v>
+        <v>58874480.314</v>
       </c>
       <c r="H1545" t="inlineStr"/>
     </row>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="n">
-        <v>58487054.356</v>
+        <v>58487697.356</v>
       </c>
       <c r="H1546" t="inlineStr"/>
     </row>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="F1547" t="inlineStr"/>
       <c r="G1547" t="n">
-        <v>58201446.536</v>
+        <v>58201620.536</v>
       </c>
       <c r="H1547" t="inlineStr"/>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="F1548" t="inlineStr"/>
       <c r="G1548" t="n">
-        <v>57481345.632</v>
+        <v>57482687.632</v>
       </c>
       <c r="H1548" t="inlineStr"/>
     </row>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="n">
-        <v>56939139.446</v>
+        <v>56939398.446</v>
       </c>
       <c r="H1549" t="inlineStr"/>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="F1550" t="inlineStr"/>
       <c r="G1550" t="n">
-        <v>55945330.207</v>
+        <v>55945549.207</v>
       </c>
       <c r="H1550" t="inlineStr"/>
     </row>
@@ -34098,7 +34098,7 @@
       </c>
       <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="n">
-        <v>55757380.443</v>
+        <v>55757409.443</v>
       </c>
       <c r="H1551" t="inlineStr"/>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="F1552" t="inlineStr"/>
       <c r="G1552" t="n">
-        <v>56293938.934</v>
+        <v>56295795.934</v>
       </c>
       <c r="H1552" t="inlineStr"/>
     </row>
@@ -34142,7 +34142,7 @@
       </c>
       <c r="F1553" t="inlineStr"/>
       <c r="G1553" t="n">
-        <v>55510660.762</v>
+        <v>55510675.762</v>
       </c>
       <c r="H1553" t="inlineStr"/>
     </row>
@@ -34164,7 +34164,7 @@
       </c>
       <c r="F1554" t="inlineStr"/>
       <c r="G1554" t="n">
-        <v>55092484.13</v>
+        <v>55092599.13</v>
       </c>
       <c r="H1554" t="inlineStr"/>
     </row>
@@ -34186,7 +34186,7 @@
       </c>
       <c r="F1555" t="inlineStr"/>
       <c r="G1555" t="n">
-        <v>55048487.313</v>
+        <v>55049779.313</v>
       </c>
       <c r="H1555" t="inlineStr"/>
     </row>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="F1556" t="inlineStr"/>
       <c r="G1556" t="n">
-        <v>54449986.246</v>
+        <v>54450051.246</v>
       </c>
       <c r="H1556" t="inlineStr"/>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="F1557" t="inlineStr"/>
       <c r="G1557" t="n">
-        <v>53870197.057</v>
+        <v>53870230.057</v>
       </c>
       <c r="H1557" t="inlineStr"/>
     </row>
@@ -34252,7 +34252,7 @@
       </c>
       <c r="F1558" t="inlineStr"/>
       <c r="G1558" t="n">
-        <v>53999813.573</v>
+        <v>53999906.573</v>
       </c>
       <c r="H1558" t="inlineStr"/>
     </row>
@@ -34274,7 +34274,7 @@
       </c>
       <c r="F1559" t="inlineStr"/>
       <c r="G1559" t="n">
-        <v>54422383.702</v>
+        <v>54422370.702</v>
       </c>
       <c r="H1559" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
       </c>
       <c r="F1560" t="inlineStr"/>
       <c r="G1560" t="n">
-        <v>55394850.514</v>
+        <v>55394852.514</v>
       </c>
       <c r="H1560" t="inlineStr"/>
     </row>
@@ -34318,7 +34318,7 @@
       </c>
       <c r="F1561" t="inlineStr"/>
       <c r="G1561" t="n">
-        <v>55801821.608</v>
+        <v>55801851.608</v>
       </c>
       <c r="H1561" t="inlineStr"/>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="F1562" t="inlineStr"/>
       <c r="G1562" t="n">
-        <v>58993120.116</v>
+        <v>58993125.116</v>
       </c>
       <c r="H1562" t="inlineStr"/>
     </row>
@@ -34364,7 +34364,7 @@
         <v>24.2</v>
       </c>
       <c r="G1563" t="n">
-        <v>63101673.437</v>
+        <v>62700673.437</v>
       </c>
       <c r="H1563" t="n">
         <v>2.6</v>
@@ -34432,7 +34432,7 @@
       </c>
       <c r="F1566" t="inlineStr"/>
       <c r="G1566" t="n">
-        <v>60065858.626</v>
+        <v>60065942.457</v>
       </c>
       <c r="H1566" t="inlineStr"/>
     </row>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="F1567" t="inlineStr"/>
       <c r="G1567" t="n">
-        <v>60734957.627</v>
+        <v>60734349.321</v>
       </c>
       <c r="H1567" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
       </c>
       <c r="F1568" t="inlineStr"/>
       <c r="G1568" t="n">
-        <v>59028650.836</v>
+        <v>59028098.089</v>
       </c>
       <c r="H1568" t="inlineStr"/>
     </row>
@@ -34498,7 +34498,7 @@
       </c>
       <c r="F1569" t="inlineStr"/>
       <c r="G1569" t="n">
-        <v>58186149.116</v>
+        <v>58185666.149</v>
       </c>
       <c r="H1569" t="inlineStr"/>
     </row>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="n">
-        <v>57620563.847</v>
+        <v>57619910.887</v>
       </c>
       <c r="H1570" t="inlineStr"/>
     </row>
@@ -34542,7 +34542,7 @@
       </c>
       <c r="F1571" t="inlineStr"/>
       <c r="G1571" t="n">
-        <v>57626140.19</v>
+        <v>57625175.677</v>
       </c>
       <c r="H1571" t="inlineStr"/>
     </row>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="F1574" t="inlineStr"/>
       <c r="G1574" t="n">
-        <v>56575494.718</v>
+        <v>56568492.718</v>
       </c>
       <c r="H1574" t="inlineStr"/>
     </row>
@@ -34630,7 +34630,7 @@
       </c>
       <c r="F1575" t="inlineStr"/>
       <c r="G1575" t="n">
-        <v>56516777.683</v>
+        <v>56515467.683</v>
       </c>
       <c r="H1575" t="inlineStr"/>
     </row>
@@ -34652,7 +34652,7 @@
       </c>
       <c r="F1576" t="inlineStr"/>
       <c r="G1576" t="n">
-        <v>56520085.473</v>
+        <v>56518765.473</v>
       </c>
       <c r="H1576" t="inlineStr"/>
     </row>
@@ -34674,7 +34674,7 @@
       </c>
       <c r="F1577" t="inlineStr"/>
       <c r="G1577" t="n">
-        <v>56614291.751</v>
+        <v>56614292.751</v>
       </c>
       <c r="H1577" t="inlineStr"/>
     </row>
@@ -34696,7 +34696,7 @@
       </c>
       <c r="F1578" t="inlineStr"/>
       <c r="G1578" t="n">
-        <v>56497098.527</v>
+        <v>56497100.527</v>
       </c>
       <c r="H1578" t="inlineStr"/>
     </row>
@@ -34718,7 +34718,7 @@
       </c>
       <c r="F1579" t="inlineStr"/>
       <c r="G1579" t="n">
-        <v>57014645.328</v>
+        <v>57013546.328</v>
       </c>
       <c r="H1579" t="inlineStr"/>
     </row>
@@ -34740,7 +34740,7 @@
       </c>
       <c r="F1580" t="inlineStr"/>
       <c r="G1580" t="n">
-        <v>57904727.253</v>
+        <v>57903916.253</v>
       </c>
       <c r="H1580" t="inlineStr"/>
     </row>
@@ -34762,7 +34762,7 @@
       </c>
       <c r="F1581" t="inlineStr"/>
       <c r="G1581" t="n">
-        <v>59936655.953</v>
+        <v>59896735.035</v>
       </c>
       <c r="H1581" t="inlineStr"/>
     </row>
@@ -34784,7 +34784,7 @@
       </c>
       <c r="F1582" t="inlineStr"/>
       <c r="G1582" t="n">
-        <v>63046049.566</v>
+        <v>63009605.598</v>
       </c>
       <c r="H1582" t="inlineStr"/>
     </row>
@@ -34800,7 +34800,9 @@
         <v>23.3</v>
       </c>
       <c r="G1583" t="inlineStr"/>
-      <c r="H1583" t="inlineStr"/>
+      <c r="H1583" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="1584">
       <c r="A1584" s="1" t="n">
@@ -34820,7 +34822,7 @@
       </c>
       <c r="F1584" t="inlineStr"/>
       <c r="G1584" t="n">
-        <v>62058011.211</v>
+        <v>62211472.5</v>
       </c>
       <c r="H1584" t="inlineStr"/>
     </row>
@@ -34842,7 +34844,7 @@
       </c>
       <c r="F1585" t="inlineStr"/>
       <c r="G1585" t="n">
-        <v>62126067.903</v>
+        <v>62243940.556</v>
       </c>
       <c r="H1585" t="inlineStr"/>
     </row>
@@ -34863,15 +34865,21 @@
         <v>21</v>
       </c>
       <c r="F1586" t="inlineStr"/>
-      <c r="G1586" t="inlineStr"/>
+      <c r="G1586" t="n">
+        <v>62058212.549</v>
+      </c>
       <c r="H1586" t="inlineStr"/>
     </row>
     <row r="1587">
       <c r="A1587" s="1" t="n">
         <v>46177</v>
       </c>
-      <c r="B1587" t="inlineStr"/>
-      <c r="C1587" t="inlineStr"/>
+      <c r="B1587" t="n">
+        <v>48372</v>
+      </c>
+      <c r="C1587" t="n">
+        <v>42354469</v>
+      </c>
       <c r="D1587" t="n">
         <v>1458.02</v>
       </c>
@@ -34879,22 +34887,126 @@
         <v>21.0625</v>
       </c>
       <c r="F1587" t="inlineStr"/>
-      <c r="G1587" t="inlineStr"/>
+      <c r="G1587" t="n">
+        <v>62834794.635</v>
+      </c>
       <c r="H1587" t="inlineStr"/>
     </row>
     <row r="1588">
       <c r="A1588" s="1" t="n">
         <v>46178</v>
       </c>
-      <c r="B1588" t="inlineStr"/>
-      <c r="C1588" t="inlineStr"/>
+      <c r="B1588" t="n">
+        <v>47867</v>
+      </c>
+      <c r="C1588" t="n">
+        <v>42506211</v>
+      </c>
       <c r="D1588" t="n">
         <v>1462.88</v>
       </c>
-      <c r="E1588" t="inlineStr"/>
+      <c r="E1588" t="n">
+        <v>19.75</v>
+      </c>
       <c r="F1588" t="inlineStr"/>
-      <c r="G1588" t="inlineStr"/>
+      <c r="G1588" t="n">
+        <v>61618792.47</v>
+      </c>
       <c r="H1588" t="inlineStr"/>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B1589" t="n">
+        <v>47800</v>
+      </c>
+      <c r="C1589" t="n">
+        <v>42401196</v>
+      </c>
+      <c r="D1589" t="n">
+        <v>1464.3</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>19.875</v>
+      </c>
+      <c r="F1589" t="inlineStr"/>
+      <c r="G1589" t="n">
+        <v>60972086.633</v>
+      </c>
+      <c r="H1589" t="inlineStr"/>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B1590" t="n">
+        <v>47834</v>
+      </c>
+      <c r="C1590" t="n">
+        <v>41830730</v>
+      </c>
+      <c r="D1590" t="n">
+        <v>1463.83</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>20.375</v>
+      </c>
+      <c r="F1590" t="inlineStr"/>
+      <c r="G1590" t="n">
+        <v>60781694.954</v>
+      </c>
+      <c r="H1590" t="inlineStr"/>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B1591" t="n">
+        <v>47559</v>
+      </c>
+      <c r="C1591" t="n">
+        <v>41998049</v>
+      </c>
+      <c r="D1591" t="n">
+        <v>1460.67</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>19.6875</v>
+      </c>
+      <c r="F1591" t="inlineStr"/>
+      <c r="G1591" t="inlineStr"/>
+      <c r="H1591" t="inlineStr"/>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B1592" t="inlineStr"/>
+      <c r="C1592" t="inlineStr"/>
+      <c r="D1592" t="n">
+        <v>1453.6</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>20.1875</v>
+      </c>
+      <c r="F1592" t="inlineStr"/>
+      <c r="G1592" t="inlineStr"/>
+      <c r="H1592" t="inlineStr"/>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B1593" t="inlineStr"/>
+      <c r="C1593" t="inlineStr"/>
+      <c r="D1593" t="n">
+        <v>1452.55</v>
+      </c>
+      <c r="E1593" t="inlineStr"/>
+      <c r="F1593" t="inlineStr"/>
+      <c r="G1593" t="inlineStr"/>
+      <c r="H1593" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1593"/>
+  <dimension ref="A1:H1597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.48</v>
+        <v>108.29</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.61</v>
+        <v>108.48</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.63</v>
+        <v>108.61</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.72</v>
+        <v>108.63</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.86</v>
+        <v>108.72</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.96</v>
+        <v>108.86</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.97</v>
+        <v>108.96</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>109.05</v>
+        <v>108.97</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.11</v>
+        <v>109.05</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.21</v>
+        <v>109.11</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.46</v>
+        <v>109.21</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.64</v>
+        <v>109.46</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.67</v>
+        <v>109.64</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.71</v>
+        <v>109.67</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.79</v>
+        <v>109.71</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>110.08</v>
+        <v>109.79</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.11</v>
+        <v>110.08</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.15</v>
+        <v>110.11</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.5</v>
+        <v>110.15</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.68</v>
+        <v>110.5</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.71</v>
+        <v>110.68</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.92</v>
+        <v>110.75</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>111.37</v>
+        <v>110.92</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.46</v>
+        <v>111.37</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.49</v>
+        <v>111.46</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.52</v>
+        <v>111.49</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.59</v>
+        <v>111.52</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.67</v>
+        <v>111.59</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>112.01</v>
+        <v>111.67</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.17</v>
+        <v>112.01</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.21</v>
+        <v>112.17</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.24</v>
+        <v>112.21</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.48</v>
+        <v>112.24</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.71</v>
+        <v>112.48</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.8</v>
+        <v>112.71</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.83</v>
+        <v>112.8</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.89</v>
+        <v>112.83</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.95</v>
+        <v>112.89</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -34364,7 +34364,7 @@
         <v>24.2</v>
       </c>
       <c r="G1563" t="n">
-        <v>62700673.437</v>
+        <v>62700673.443</v>
       </c>
       <c r="H1563" t="n">
         <v>2.6</v>
@@ -34762,7 +34762,7 @@
       </c>
       <c r="F1581" t="inlineStr"/>
       <c r="G1581" t="n">
-        <v>59896735.035</v>
+        <v>59897159.035</v>
       </c>
       <c r="H1581" t="inlineStr"/>
     </row>
@@ -34822,7 +34822,7 @@
       </c>
       <c r="F1584" t="inlineStr"/>
       <c r="G1584" t="n">
-        <v>62211472.5</v>
+        <v>62211453.5</v>
       </c>
       <c r="H1584" t="inlineStr"/>
     </row>
@@ -34844,7 +34844,7 @@
       </c>
       <c r="F1585" t="inlineStr"/>
       <c r="G1585" t="n">
-        <v>62243940.556</v>
+        <v>62231707.556</v>
       </c>
       <c r="H1585" t="inlineStr"/>
     </row>
@@ -34866,7 +34866,7 @@
       </c>
       <c r="F1586" t="inlineStr"/>
       <c r="G1586" t="n">
-        <v>62058212.549</v>
+        <v>62043976.047</v>
       </c>
       <c r="H1586" t="inlineStr"/>
     </row>
@@ -34888,7 +34888,7 @@
       </c>
       <c r="F1587" t="inlineStr"/>
       <c r="G1587" t="n">
-        <v>62834794.635</v>
+        <v>62802346.612</v>
       </c>
       <c r="H1587" t="inlineStr"/>
     </row>
@@ -34910,7 +34910,7 @@
       </c>
       <c r="F1588" t="inlineStr"/>
       <c r="G1588" t="n">
-        <v>61618792.47</v>
+        <v>61581760.134</v>
       </c>
       <c r="H1588" t="inlineStr"/>
     </row>
@@ -34932,7 +34932,7 @@
       </c>
       <c r="F1589" t="inlineStr"/>
       <c r="G1589" t="n">
-        <v>60972086.633</v>
+        <v>60910235.097</v>
       </c>
       <c r="H1589" t="inlineStr"/>
     </row>
@@ -34954,7 +34954,7 @@
       </c>
       <c r="F1590" t="inlineStr"/>
       <c r="G1590" t="n">
-        <v>60781694.954</v>
+        <v>60782195.058</v>
       </c>
       <c r="H1590" t="inlineStr"/>
     </row>
@@ -34975,15 +34975,21 @@
         <v>19.6875</v>
       </c>
       <c r="F1591" t="inlineStr"/>
-      <c r="G1591" t="inlineStr"/>
+      <c r="G1591" t="n">
+        <v>60471275.058</v>
+      </c>
       <c r="H1591" t="inlineStr"/>
     </row>
     <row r="1592">
       <c r="A1592" s="1" t="n">
         <v>46184</v>
       </c>
-      <c r="B1592" t="inlineStr"/>
-      <c r="C1592" t="inlineStr"/>
+      <c r="B1592" t="n">
+        <v>47619</v>
+      </c>
+      <c r="C1592" t="n">
+        <v>43722386</v>
+      </c>
       <c r="D1592" t="n">
         <v>1453.6</v>
       </c>
@@ -34991,22 +34997,104 @@
         <v>20.1875</v>
       </c>
       <c r="F1592" t="inlineStr"/>
-      <c r="G1592" t="inlineStr"/>
+      <c r="G1592" t="n">
+        <v>60437821.246</v>
+      </c>
       <c r="H1592" t="inlineStr"/>
     </row>
     <row r="1593">
       <c r="A1593" s="1" t="n">
         <v>46185</v>
       </c>
-      <c r="B1593" t="inlineStr"/>
-      <c r="C1593" t="inlineStr"/>
+      <c r="B1593" t="n">
+        <v>47419</v>
+      </c>
+      <c r="C1593" t="n">
+        <v>43128652</v>
+      </c>
       <c r="D1593" t="n">
         <v>1452.55</v>
       </c>
-      <c r="E1593" t="inlineStr"/>
+      <c r="E1593" t="n">
+        <v>20</v>
+      </c>
       <c r="F1593" t="inlineStr"/>
-      <c r="G1593" t="inlineStr"/>
+      <c r="G1593" t="n">
+        <v>60556509.794</v>
+      </c>
       <c r="H1593" t="inlineStr"/>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B1594" t="n">
+        <v>47656</v>
+      </c>
+      <c r="C1594" t="n">
+        <v>43652914</v>
+      </c>
+      <c r="D1594" t="n">
+        <v>1453.61</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1594" t="inlineStr"/>
+      <c r="G1594" t="n">
+        <v>61222206.988</v>
+      </c>
+      <c r="H1594" t="inlineStr"/>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B1595" t="n">
+        <v>47503</v>
+      </c>
+      <c r="C1595" t="n">
+        <v>43736344</v>
+      </c>
+      <c r="D1595" t="n">
+        <v>1461.27</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="F1595" t="inlineStr"/>
+      <c r="G1595" t="inlineStr"/>
+      <c r="H1595" t="inlineStr"/>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B1596" t="inlineStr"/>
+      <c r="C1596" t="inlineStr"/>
+      <c r="D1596" t="n">
+        <v>1470.01</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1596" t="inlineStr"/>
+      <c r="G1596" t="inlineStr"/>
+      <c r="H1596" t="inlineStr"/>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B1597" t="inlineStr"/>
+      <c r="C1597" t="inlineStr"/>
+      <c r="D1597" t="n">
+        <v>1481.94</v>
+      </c>
+      <c r="E1597" t="inlineStr"/>
+      <c r="F1597" t="inlineStr"/>
+      <c r="G1597" t="inlineStr"/>
+      <c r="H1597" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1597"/>
+  <dimension ref="A1:H1602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57849024.056</v>
+        <v>57849020.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="n">
-        <v>56669690.267</v>
+        <v>56669687.267</v>
       </c>
       <c r="H1358" t="inlineStr"/>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="F1359" t="inlineStr"/>
       <c r="G1359" t="n">
-        <v>56029603.372</v>
+        <v>56029599.372</v>
       </c>
       <c r="H1359" t="inlineStr"/>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="n">
-        <v>56588561.504</v>
+        <v>56588557.504</v>
       </c>
       <c r="H1360" t="inlineStr"/>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="n">
-        <v>56826429.839</v>
+        <v>56826425.839</v>
       </c>
       <c r="H1361" t="inlineStr"/>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="n">
-        <v>55507108.571</v>
+        <v>55507104.571</v>
       </c>
       <c r="H1362" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="n">
-        <v>55317111.556</v>
+        <v>55317108.556</v>
       </c>
       <c r="H1363" t="inlineStr"/>
     </row>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="n">
-        <v>54530587.68</v>
+        <v>54530583.68</v>
       </c>
       <c r="H1364" t="inlineStr"/>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="n">
-        <v>53951999.241</v>
+        <v>53951995.241</v>
       </c>
       <c r="H1365" t="inlineStr"/>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="n">
-        <v>53559403.918</v>
+        <v>53559399.918</v>
       </c>
       <c r="H1366" t="inlineStr"/>
     </row>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F1367" t="inlineStr"/>
       <c r="G1367" t="n">
-        <v>53693196.53</v>
+        <v>53693193.53</v>
       </c>
       <c r="H1367" t="inlineStr"/>
     </row>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="n">
-        <v>52779319.228</v>
+        <v>52779315.228</v>
       </c>
       <c r="H1368" t="inlineStr"/>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53008454.434</v>
+        <v>53008451.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30130,7 +30130,7 @@
       </c>
       <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="n">
-        <v>52789885.166</v>
+        <v>52789881.166</v>
       </c>
       <c r="H1370" t="inlineStr"/>
     </row>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="F1371" t="inlineStr"/>
       <c r="G1371" t="n">
-        <v>52579574.418</v>
+        <v>52579570.418</v>
       </c>
       <c r="H1371" t="inlineStr"/>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="n">
-        <v>52219555.099</v>
+        <v>52219551.099</v>
       </c>
       <c r="H1372" t="inlineStr"/>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="n">
-        <v>52314947.713</v>
+        <v>52314943.713</v>
       </c>
       <c r="H1373" t="inlineStr"/>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="n">
-        <v>52858345.596</v>
+        <v>52858341.596</v>
       </c>
       <c r="H1374" t="inlineStr"/>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="n">
-        <v>52208926.178</v>
+        <v>52208922.178</v>
       </c>
       <c r="H1375" t="inlineStr"/>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="n">
-        <v>52590301.503</v>
+        <v>52590298.503</v>
       </c>
       <c r="H1376" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="n">
-        <v>52809704.197</v>
+        <v>52809701.197</v>
       </c>
       <c r="H1377" t="inlineStr"/>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="n">
-        <v>54082615.568</v>
+        <v>54082611.568</v>
       </c>
       <c r="H1378" t="inlineStr"/>
     </row>
@@ -32764,7 +32764,7 @@
       </c>
       <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="n">
-        <v>57244504.101</v>
+        <v>57233102.101</v>
       </c>
       <c r="H1490" t="inlineStr"/>
     </row>
@@ -34364,7 +34364,7 @@
         <v>24.2</v>
       </c>
       <c r="G1563" t="n">
-        <v>62700673.443</v>
+        <v>62688303.443</v>
       </c>
       <c r="H1563" t="n">
         <v>2.6</v>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="n">
-        <v>57619910.887</v>
+        <v>57616326.887</v>
       </c>
       <c r="H1570" t="inlineStr"/>
     </row>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="F1574" t="inlineStr"/>
       <c r="G1574" t="n">
-        <v>56568492.718</v>
+        <v>56580189.718</v>
       </c>
       <c r="H1574" t="inlineStr"/>
     </row>
@@ -34630,7 +34630,7 @@
       </c>
       <c r="F1575" t="inlineStr"/>
       <c r="G1575" t="n">
-        <v>56515467.683</v>
+        <v>56533803.683</v>
       </c>
       <c r="H1575" t="inlineStr"/>
     </row>
@@ -34784,7 +34784,7 @@
       </c>
       <c r="F1582" t="inlineStr"/>
       <c r="G1582" t="n">
-        <v>63009605.598</v>
+        <v>63213563.935</v>
       </c>
       <c r="H1582" t="inlineStr"/>
     </row>
@@ -34822,7 +34822,7 @@
       </c>
       <c r="F1584" t="inlineStr"/>
       <c r="G1584" t="n">
-        <v>62211453.5</v>
+        <v>62195108.5</v>
       </c>
       <c r="H1584" t="inlineStr"/>
     </row>
@@ -34844,7 +34844,7 @@
       </c>
       <c r="F1585" t="inlineStr"/>
       <c r="G1585" t="n">
-        <v>62231707.556</v>
+        <v>62223328.556</v>
       </c>
       <c r="H1585" t="inlineStr"/>
     </row>
@@ -34866,7 +34866,7 @@
       </c>
       <c r="F1586" t="inlineStr"/>
       <c r="G1586" t="n">
-        <v>62043976.047</v>
+        <v>62053283.047</v>
       </c>
       <c r="H1586" t="inlineStr"/>
     </row>
@@ -34888,7 +34888,7 @@
       </c>
       <c r="F1587" t="inlineStr"/>
       <c r="G1587" t="n">
-        <v>62802346.612</v>
+        <v>62802349.612</v>
       </c>
       <c r="H1587" t="inlineStr"/>
     </row>
@@ -34910,7 +34910,7 @@
       </c>
       <c r="F1588" t="inlineStr"/>
       <c r="G1588" t="n">
-        <v>61581760.134</v>
+        <v>61600751.134</v>
       </c>
       <c r="H1588" t="inlineStr"/>
     </row>
@@ -34932,7 +34932,7 @@
       </c>
       <c r="F1589" t="inlineStr"/>
       <c r="G1589" t="n">
-        <v>60910235.097</v>
+        <v>60923436.097</v>
       </c>
       <c r="H1589" t="inlineStr"/>
     </row>
@@ -34954,7 +34954,7 @@
       </c>
       <c r="F1590" t="inlineStr"/>
       <c r="G1590" t="n">
-        <v>60782195.058</v>
+        <v>60712155.135</v>
       </c>
       <c r="H1590" t="inlineStr"/>
     </row>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="F1591" t="inlineStr"/>
       <c r="G1591" t="n">
-        <v>60471275.058</v>
+        <v>60420458.682</v>
       </c>
       <c r="H1591" t="inlineStr"/>
     </row>
@@ -34998,7 +34998,7 @@
       </c>
       <c r="F1592" t="inlineStr"/>
       <c r="G1592" t="n">
-        <v>60437821.246</v>
+        <v>60426976.832</v>
       </c>
       <c r="H1592" t="inlineStr"/>
     </row>
@@ -35020,7 +35020,7 @@
       </c>
       <c r="F1593" t="inlineStr"/>
       <c r="G1593" t="n">
-        <v>60556509.794</v>
+        <v>60552560.856</v>
       </c>
       <c r="H1593" t="inlineStr"/>
     </row>
@@ -35042,7 +35042,7 @@
       </c>
       <c r="F1594" t="inlineStr"/>
       <c r="G1594" t="n">
-        <v>61222206.988</v>
+        <v>61231451.499</v>
       </c>
       <c r="H1594" t="inlineStr"/>
     </row>
@@ -35063,15 +35063,21 @@
         <v>20.75</v>
       </c>
       <c r="F1595" t="inlineStr"/>
-      <c r="G1595" t="inlineStr"/>
+      <c r="G1595" t="n">
+        <v>61128868.983</v>
+      </c>
       <c r="H1595" t="inlineStr"/>
     </row>
     <row r="1596">
       <c r="A1596" s="1" t="n">
         <v>46191</v>
       </c>
-      <c r="B1596" t="inlineStr"/>
-      <c r="C1596" t="inlineStr"/>
+      <c r="B1596" t="n">
+        <v>47500</v>
+      </c>
+      <c r="C1596" t="n">
+        <v>43235697</v>
+      </c>
       <c r="D1596" t="n">
         <v>1470.01</v>
       </c>
@@ -35079,22 +35085,126 @@
         <v>21</v>
       </c>
       <c r="F1596" t="inlineStr"/>
-      <c r="G1596" t="inlineStr"/>
+      <c r="G1596" t="n">
+        <v>61225651.482</v>
+      </c>
       <c r="H1596" t="inlineStr"/>
     </row>
     <row r="1597">
       <c r="A1597" s="1" t="n">
         <v>46192</v>
       </c>
-      <c r="B1597" t="inlineStr"/>
-      <c r="C1597" t="inlineStr"/>
+      <c r="B1597" t="n">
+        <v>47373</v>
+      </c>
+      <c r="C1597" t="n">
+        <v>43144287</v>
+      </c>
       <c r="D1597" t="n">
         <v>1481.94</v>
       </c>
-      <c r="E1597" t="inlineStr"/>
+      <c r="E1597" t="n">
+        <v>20.6875</v>
+      </c>
       <c r="F1597" t="inlineStr"/>
-      <c r="G1597" t="inlineStr"/>
+      <c r="G1597" t="n">
+        <v>60964834.287</v>
+      </c>
       <c r="H1597" t="inlineStr"/>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B1598" t="n">
+        <v>47508</v>
+      </c>
+      <c r="C1598" t="n">
+        <v>43380086</v>
+      </c>
+      <c r="D1598" t="n">
+        <v>1481.79</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>20.875</v>
+      </c>
+      <c r="F1598" t="inlineStr"/>
+      <c r="G1598" t="n">
+        <v>60977544.256</v>
+      </c>
+      <c r="H1598" t="inlineStr"/>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B1599" t="n">
+        <v>47474</v>
+      </c>
+      <c r="C1599" t="n">
+        <v>43386638</v>
+      </c>
+      <c r="D1599" t="n">
+        <v>1491.13</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>21.6875</v>
+      </c>
+      <c r="F1599" t="inlineStr"/>
+      <c r="G1599" t="n">
+        <v>61338903.813</v>
+      </c>
+      <c r="H1599" t="inlineStr"/>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B1600" t="n">
+        <v>46936</v>
+      </c>
+      <c r="C1600" t="n">
+        <v>44249822</v>
+      </c>
+      <c r="D1600" t="n">
+        <v>1498.05</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>21.5625</v>
+      </c>
+      <c r="F1600" t="inlineStr"/>
+      <c r="G1600" t="inlineStr"/>
+      <c r="H1600" t="inlineStr"/>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B1601" t="inlineStr"/>
+      <c r="C1601" t="inlineStr"/>
+      <c r="D1601" t="n">
+        <v>1498.12</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="F1601" t="inlineStr"/>
+      <c r="G1601" t="inlineStr"/>
+      <c r="H1601" t="inlineStr"/>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B1602" t="inlineStr"/>
+      <c r="C1602" t="inlineStr"/>
+      <c r="D1602" t="n">
+        <v>1495.57</v>
+      </c>
+      <c r="E1602" t="inlineStr"/>
+      <c r="F1602" t="inlineStr"/>
+      <c r="G1602" t="inlineStr"/>
+      <c r="H1602" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1602"/>
+  <dimension ref="A1:H1607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.29</v>
+        <v>108.48</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.48</v>
+        <v>108.61</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.61</v>
+        <v>108.63</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.63</v>
+        <v>108.72</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.72</v>
+        <v>108.86</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.86</v>
+        <v>108.96</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.96</v>
+        <v>108.97</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>108.97</v>
+        <v>109.05</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.05</v>
+        <v>109.11</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.11</v>
+        <v>109.21</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.21</v>
+        <v>109.46</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.46</v>
+        <v>109.64</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.64</v>
+        <v>109.67</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.67</v>
+        <v>109.71</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.71</v>
+        <v>109.79</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>109.79</v>
+        <v>110.08</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.08</v>
+        <v>110.11</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.11</v>
+        <v>110.15</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.15</v>
+        <v>110.5</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.5</v>
+        <v>110.68</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.68</v>
+        <v>110.71</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.71</v>
+        <v>110.75</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.75</v>
+        <v>110.92</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>110.92</v>
+        <v>111.37</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.37</v>
+        <v>111.46</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.46</v>
+        <v>111.49</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.49</v>
+        <v>111.52</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.52</v>
+        <v>111.59</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.59</v>
+        <v>111.67</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>111.67</v>
+        <v>112.01</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.01</v>
+        <v>112.17</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.17</v>
+        <v>112.21</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.21</v>
+        <v>112.24</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.24</v>
+        <v>112.48</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.48</v>
+        <v>112.71</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.71</v>
+        <v>112.8</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.8</v>
+        <v>112.83</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.83</v>
+        <v>112.89</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.89</v>
+        <v>112.95</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57849020.056</v>
+        <v>57738916.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -31274,7 +31274,7 @@
         <v>21.9</v>
       </c>
       <c r="G1422" t="n">
-        <v>55345804.222</v>
+        <v>55345798.222</v>
       </c>
       <c r="H1422" t="n">
         <v>2.1</v>
@@ -31298,7 +31298,7 @@
       </c>
       <c r="F1423" t="inlineStr"/>
       <c r="G1423" t="n">
-        <v>55584399.331</v>
+        <v>55584393.331</v>
       </c>
       <c r="H1423" t="inlineStr"/>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="F1424" t="inlineStr"/>
       <c r="G1424" t="n">
-        <v>55646325.151</v>
+        <v>55646318.151</v>
       </c>
       <c r="H1424" t="inlineStr"/>
     </row>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="F1425" t="inlineStr"/>
       <c r="G1425" t="n">
-        <v>55912037.978</v>
+        <v>55912030.978</v>
       </c>
       <c r="H1425" t="inlineStr"/>
     </row>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="F1426" t="inlineStr"/>
       <c r="G1426" t="n">
-        <v>55683740.241</v>
+        <v>55683733.241</v>
       </c>
       <c r="H1426" t="inlineStr"/>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="F1427" t="inlineStr"/>
       <c r="G1427" t="n">
-        <v>54846916.217</v>
+        <v>54846909.217</v>
       </c>
       <c r="H1427" t="inlineStr"/>
     </row>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="F1428" t="inlineStr"/>
       <c r="G1428" t="n">
-        <v>54725217.24</v>
+        <v>54725211.24</v>
       </c>
       <c r="H1428" t="inlineStr"/>
     </row>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="F1429" t="inlineStr"/>
       <c r="G1429" t="n">
-        <v>54438345.576</v>
+        <v>54438339.576</v>
       </c>
       <c r="H1429" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="F1430" t="inlineStr"/>
       <c r="G1430" t="n">
-        <v>54449761.621</v>
+        <v>54449755.621</v>
       </c>
       <c r="H1430" t="inlineStr"/>
     </row>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="F1431" t="inlineStr"/>
       <c r="G1431" t="n">
-        <v>51917834.914</v>
+        <v>51917828.914</v>
       </c>
       <c r="H1431" t="inlineStr"/>
     </row>
@@ -31496,7 +31496,7 @@
       </c>
       <c r="F1432" t="inlineStr"/>
       <c r="G1432" t="n">
-        <v>52476658.382</v>
+        <v>52476651.382</v>
       </c>
       <c r="H1432" t="inlineStr"/>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="F1433" t="inlineStr"/>
       <c r="G1433" t="n">
-        <v>51681176.388</v>
+        <v>51681169.388</v>
       </c>
       <c r="H1433" t="inlineStr"/>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="F1434" t="inlineStr"/>
       <c r="G1434" t="n">
-        <v>50448626.623</v>
+        <v>50448620.623</v>
       </c>
       <c r="H1434" t="inlineStr"/>
     </row>
@@ -31562,7 +31562,7 @@
       </c>
       <c r="F1435" t="inlineStr"/>
       <c r="G1435" t="n">
-        <v>50493998.287</v>
+        <v>50493991.287</v>
       </c>
       <c r="H1435" t="inlineStr"/>
     </row>
@@ -31584,7 +31584,7 @@
       </c>
       <c r="F1436" t="inlineStr"/>
       <c r="G1436" t="n">
-        <v>50027576.307</v>
+        <v>50027570.307</v>
       </c>
       <c r="H1436" t="inlineStr"/>
     </row>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="F1437" t="inlineStr"/>
       <c r="G1437" t="n">
-        <v>50747924.53</v>
+        <v>50747917.53</v>
       </c>
       <c r="H1437" t="inlineStr"/>
     </row>
@@ -31628,7 +31628,7 @@
       </c>
       <c r="F1438" t="inlineStr"/>
       <c r="G1438" t="n">
-        <v>49992003.981</v>
+        <v>49991996.981</v>
       </c>
       <c r="H1438" t="inlineStr"/>
     </row>
@@ -31650,7 +31650,7 @@
       </c>
       <c r="F1439" t="inlineStr"/>
       <c r="G1439" t="n">
-        <v>49837487.76</v>
+        <v>49837481.76</v>
       </c>
       <c r="H1439" t="inlineStr"/>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="F1440" t="inlineStr"/>
       <c r="G1440" t="n">
-        <v>49753107.195</v>
+        <v>49753101.195</v>
       </c>
       <c r="H1440" t="inlineStr"/>
     </row>
@@ -31694,7 +31694,7 @@
       </c>
       <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="n">
-        <v>49495942.045</v>
+        <v>49495936.045</v>
       </c>
       <c r="H1441" t="inlineStr"/>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="F1442" t="inlineStr"/>
       <c r="G1442" t="n">
-        <v>50043634.504</v>
+        <v>50043627.504</v>
       </c>
       <c r="H1442" t="inlineStr"/>
     </row>
@@ -31738,7 +31738,7 @@
       </c>
       <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="n">
-        <v>51498315.942</v>
+        <v>51498309.942</v>
       </c>
       <c r="H1443" t="inlineStr"/>
     </row>
@@ -31762,7 +31762,7 @@
         <v>20.8</v>
       </c>
       <c r="G1444" t="n">
-        <v>53885494.608</v>
+        <v>53885545.608</v>
       </c>
       <c r="H1444" t="n">
         <v>2.3</v>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="n">
-        <v>56142263.43</v>
+        <v>56142212.43</v>
       </c>
       <c r="H1461" t="inlineStr"/>
     </row>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="F1463" t="inlineStr"/>
       <c r="G1463" t="n">
-        <v>56164903.367</v>
+        <v>56164845.367</v>
       </c>
       <c r="H1463" t="inlineStr"/>
     </row>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="F1464" t="inlineStr"/>
       <c r="G1464" t="n">
-        <v>55033908.993</v>
+        <v>55033850.993</v>
       </c>
       <c r="H1464" t="inlineStr"/>
     </row>
@@ -32220,7 +32220,7 @@
       </c>
       <c r="F1465" t="inlineStr"/>
       <c r="G1465" t="n">
-        <v>55457251.785</v>
+        <v>55457193.785</v>
       </c>
       <c r="H1465" t="inlineStr"/>
     </row>
@@ -32242,7 +32242,7 @@
       </c>
       <c r="F1466" t="inlineStr"/>
       <c r="G1466" t="n">
-        <v>56337129.518</v>
+        <v>56337071.518</v>
       </c>
       <c r="H1466" t="inlineStr"/>
     </row>
@@ -32264,7 +32264,7 @@
       </c>
       <c r="F1467" t="inlineStr"/>
       <c r="G1467" t="n">
-        <v>55346859.095</v>
+        <v>55346801.095</v>
       </c>
       <c r="H1467" t="inlineStr"/>
     </row>
@@ -32286,7 +32286,7 @@
       </c>
       <c r="F1468" t="inlineStr"/>
       <c r="G1468" t="n">
-        <v>54679758.736</v>
+        <v>54679700.736</v>
       </c>
       <c r="H1468" t="inlineStr"/>
     </row>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="F1469" t="inlineStr"/>
       <c r="G1469" t="n">
-        <v>54555897.54</v>
+        <v>54555839.54</v>
       </c>
       <c r="H1469" t="inlineStr"/>
     </row>
@@ -32330,7 +32330,7 @@
       </c>
       <c r="F1470" t="inlineStr"/>
       <c r="G1470" t="n">
-        <v>55263429.612</v>
+        <v>55263372.612</v>
       </c>
       <c r="H1470" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
       </c>
       <c r="F1471" t="inlineStr"/>
       <c r="G1471" t="n">
-        <v>55077749.123</v>
+        <v>55077691.123</v>
       </c>
       <c r="H1471" t="inlineStr"/>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="F1472" t="inlineStr"/>
       <c r="G1472" t="n">
-        <v>56288698.956</v>
+        <v>56288640.956</v>
       </c>
       <c r="H1472" t="inlineStr"/>
     </row>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="F1473" t="inlineStr"/>
       <c r="G1473" t="n">
-        <v>56126981.885</v>
+        <v>56126923.885</v>
       </c>
       <c r="H1473" t="inlineStr"/>
     </row>
@@ -32418,7 +32418,7 @@
       </c>
       <c r="F1474" t="inlineStr"/>
       <c r="G1474" t="n">
-        <v>57302255.778</v>
+        <v>57302197.778</v>
       </c>
       <c r="H1474" t="inlineStr"/>
     </row>
@@ -32440,7 +32440,7 @@
       </c>
       <c r="F1475" t="inlineStr"/>
       <c r="G1475" t="n">
-        <v>58733870.611</v>
+        <v>58733812.611</v>
       </c>
       <c r="H1475" t="inlineStr"/>
     </row>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="F1476" t="inlineStr"/>
       <c r="G1476" t="n">
-        <v>59890935.332</v>
+        <v>59890877.332</v>
       </c>
       <c r="H1476" t="inlineStr"/>
     </row>
@@ -32484,7 +32484,7 @@
       </c>
       <c r="F1477" t="inlineStr"/>
       <c r="G1477" t="n">
-        <v>60274130.984</v>
+        <v>60274072.984</v>
       </c>
       <c r="H1477" t="inlineStr"/>
     </row>
@@ -32506,7 +32506,7 @@
       </c>
       <c r="F1478" t="inlineStr"/>
       <c r="G1478" t="n">
-        <v>60798977.024</v>
+        <v>60798919.024</v>
       </c>
       <c r="H1478" t="inlineStr"/>
     </row>
@@ -32528,7 +32528,7 @@
       </c>
       <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="n">
-        <v>60726182.044</v>
+        <v>60726124.044</v>
       </c>
       <c r="H1479" t="inlineStr"/>
     </row>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="F1480" t="inlineStr"/>
       <c r="G1480" t="n">
-        <v>62881194.767</v>
+        <v>62881136.767</v>
       </c>
       <c r="H1480" t="inlineStr"/>
     </row>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65326084.703</v>
+        <v>65326165.703</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60853987.977</v>
+        <v>60856267.723</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -33944,7 +33944,7 @@
       </c>
       <c r="F1544" t="inlineStr"/>
       <c r="G1544" t="n">
-        <v>59401779.307</v>
+        <v>59401786.307</v>
       </c>
       <c r="H1544" t="inlineStr"/>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="F1545" t="inlineStr"/>
       <c r="G1545" t="n">
-        <v>58874480.314</v>
+        <v>58874485.314</v>
       </c>
       <c r="H1545" t="inlineStr"/>
     </row>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="n">
-        <v>58487697.356</v>
+        <v>58487701.356</v>
       </c>
       <c r="H1546" t="inlineStr"/>
     </row>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="F1547" t="inlineStr"/>
       <c r="G1547" t="n">
-        <v>58201620.536</v>
+        <v>58201633.536</v>
       </c>
       <c r="H1547" t="inlineStr"/>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="F1548" t="inlineStr"/>
       <c r="G1548" t="n">
-        <v>57482687.632</v>
+        <v>57482694.632</v>
       </c>
       <c r="H1548" t="inlineStr"/>
     </row>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="n">
-        <v>56939398.446</v>
+        <v>56939396.446</v>
       </c>
       <c r="H1549" t="inlineStr"/>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="F1550" t="inlineStr"/>
       <c r="G1550" t="n">
-        <v>55945549.207</v>
+        <v>55945548.207</v>
       </c>
       <c r="H1550" t="inlineStr"/>
     </row>
@@ -34098,7 +34098,7 @@
       </c>
       <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="n">
-        <v>55757409.443</v>
+        <v>55757413.443</v>
       </c>
       <c r="H1551" t="inlineStr"/>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="F1552" t="inlineStr"/>
       <c r="G1552" t="n">
-        <v>56295795.934</v>
+        <v>56295798.934</v>
       </c>
       <c r="H1552" t="inlineStr"/>
     </row>
@@ -34142,7 +34142,7 @@
       </c>
       <c r="F1553" t="inlineStr"/>
       <c r="G1553" t="n">
-        <v>55510675.762</v>
+        <v>55520686.762</v>
       </c>
       <c r="H1553" t="inlineStr"/>
     </row>
@@ -34164,7 +34164,7 @@
       </c>
       <c r="F1554" t="inlineStr"/>
       <c r="G1554" t="n">
-        <v>55092599.13</v>
+        <v>55092604.13</v>
       </c>
       <c r="H1554" t="inlineStr"/>
     </row>
@@ -34186,7 +34186,7 @@
       </c>
       <c r="F1555" t="inlineStr"/>
       <c r="G1555" t="n">
-        <v>55049779.313</v>
+        <v>55049782.313</v>
       </c>
       <c r="H1555" t="inlineStr"/>
     </row>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="F1556" t="inlineStr"/>
       <c r="G1556" t="n">
-        <v>54450051.246</v>
+        <v>54450083.246</v>
       </c>
       <c r="H1556" t="inlineStr"/>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="F1557" t="inlineStr"/>
       <c r="G1557" t="n">
-        <v>53870230.057</v>
+        <v>53870235.057</v>
       </c>
       <c r="H1557" t="inlineStr"/>
     </row>
@@ -34252,7 +34252,7 @@
       </c>
       <c r="F1558" t="inlineStr"/>
       <c r="G1558" t="n">
-        <v>53999906.573</v>
+        <v>53999907.573</v>
       </c>
       <c r="H1558" t="inlineStr"/>
     </row>
@@ -34274,7 +34274,7 @@
       </c>
       <c r="F1559" t="inlineStr"/>
       <c r="G1559" t="n">
-        <v>54422370.702</v>
+        <v>54422367.702</v>
       </c>
       <c r="H1559" t="inlineStr"/>
     </row>
@@ -34296,7 +34296,7 @@
       </c>
       <c r="F1560" t="inlineStr"/>
       <c r="G1560" t="n">
-        <v>55394852.514</v>
+        <v>55394857.514</v>
       </c>
       <c r="H1560" t="inlineStr"/>
     </row>
@@ -34318,7 +34318,7 @@
       </c>
       <c r="F1561" t="inlineStr"/>
       <c r="G1561" t="n">
-        <v>55801851.608</v>
+        <v>55801860.608</v>
       </c>
       <c r="H1561" t="inlineStr"/>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="F1562" t="inlineStr"/>
       <c r="G1562" t="n">
-        <v>58993125.116</v>
+        <v>58993140.116</v>
       </c>
       <c r="H1562" t="inlineStr"/>
     </row>
@@ -34388,7 +34388,7 @@
       </c>
       <c r="F1564" t="inlineStr"/>
       <c r="G1564" t="n">
-        <v>60730926.828</v>
+        <v>60731125.828</v>
       </c>
       <c r="H1564" t="inlineStr"/>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="F1565" t="inlineStr"/>
       <c r="G1565" t="n">
-        <v>60125037.987</v>
+        <v>60125054.987</v>
       </c>
       <c r="H1565" t="inlineStr"/>
     </row>
@@ -34432,7 +34432,7 @@
       </c>
       <c r="F1566" t="inlineStr"/>
       <c r="G1566" t="n">
-        <v>60065942.457</v>
+        <v>60067678.457</v>
       </c>
       <c r="H1566" t="inlineStr"/>
     </row>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="F1567" t="inlineStr"/>
       <c r="G1567" t="n">
-        <v>60734349.321</v>
+        <v>60734761.321</v>
       </c>
       <c r="H1567" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
       </c>
       <c r="F1568" t="inlineStr"/>
       <c r="G1568" t="n">
-        <v>59028098.089</v>
+        <v>59028364.089</v>
       </c>
       <c r="H1568" t="inlineStr"/>
     </row>
@@ -34498,7 +34498,7 @@
       </c>
       <c r="F1569" t="inlineStr"/>
       <c r="G1569" t="n">
-        <v>58185666.149</v>
+        <v>58185748.149</v>
       </c>
       <c r="H1569" t="inlineStr"/>
     </row>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="n">
-        <v>57616326.887</v>
+        <v>57616407.887</v>
       </c>
       <c r="H1570" t="inlineStr"/>
     </row>
@@ -34542,7 +34542,7 @@
       </c>
       <c r="F1571" t="inlineStr"/>
       <c r="G1571" t="n">
-        <v>57625175.677</v>
+        <v>57625212.677</v>
       </c>
       <c r="H1571" t="inlineStr"/>
     </row>
@@ -34564,7 +34564,7 @@
       </c>
       <c r="F1572" t="inlineStr"/>
       <c r="G1572" t="n">
-        <v>57692353.026</v>
+        <v>57692358.026</v>
       </c>
       <c r="H1572" t="inlineStr"/>
     </row>
@@ -34586,7 +34586,7 @@
       </c>
       <c r="F1573" t="inlineStr"/>
       <c r="G1573" t="n">
-        <v>58024078.6</v>
+        <v>58028430.6</v>
       </c>
       <c r="H1573" t="inlineStr"/>
     </row>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="F1574" t="inlineStr"/>
       <c r="G1574" t="n">
-        <v>56580189.718</v>
+        <v>56580209.718</v>
       </c>
       <c r="H1574" t="inlineStr"/>
     </row>
@@ -34630,7 +34630,7 @@
       </c>
       <c r="F1575" t="inlineStr"/>
       <c r="G1575" t="n">
-        <v>56533803.683</v>
+        <v>56533813.683</v>
       </c>
       <c r="H1575" t="inlineStr"/>
     </row>
@@ -34652,7 +34652,7 @@
       </c>
       <c r="F1576" t="inlineStr"/>
       <c r="G1576" t="n">
-        <v>56518765.473</v>
+        <v>56518774.473</v>
       </c>
       <c r="H1576" t="inlineStr"/>
     </row>
@@ -34674,7 +34674,7 @@
       </c>
       <c r="F1577" t="inlineStr"/>
       <c r="G1577" t="n">
-        <v>56614292.751</v>
+        <v>56615129.751</v>
       </c>
       <c r="H1577" t="inlineStr"/>
     </row>
@@ -34696,7 +34696,7 @@
       </c>
       <c r="F1578" t="inlineStr"/>
       <c r="G1578" t="n">
-        <v>56497100.527</v>
+        <v>56497122.527</v>
       </c>
       <c r="H1578" t="inlineStr"/>
     </row>
@@ -34718,7 +34718,7 @@
       </c>
       <c r="F1579" t="inlineStr"/>
       <c r="G1579" t="n">
-        <v>57013546.328</v>
+        <v>57013567.328</v>
       </c>
       <c r="H1579" t="inlineStr"/>
     </row>
@@ -34740,7 +34740,7 @@
       </c>
       <c r="F1580" t="inlineStr"/>
       <c r="G1580" t="n">
-        <v>57903916.253</v>
+        <v>57904028.253</v>
       </c>
       <c r="H1580" t="inlineStr"/>
     </row>
@@ -34762,7 +34762,7 @@
       </c>
       <c r="F1581" t="inlineStr"/>
       <c r="G1581" t="n">
-        <v>59897159.035</v>
+        <v>59897249.035</v>
       </c>
       <c r="H1581" t="inlineStr"/>
     </row>
@@ -34784,7 +34784,7 @@
       </c>
       <c r="F1582" t="inlineStr"/>
       <c r="G1582" t="n">
-        <v>63213563.935</v>
+        <v>63456427.9</v>
       </c>
       <c r="H1582" t="inlineStr"/>
     </row>
@@ -34910,7 +34910,7 @@
       </c>
       <c r="F1588" t="inlineStr"/>
       <c r="G1588" t="n">
-        <v>61600751.134</v>
+        <v>61600761.134</v>
       </c>
       <c r="H1588" t="inlineStr"/>
     </row>
@@ -34932,7 +34932,7 @@
       </c>
       <c r="F1589" t="inlineStr"/>
       <c r="G1589" t="n">
-        <v>60923436.097</v>
+        <v>60923445.097</v>
       </c>
       <c r="H1589" t="inlineStr"/>
     </row>
@@ -34954,7 +34954,7 @@
       </c>
       <c r="F1590" t="inlineStr"/>
       <c r="G1590" t="n">
-        <v>60712155.135</v>
+        <v>60712164.135</v>
       </c>
       <c r="H1590" t="inlineStr"/>
     </row>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="F1591" t="inlineStr"/>
       <c r="G1591" t="n">
-        <v>60420458.682</v>
+        <v>60429512.682</v>
       </c>
       <c r="H1591" t="inlineStr"/>
     </row>
@@ -34998,7 +34998,7 @@
       </c>
       <c r="F1592" t="inlineStr"/>
       <c r="G1592" t="n">
-        <v>60426976.832</v>
+        <v>60439733.832</v>
       </c>
       <c r="H1592" t="inlineStr"/>
     </row>
@@ -35020,7 +35020,7 @@
       </c>
       <c r="F1593" t="inlineStr"/>
       <c r="G1593" t="n">
-        <v>60552560.856</v>
+        <v>60560534.856</v>
       </c>
       <c r="H1593" t="inlineStr"/>
     </row>
@@ -35042,7 +35042,7 @@
       </c>
       <c r="F1594" t="inlineStr"/>
       <c r="G1594" t="n">
-        <v>61231451.499</v>
+        <v>61239600.499</v>
       </c>
       <c r="H1594" t="inlineStr"/>
     </row>
@@ -35064,7 +35064,7 @@
       </c>
       <c r="F1595" t="inlineStr"/>
       <c r="G1595" t="n">
-        <v>61128868.983</v>
+        <v>61076229.917</v>
       </c>
       <c r="H1595" t="inlineStr"/>
     </row>
@@ -35086,7 +35086,7 @@
       </c>
       <c r="F1596" t="inlineStr"/>
       <c r="G1596" t="n">
-        <v>61225651.482</v>
+        <v>61211556.503</v>
       </c>
       <c r="H1596" t="inlineStr"/>
     </row>
@@ -35108,7 +35108,7 @@
       </c>
       <c r="F1597" t="inlineStr"/>
       <c r="G1597" t="n">
-        <v>60964834.287</v>
+        <v>60949984.644</v>
       </c>
       <c r="H1597" t="inlineStr"/>
     </row>
@@ -35130,7 +35130,7 @@
       </c>
       <c r="F1598" t="inlineStr"/>
       <c r="G1598" t="n">
-        <v>60977544.256</v>
+        <v>61008690.083</v>
       </c>
       <c r="H1598" t="inlineStr"/>
     </row>
@@ -35152,7 +35152,7 @@
       </c>
       <c r="F1599" t="inlineStr"/>
       <c r="G1599" t="n">
-        <v>61338903.813</v>
+        <v>61310669.16</v>
       </c>
       <c r="H1599" t="inlineStr"/>
     </row>
@@ -35173,15 +35173,21 @@
         <v>21.5625</v>
       </c>
       <c r="F1600" t="inlineStr"/>
-      <c r="G1600" t="inlineStr"/>
+      <c r="G1600" t="n">
+        <v>61354540.99</v>
+      </c>
       <c r="H1600" t="inlineStr"/>
     </row>
     <row r="1601">
       <c r="A1601" s="1" t="n">
         <v>46198</v>
       </c>
-      <c r="B1601" t="inlineStr"/>
-      <c r="C1601" t="inlineStr"/>
+      <c r="B1601" t="n">
+        <v>46968</v>
+      </c>
+      <c r="C1601" t="n">
+        <v>44451195</v>
+      </c>
       <c r="D1601" t="n">
         <v>1498.12</v>
       </c>
@@ -35189,22 +35195,126 @@
         <v>21.25</v>
       </c>
       <c r="F1601" t="inlineStr"/>
-      <c r="G1601" t="inlineStr"/>
+      <c r="G1601" t="n">
+        <v>62987011.162</v>
+      </c>
       <c r="H1601" t="inlineStr"/>
     </row>
     <row r="1602">
       <c r="A1602" s="1" t="n">
         <v>46199</v>
       </c>
-      <c r="B1602" t="inlineStr"/>
-      <c r="C1602" t="inlineStr"/>
+      <c r="B1602" t="n">
+        <v>47082</v>
+      </c>
+      <c r="C1602" t="n">
+        <v>43761087</v>
+      </c>
       <c r="D1602" t="n">
         <v>1495.57</v>
       </c>
-      <c r="E1602" t="inlineStr"/>
+      <c r="E1602" t="n">
+        <v>20.25</v>
+      </c>
       <c r="F1602" t="inlineStr"/>
-      <c r="G1602" t="inlineStr"/>
+      <c r="G1602" t="n">
+        <v>63958346.94</v>
+      </c>
       <c r="H1602" t="inlineStr"/>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B1603" t="n">
+        <v>46577</v>
+      </c>
+      <c r="C1603" t="n">
+        <v>44953461</v>
+      </c>
+      <c r="D1603" t="n">
+        <v>1498.22</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1603" t="inlineStr"/>
+      <c r="G1603" t="n">
+        <v>67282352.58499999</v>
+      </c>
+      <c r="H1603" t="inlineStr"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B1604" t="n">
+        <v>44870</v>
+      </c>
+      <c r="C1604" t="n">
+        <v>45711975</v>
+      </c>
+      <c r="D1604" t="n">
+        <v>1502.09</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1604" t="inlineStr"/>
+      <c r="G1604" t="n">
+        <v>70509860.788</v>
+      </c>
+      <c r="H1604" t="inlineStr"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B1605" t="n">
+        <v>47067</v>
+      </c>
+      <c r="C1605" t="n">
+        <v>46035751</v>
+      </c>
+      <c r="D1605" t="n">
+        <v>1511.11</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>20.9375</v>
+      </c>
+      <c r="F1605" t="inlineStr"/>
+      <c r="G1605" t="inlineStr"/>
+      <c r="H1605" t="inlineStr"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B1606" t="inlineStr"/>
+      <c r="C1606" t="inlineStr"/>
+      <c r="D1606" t="n">
+        <v>1512.64</v>
+      </c>
+      <c r="E1606" t="n">
+        <v>21.3125</v>
+      </c>
+      <c r="F1606" t="inlineStr"/>
+      <c r="G1606" t="inlineStr"/>
+      <c r="H1606" t="inlineStr"/>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B1607" t="inlineStr"/>
+      <c r="C1607" t="inlineStr"/>
+      <c r="D1607" t="n">
+        <v>1507.05</v>
+      </c>
+      <c r="E1607" t="inlineStr"/>
+      <c r="F1607" t="inlineStr"/>
+      <c r="G1607" t="inlineStr"/>
+      <c r="H1607" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1607"/>
+  <dimension ref="A1:H1610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.48</v>
+        <v>108.29</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.61</v>
+        <v>108.48</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.63</v>
+        <v>108.61</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.72</v>
+        <v>108.63</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.86</v>
+        <v>108.72</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.96</v>
+        <v>108.86</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.97</v>
+        <v>108.96</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>109.05</v>
+        <v>108.97</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.11</v>
+        <v>109.05</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.21</v>
+        <v>109.11</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.46</v>
+        <v>109.21</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.64</v>
+        <v>109.46</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.67</v>
+        <v>109.64</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.71</v>
+        <v>109.67</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.79</v>
+        <v>109.71</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>110.08</v>
+        <v>109.79</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.11</v>
+        <v>110.08</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.15</v>
+        <v>110.11</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.5</v>
+        <v>110.15</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.68</v>
+        <v>110.5</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.71</v>
+        <v>110.68</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.92</v>
+        <v>110.75</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>111.37</v>
+        <v>110.92</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.46</v>
+        <v>111.37</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.49</v>
+        <v>111.46</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.52</v>
+        <v>111.49</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.59</v>
+        <v>111.52</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.67</v>
+        <v>111.59</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>112.01</v>
+        <v>111.67</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.17</v>
+        <v>112.01</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.21</v>
+        <v>112.17</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.24</v>
+        <v>112.21</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.48</v>
+        <v>112.24</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.71</v>
+        <v>112.48</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.8</v>
+        <v>112.71</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.83</v>
+        <v>112.8</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.89</v>
+        <v>112.83</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.95</v>
+        <v>112.89</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57738916.056</v>
+        <v>57851193.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60140783.818</v>
+        <v>60140782.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60377527.102</v>
+        <v>60377522.102</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -33920,7 +33920,7 @@
         <v>23.8</v>
       </c>
       <c r="G1543" t="n">
-        <v>60856267.723</v>
+        <v>60856252.723</v>
       </c>
       <c r="H1543" t="n">
         <v>3.4</v>
@@ -34364,7 +34364,7 @@
         <v>24.2</v>
       </c>
       <c r="G1563" t="n">
-        <v>62688303.443</v>
+        <v>62688422.443</v>
       </c>
       <c r="H1563" t="n">
         <v>2.6</v>
@@ -34784,7 +34784,7 @@
       </c>
       <c r="F1582" t="inlineStr"/>
       <c r="G1582" t="n">
-        <v>63456427.9</v>
+        <v>63455403.9</v>
       </c>
       <c r="H1582" t="inlineStr"/>
     </row>
@@ -35064,7 +35064,7 @@
       </c>
       <c r="F1595" t="inlineStr"/>
       <c r="G1595" t="n">
-        <v>61076229.917</v>
+        <v>61081745.917</v>
       </c>
       <c r="H1595" t="inlineStr"/>
     </row>
@@ -35130,7 +35130,7 @@
       </c>
       <c r="F1598" t="inlineStr"/>
       <c r="G1598" t="n">
-        <v>61008690.083</v>
+        <v>61008692.083</v>
       </c>
       <c r="H1598" t="inlineStr"/>
     </row>
@@ -35152,7 +35152,7 @@
       </c>
       <c r="F1599" t="inlineStr"/>
       <c r="G1599" t="n">
-        <v>61310669.16</v>
+        <v>61307914.16</v>
       </c>
       <c r="H1599" t="inlineStr"/>
     </row>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="F1600" t="inlineStr"/>
       <c r="G1600" t="n">
-        <v>61354540.99</v>
+        <v>61349152.919</v>
       </c>
       <c r="H1600" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
       </c>
       <c r="F1601" t="inlineStr"/>
       <c r="G1601" t="n">
-        <v>62987011.162</v>
+        <v>62937164.868</v>
       </c>
       <c r="H1601" t="inlineStr"/>
     </row>
@@ -35218,7 +35218,7 @@
       </c>
       <c r="F1602" t="inlineStr"/>
       <c r="G1602" t="n">
-        <v>63958346.94</v>
+        <v>63873582.573</v>
       </c>
       <c r="H1602" t="inlineStr"/>
     </row>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="F1603" t="inlineStr"/>
       <c r="G1603" t="n">
-        <v>67282352.58499999</v>
+        <v>68463313.215</v>
       </c>
       <c r="H1603" t="inlineStr"/>
     </row>
@@ -35260,9 +35260,11 @@
       <c r="E1604" t="n">
         <v>21</v>
       </c>
-      <c r="F1604" t="inlineStr"/>
+      <c r="F1604" t="n">
+        <v>22.3</v>
+      </c>
       <c r="G1604" t="n">
-        <v>70509860.788</v>
+        <v>70406262.36499999</v>
       </c>
       <c r="H1604" t="inlineStr"/>
     </row>
@@ -35283,15 +35285,21 @@
         <v>20.9375</v>
       </c>
       <c r="F1605" t="inlineStr"/>
-      <c r="G1605" t="inlineStr"/>
+      <c r="G1605" t="n">
+        <v>71419580.325</v>
+      </c>
       <c r="H1605" t="inlineStr"/>
     </row>
     <row r="1606">
       <c r="A1606" s="1" t="n">
         <v>46205</v>
       </c>
-      <c r="B1606" t="inlineStr"/>
-      <c r="C1606" t="inlineStr"/>
+      <c r="B1606" t="n">
+        <v>47996</v>
+      </c>
+      <c r="C1606" t="n">
+        <v>45099295</v>
+      </c>
       <c r="D1606" t="n">
         <v>1512.64</v>
       </c>
@@ -35299,22 +35307,82 @@
         <v>21.3125</v>
       </c>
       <c r="F1606" t="inlineStr"/>
-      <c r="G1606" t="inlineStr"/>
+      <c r="G1606" t="n">
+        <v>70341084.71799999</v>
+      </c>
       <c r="H1606" t="inlineStr"/>
     </row>
     <row r="1607">
       <c r="A1607" s="1" t="n">
         <v>46206</v>
       </c>
-      <c r="B1607" t="inlineStr"/>
-      <c r="C1607" t="inlineStr"/>
+      <c r="B1607" t="n">
+        <v>48241</v>
+      </c>
+      <c r="C1607" t="n">
+        <v>45368949</v>
+      </c>
       <c r="D1607" t="n">
         <v>1507.05</v>
       </c>
-      <c r="E1607" t="inlineStr"/>
+      <c r="E1607" t="n">
+        <v>20.8125</v>
+      </c>
       <c r="F1607" t="inlineStr"/>
-      <c r="G1607" t="inlineStr"/>
+      <c r="G1607" t="n">
+        <v>70598095.941</v>
+      </c>
       <c r="H1607" t="inlineStr"/>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B1608" t="n">
+        <v>48273</v>
+      </c>
+      <c r="C1608" t="n">
+        <v>45569923</v>
+      </c>
+      <c r="D1608" t="n">
+        <v>1512.5</v>
+      </c>
+      <c r="E1608" t="n">
+        <v>20.3125</v>
+      </c>
+      <c r="F1608" t="inlineStr"/>
+      <c r="G1608" t="inlineStr"/>
+      <c r="H1608" t="inlineStr"/>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B1609" t="inlineStr"/>
+      <c r="C1609" t="inlineStr"/>
+      <c r="D1609" t="n">
+        <v>1513.07</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1609" t="inlineStr"/>
+      <c r="G1609" t="inlineStr"/>
+      <c r="H1609" t="inlineStr"/>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B1610" t="inlineStr"/>
+      <c r="C1610" t="inlineStr"/>
+      <c r="D1610" t="n">
+        <v>1513.22</v>
+      </c>
+      <c r="E1610" t="inlineStr"/>
+      <c r="F1610" t="inlineStr"/>
+      <c r="G1610" t="inlineStr"/>
+      <c r="H1610" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1610"/>
+  <dimension ref="A1:H1615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="F1337" t="inlineStr"/>
       <c r="G1337" t="n">
-        <v>51108699.335</v>
+        <v>51107673.335</v>
       </c>
       <c r="H1337" t="inlineStr"/>
     </row>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="F1339" t="inlineStr"/>
       <c r="G1339" t="n">
-        <v>50263288.099</v>
+        <v>50262264.099</v>
       </c>
       <c r="H1339" t="inlineStr"/>
     </row>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="F1340" t="inlineStr"/>
       <c r="G1340" t="n">
-        <v>50104901.2</v>
+        <v>50103876.2</v>
       </c>
       <c r="H1340" t="inlineStr"/>
     </row>
@@ -29488,7 +29488,7 @@
       </c>
       <c r="F1341" t="inlineStr"/>
       <c r="G1341" t="n">
-        <v>50621412.622</v>
+        <v>50620386.622</v>
       </c>
       <c r="H1341" t="inlineStr"/>
     </row>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="F1342" t="inlineStr"/>
       <c r="G1342" t="n">
-        <v>51314544.846</v>
+        <v>51313519.846</v>
       </c>
       <c r="H1342" t="inlineStr"/>
     </row>
@@ -29532,7 +29532,7 @@
       </c>
       <c r="F1343" t="inlineStr"/>
       <c r="G1343" t="n">
-        <v>49787923.676</v>
+        <v>49786898.676</v>
       </c>
       <c r="H1343" t="inlineStr"/>
     </row>
@@ -29554,7 +29554,7 @@
       </c>
       <c r="F1344" t="inlineStr"/>
       <c r="G1344" t="n">
-        <v>49516455.468</v>
+        <v>49515431.468</v>
       </c>
       <c r="H1344" t="inlineStr"/>
     </row>
@@ -29576,7 +29576,7 @@
       </c>
       <c r="F1345" t="inlineStr"/>
       <c r="G1345" t="n">
-        <v>48925218.358</v>
+        <v>48924193.358</v>
       </c>
       <c r="H1345" t="inlineStr"/>
     </row>
@@ -29598,7 +29598,7 @@
       </c>
       <c r="F1346" t="inlineStr"/>
       <c r="G1346" t="n">
-        <v>49396994.152</v>
+        <v>49395968.152</v>
       </c>
       <c r="H1346" t="inlineStr"/>
     </row>
@@ -29620,7 +29620,7 @@
       </c>
       <c r="F1347" t="inlineStr"/>
       <c r="G1347" t="n">
-        <v>49069360.486</v>
+        <v>49068336.486</v>
       </c>
       <c r="H1347" t="inlineStr"/>
     </row>
@@ -29642,7 +29642,7 @@
       </c>
       <c r="F1348" t="inlineStr"/>
       <c r="G1348" t="n">
-        <v>49132002.452</v>
+        <v>49130977.452</v>
       </c>
       <c r="H1348" t="inlineStr"/>
     </row>
@@ -29664,7 +29664,7 @@
       </c>
       <c r="F1349" t="inlineStr"/>
       <c r="G1349" t="n">
-        <v>49198371.726</v>
+        <v>49197347.726</v>
       </c>
       <c r="H1349" t="inlineStr"/>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="F1350" t="inlineStr"/>
       <c r="G1350" t="n">
-        <v>49597800.914</v>
+        <v>49596775.914</v>
       </c>
       <c r="H1350" t="inlineStr"/>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="F1351" t="inlineStr"/>
       <c r="G1351" t="n">
-        <v>49107815.391</v>
+        <v>49106790.391</v>
       </c>
       <c r="H1351" t="inlineStr"/>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="F1352" t="inlineStr"/>
       <c r="G1352" t="n">
-        <v>49691795.724</v>
+        <v>49690769.724</v>
       </c>
       <c r="H1352" t="inlineStr"/>
     </row>
@@ -29752,7 +29752,7 @@
       </c>
       <c r="F1353" t="inlineStr"/>
       <c r="G1353" t="n">
-        <v>50164334.696</v>
+        <v>50163310.696</v>
       </c>
       <c r="H1353" t="inlineStr"/>
     </row>
@@ -29774,7 +29774,7 @@
       </c>
       <c r="F1354" t="inlineStr"/>
       <c r="G1354" t="n">
-        <v>50577249.767</v>
+        <v>50576224.767</v>
       </c>
       <c r="H1354" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
       </c>
       <c r="F1355" t="inlineStr"/>
       <c r="G1355" t="n">
-        <v>52847683.995</v>
+        <v>52846658.995</v>
       </c>
       <c r="H1355" t="inlineStr"/>
     </row>
@@ -29818,7 +29818,7 @@
       </c>
       <c r="F1356" t="inlineStr"/>
       <c r="G1356" t="n">
-        <v>53900981.682</v>
+        <v>53899955.682</v>
       </c>
       <c r="H1356" t="inlineStr"/>
     </row>
@@ -34388,7 +34388,7 @@
       </c>
       <c r="F1564" t="inlineStr"/>
       <c r="G1564" t="n">
-        <v>60731125.828</v>
+        <v>60731235.828</v>
       </c>
       <c r="H1564" t="inlineStr"/>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="F1565" t="inlineStr"/>
       <c r="G1565" t="n">
-        <v>60125054.987</v>
+        <v>60125064.987</v>
       </c>
       <c r="H1565" t="inlineStr"/>
     </row>
@@ -34432,7 +34432,7 @@
       </c>
       <c r="F1566" t="inlineStr"/>
       <c r="G1566" t="n">
-        <v>60067678.457</v>
+        <v>60067676.457</v>
       </c>
       <c r="H1566" t="inlineStr"/>
     </row>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="F1567" t="inlineStr"/>
       <c r="G1567" t="n">
-        <v>60734761.321</v>
+        <v>60734769.321</v>
       </c>
       <c r="H1567" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
       </c>
       <c r="F1568" t="inlineStr"/>
       <c r="G1568" t="n">
-        <v>59028364.089</v>
+        <v>59028363.089</v>
       </c>
       <c r="H1568" t="inlineStr"/>
     </row>
@@ -34498,7 +34498,7 @@
       </c>
       <c r="F1569" t="inlineStr"/>
       <c r="G1569" t="n">
-        <v>58185748.149</v>
+        <v>58185751.149</v>
       </c>
       <c r="H1569" t="inlineStr"/>
     </row>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="n">
-        <v>57616407.887</v>
+        <v>57616409.887</v>
       </c>
       <c r="H1570" t="inlineStr"/>
     </row>
@@ -34542,7 +34542,7 @@
       </c>
       <c r="F1571" t="inlineStr"/>
       <c r="G1571" t="n">
-        <v>57625212.677</v>
+        <v>57625223.677</v>
       </c>
       <c r="H1571" t="inlineStr"/>
     </row>
@@ -34564,7 +34564,7 @@
       </c>
       <c r="F1572" t="inlineStr"/>
       <c r="G1572" t="n">
-        <v>57692358.026</v>
+        <v>57692366.026</v>
       </c>
       <c r="H1572" t="inlineStr"/>
     </row>
@@ -34586,7 +34586,7 @@
       </c>
       <c r="F1573" t="inlineStr"/>
       <c r="G1573" t="n">
-        <v>58028430.6</v>
+        <v>58028441.6</v>
       </c>
       <c r="H1573" t="inlineStr"/>
     </row>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="F1574" t="inlineStr"/>
       <c r="G1574" t="n">
-        <v>56580209.718</v>
+        <v>56580206.718</v>
       </c>
       <c r="H1574" t="inlineStr"/>
     </row>
@@ -34630,7 +34630,7 @@
       </c>
       <c r="F1575" t="inlineStr"/>
       <c r="G1575" t="n">
-        <v>56533813.683</v>
+        <v>56533814.683</v>
       </c>
       <c r="H1575" t="inlineStr"/>
     </row>
@@ -34652,7 +34652,7 @@
       </c>
       <c r="F1576" t="inlineStr"/>
       <c r="G1576" t="n">
-        <v>56518774.473</v>
+        <v>56518778.473</v>
       </c>
       <c r="H1576" t="inlineStr"/>
     </row>
@@ -34674,7 +34674,7 @@
       </c>
       <c r="F1577" t="inlineStr"/>
       <c r="G1577" t="n">
-        <v>56615129.751</v>
+        <v>56615131.751</v>
       </c>
       <c r="H1577" t="inlineStr"/>
     </row>
@@ -34696,7 +34696,7 @@
       </c>
       <c r="F1578" t="inlineStr"/>
       <c r="G1578" t="n">
-        <v>56497122.527</v>
+        <v>56497124.527</v>
       </c>
       <c r="H1578" t="inlineStr"/>
     </row>
@@ -34718,7 +34718,7 @@
       </c>
       <c r="F1579" t="inlineStr"/>
       <c r="G1579" t="n">
-        <v>57013567.328</v>
+        <v>57013570.328</v>
       </c>
       <c r="H1579" t="inlineStr"/>
     </row>
@@ -34740,7 +34740,7 @@
       </c>
       <c r="F1580" t="inlineStr"/>
       <c r="G1580" t="n">
-        <v>57904028.253</v>
+        <v>57904032.253</v>
       </c>
       <c r="H1580" t="inlineStr"/>
     </row>
@@ -34762,7 +34762,7 @@
       </c>
       <c r="F1581" t="inlineStr"/>
       <c r="G1581" t="n">
-        <v>59897249.035</v>
+        <v>59897314.035</v>
       </c>
       <c r="H1581" t="inlineStr"/>
     </row>
@@ -34784,7 +34784,7 @@
       </c>
       <c r="F1582" t="inlineStr"/>
       <c r="G1582" t="n">
-        <v>63455403.9</v>
+        <v>63455187.9</v>
       </c>
       <c r="H1582" t="inlineStr"/>
     </row>
@@ -35086,7 +35086,7 @@
       </c>
       <c r="F1596" t="inlineStr"/>
       <c r="G1596" t="n">
-        <v>61211556.503</v>
+        <v>61219718.503</v>
       </c>
       <c r="H1596" t="inlineStr"/>
     </row>
@@ -35108,7 +35108,7 @@
       </c>
       <c r="F1597" t="inlineStr"/>
       <c r="G1597" t="n">
-        <v>60949984.644</v>
+        <v>60957928.644</v>
       </c>
       <c r="H1597" t="inlineStr"/>
     </row>
@@ -35130,7 +35130,7 @@
       </c>
       <c r="F1598" t="inlineStr"/>
       <c r="G1598" t="n">
-        <v>61008692.083</v>
+        <v>61017977.083</v>
       </c>
       <c r="H1598" t="inlineStr"/>
     </row>
@@ -35152,7 +35152,7 @@
       </c>
       <c r="F1599" t="inlineStr"/>
       <c r="G1599" t="n">
-        <v>61307914.16</v>
+        <v>61317727.16</v>
       </c>
       <c r="H1599" t="inlineStr"/>
     </row>
@@ -35218,7 +35218,7 @@
       </c>
       <c r="F1602" t="inlineStr"/>
       <c r="G1602" t="n">
-        <v>63873582.573</v>
+        <v>63919260.573</v>
       </c>
       <c r="H1602" t="inlineStr"/>
     </row>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="F1603" t="inlineStr"/>
       <c r="G1603" t="n">
-        <v>68463313.215</v>
+        <v>68438528.31200001</v>
       </c>
       <c r="H1603" t="inlineStr"/>
     </row>
@@ -35264,9 +35264,11 @@
         <v>22.3</v>
       </c>
       <c r="G1604" t="n">
-        <v>70406262.36499999</v>
-      </c>
-      <c r="H1604" t="inlineStr"/>
+        <v>70389412.197</v>
+      </c>
+      <c r="H1604" t="n">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="1605">
       <c r="A1605" s="1" t="n">
@@ -35286,7 +35288,7 @@
       </c>
       <c r="F1605" t="inlineStr"/>
       <c r="G1605" t="n">
-        <v>71419580.325</v>
+        <v>70636972.21600001</v>
       </c>
       <c r="H1605" t="inlineStr"/>
     </row>
@@ -35308,7 +35310,7 @@
       </c>
       <c r="F1606" t="inlineStr"/>
       <c r="G1606" t="n">
-        <v>70341084.71799999</v>
+        <v>70301736.822</v>
       </c>
       <c r="H1606" t="inlineStr"/>
     </row>
@@ -35330,7 +35332,7 @@
       </c>
       <c r="F1607" t="inlineStr"/>
       <c r="G1607" t="n">
-        <v>70598095.941</v>
+        <v>70595088.83499999</v>
       </c>
       <c r="H1607" t="inlineStr"/>
     </row>
@@ -35351,15 +35353,21 @@
         <v>20.3125</v>
       </c>
       <c r="F1608" t="inlineStr"/>
-      <c r="G1608" t="inlineStr"/>
+      <c r="G1608" t="n">
+        <v>70201731.022</v>
+      </c>
       <c r="H1608" t="inlineStr"/>
     </row>
     <row r="1609">
       <c r="A1609" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="B1609" t="inlineStr"/>
-      <c r="C1609" t="inlineStr"/>
+      <c r="B1609" t="n">
+        <v>49535</v>
+      </c>
+      <c r="C1609" t="n">
+        <v>45511522</v>
+      </c>
       <c r="D1609" t="n">
         <v>1513.07</v>
       </c>
@@ -35367,22 +35375,126 @@
         <v>21</v>
       </c>
       <c r="F1609" t="inlineStr"/>
-      <c r="G1609" t="inlineStr"/>
+      <c r="G1609" t="n">
+        <v>69883335.862</v>
+      </c>
       <c r="H1609" t="inlineStr"/>
     </row>
     <row r="1610">
       <c r="A1610" s="1" t="n">
         <v>46211</v>
       </c>
-      <c r="B1610" t="inlineStr"/>
-      <c r="C1610" t="inlineStr"/>
+      <c r="B1610" t="n">
+        <v>48724</v>
+      </c>
+      <c r="C1610" t="n">
+        <v>45827619</v>
+      </c>
       <c r="D1610" t="n">
         <v>1513.22</v>
       </c>
-      <c r="E1610" t="inlineStr"/>
+      <c r="E1610" t="n">
+        <v>20.5</v>
+      </c>
       <c r="F1610" t="inlineStr"/>
-      <c r="G1610" t="inlineStr"/>
+      <c r="G1610" t="n">
+        <v>70035045.359</v>
+      </c>
       <c r="H1610" t="inlineStr"/>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B1611" t="n">
+        <v>48208</v>
+      </c>
+      <c r="C1611" t="n">
+        <v>46817025</v>
+      </c>
+      <c r="D1611" t="n">
+        <v>1508.83</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1611" t="inlineStr"/>
+      <c r="G1611" t="n">
+        <v>67151032.69</v>
+      </c>
+      <c r="H1611" t="inlineStr"/>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B1612" t="n">
+        <v>48687</v>
+      </c>
+      <c r="C1612" t="n">
+        <v>45312132</v>
+      </c>
+      <c r="D1612" t="n">
+        <v>1500.76</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>21.3125</v>
+      </c>
+      <c r="F1612" t="inlineStr"/>
+      <c r="G1612" t="n">
+        <v>66482022.426</v>
+      </c>
+      <c r="H1612" t="inlineStr"/>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B1613" t="n">
+        <v>48617</v>
+      </c>
+      <c r="C1613" t="n">
+        <v>45210224</v>
+      </c>
+      <c r="D1613" t="n">
+        <v>1497.61</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="F1613" t="inlineStr"/>
+      <c r="G1613" t="inlineStr"/>
+      <c r="H1613" t="inlineStr"/>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B1614" t="inlineStr"/>
+      <c r="C1614" t="inlineStr"/>
+      <c r="D1614" t="n">
+        <v>1495.93</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1614" t="inlineStr"/>
+      <c r="G1614" t="inlineStr"/>
+      <c r="H1614" t="inlineStr"/>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B1615" t="inlineStr"/>
+      <c r="C1615" t="inlineStr"/>
+      <c r="D1615" t="n">
+        <v>1501.67</v>
+      </c>
+      <c r="E1615" t="inlineStr"/>
+      <c r="F1615" t="inlineStr"/>
+      <c r="G1615" t="inlineStr"/>
+      <c r="H1615" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1615"/>
+  <dimension ref="A1:H1620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57851193.056</v>
+        <v>57851174.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="n">
-        <v>56669687.267</v>
+        <v>56669668.267</v>
       </c>
       <c r="H1358" t="inlineStr"/>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="F1359" t="inlineStr"/>
       <c r="G1359" t="n">
-        <v>56029599.372</v>
+        <v>56029580.372</v>
       </c>
       <c r="H1359" t="inlineStr"/>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="n">
-        <v>56588557.504</v>
+        <v>56588538.504</v>
       </c>
       <c r="H1360" t="inlineStr"/>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="n">
-        <v>56826425.839</v>
+        <v>56826406.839</v>
       </c>
       <c r="H1361" t="inlineStr"/>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="n">
-        <v>55507104.571</v>
+        <v>55507085.571</v>
       </c>
       <c r="H1362" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="n">
-        <v>55317108.556</v>
+        <v>55317089.556</v>
       </c>
       <c r="H1363" t="inlineStr"/>
     </row>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="n">
-        <v>54530583.68</v>
+        <v>54530563.68</v>
       </c>
       <c r="H1364" t="inlineStr"/>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="n">
-        <v>53951995.241</v>
+        <v>53951975.241</v>
       </c>
       <c r="H1365" t="inlineStr"/>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="n">
-        <v>53559399.918</v>
+        <v>53559380.918</v>
       </c>
       <c r="H1366" t="inlineStr"/>
     </row>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F1367" t="inlineStr"/>
       <c r="G1367" t="n">
-        <v>53693193.53</v>
+        <v>53693173.53</v>
       </c>
       <c r="H1367" t="inlineStr"/>
     </row>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="n">
-        <v>52779315.228</v>
+        <v>52779296.228</v>
       </c>
       <c r="H1368" t="inlineStr"/>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53008451.434</v>
+        <v>53008432.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30130,7 +30130,7 @@
       </c>
       <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="n">
-        <v>52789881.166</v>
+        <v>52789862.166</v>
       </c>
       <c r="H1370" t="inlineStr"/>
     </row>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="F1371" t="inlineStr"/>
       <c r="G1371" t="n">
-        <v>52579570.418</v>
+        <v>52579551.418</v>
       </c>
       <c r="H1371" t="inlineStr"/>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="n">
-        <v>52219551.099</v>
+        <v>52219532.099</v>
       </c>
       <c r="H1372" t="inlineStr"/>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="n">
-        <v>52314943.713</v>
+        <v>52314924.713</v>
       </c>
       <c r="H1373" t="inlineStr"/>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="n">
-        <v>52858341.596</v>
+        <v>52858322.596</v>
       </c>
       <c r="H1374" t="inlineStr"/>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="n">
-        <v>52208922.178</v>
+        <v>52208903.178</v>
       </c>
       <c r="H1375" t="inlineStr"/>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="n">
-        <v>52590298.503</v>
+        <v>52590279.503</v>
       </c>
       <c r="H1376" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="n">
-        <v>52809701.197</v>
+        <v>52809682.197</v>
       </c>
       <c r="H1377" t="inlineStr"/>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="n">
-        <v>54082611.568</v>
+        <v>54082592.568</v>
       </c>
       <c r="H1378" t="inlineStr"/>
     </row>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="F1600" t="inlineStr"/>
       <c r="G1600" t="n">
-        <v>61349152.919</v>
+        <v>61352968.919</v>
       </c>
       <c r="H1600" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
       </c>
       <c r="F1601" t="inlineStr"/>
       <c r="G1601" t="n">
-        <v>62937164.868</v>
+        <v>62943174.868</v>
       </c>
       <c r="H1601" t="inlineStr"/>
     </row>
@@ -35264,7 +35264,7 @@
         <v>22.3</v>
       </c>
       <c r="G1604" t="n">
-        <v>70389412.197</v>
+        <v>70419914.642</v>
       </c>
       <c r="H1604" t="n">
         <v>1.9</v>
@@ -35288,7 +35288,7 @@
       </c>
       <c r="F1605" t="inlineStr"/>
       <c r="G1605" t="n">
-        <v>70636972.21600001</v>
+        <v>70635006.21600001</v>
       </c>
       <c r="H1605" t="inlineStr"/>
     </row>
@@ -35310,7 +35310,7 @@
       </c>
       <c r="F1606" t="inlineStr"/>
       <c r="G1606" t="n">
-        <v>70301736.822</v>
+        <v>70299771.822</v>
       </c>
       <c r="H1606" t="inlineStr"/>
     </row>
@@ -35332,7 +35332,7 @@
       </c>
       <c r="F1607" t="inlineStr"/>
       <c r="G1607" t="n">
-        <v>70595088.83499999</v>
+        <v>70580487.83499999</v>
       </c>
       <c r="H1607" t="inlineStr"/>
     </row>
@@ -35354,7 +35354,7 @@
       </c>
       <c r="F1608" t="inlineStr"/>
       <c r="G1608" t="n">
-        <v>70201731.022</v>
+        <v>70224278.022</v>
       </c>
       <c r="H1608" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
       </c>
       <c r="F1609" t="inlineStr"/>
       <c r="G1609" t="n">
-        <v>69883335.862</v>
+        <v>69896072.40099999</v>
       </c>
       <c r="H1609" t="inlineStr"/>
     </row>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="F1610" t="inlineStr"/>
       <c r="G1610" t="n">
-        <v>70035045.359</v>
+        <v>69964193.51100001</v>
       </c>
       <c r="H1610" t="inlineStr"/>
     </row>
@@ -35420,7 +35420,7 @@
       </c>
       <c r="F1611" t="inlineStr"/>
       <c r="G1611" t="n">
-        <v>67151032.69</v>
+        <v>67066586.292</v>
       </c>
       <c r="H1611" t="inlineStr"/>
     </row>
@@ -35442,7 +35442,7 @@
       </c>
       <c r="F1612" t="inlineStr"/>
       <c r="G1612" t="n">
-        <v>66482022.426</v>
+        <v>66298497.61</v>
       </c>
       <c r="H1612" t="inlineStr"/>
     </row>
@@ -35463,15 +35463,21 @@
         <v>21.875</v>
       </c>
       <c r="F1613" t="inlineStr"/>
-      <c r="G1613" t="inlineStr"/>
+      <c r="G1613" t="n">
+        <v>65297143.72</v>
+      </c>
       <c r="H1613" t="inlineStr"/>
     </row>
     <row r="1614">
       <c r="A1614" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="B1614" t="inlineStr"/>
-      <c r="C1614" t="inlineStr"/>
+      <c r="B1614" t="n">
+        <v>48530</v>
+      </c>
+      <c r="C1614" t="n">
+        <v>46019844</v>
+      </c>
       <c r="D1614" t="n">
         <v>1495.93</v>
       </c>
@@ -35479,22 +35485,126 @@
         <v>21</v>
       </c>
       <c r="F1614" t="inlineStr"/>
-      <c r="G1614" t="inlineStr"/>
+      <c r="G1614" t="n">
+        <v>65479549.226</v>
+      </c>
       <c r="H1614" t="inlineStr"/>
     </row>
     <row r="1615">
       <c r="A1615" s="1" t="n">
         <v>46220</v>
       </c>
-      <c r="B1615" t="inlineStr"/>
-      <c r="C1615" t="inlineStr"/>
+      <c r="B1615" t="n">
+        <v>48790</v>
+      </c>
+      <c r="C1615" t="n">
+        <v>45054096</v>
+      </c>
       <c r="D1615" t="n">
         <v>1501.67</v>
       </c>
-      <c r="E1615" t="inlineStr"/>
+      <c r="E1615" t="n">
+        <v>21.6875</v>
+      </c>
       <c r="F1615" t="inlineStr"/>
-      <c r="G1615" t="inlineStr"/>
+      <c r="G1615" t="n">
+        <v>64047105.272</v>
+      </c>
       <c r="H1615" t="inlineStr"/>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B1616" t="n">
+        <v>48809</v>
+      </c>
+      <c r="C1616" t="n">
+        <v>45661395</v>
+      </c>
+      <c r="D1616" t="n">
+        <v>1502.04</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>21.125</v>
+      </c>
+      <c r="F1616" t="inlineStr"/>
+      <c r="G1616" t="n">
+        <v>64527312.022</v>
+      </c>
+      <c r="H1616" t="inlineStr"/>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B1617" t="n">
+        <v>48921</v>
+      </c>
+      <c r="C1617" t="n">
+        <v>45294415</v>
+      </c>
+      <c r="D1617" t="n">
+        <v>1498.4</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>21.875</v>
+      </c>
+      <c r="F1617" t="inlineStr"/>
+      <c r="G1617" t="n">
+        <v>64151259.111</v>
+      </c>
+      <c r="H1617" t="inlineStr"/>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B1618" t="n">
+        <v>49036</v>
+      </c>
+      <c r="C1618" t="n">
+        <v>45839793</v>
+      </c>
+      <c r="D1618" t="n">
+        <v>1502.35</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1618" t="inlineStr"/>
+      <c r="G1618" t="inlineStr"/>
+      <c r="H1618" t="inlineStr"/>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B1619" t="inlineStr"/>
+      <c r="C1619" t="inlineStr"/>
+      <c r="D1619" t="n">
+        <v>1510.8</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>22.1875</v>
+      </c>
+      <c r="F1619" t="inlineStr"/>
+      <c r="G1619" t="inlineStr"/>
+      <c r="H1619" t="inlineStr"/>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B1620" t="inlineStr"/>
+      <c r="C1620" t="inlineStr"/>
+      <c r="D1620" t="n">
+        <v>1518.86</v>
+      </c>
+      <c r="E1620" t="inlineStr"/>
+      <c r="F1620" t="inlineStr"/>
+      <c r="G1620" t="inlineStr"/>
+      <c r="H1620" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1620"/>
+  <dimension ref="A1:H1625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28188,7 +28188,7 @@
       </c>
       <c r="F1282" t="inlineStr"/>
       <c r="G1282" t="n">
-        <v>48328769.475</v>
+        <v>48322801.475</v>
       </c>
       <c r="H1282" t="inlineStr"/>
     </row>
@@ -28210,7 +28210,7 @@
       </c>
       <c r="F1283" t="inlineStr"/>
       <c r="G1283" t="n">
-        <v>48336198.734</v>
+        <v>48321156.734</v>
       </c>
       <c r="H1283" t="inlineStr"/>
     </row>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="F1284" t="inlineStr"/>
       <c r="G1284" t="n">
-        <v>46569989.614</v>
+        <v>46554947.614</v>
       </c>
       <c r="H1284" t="inlineStr"/>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="F1285" t="inlineStr"/>
       <c r="G1285" t="n">
-        <v>46020323.384</v>
+        <v>46005280.384</v>
       </c>
       <c r="H1285" t="inlineStr"/>
     </row>
@@ -28276,7 +28276,7 @@
       </c>
       <c r="F1286" t="inlineStr"/>
       <c r="G1286" t="n">
-        <v>45853774.348</v>
+        <v>45838732.348</v>
       </c>
       <c r="H1286" t="inlineStr"/>
     </row>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="F1287" t="inlineStr"/>
       <c r="G1287" t="n">
-        <v>46136403.268</v>
+        <v>46113624.268</v>
       </c>
       <c r="H1287" t="inlineStr"/>
     </row>
@@ -28320,7 +28320,7 @@
       </c>
       <c r="F1288" t="inlineStr"/>
       <c r="G1288" t="n">
-        <v>46150853.624</v>
+        <v>46128074.624</v>
       </c>
       <c r="H1288" t="inlineStr"/>
     </row>
@@ -28342,7 +28342,7 @@
       </c>
       <c r="F1289" t="inlineStr"/>
       <c r="G1289" t="n">
-        <v>45440043.744</v>
+        <v>45417264.744</v>
       </c>
       <c r="H1289" t="inlineStr"/>
     </row>
@@ -28364,7 +28364,7 @@
       </c>
       <c r="F1290" t="inlineStr"/>
       <c r="G1290" t="n">
-        <v>45462223.72</v>
+        <v>45439444.72</v>
       </c>
       <c r="H1290" t="inlineStr"/>
     </row>
@@ -28386,7 +28386,7 @@
       </c>
       <c r="F1291" t="inlineStr"/>
       <c r="G1291" t="n">
-        <v>45753992.502</v>
+        <v>45731213.502</v>
       </c>
       <c r="H1291" t="inlineStr"/>
     </row>
@@ -28408,7 +28408,7 @@
       </c>
       <c r="F1292" t="inlineStr"/>
       <c r="G1292" t="n">
-        <v>45684933.131</v>
+        <v>45662154.131</v>
       </c>
       <c r="H1292" t="inlineStr"/>
     </row>
@@ -28430,7 +28430,7 @@
       </c>
       <c r="F1293" t="inlineStr"/>
       <c r="G1293" t="n">
-        <v>45885958.473</v>
+        <v>45863179.473</v>
       </c>
       <c r="H1293" t="inlineStr"/>
     </row>
@@ -28452,7 +28452,7 @@
       </c>
       <c r="F1294" t="inlineStr"/>
       <c r="G1294" t="n">
-        <v>46106105.998</v>
+        <v>46063546.998</v>
       </c>
       <c r="H1294" t="inlineStr"/>
     </row>
@@ -28474,7 +28474,7 @@
       </c>
       <c r="F1295" t="inlineStr"/>
       <c r="G1295" t="n">
-        <v>46492305.702</v>
+        <v>46449746.702</v>
       </c>
       <c r="H1295" t="inlineStr"/>
     </row>
@@ -28496,7 +28496,7 @@
       </c>
       <c r="F1296" t="inlineStr"/>
       <c r="G1296" t="n">
-        <v>46832116.161</v>
+        <v>46789558.161</v>
       </c>
       <c r="H1296" t="inlineStr"/>
     </row>
@@ -28518,7 +28518,7 @@
       </c>
       <c r="F1297" t="inlineStr"/>
       <c r="G1297" t="n">
-        <v>47958273.473</v>
+        <v>47915714.473</v>
       </c>
       <c r="H1297" t="inlineStr"/>
     </row>
@@ -28964,7 +28964,7 @@
         <v>26.3</v>
       </c>
       <c r="G1317" t="n">
-        <v>51201565.522</v>
+        <v>51200765.522</v>
       </c>
       <c r="H1317" t="n">
         <v>2.8</v>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="F1318" t="inlineStr"/>
       <c r="G1318" t="n">
-        <v>50648619.384</v>
+        <v>50654414.384</v>
       </c>
       <c r="H1318" t="inlineStr"/>
     </row>
@@ -29010,7 +29010,7 @@
       </c>
       <c r="F1319" t="inlineStr"/>
       <c r="G1319" t="n">
-        <v>50109486.371</v>
+        <v>50113704.371</v>
       </c>
       <c r="H1319" t="inlineStr"/>
     </row>
@@ -29032,7 +29032,7 @@
       </c>
       <c r="F1320" t="inlineStr"/>
       <c r="G1320" t="n">
-        <v>50589193.593</v>
+        <v>50594625.593</v>
       </c>
       <c r="H1320" t="inlineStr"/>
     </row>
@@ -29054,7 +29054,7 @@
       </c>
       <c r="F1321" t="inlineStr"/>
       <c r="G1321" t="n">
-        <v>49951751.095</v>
+        <v>49955853.095</v>
       </c>
       <c r="H1321" t="inlineStr"/>
     </row>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="F1322" t="inlineStr"/>
       <c r="G1322" t="n">
-        <v>48849641.5</v>
+        <v>48853332.5</v>
       </c>
       <c r="H1322" t="inlineStr"/>
     </row>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="F1323" t="inlineStr"/>
       <c r="G1323" t="n">
-        <v>47672331.888</v>
+        <v>47678478.888</v>
       </c>
       <c r="H1323" t="inlineStr"/>
     </row>
@@ -29120,7 +29120,7 @@
       </c>
       <c r="F1324" t="inlineStr"/>
       <c r="G1324" t="n">
-        <v>47135373.957</v>
+        <v>47141482.957</v>
       </c>
       <c r="H1324" t="inlineStr"/>
     </row>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="F1325" t="inlineStr"/>
       <c r="G1325" t="n">
-        <v>47120778.466</v>
+        <v>47128916.466</v>
       </c>
       <c r="H1325" t="inlineStr"/>
     </row>
@@ -29164,7 +29164,7 @@
       </c>
       <c r="F1326" t="inlineStr"/>
       <c r="G1326" t="n">
-        <v>47381348.259</v>
+        <v>47390892.259</v>
       </c>
       <c r="H1326" t="inlineStr"/>
     </row>
@@ -29186,7 +29186,7 @@
       </c>
       <c r="F1327" t="inlineStr"/>
       <c r="G1327" t="n">
-        <v>46691432.658</v>
+        <v>46701768.658</v>
       </c>
       <c r="H1327" t="inlineStr"/>
     </row>
@@ -29208,7 +29208,7 @@
       </c>
       <c r="F1328" t="inlineStr"/>
       <c r="G1328" t="n">
-        <v>46322277.919</v>
+        <v>46331322.919</v>
       </c>
       <c r="H1328" t="inlineStr"/>
     </row>
@@ -29230,7 +29230,7 @@
       </c>
       <c r="F1329" t="inlineStr"/>
       <c r="G1329" t="n">
-        <v>46041774.839</v>
+        <v>46049625.839</v>
       </c>
       <c r="H1329" t="inlineStr"/>
     </row>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="F1330" t="inlineStr"/>
       <c r="G1330" t="n">
-        <v>46171959.497</v>
+        <v>46180967.497</v>
       </c>
       <c r="H1330" t="inlineStr"/>
     </row>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="F1331" t="inlineStr"/>
       <c r="G1331" t="n">
-        <v>46164806.925</v>
+        <v>46174336.925</v>
       </c>
       <c r="H1331" t="inlineStr"/>
     </row>
@@ -29296,7 +29296,7 @@
       </c>
       <c r="F1332" t="inlineStr"/>
       <c r="G1332" t="n">
-        <v>46027039.945</v>
+        <v>46036853.945</v>
       </c>
       <c r="H1332" t="inlineStr"/>
     </row>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="F1333" t="inlineStr"/>
       <c r="G1333" t="n">
-        <v>46302832.278</v>
+        <v>46312273.278</v>
       </c>
       <c r="H1333" t="inlineStr"/>
     </row>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="F1334" t="inlineStr"/>
       <c r="G1334" t="n">
-        <v>46700006.056</v>
+        <v>46709112.056</v>
       </c>
       <c r="H1334" t="inlineStr"/>
     </row>
@@ -29362,7 +29362,7 @@
       </c>
       <c r="F1335" t="inlineStr"/>
       <c r="G1335" t="n">
-        <v>47691055.807</v>
+        <v>47700487.807</v>
       </c>
       <c r="H1335" t="inlineStr"/>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="F1336" t="inlineStr"/>
       <c r="G1336" t="n">
-        <v>48949973.485</v>
+        <v>48960544.485</v>
       </c>
       <c r="H1336" t="inlineStr"/>
     </row>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="F1339" t="inlineStr"/>
       <c r="G1339" t="n">
-        <v>50262264.099</v>
+        <v>50254412.099</v>
       </c>
       <c r="H1339" t="inlineStr"/>
     </row>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="F1340" t="inlineStr"/>
       <c r="G1340" t="n">
-        <v>50103876.2</v>
+        <v>50096175.2</v>
       </c>
       <c r="H1340" t="inlineStr"/>
     </row>
@@ -29488,7 +29488,7 @@
       </c>
       <c r="F1341" t="inlineStr"/>
       <c r="G1341" t="n">
-        <v>50620386.622</v>
+        <v>50614501.622</v>
       </c>
       <c r="H1341" t="inlineStr"/>
     </row>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="F1342" t="inlineStr"/>
       <c r="G1342" t="n">
-        <v>51313519.846</v>
+        <v>51311184.846</v>
       </c>
       <c r="H1342" t="inlineStr"/>
     </row>
@@ -29532,7 +29532,7 @@
       </c>
       <c r="F1343" t="inlineStr"/>
       <c r="G1343" t="n">
-        <v>49786898.676</v>
+        <v>49787130.676</v>
       </c>
       <c r="H1343" t="inlineStr"/>
     </row>
@@ -29554,7 +29554,7 @@
       </c>
       <c r="F1344" t="inlineStr"/>
       <c r="G1344" t="n">
-        <v>49515431.468</v>
+        <v>49518058.468</v>
       </c>
       <c r="H1344" t="inlineStr"/>
     </row>
@@ -29576,7 +29576,7 @@
       </c>
       <c r="F1345" t="inlineStr"/>
       <c r="G1345" t="n">
-        <v>48924193.358</v>
+        <v>48928745.358</v>
       </c>
       <c r="H1345" t="inlineStr"/>
     </row>
@@ -29598,7 +29598,7 @@
       </c>
       <c r="F1346" t="inlineStr"/>
       <c r="G1346" t="n">
-        <v>49395968.152</v>
+        <v>49399071.152</v>
       </c>
       <c r="H1346" t="inlineStr"/>
     </row>
@@ -29620,7 +29620,7 @@
       </c>
       <c r="F1347" t="inlineStr"/>
       <c r="G1347" t="n">
-        <v>49068336.486</v>
+        <v>49070495.486</v>
       </c>
       <c r="H1347" t="inlineStr"/>
     </row>
@@ -29642,7 +29642,7 @@
       </c>
       <c r="F1348" t="inlineStr"/>
       <c r="G1348" t="n">
-        <v>49130977.452</v>
+        <v>49133891.452</v>
       </c>
       <c r="H1348" t="inlineStr"/>
     </row>
@@ -29664,7 +29664,7 @@
       </c>
       <c r="F1349" t="inlineStr"/>
       <c r="G1349" t="n">
-        <v>49197347.726</v>
+        <v>49202533.726</v>
       </c>
       <c r="H1349" t="inlineStr"/>
     </row>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="F1350" t="inlineStr"/>
       <c r="G1350" t="n">
-        <v>49596775.914</v>
+        <v>49600234.914</v>
       </c>
       <c r="H1350" t="inlineStr"/>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="F1351" t="inlineStr"/>
       <c r="G1351" t="n">
-        <v>49106790.391</v>
+        <v>49108009.391</v>
       </c>
       <c r="H1351" t="inlineStr"/>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="F1352" t="inlineStr"/>
       <c r="G1352" t="n">
-        <v>49690769.724</v>
+        <v>49691610.724</v>
       </c>
       <c r="H1352" t="inlineStr"/>
     </row>
@@ -29752,7 +29752,7 @@
       </c>
       <c r="F1353" t="inlineStr"/>
       <c r="G1353" t="n">
-        <v>50163310.696</v>
+        <v>50164111.696</v>
       </c>
       <c r="H1353" t="inlineStr"/>
     </row>
@@ -29774,7 +29774,7 @@
       </c>
       <c r="F1354" t="inlineStr"/>
       <c r="G1354" t="n">
-        <v>50576224.767</v>
+        <v>50576353.767</v>
       </c>
       <c r="H1354" t="inlineStr"/>
     </row>
@@ -29796,7 +29796,7 @@
       </c>
       <c r="F1355" t="inlineStr"/>
       <c r="G1355" t="n">
-        <v>52846658.995</v>
+        <v>52847192.995</v>
       </c>
       <c r="H1355" t="inlineStr"/>
     </row>
@@ -29818,7 +29818,7 @@
       </c>
       <c r="F1356" t="inlineStr"/>
       <c r="G1356" t="n">
-        <v>53899955.682</v>
+        <v>53902217.682</v>
       </c>
       <c r="H1356" t="inlineStr"/>
     </row>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="n">
-        <v>56669668.267</v>
+        <v>56662379.267</v>
       </c>
       <c r="H1358" t="inlineStr"/>
     </row>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="F1359" t="inlineStr"/>
       <c r="G1359" t="n">
-        <v>56029580.372</v>
+        <v>56025060.372</v>
       </c>
       <c r="H1359" t="inlineStr"/>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="n">
-        <v>56588538.504</v>
+        <v>56586387.504</v>
       </c>
       <c r="H1360" t="inlineStr"/>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="n">
-        <v>56826406.839</v>
+        <v>56827806.839</v>
       </c>
       <c r="H1361" t="inlineStr"/>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="n">
-        <v>55507085.571</v>
+        <v>55512221.571</v>
       </c>
       <c r="H1362" t="inlineStr"/>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="n">
-        <v>55317089.556</v>
+        <v>55320764.556</v>
       </c>
       <c r="H1363" t="inlineStr"/>
     </row>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="n">
-        <v>54530563.68</v>
+        <v>54537092.68</v>
       </c>
       <c r="H1364" t="inlineStr"/>
     </row>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="n">
-        <v>53951975.241</v>
+        <v>53958994.241</v>
       </c>
       <c r="H1365" t="inlineStr"/>
     </row>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="n">
-        <v>53559380.918</v>
+        <v>53567774.918</v>
       </c>
       <c r="H1366" t="inlineStr"/>
     </row>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="F1367" t="inlineStr"/>
       <c r="G1367" t="n">
-        <v>53693173.53</v>
+        <v>53700572.53</v>
       </c>
       <c r="H1367" t="inlineStr"/>
     </row>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="n">
-        <v>52779296.228</v>
+        <v>52786695.228</v>
       </c>
       <c r="H1368" t="inlineStr"/>
     </row>
@@ -30108,7 +30108,7 @@
       </c>
       <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="n">
-        <v>53008432.434</v>
+        <v>53016773.434</v>
       </c>
       <c r="H1369" t="inlineStr"/>
     </row>
@@ -30130,7 +30130,7 @@
       </c>
       <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="n">
-        <v>52789862.166</v>
+        <v>52798903.166</v>
       </c>
       <c r="H1370" t="inlineStr"/>
     </row>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="F1371" t="inlineStr"/>
       <c r="G1371" t="n">
-        <v>52579551.418</v>
+        <v>52588643.418</v>
       </c>
       <c r="H1371" t="inlineStr"/>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="n">
-        <v>52219532.099</v>
+        <v>52226580.099</v>
       </c>
       <c r="H1372" t="inlineStr"/>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="n">
-        <v>52314924.713</v>
+        <v>52321972.713</v>
       </c>
       <c r="H1373" t="inlineStr"/>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="n">
-        <v>52858322.596</v>
+        <v>52865765.596</v>
       </c>
       <c r="H1374" t="inlineStr"/>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="n">
-        <v>52208903.178</v>
+        <v>52216347.178</v>
       </c>
       <c r="H1375" t="inlineStr"/>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="n">
-        <v>52590279.503</v>
+        <v>52596388.503</v>
       </c>
       <c r="H1376" t="inlineStr"/>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="n">
-        <v>52809682.197</v>
+        <v>52814677.197</v>
       </c>
       <c r="H1377" t="inlineStr"/>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="n">
-        <v>54082592.568</v>
+        <v>54087587.568</v>
       </c>
       <c r="H1378" t="inlineStr"/>
     </row>
@@ -30354,7 +30354,7 @@
       </c>
       <c r="F1380" t="inlineStr"/>
       <c r="G1380" t="n">
-        <v>56809196.779</v>
+        <v>56803765.779</v>
       </c>
       <c r="H1380" t="inlineStr"/>
     </row>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="F1381" t="inlineStr"/>
       <c r="G1381" t="n">
-        <v>55249467.451</v>
+        <v>55249023.451</v>
       </c>
       <c r="H1381" t="inlineStr"/>
     </row>
@@ -30398,7 +30398,7 @@
       </c>
       <c r="F1382" t="inlineStr"/>
       <c r="G1382" t="n">
-        <v>55291353.742</v>
+        <v>55292366.742</v>
       </c>
       <c r="H1382" t="inlineStr"/>
     </row>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="F1383" t="inlineStr"/>
       <c r="G1383" t="n">
-        <v>55566121.888</v>
+        <v>55569981.888</v>
       </c>
       <c r="H1383" t="inlineStr"/>
     </row>
@@ -30442,7 +30442,7 @@
       </c>
       <c r="F1384" t="inlineStr"/>
       <c r="G1384" t="n">
-        <v>55047269.049</v>
+        <v>55053330.049</v>
       </c>
       <c r="H1384" t="inlineStr"/>
     </row>
@@ -30464,7 +30464,7 @@
       </c>
       <c r="F1385" t="inlineStr"/>
       <c r="G1385" t="n">
-        <v>53792908.218</v>
+        <v>53799200.218</v>
       </c>
       <c r="H1385" t="inlineStr"/>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="F1386" t="inlineStr"/>
       <c r="G1386" t="n">
-        <v>52819932.644</v>
+        <v>52827018.644</v>
       </c>
       <c r="H1386" t="inlineStr"/>
     </row>
@@ -30508,7 +30508,7 @@
       </c>
       <c r="F1387" t="inlineStr"/>
       <c r="G1387" t="n">
-        <v>52099941.57</v>
+        <v>52106760.57</v>
       </c>
       <c r="H1387" t="inlineStr"/>
     </row>
@@ -30530,7 +30530,7 @@
       </c>
       <c r="F1388" t="inlineStr"/>
       <c r="G1388" t="n">
-        <v>51872717.889</v>
+        <v>51879515.889</v>
       </c>
       <c r="H1388" t="inlineStr"/>
     </row>
@@ -30552,7 +30552,7 @@
       </c>
       <c r="F1389" t="inlineStr"/>
       <c r="G1389" t="n">
-        <v>51834504.679</v>
+        <v>51840552.679</v>
       </c>
       <c r="H1389" t="inlineStr"/>
     </row>
@@ -30574,7 +30574,7 @@
       </c>
       <c r="F1390" t="inlineStr"/>
       <c r="G1390" t="n">
-        <v>51727650.828</v>
+        <v>51734898.828</v>
       </c>
       <c r="H1390" t="inlineStr"/>
     </row>
@@ -30596,7 +30596,7 @@
       </c>
       <c r="F1391" t="inlineStr"/>
       <c r="G1391" t="n">
-        <v>51310361.283</v>
+        <v>51316809.283</v>
       </c>
       <c r="H1391" t="inlineStr"/>
     </row>
@@ -30618,7 +30618,7 @@
       </c>
       <c r="F1392" t="inlineStr"/>
       <c r="G1392" t="n">
-        <v>50707116.116</v>
+        <v>50714667.116</v>
       </c>
       <c r="H1392" t="inlineStr"/>
     </row>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="F1393" t="inlineStr"/>
       <c r="G1393" t="n">
-        <v>50559184.926</v>
+        <v>50568665.926</v>
       </c>
       <c r="H1393" t="inlineStr"/>
     </row>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="F1394" t="inlineStr"/>
       <c r="G1394" t="n">
-        <v>50214847.764</v>
+        <v>50225111.764</v>
       </c>
       <c r="H1394" t="inlineStr"/>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="F1395" t="inlineStr"/>
       <c r="G1395" t="n">
-        <v>50099850.563</v>
+        <v>50109671.563</v>
       </c>
       <c r="H1395" t="inlineStr"/>
     </row>
@@ -30706,7 +30706,7 @@
       </c>
       <c r="F1396" t="inlineStr"/>
       <c r="G1396" t="n">
-        <v>49632318.924</v>
+        <v>49641446.924</v>
       </c>
       <c r="H1396" t="inlineStr"/>
     </row>
@@ -30728,7 +30728,7 @@
       </c>
       <c r="F1397" t="inlineStr"/>
       <c r="G1397" t="n">
-        <v>51027847.556</v>
+        <v>51038186.556</v>
       </c>
       <c r="H1397" t="inlineStr"/>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="F1398" t="inlineStr"/>
       <c r="G1398" t="n">
-        <v>51900840.644</v>
+        <v>51911525.644</v>
       </c>
       <c r="H1398" t="inlineStr"/>
     </row>
@@ -30810,7 +30810,7 @@
       </c>
       <c r="F1401" t="inlineStr"/>
       <c r="G1401" t="n">
-        <v>53373965.53</v>
+        <v>53365993.53</v>
       </c>
       <c r="H1401" t="inlineStr"/>
     </row>
@@ -30832,7 +30832,7 @@
       </c>
       <c r="F1402" t="inlineStr"/>
       <c r="G1402" t="n">
-        <v>52766522.855</v>
+        <v>52755256.855</v>
       </c>
       <c r="H1402" t="inlineStr"/>
     </row>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="F1403" t="inlineStr"/>
       <c r="G1403" t="n">
-        <v>53251103.593</v>
+        <v>53242341.593</v>
       </c>
       <c r="H1403" t="inlineStr"/>
     </row>
@@ -30876,7 +30876,7 @@
       </c>
       <c r="F1404" t="inlineStr"/>
       <c r="G1404" t="n">
-        <v>54190186.308</v>
+        <v>54182420.308</v>
       </c>
       <c r="H1404" t="inlineStr"/>
     </row>
@@ -30898,7 +30898,7 @@
       </c>
       <c r="F1405" t="inlineStr"/>
       <c r="G1405" t="n">
-        <v>53200502.494</v>
+        <v>53193611.494</v>
       </c>
       <c r="H1405" t="inlineStr"/>
     </row>
@@ -30920,7 +30920,7 @@
       </c>
       <c r="F1406" t="inlineStr"/>
       <c r="G1406" t="n">
-        <v>52633619.98</v>
+        <v>52628050.98</v>
       </c>
       <c r="H1406" t="inlineStr"/>
     </row>
@@ -30942,7 +30942,7 @@
       </c>
       <c r="F1407" t="inlineStr"/>
       <c r="G1407" t="n">
-        <v>51777162.704</v>
+        <v>51771655.704</v>
       </c>
       <c r="H1407" t="inlineStr"/>
     </row>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="F1408" t="inlineStr"/>
       <c r="G1408" t="n">
-        <v>51784902.154</v>
+        <v>51779933.154</v>
       </c>
       <c r="H1408" t="inlineStr"/>
     </row>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="F1409" t="inlineStr"/>
       <c r="G1409" t="n">
-        <v>51659925.007</v>
+        <v>51655436.007</v>
       </c>
       <c r="H1409" t="inlineStr"/>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="F1410" t="inlineStr"/>
       <c r="G1410" t="n">
-        <v>50935081.014</v>
+        <v>50932001.014</v>
       </c>
       <c r="H1410" t="inlineStr"/>
     </row>
@@ -31030,7 +31030,7 @@
       </c>
       <c r="F1411" t="inlineStr"/>
       <c r="G1411" t="n">
-        <v>51271129.064</v>
+        <v>51269939.064</v>
       </c>
       <c r="H1411" t="inlineStr"/>
     </row>
@@ -31052,7 +31052,7 @@
       </c>
       <c r="F1412" t="inlineStr"/>
       <c r="G1412" t="n">
-        <v>50216701.352</v>
+        <v>50215200.352</v>
       </c>
       <c r="H1412" t="inlineStr"/>
     </row>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="F1413" t="inlineStr"/>
       <c r="G1413" t="n">
-        <v>50369114.972</v>
+        <v>50368962.972</v>
       </c>
       <c r="H1413" t="inlineStr"/>
     </row>
@@ -31096,7 +31096,7 @@
       </c>
       <c r="F1414" t="inlineStr"/>
       <c r="G1414" t="n">
-        <v>50463265.477</v>
+        <v>50464202.477</v>
       </c>
       <c r="H1414" t="inlineStr"/>
     </row>
@@ -31118,7 +31118,7 @@
       </c>
       <c r="F1415" t="inlineStr"/>
       <c r="G1415" t="n">
-        <v>50402497.859</v>
+        <v>50404362.859</v>
       </c>
       <c r="H1415" t="inlineStr"/>
     </row>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="F1416" t="inlineStr"/>
       <c r="G1416" t="n">
-        <v>50443702.937</v>
+        <v>50446123.937</v>
       </c>
       <c r="H1416" t="inlineStr"/>
     </row>
@@ -31162,7 +31162,7 @@
       </c>
       <c r="F1417" t="inlineStr"/>
       <c r="G1417" t="n">
-        <v>50321247.92</v>
+        <v>50322959.92</v>
       </c>
       <c r="H1417" t="inlineStr"/>
     </row>
@@ -31184,7 +31184,7 @@
       </c>
       <c r="F1418" t="inlineStr"/>
       <c r="G1418" t="n">
-        <v>50577394.87</v>
+        <v>50578817.87</v>
       </c>
       <c r="H1418" t="inlineStr"/>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="F1419" t="inlineStr"/>
       <c r="G1419" t="n">
-        <v>51114151.993</v>
+        <v>51116279.993</v>
       </c>
       <c r="H1419" t="inlineStr"/>
     </row>
@@ -31228,7 +31228,7 @@
       </c>
       <c r="F1420" t="inlineStr"/>
       <c r="G1420" t="n">
-        <v>51112474.537</v>
+        <v>51114602.537</v>
       </c>
       <c r="H1420" t="inlineStr"/>
     </row>
@@ -31250,7 +31250,7 @@
       </c>
       <c r="F1421" t="inlineStr"/>
       <c r="G1421" t="n">
-        <v>52908295.45</v>
+        <v>52896818.45</v>
       </c>
       <c r="H1421" t="inlineStr"/>
     </row>
@@ -31298,7 +31298,7 @@
       </c>
       <c r="F1423" t="inlineStr"/>
       <c r="G1423" t="n">
-        <v>55584393.331</v>
+        <v>55583862.331</v>
       </c>
       <c r="H1423" t="inlineStr"/>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="F1424" t="inlineStr"/>
       <c r="G1424" t="n">
-        <v>55646318.151</v>
+        <v>55650853.151</v>
       </c>
       <c r="H1424" t="inlineStr"/>
     </row>
@@ -31342,7 +31342,7 @@
       </c>
       <c r="F1425" t="inlineStr"/>
       <c r="G1425" t="n">
-        <v>55912030.978</v>
+        <v>55921165.978</v>
       </c>
       <c r="H1425" t="inlineStr"/>
     </row>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="F1426" t="inlineStr"/>
       <c r="G1426" t="n">
-        <v>55683733.241</v>
+        <v>55699034.241</v>
       </c>
       <c r="H1426" t="inlineStr"/>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="F1427" t="inlineStr"/>
       <c r="G1427" t="n">
-        <v>54846909.217</v>
+        <v>54863096.217</v>
       </c>
       <c r="H1427" t="inlineStr"/>
     </row>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="F1428" t="inlineStr"/>
       <c r="G1428" t="n">
-        <v>54725211.24</v>
+        <v>54742336.24</v>
       </c>
       <c r="H1428" t="inlineStr"/>
     </row>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="F1429" t="inlineStr"/>
       <c r="G1429" t="n">
-        <v>54438339.576</v>
+        <v>54458221.576</v>
       </c>
       <c r="H1429" t="inlineStr"/>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="F1430" t="inlineStr"/>
       <c r="G1430" t="n">
-        <v>54449755.621</v>
+        <v>54473214.621</v>
       </c>
       <c r="H1430" t="inlineStr"/>
     </row>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="F1431" t="inlineStr"/>
       <c r="G1431" t="n">
-        <v>51917828.914</v>
+        <v>51940724.914</v>
       </c>
       <c r="H1431" t="inlineStr"/>
     </row>
@@ -31496,7 +31496,7 @@
       </c>
       <c r="F1432" t="inlineStr"/>
       <c r="G1432" t="n">
-        <v>52476651.382</v>
+        <v>52499551.382</v>
       </c>
       <c r="H1432" t="inlineStr"/>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="F1433" t="inlineStr"/>
       <c r="G1433" t="n">
-        <v>51681169.388</v>
+        <v>51704069.388</v>
       </c>
       <c r="H1433" t="inlineStr"/>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="F1434" t="inlineStr"/>
       <c r="G1434" t="n">
-        <v>50448620.623</v>
+        <v>50473559.623</v>
       </c>
       <c r="H1434" t="inlineStr"/>
     </row>
@@ -31562,7 +31562,7 @@
       </c>
       <c r="F1435" t="inlineStr"/>
       <c r="G1435" t="n">
-        <v>50493991.287</v>
+        <v>50519943.287</v>
       </c>
       <c r="H1435" t="inlineStr"/>
     </row>
@@ -31584,7 +31584,7 @@
       </c>
       <c r="F1436" t="inlineStr"/>
       <c r="G1436" t="n">
-        <v>50027570.307</v>
+        <v>50053868.307</v>
       </c>
       <c r="H1436" t="inlineStr"/>
     </row>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="F1437" t="inlineStr"/>
       <c r="G1437" t="n">
-        <v>50747917.53</v>
+        <v>50775066.53</v>
       </c>
       <c r="H1437" t="inlineStr"/>
     </row>
@@ -31628,7 +31628,7 @@
       </c>
       <c r="F1438" t="inlineStr"/>
       <c r="G1438" t="n">
-        <v>49991996.981</v>
+        <v>50018529.981</v>
       </c>
       <c r="H1438" t="inlineStr"/>
     </row>
@@ -31650,7 +31650,7 @@
       </c>
       <c r="F1439" t="inlineStr"/>
       <c r="G1439" t="n">
-        <v>49837481.76</v>
+        <v>49864170.76</v>
       </c>
       <c r="H1439" t="inlineStr"/>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="F1440" t="inlineStr"/>
       <c r="G1440" t="n">
-        <v>49753101.195</v>
+        <v>49779626.195</v>
       </c>
       <c r="H1440" t="inlineStr"/>
     </row>
@@ -31694,7 +31694,7 @@
       </c>
       <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="n">
-        <v>49495936.045</v>
+        <v>49522331.045</v>
       </c>
       <c r="H1441" t="inlineStr"/>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="F1442" t="inlineStr"/>
       <c r="G1442" t="n">
-        <v>50043627.504</v>
+        <v>50070215.504</v>
       </c>
       <c r="H1442" t="inlineStr"/>
     </row>
@@ -31738,7 +31738,7 @@
       </c>
       <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="n">
-        <v>51498309.942</v>
+        <v>51525403.942</v>
       </c>
       <c r="H1443" t="inlineStr"/>
     </row>
@@ -31786,7 +31786,7 @@
       </c>
       <c r="F1445" t="inlineStr"/>
       <c r="G1445" t="n">
-        <v>53458135.301</v>
+        <v>53450206.301</v>
       </c>
       <c r="H1445" t="inlineStr"/>
     </row>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="F1446" t="inlineStr"/>
       <c r="G1446" t="n">
-        <v>53030944.662</v>
+        <v>53020029.662</v>
       </c>
       <c r="H1446" t="inlineStr"/>
     </row>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="F1447" t="inlineStr"/>
       <c r="G1447" t="n">
-        <v>53697167.632</v>
+        <v>53686711.632</v>
       </c>
       <c r="H1447" t="inlineStr"/>
     </row>
@@ -31852,7 +31852,7 @@
       </c>
       <c r="F1448" t="inlineStr"/>
       <c r="G1448" t="n">
-        <v>52964132.148</v>
+        <v>52955080.148</v>
       </c>
       <c r="H1448" t="inlineStr"/>
     </row>
@@ -31874,7 +31874,7 @@
       </c>
       <c r="F1449" t="inlineStr"/>
       <c r="G1449" t="n">
-        <v>51749972.271</v>
+        <v>51742984.271</v>
       </c>
       <c r="H1449" t="inlineStr"/>
     </row>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="F1450" t="inlineStr"/>
       <c r="G1450" t="n">
-        <v>50251414.976</v>
+        <v>50244799.976</v>
       </c>
       <c r="H1450" t="inlineStr"/>
     </row>
@@ -31918,7 +31918,7 @@
       </c>
       <c r="F1451" t="inlineStr"/>
       <c r="G1451" t="n">
-        <v>50812140.288</v>
+        <v>50808053.288</v>
       </c>
       <c r="H1451" t="inlineStr"/>
     </row>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="F1452" t="inlineStr"/>
       <c r="G1452" t="n">
-        <v>50542959.336</v>
+        <v>50539304.336</v>
       </c>
       <c r="H1452" t="inlineStr"/>
     </row>
@@ -31962,7 +31962,7 @@
       </c>
       <c r="F1453" t="inlineStr"/>
       <c r="G1453" t="n">
-        <v>50537135.135</v>
+        <v>50536326.135</v>
       </c>
       <c r="H1453" t="inlineStr"/>
     </row>
@@ -31984,7 +31984,7 @@
       </c>
       <c r="F1454" t="inlineStr"/>
       <c r="G1454" t="n">
-        <v>50351866.524</v>
+        <v>50351680.524</v>
       </c>
       <c r="H1454" t="inlineStr"/>
     </row>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="F1455" t="inlineStr"/>
       <c r="G1455" t="n">
-        <v>50189762.389</v>
+        <v>50189652.389</v>
       </c>
       <c r="H1455" t="inlineStr"/>
     </row>
@@ -32028,7 +32028,7 @@
       </c>
       <c r="F1456" t="inlineStr"/>
       <c r="G1456" t="n">
-        <v>50006424.804</v>
+        <v>50006041.804</v>
       </c>
       <c r="H1456" t="inlineStr"/>
     </row>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="F1457" t="inlineStr"/>
       <c r="G1457" t="n">
-        <v>50601927.035</v>
+        <v>50599945.035</v>
       </c>
       <c r="H1457" t="inlineStr"/>
     </row>
@@ -32072,7 +32072,7 @@
       </c>
       <c r="F1458" t="inlineStr"/>
       <c r="G1458" t="n">
-        <v>51396389.263</v>
+        <v>51393353.263</v>
       </c>
       <c r="H1458" t="inlineStr"/>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="F1459" t="inlineStr"/>
       <c r="G1459" t="n">
-        <v>51879962.288</v>
+        <v>51877590.288</v>
       </c>
       <c r="H1459" t="inlineStr"/>
     </row>
@@ -32116,7 +32116,7 @@
       </c>
       <c r="F1460" t="inlineStr"/>
       <c r="G1460" t="n">
-        <v>53262990.364</v>
+        <v>53262111.364</v>
       </c>
       <c r="H1460" t="inlineStr"/>
     </row>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="F1463" t="inlineStr"/>
       <c r="G1463" t="n">
-        <v>56164845.367</v>
+        <v>56164428.367</v>
       </c>
       <c r="H1463" t="inlineStr"/>
     </row>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="F1464" t="inlineStr"/>
       <c r="G1464" t="n">
-        <v>55033850.993</v>
+        <v>55019386.993</v>
       </c>
       <c r="H1464" t="inlineStr"/>
     </row>
@@ -32220,7 +32220,7 @@
       </c>
       <c r="F1465" t="inlineStr"/>
       <c r="G1465" t="n">
-        <v>55457193.785</v>
+        <v>55447003.785</v>
       </c>
       <c r="H1465" t="inlineStr"/>
     </row>
@@ -32242,7 +32242,7 @@
       </c>
       <c r="F1466" t="inlineStr"/>
       <c r="G1466" t="n">
-        <v>56337071.518</v>
+        <v>56329037.518</v>
       </c>
       <c r="H1466" t="inlineStr"/>
     </row>
@@ -32264,7 +32264,7 @@
       </c>
       <c r="F1467" t="inlineStr"/>
       <c r="G1467" t="n">
-        <v>55346801.095</v>
+        <v>55339388.095</v>
       </c>
       <c r="H1467" t="inlineStr"/>
     </row>
@@ -32286,7 +32286,7 @@
       </c>
       <c r="F1468" t="inlineStr"/>
       <c r="G1468" t="n">
-        <v>54679700.736</v>
+        <v>54672675.736</v>
       </c>
       <c r="H1468" t="inlineStr"/>
     </row>
@@ -32308,7 +32308,7 @@
       </c>
       <c r="F1469" t="inlineStr"/>
       <c r="G1469" t="n">
-        <v>54555839.54</v>
+        <v>54550262.54</v>
       </c>
       <c r="H1469" t="inlineStr"/>
     </row>
@@ -32330,7 +32330,7 @@
       </c>
       <c r="F1470" t="inlineStr"/>
       <c r="G1470" t="n">
-        <v>55263372.612</v>
+        <v>55260922.612</v>
       </c>
       <c r="H1470" t="inlineStr"/>
     </row>
@@ -32352,7 +32352,7 @@
       </c>
       <c r="F1471" t="inlineStr"/>
       <c r="G1471" t="n">
-        <v>55077691.123</v>
+        <v>55075529.123</v>
       </c>
       <c r="H1471" t="inlineStr"/>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="F1472" t="inlineStr"/>
       <c r="G1472" t="n">
-        <v>56288640.956</v>
+        <v>56286478.956</v>
       </c>
       <c r="H1472" t="inlineStr"/>
     </row>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="F1473" t="inlineStr"/>
       <c r="G1473" t="n">
-        <v>56126923.885</v>
+        <v>56125786.885</v>
       </c>
       <c r="H1473" t="inlineStr"/>
     </row>
@@ -32418,7 +32418,7 @@
       </c>
       <c r="F1474" t="inlineStr"/>
       <c r="G1474" t="n">
-        <v>57302197.778</v>
+        <v>57297336.778</v>
       </c>
       <c r="H1474" t="inlineStr"/>
     </row>
@@ -32440,7 +32440,7 @@
       </c>
       <c r="F1475" t="inlineStr"/>
       <c r="G1475" t="n">
-        <v>58733812.611</v>
+        <v>58724869.611</v>
       </c>
       <c r="H1475" t="inlineStr"/>
     </row>
@@ -32462,7 +32462,7 @@
       </c>
       <c r="F1476" t="inlineStr"/>
       <c r="G1476" t="n">
-        <v>59890877.332</v>
+        <v>59879921.332</v>
       </c>
       <c r="H1476" t="inlineStr"/>
     </row>
@@ -32484,7 +32484,7 @@
       </c>
       <c r="F1477" t="inlineStr"/>
       <c r="G1477" t="n">
-        <v>60274072.984</v>
+        <v>60262522.984</v>
       </c>
       <c r="H1477" t="inlineStr"/>
     </row>
@@ -32506,7 +32506,7 @@
       </c>
       <c r="F1478" t="inlineStr"/>
       <c r="G1478" t="n">
-        <v>60798919.024</v>
+        <v>60787887.024</v>
       </c>
       <c r="H1478" t="inlineStr"/>
     </row>
@@ -32528,7 +32528,7 @@
       </c>
       <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="n">
-        <v>60726124.044</v>
+        <v>60717664.044</v>
       </c>
       <c r="H1479" t="inlineStr"/>
     </row>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="F1480" t="inlineStr"/>
       <c r="G1480" t="n">
-        <v>62881136.767</v>
+        <v>62875841.767</v>
       </c>
       <c r="H1480" t="inlineStr"/>
     </row>
@@ -32610,7 +32610,7 @@
       </c>
       <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="n">
-        <v>64612279.281</v>
+        <v>64612564.281</v>
       </c>
       <c r="H1483" t="inlineStr"/>
     </row>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61896822.993</v>
+        <v>61885467.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61214488.519</v>
+        <v>61207816.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61746796.076</v>
+        <v>61743079.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32698,7 +32698,7 @@
       </c>
       <c r="F1487" t="inlineStr"/>
       <c r="G1487" t="n">
-        <v>60510736.004</v>
+        <v>60508250.004</v>
       </c>
       <c r="H1487" t="inlineStr"/>
     </row>
@@ -32720,7 +32720,7 @@
       </c>
       <c r="F1488" t="inlineStr"/>
       <c r="G1488" t="n">
-        <v>59557006.211</v>
+        <v>59554425.211</v>
       </c>
       <c r="H1488" t="inlineStr"/>
     </row>
@@ -32742,7 +32742,7 @@
       </c>
       <c r="F1489" t="inlineStr"/>
       <c r="G1489" t="n">
-        <v>57835851.381</v>
+        <v>57836224.381</v>
       </c>
       <c r="H1489" t="inlineStr"/>
     </row>
@@ -32764,7 +32764,7 @@
       </c>
       <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="n">
-        <v>57233102.101</v>
+        <v>57233592.101</v>
       </c>
       <c r="H1490" t="inlineStr"/>
     </row>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="n">
-        <v>57172449.244</v>
+        <v>57172528.244</v>
       </c>
       <c r="H1491" t="inlineStr"/>
     </row>
@@ -32808,7 +32808,7 @@
       </c>
       <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="n">
-        <v>57600421.399</v>
+        <v>57603059.399</v>
       </c>
       <c r="H1492" t="inlineStr"/>
     </row>
@@ -32830,7 +32830,7 @@
       </c>
       <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="n">
-        <v>56274804.088</v>
+        <v>56277371.088</v>
       </c>
       <c r="H1493" t="inlineStr"/>
     </row>
@@ -32852,7 +32852,7 @@
       </c>
       <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="n">
-        <v>55651580.47</v>
+        <v>55654720.47</v>
       </c>
       <c r="H1494" t="inlineStr"/>
     </row>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="n">
-        <v>55478031.492</v>
+        <v>55481658.492</v>
       </c>
       <c r="H1495" t="inlineStr"/>
     </row>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55307343.796</v>
+        <v>55311997.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="n">
-        <v>55070076.613</v>
+        <v>55075460.613</v>
       </c>
       <c r="H1497" t="inlineStr"/>
     </row>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="n">
-        <v>54770646.758</v>
+        <v>54776610.758</v>
       </c>
       <c r="H1498" t="inlineStr"/>
     </row>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54925875.349</v>
+        <v>54932391.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -32984,7 +32984,7 @@
       </c>
       <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="n">
-        <v>55180316.773</v>
+        <v>55186744.773</v>
       </c>
       <c r="H1500" t="inlineStr"/>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="n">
-        <v>55935996.062</v>
+        <v>55943082.062</v>
       </c>
       <c r="H1501" t="inlineStr"/>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="n">
-        <v>57630894.416</v>
+        <v>57638505.416</v>
       </c>
       <c r="H1502" t="inlineStr"/>
     </row>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60140782.818</v>
+        <v>60140775.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -34364,7 +34364,7 @@
         <v>24.2</v>
       </c>
       <c r="G1563" t="n">
-        <v>62688422.443</v>
+        <v>62688487.443</v>
       </c>
       <c r="H1563" t="n">
         <v>2.6</v>
@@ -34784,7 +34784,7 @@
       </c>
       <c r="F1582" t="inlineStr"/>
       <c r="G1582" t="n">
-        <v>63455187.9</v>
+        <v>63455237.9</v>
       </c>
       <c r="H1582" t="inlineStr"/>
     </row>
@@ -34822,7 +34822,7 @@
       </c>
       <c r="F1584" t="inlineStr"/>
       <c r="G1584" t="n">
-        <v>62195108.5</v>
+        <v>62192354.5</v>
       </c>
       <c r="H1584" t="inlineStr"/>
     </row>
@@ -34844,7 +34844,7 @@
       </c>
       <c r="F1585" t="inlineStr"/>
       <c r="G1585" t="n">
-        <v>62223328.556</v>
+        <v>62220529.556</v>
       </c>
       <c r="H1585" t="inlineStr"/>
     </row>
@@ -34866,7 +34866,7 @@
       </c>
       <c r="F1586" t="inlineStr"/>
       <c r="G1586" t="n">
-        <v>62053283.047</v>
+        <v>62051376.047</v>
       </c>
       <c r="H1586" t="inlineStr"/>
     </row>
@@ -34888,7 +34888,7 @@
       </c>
       <c r="F1587" t="inlineStr"/>
       <c r="G1587" t="n">
-        <v>62802349.612</v>
+        <v>62801234.612</v>
       </c>
       <c r="H1587" t="inlineStr"/>
     </row>
@@ -34910,7 +34910,7 @@
       </c>
       <c r="F1588" t="inlineStr"/>
       <c r="G1588" t="n">
-        <v>61600761.134</v>
+        <v>61599993.134</v>
       </c>
       <c r="H1588" t="inlineStr"/>
     </row>
@@ -34932,7 +34932,7 @@
       </c>
       <c r="F1589" t="inlineStr"/>
       <c r="G1589" t="n">
-        <v>60923445.097</v>
+        <v>60922773.097</v>
       </c>
       <c r="H1589" t="inlineStr"/>
     </row>
@@ -34954,7 +34954,7 @@
       </c>
       <c r="F1590" t="inlineStr"/>
       <c r="G1590" t="n">
-        <v>60712164.135</v>
+        <v>60711478.135</v>
       </c>
       <c r="H1590" t="inlineStr"/>
     </row>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="F1591" t="inlineStr"/>
       <c r="G1591" t="n">
-        <v>60429512.682</v>
+        <v>60428863.682</v>
       </c>
       <c r="H1591" t="inlineStr"/>
     </row>
@@ -34998,7 +34998,7 @@
       </c>
       <c r="F1592" t="inlineStr"/>
       <c r="G1592" t="n">
-        <v>60439733.832</v>
+        <v>60439087.832</v>
       </c>
       <c r="H1592" t="inlineStr"/>
     </row>
@@ -35020,7 +35020,7 @@
       </c>
       <c r="F1593" t="inlineStr"/>
       <c r="G1593" t="n">
-        <v>60560534.856</v>
+        <v>60559823.856</v>
       </c>
       <c r="H1593" t="inlineStr"/>
     </row>
@@ -35042,7 +35042,7 @@
       </c>
       <c r="F1594" t="inlineStr"/>
       <c r="G1594" t="n">
-        <v>61239600.499</v>
+        <v>61238468.499</v>
       </c>
       <c r="H1594" t="inlineStr"/>
     </row>
@@ -35064,7 +35064,7 @@
       </c>
       <c r="F1595" t="inlineStr"/>
       <c r="G1595" t="n">
-        <v>61081745.917</v>
+        <v>61080610.917</v>
       </c>
       <c r="H1595" t="inlineStr"/>
     </row>
@@ -35086,7 +35086,7 @@
       </c>
       <c r="F1596" t="inlineStr"/>
       <c r="G1596" t="n">
-        <v>61219718.503</v>
+        <v>61218542.503</v>
       </c>
       <c r="H1596" t="inlineStr"/>
     </row>
@@ -35108,7 +35108,7 @@
       </c>
       <c r="F1597" t="inlineStr"/>
       <c r="G1597" t="n">
-        <v>60957928.644</v>
+        <v>60956718.644</v>
       </c>
       <c r="H1597" t="inlineStr"/>
     </row>
@@ -35130,7 +35130,7 @@
       </c>
       <c r="F1598" t="inlineStr"/>
       <c r="G1598" t="n">
-        <v>61017977.083</v>
+        <v>61019953.083</v>
       </c>
       <c r="H1598" t="inlineStr"/>
     </row>
@@ -35152,7 +35152,7 @@
       </c>
       <c r="F1599" t="inlineStr"/>
       <c r="G1599" t="n">
-        <v>61317727.16</v>
+        <v>61314233.16</v>
       </c>
       <c r="H1599" t="inlineStr"/>
     </row>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="F1600" t="inlineStr"/>
       <c r="G1600" t="n">
-        <v>61352968.919</v>
+        <v>61350952.919</v>
       </c>
       <c r="H1600" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
       </c>
       <c r="F1601" t="inlineStr"/>
       <c r="G1601" t="n">
-        <v>62943174.868</v>
+        <v>62941125.868</v>
       </c>
       <c r="H1601" t="inlineStr"/>
     </row>
@@ -35218,7 +35218,7 @@
       </c>
       <c r="F1602" t="inlineStr"/>
       <c r="G1602" t="n">
-        <v>63919260.573</v>
+        <v>63919238.573</v>
       </c>
       <c r="H1602" t="inlineStr"/>
     </row>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="F1603" t="inlineStr"/>
       <c r="G1603" t="n">
-        <v>68438528.31200001</v>
+        <v>68450812.31200001</v>
       </c>
       <c r="H1603" t="inlineStr"/>
     </row>
@@ -35264,7 +35264,7 @@
         <v>22.3</v>
       </c>
       <c r="G1604" t="n">
-        <v>70419914.642</v>
+        <v>70408302.236</v>
       </c>
       <c r="H1604" t="n">
         <v>1.9</v>
@@ -35332,7 +35332,7 @@
       </c>
       <c r="F1607" t="inlineStr"/>
       <c r="G1607" t="n">
-        <v>70580487.83499999</v>
+        <v>70587774.83499999</v>
       </c>
       <c r="H1607" t="inlineStr"/>
     </row>
@@ -35354,7 +35354,7 @@
       </c>
       <c r="F1608" t="inlineStr"/>
       <c r="G1608" t="n">
-        <v>70224278.022</v>
+        <v>70229580.022</v>
       </c>
       <c r="H1608" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
       </c>
       <c r="F1609" t="inlineStr"/>
       <c r="G1609" t="n">
-        <v>69896072.40099999</v>
+        <v>69901372.40099999</v>
       </c>
       <c r="H1609" t="inlineStr"/>
     </row>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="F1610" t="inlineStr"/>
       <c r="G1610" t="n">
-        <v>69964193.51100001</v>
+        <v>69964158.51100001</v>
       </c>
       <c r="H1610" t="inlineStr"/>
     </row>
@@ -35420,7 +35420,7 @@
       </c>
       <c r="F1611" t="inlineStr"/>
       <c r="G1611" t="n">
-        <v>67066586.292</v>
+        <v>67071887.292</v>
       </c>
       <c r="H1611" t="inlineStr"/>
     </row>
@@ -35442,7 +35442,7 @@
       </c>
       <c r="F1612" t="inlineStr"/>
       <c r="G1612" t="n">
-        <v>66298497.61</v>
+        <v>66241955.61</v>
       </c>
       <c r="H1612" t="inlineStr"/>
     </row>
@@ -35464,7 +35464,7 @@
       </c>
       <c r="F1613" t="inlineStr"/>
       <c r="G1613" t="n">
-        <v>65297143.72</v>
+        <v>65273840.255</v>
       </c>
       <c r="H1613" t="inlineStr"/>
     </row>
@@ -35486,7 +35486,7 @@
       </c>
       <c r="F1614" t="inlineStr"/>
       <c r="G1614" t="n">
-        <v>65479549.226</v>
+        <v>65467784.441</v>
       </c>
       <c r="H1614" t="inlineStr"/>
     </row>
@@ -35508,7 +35508,7 @@
       </c>
       <c r="F1615" t="inlineStr"/>
       <c r="G1615" t="n">
-        <v>64047105.272</v>
+        <v>64017099.835</v>
       </c>
       <c r="H1615" t="inlineStr"/>
     </row>
@@ -35530,7 +35530,7 @@
       </c>
       <c r="F1616" t="inlineStr"/>
       <c r="G1616" t="n">
-        <v>64527312.022</v>
+        <v>64510440.378</v>
       </c>
       <c r="H1616" t="inlineStr"/>
     </row>
@@ -35552,7 +35552,7 @@
       </c>
       <c r="F1617" t="inlineStr"/>
       <c r="G1617" t="n">
-        <v>64151259.111</v>
+        <v>64114734.533</v>
       </c>
       <c r="H1617" t="inlineStr"/>
     </row>
@@ -35573,15 +35573,21 @@
         <v>22</v>
       </c>
       <c r="F1618" t="inlineStr"/>
-      <c r="G1618" t="inlineStr"/>
+      <c r="G1618" t="n">
+        <v>63344780.404</v>
+      </c>
       <c r="H1618" t="inlineStr"/>
     </row>
     <row r="1619">
       <c r="A1619" s="1" t="n">
         <v>46226</v>
       </c>
-      <c r="B1619" t="inlineStr"/>
-      <c r="C1619" t="inlineStr"/>
+      <c r="B1619" t="n">
+        <v>48686</v>
+      </c>
+      <c r="C1619" t="n">
+        <v>45813184</v>
+      </c>
       <c r="D1619" t="n">
         <v>1510.8</v>
       </c>
@@ -35589,22 +35595,126 @@
         <v>22.1875</v>
       </c>
       <c r="F1619" t="inlineStr"/>
-      <c r="G1619" t="inlineStr"/>
+      <c r="G1619" t="n">
+        <v>63721620.522</v>
+      </c>
       <c r="H1619" t="inlineStr"/>
     </row>
     <row r="1620">
       <c r="A1620" s="1" t="n">
         <v>46227</v>
       </c>
-      <c r="B1620" t="inlineStr"/>
-      <c r="C1620" t="inlineStr"/>
+      <c r="B1620" t="n">
+        <v>49187</v>
+      </c>
+      <c r="C1620" t="n">
+        <v>46087590</v>
+      </c>
       <c r="D1620" t="n">
         <v>1518.86</v>
       </c>
-      <c r="E1620" t="inlineStr"/>
+      <c r="E1620" t="n">
+        <v>22</v>
+      </c>
       <c r="F1620" t="inlineStr"/>
-      <c r="G1620" t="inlineStr"/>
+      <c r="G1620" t="n">
+        <v>63533632.405</v>
+      </c>
       <c r="H1620" t="inlineStr"/>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B1621" t="n">
+        <v>49164</v>
+      </c>
+      <c r="C1621" t="n">
+        <v>46324059</v>
+      </c>
+      <c r="D1621" t="n">
+        <v>1520.47</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>20.9375</v>
+      </c>
+      <c r="F1621" t="inlineStr"/>
+      <c r="G1621" t="n">
+        <v>64270390.708</v>
+      </c>
+      <c r="H1621" t="inlineStr"/>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1622" t="n">
+        <v>48935</v>
+      </c>
+      <c r="C1622" t="n">
+        <v>45044437</v>
+      </c>
+      <c r="D1622" t="n">
+        <v>1520.82</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1622" t="inlineStr"/>
+      <c r="G1622" t="n">
+        <v>63963066.865</v>
+      </c>
+      <c r="H1622" t="inlineStr"/>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1623" t="n">
+        <v>49196</v>
+      </c>
+      <c r="C1623" t="n">
+        <v>44055898</v>
+      </c>
+      <c r="D1623" t="n">
+        <v>1518.59</v>
+      </c>
+      <c r="E1623" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="F1623" t="inlineStr"/>
+      <c r="G1623" t="inlineStr"/>
+      <c r="H1623" t="inlineStr"/>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B1624" t="inlineStr"/>
+      <c r="C1624" t="inlineStr"/>
+      <c r="D1624" t="n">
+        <v>1512.02</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>21.9375</v>
+      </c>
+      <c r="F1624" t="inlineStr"/>
+      <c r="G1624" t="inlineStr"/>
+      <c r="H1624" t="inlineStr"/>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1625" t="inlineStr"/>
+      <c r="C1625" t="inlineStr"/>
+      <c r="D1625" t="n">
+        <v>1511.12</v>
+      </c>
+      <c r="E1625" t="inlineStr"/>
+      <c r="F1625" t="inlineStr"/>
+      <c r="G1625" t="inlineStr"/>
+      <c r="H1625" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1625"/>
+  <dimension ref="A1:H1630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.29</v>
+        <v>108.48</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.48</v>
+        <v>108.61</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.61</v>
+        <v>108.63</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.63</v>
+        <v>108.72</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.72</v>
+        <v>108.86</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.86</v>
+        <v>108.96</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.96</v>
+        <v>108.97</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>108.97</v>
+        <v>109.05</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.05</v>
+        <v>109.11</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.11</v>
+        <v>109.21</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.21</v>
+        <v>109.46</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.46</v>
+        <v>109.64</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.64</v>
+        <v>109.67</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.67</v>
+        <v>109.71</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.71</v>
+        <v>109.79</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>109.79</v>
+        <v>110.08</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.08</v>
+        <v>110.11</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.11</v>
+        <v>110.15</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.15</v>
+        <v>110.5</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.5</v>
+        <v>110.68</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.68</v>
+        <v>110.71</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.71</v>
+        <v>110.75</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.75</v>
+        <v>110.92</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>110.92</v>
+        <v>111.37</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.37</v>
+        <v>111.46</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.46</v>
+        <v>111.49</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.49</v>
+        <v>111.52</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.52</v>
+        <v>111.59</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.59</v>
+        <v>111.67</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>111.67</v>
+        <v>112.01</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.01</v>
+        <v>112.17</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.17</v>
+        <v>112.21</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.21</v>
+        <v>112.24</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.24</v>
+        <v>112.48</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.48</v>
+        <v>112.71</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.71</v>
+        <v>112.8</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.8</v>
+        <v>112.83</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.83</v>
+        <v>112.89</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.89</v>
+        <v>112.95</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -31762,7 +31762,7 @@
         <v>20.8</v>
       </c>
       <c r="G1444" t="n">
-        <v>53885545.608</v>
+        <v>53885793.608</v>
       </c>
       <c r="H1444" t="n">
         <v>2.3</v>
@@ -32610,7 +32610,7 @@
       </c>
       <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="n">
-        <v>64612564.281</v>
+        <v>64612815.281</v>
       </c>
       <c r="H1483" t="inlineStr"/>
     </row>
@@ -32632,7 +32632,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61885467.993</v>
+        <v>61885718.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61207816.519</v>
+        <v>61208067.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="n">
-        <v>60140775.818</v>
+        <v>60140772.818</v>
       </c>
       <c r="H1503" t="inlineStr"/>
     </row>
@@ -33088,7 +33088,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59044753.841</v>
+        <v>59044750.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="n">
-        <v>58347447.213</v>
+        <v>58415975.213</v>
       </c>
       <c r="H1506" t="inlineStr"/>
     </row>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58573801.727</v>
+        <v>58642328.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59670261.587</v>
+        <v>59738789.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="n">
-        <v>58037015.8</v>
+        <v>58067830.8</v>
       </c>
       <c r="H1509" t="inlineStr"/>
     </row>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="n">
-        <v>57269578.786</v>
+        <v>57290468.786</v>
       </c>
       <c r="H1510" t="inlineStr"/>
     </row>
@@ -33220,7 +33220,7 @@
       </c>
       <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="n">
-        <v>56151360.11</v>
+        <v>56162250.11</v>
       </c>
       <c r="H1511" t="inlineStr"/>
     </row>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="n">
-        <v>56465283.744</v>
+        <v>56474430.744</v>
       </c>
       <c r="H1512" t="inlineStr"/>
     </row>
@@ -33264,7 +33264,7 @@
       </c>
       <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="n">
-        <v>55882847.876</v>
+        <v>55892587.876</v>
       </c>
       <c r="H1513" t="inlineStr"/>
     </row>
@@ -33286,7 +33286,7 @@
       </c>
       <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="n">
-        <v>55601466.143</v>
+        <v>55613521.143</v>
       </c>
       <c r="H1514" t="inlineStr"/>
     </row>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55635513.479</v>
+        <v>55647569.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55686435.733</v>
+        <v>55698491.733</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33352,7 +33352,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55258365.15</v>
+        <v>55270421.15</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33374,7 +33374,7 @@
       </c>
       <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="n">
-        <v>55302210.162</v>
+        <v>55289724.162</v>
       </c>
       <c r="H1518" t="inlineStr"/>
     </row>
@@ -33396,7 +33396,7 @@
       </c>
       <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="n">
-        <v>54724945.928</v>
+        <v>54707358.928</v>
       </c>
       <c r="H1519" t="inlineStr"/>
     </row>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="n">
-        <v>55626110.663</v>
+        <v>55611981.663</v>
       </c>
       <c r="H1520" t="inlineStr"/>
     </row>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="n">
-        <v>57381756.612</v>
+        <v>57370683.612</v>
       </c>
       <c r="H1521" t="inlineStr"/>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="n">
-        <v>59177586.726</v>
+        <v>59214281.726</v>
       </c>
       <c r="H1524" t="inlineStr"/>
     </row>
@@ -33522,7 +33522,7 @@
       </c>
       <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="n">
-        <v>58635334.442</v>
+        <v>58708470.442</v>
       </c>
       <c r="H1525" t="inlineStr"/>
     </row>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="n">
-        <v>58664488.045</v>
+        <v>58722170.045</v>
       </c>
       <c r="H1526" t="inlineStr"/>
     </row>
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="n">
-        <v>59444502.107</v>
+        <v>59483544.107</v>
       </c>
       <c r="H1527" t="inlineStr"/>
     </row>
@@ -33588,7 +33588,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57845133.899</v>
+        <v>57884175.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="n">
-        <v>57137896.668</v>
+        <v>57156158.668</v>
       </c>
       <c r="H1529" t="inlineStr"/>
     </row>
@@ -33632,7 +33632,7 @@
       </c>
       <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="n">
-        <v>56165913.566</v>
+        <v>56176347.566</v>
       </c>
       <c r="H1530" t="inlineStr"/>
     </row>
@@ -33654,7 +33654,7 @@
       </c>
       <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="n">
-        <v>56053389.838</v>
+        <v>56061256.838</v>
       </c>
       <c r="H1531" t="inlineStr"/>
     </row>
@@ -33676,7 +33676,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55943263.807</v>
+        <v>55951130.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="n">
-        <v>56231299.122</v>
+        <v>56236457.122</v>
       </c>
       <c r="H1533" t="inlineStr"/>
     </row>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="n">
-        <v>55949101.807</v>
+        <v>55946947.807</v>
       </c>
       <c r="H1534" t="inlineStr"/>
     </row>
@@ -33742,7 +33742,7 @@
       </c>
       <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="n">
-        <v>55099236.219</v>
+        <v>55102329.219</v>
       </c>
       <c r="H1535" t="inlineStr"/>
     </row>
@@ -33764,7 +33764,7 @@
       </c>
       <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="n">
-        <v>54550632.642</v>
+        <v>54547341.642</v>
       </c>
       <c r="H1536" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54505274.849</v>
+        <v>54501982.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54979265.591</v>
+        <v>54975973.591</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="n">
-        <v>56106414.145</v>
+        <v>56095829.145</v>
       </c>
       <c r="H1539" t="inlineStr"/>
     </row>
@@ -33852,7 +33852,7 @@
       </c>
       <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="n">
-        <v>55843411.824</v>
+        <v>55828089.824</v>
       </c>
       <c r="H1540" t="inlineStr"/>
     </row>
@@ -33874,7 +33874,7 @@
       </c>
       <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="n">
-        <v>55925797.906</v>
+        <v>55910510.906</v>
       </c>
       <c r="H1541" t="inlineStr"/>
     </row>
@@ -33896,7 +33896,7 @@
       </c>
       <c r="F1542" t="inlineStr"/>
       <c r="G1542" t="n">
-        <v>58239872.582</v>
+        <v>58221917.582</v>
       </c>
       <c r="H1542" t="inlineStr"/>
     </row>
@@ -34784,7 +34784,7 @@
       </c>
       <c r="F1582" t="inlineStr"/>
       <c r="G1582" t="n">
-        <v>63455237.9</v>
+        <v>63454117.9</v>
       </c>
       <c r="H1582" t="inlineStr"/>
     </row>
@@ -35130,7 +35130,7 @@
       </c>
       <c r="F1598" t="inlineStr"/>
       <c r="G1598" t="n">
-        <v>61019953.083</v>
+        <v>60986727.083</v>
       </c>
       <c r="H1598" t="inlineStr"/>
     </row>
@@ -35152,7 +35152,7 @@
       </c>
       <c r="F1599" t="inlineStr"/>
       <c r="G1599" t="n">
-        <v>61314233.16</v>
+        <v>61282059.16</v>
       </c>
       <c r="H1599" t="inlineStr"/>
     </row>
@@ -35264,7 +35264,7 @@
         <v>22.3</v>
       </c>
       <c r="G1604" t="n">
-        <v>70408302.236</v>
+        <v>70405807.236</v>
       </c>
       <c r="H1604" t="n">
         <v>1.9</v>
@@ -35552,7 +35552,7 @@
       </c>
       <c r="F1617" t="inlineStr"/>
       <c r="G1617" t="n">
-        <v>64114734.533</v>
+        <v>64115004.533</v>
       </c>
       <c r="H1617" t="inlineStr"/>
     </row>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="F1618" t="inlineStr"/>
       <c r="G1618" t="n">
-        <v>63344780.404</v>
+        <v>63342457.238</v>
       </c>
       <c r="H1618" t="inlineStr"/>
     </row>
@@ -35596,7 +35596,7 @@
       </c>
       <c r="F1619" t="inlineStr"/>
       <c r="G1619" t="n">
-        <v>63721620.522</v>
+        <v>63711642.033</v>
       </c>
       <c r="H1619" t="inlineStr"/>
     </row>
@@ -35618,7 +35618,7 @@
       </c>
       <c r="F1620" t="inlineStr"/>
       <c r="G1620" t="n">
-        <v>63533632.405</v>
+        <v>63495417.358</v>
       </c>
       <c r="H1620" t="inlineStr"/>
     </row>
@@ -35640,7 +35640,7 @@
       </c>
       <c r="F1621" t="inlineStr"/>
       <c r="G1621" t="n">
-        <v>64270390.708</v>
+        <v>64235463.48</v>
       </c>
       <c r="H1621" t="inlineStr"/>
     </row>
@@ -35662,7 +35662,7 @@
       </c>
       <c r="F1622" t="inlineStr"/>
       <c r="G1622" t="n">
-        <v>63963066.865</v>
+        <v>63920568.385</v>
       </c>
       <c r="H1622" t="inlineStr"/>
     </row>
@@ -35683,15 +35683,21 @@
         <v>21.25</v>
       </c>
       <c r="F1623" t="inlineStr"/>
-      <c r="G1623" t="inlineStr"/>
+      <c r="G1623" t="n">
+        <v>64794627.115</v>
+      </c>
       <c r="H1623" t="inlineStr"/>
     </row>
     <row r="1624">
       <c r="A1624" s="1" t="n">
         <v>46233</v>
       </c>
-      <c r="B1624" t="inlineStr"/>
-      <c r="C1624" t="inlineStr"/>
+      <c r="B1624" t="n">
+        <v>49002</v>
+      </c>
+      <c r="C1624" t="n">
+        <v>45706709</v>
+      </c>
       <c r="D1624" t="n">
         <v>1512.02</v>
       </c>
@@ -35699,22 +35705,128 @@
         <v>21.9375</v>
       </c>
       <c r="F1624" t="inlineStr"/>
-      <c r="G1624" t="inlineStr"/>
+      <c r="G1624" t="n">
+        <v>66710168.861</v>
+      </c>
       <c r="H1624" t="inlineStr"/>
     </row>
     <row r="1625">
       <c r="A1625" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="B1625" t="inlineStr"/>
-      <c r="C1625" t="inlineStr"/>
+      <c r="B1625" t="n">
+        <v>47599</v>
+      </c>
+      <c r="C1625" t="n">
+        <v>46193622</v>
+      </c>
       <c r="D1625" t="n">
         <v>1511.12</v>
       </c>
-      <c r="E1625" t="inlineStr"/>
-      <c r="F1625" t="inlineStr"/>
-      <c r="G1625" t="inlineStr"/>
+      <c r="E1625" t="n">
+        <v>21.625</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G1625" t="n">
+        <v>69382098.93000001</v>
+      </c>
       <c r="H1625" t="inlineStr"/>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1626" t="n">
+        <v>49372</v>
+      </c>
+      <c r="C1626" t="n">
+        <v>46439196</v>
+      </c>
+      <c r="D1626" t="n">
+        <v>1515.98</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>21.4375</v>
+      </c>
+      <c r="F1626" t="inlineStr"/>
+      <c r="G1626" t="n">
+        <v>68184059.208</v>
+      </c>
+      <c r="H1626" t="inlineStr"/>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B1627" t="n">
+        <v>49639</v>
+      </c>
+      <c r="C1627" t="n">
+        <v>45693033</v>
+      </c>
+      <c r="D1627" t="n">
+        <v>1516.83</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>22.3125</v>
+      </c>
+      <c r="F1627" t="inlineStr"/>
+      <c r="G1627" t="n">
+        <v>67786167.662</v>
+      </c>
+      <c r="H1627" t="inlineStr"/>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1628" t="n">
+        <v>50058</v>
+      </c>
+      <c r="C1628" t="n">
+        <v>46530255</v>
+      </c>
+      <c r="D1628" t="n">
+        <v>1520.12</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>20.875</v>
+      </c>
+      <c r="F1628" t="inlineStr"/>
+      <c r="G1628" t="inlineStr"/>
+      <c r="H1628" t="inlineStr"/>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1629" t="inlineStr"/>
+      <c r="C1629" t="inlineStr"/>
+      <c r="D1629" t="n">
+        <v>1518.24</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1629" t="inlineStr"/>
+      <c r="G1629" t="inlineStr"/>
+      <c r="H1629" t="inlineStr"/>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B1630" t="inlineStr"/>
+      <c r="C1630" t="inlineStr"/>
+      <c r="D1630" t="n">
+        <v>1521.28</v>
+      </c>
+      <c r="E1630" t="inlineStr"/>
+      <c r="F1630" t="inlineStr"/>
+      <c r="G1630" t="inlineStr"/>
+      <c r="H1630" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1630"/>
+  <dimension ref="A1:H1635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31274,7 +31274,7 @@
         <v>21.9</v>
       </c>
       <c r="G1422" t="n">
-        <v>55345798.222</v>
+        <v>55346013.222</v>
       </c>
       <c r="H1422" t="n">
         <v>2.1</v>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="n">
-        <v>56142212.43</v>
+        <v>56142208.43</v>
       </c>
       <c r="H1461" t="inlineStr"/>
     </row>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65326165.703</v>
+        <v>65326416.703</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -34388,7 +34388,7 @@
       </c>
       <c r="F1564" t="inlineStr"/>
       <c r="G1564" t="n">
-        <v>60731235.828</v>
+        <v>60731171.828</v>
       </c>
       <c r="H1564" t="inlineStr"/>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="F1565" t="inlineStr"/>
       <c r="G1565" t="n">
-        <v>60125064.987</v>
+        <v>60134839.987</v>
       </c>
       <c r="H1565" t="inlineStr"/>
     </row>
@@ -34432,7 +34432,7 @@
       </c>
       <c r="F1566" t="inlineStr"/>
       <c r="G1566" t="n">
-        <v>60067676.457</v>
+        <v>60067563.457</v>
       </c>
       <c r="H1566" t="inlineStr"/>
     </row>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="F1567" t="inlineStr"/>
       <c r="G1567" t="n">
-        <v>60734769.321</v>
+        <v>60736930.321</v>
       </c>
       <c r="H1567" t="inlineStr"/>
     </row>
@@ -34476,7 +34476,7 @@
       </c>
       <c r="F1568" t="inlineStr"/>
       <c r="G1568" t="n">
-        <v>59028363.089</v>
+        <v>59027235.089</v>
       </c>
       <c r="H1568" t="inlineStr"/>
     </row>
@@ -34498,7 +34498,7 @@
       </c>
       <c r="F1569" t="inlineStr"/>
       <c r="G1569" t="n">
-        <v>58185751.149</v>
+        <v>58116398.149</v>
       </c>
       <c r="H1569" t="inlineStr"/>
     </row>
@@ -34520,7 +34520,7 @@
       </c>
       <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="n">
-        <v>57616409.887</v>
+        <v>57614645.887</v>
       </c>
       <c r="H1570" t="inlineStr"/>
     </row>
@@ -34542,7 +34542,7 @@
       </c>
       <c r="F1571" t="inlineStr"/>
       <c r="G1571" t="n">
-        <v>57625223.677</v>
+        <v>57624832.677</v>
       </c>
       <c r="H1571" t="inlineStr"/>
     </row>
@@ -34564,7 +34564,7 @@
       </c>
       <c r="F1572" t="inlineStr"/>
       <c r="G1572" t="n">
-        <v>57692366.026</v>
+        <v>57692457.026</v>
       </c>
       <c r="H1572" t="inlineStr"/>
     </row>
@@ -34586,7 +34586,7 @@
       </c>
       <c r="F1573" t="inlineStr"/>
       <c r="G1573" t="n">
-        <v>58028441.6</v>
+        <v>58046315.6</v>
       </c>
       <c r="H1573" t="inlineStr"/>
     </row>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="F1574" t="inlineStr"/>
       <c r="G1574" t="n">
-        <v>56580206.718</v>
+        <v>56577371.718</v>
       </c>
       <c r="H1574" t="inlineStr"/>
     </row>
@@ -34630,7 +34630,7 @@
       </c>
       <c r="F1575" t="inlineStr"/>
       <c r="G1575" t="n">
-        <v>56533814.683</v>
+        <v>56534878.683</v>
       </c>
       <c r="H1575" t="inlineStr"/>
     </row>
@@ -34652,7 +34652,7 @@
       </c>
       <c r="F1576" t="inlineStr"/>
       <c r="G1576" t="n">
-        <v>56518778.473</v>
+        <v>56518798.473</v>
       </c>
       <c r="H1576" t="inlineStr"/>
     </row>
@@ -34674,7 +34674,7 @@
       </c>
       <c r="F1577" t="inlineStr"/>
       <c r="G1577" t="n">
-        <v>56615131.751</v>
+        <v>56614484.751</v>
       </c>
       <c r="H1577" t="inlineStr"/>
     </row>
@@ -34696,7 +34696,7 @@
       </c>
       <c r="F1578" t="inlineStr"/>
       <c r="G1578" t="n">
-        <v>56497124.527</v>
+        <v>56497534.527</v>
       </c>
       <c r="H1578" t="inlineStr"/>
     </row>
@@ -34718,7 +34718,7 @@
       </c>
       <c r="F1579" t="inlineStr"/>
       <c r="G1579" t="n">
-        <v>57013570.328</v>
+        <v>57013368.328</v>
       </c>
       <c r="H1579" t="inlineStr"/>
     </row>
@@ -34740,7 +34740,7 @@
       </c>
       <c r="F1580" t="inlineStr"/>
       <c r="G1580" t="n">
-        <v>57904032.253</v>
+        <v>57904168.253</v>
       </c>
       <c r="H1580" t="inlineStr"/>
     </row>
@@ -34762,7 +34762,7 @@
       </c>
       <c r="F1581" t="inlineStr"/>
       <c r="G1581" t="n">
-        <v>59897314.035</v>
+        <v>59895840.035</v>
       </c>
       <c r="H1581" t="inlineStr"/>
     </row>
@@ -34822,7 +34822,7 @@
       </c>
       <c r="F1584" t="inlineStr"/>
       <c r="G1584" t="n">
-        <v>62192354.5</v>
+        <v>62192509.5</v>
       </c>
       <c r="H1584" t="inlineStr"/>
     </row>
@@ -34844,7 +34844,7 @@
       </c>
       <c r="F1585" t="inlineStr"/>
       <c r="G1585" t="n">
-        <v>62220529.556</v>
+        <v>62220721.556</v>
       </c>
       <c r="H1585" t="inlineStr"/>
     </row>
@@ -34866,7 +34866,7 @@
       </c>
       <c r="F1586" t="inlineStr"/>
       <c r="G1586" t="n">
-        <v>62051376.047</v>
+        <v>62051536.047</v>
       </c>
       <c r="H1586" t="inlineStr"/>
     </row>
@@ -34888,7 +34888,7 @@
       </c>
       <c r="F1587" t="inlineStr"/>
       <c r="G1587" t="n">
-        <v>62801234.612</v>
+        <v>62801506.612</v>
       </c>
       <c r="H1587" t="inlineStr"/>
     </row>
@@ -34910,7 +34910,7 @@
       </c>
       <c r="F1588" t="inlineStr"/>
       <c r="G1588" t="n">
-        <v>61599993.134</v>
+        <v>61600288.134</v>
       </c>
       <c r="H1588" t="inlineStr"/>
     </row>
@@ -34932,7 +34932,7 @@
       </c>
       <c r="F1589" t="inlineStr"/>
       <c r="G1589" t="n">
-        <v>60922773.097</v>
+        <v>60922808.097</v>
       </c>
       <c r="H1589" t="inlineStr"/>
     </row>
@@ -34954,7 +34954,7 @@
       </c>
       <c r="F1590" t="inlineStr"/>
       <c r="G1590" t="n">
-        <v>60711478.135</v>
+        <v>60711687.135</v>
       </c>
       <c r="H1590" t="inlineStr"/>
     </row>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="F1591" t="inlineStr"/>
       <c r="G1591" t="n">
-        <v>60428863.682</v>
+        <v>60428949.682</v>
       </c>
       <c r="H1591" t="inlineStr"/>
     </row>
@@ -34998,7 +34998,7 @@
       </c>
       <c r="F1592" t="inlineStr"/>
       <c r="G1592" t="n">
-        <v>60439087.832</v>
+        <v>60439115.832</v>
       </c>
       <c r="H1592" t="inlineStr"/>
     </row>
@@ -35020,7 +35020,7 @@
       </c>
       <c r="F1593" t="inlineStr"/>
       <c r="G1593" t="n">
-        <v>60559823.856</v>
+        <v>60559831.856</v>
       </c>
       <c r="H1593" t="inlineStr"/>
     </row>
@@ -35042,7 +35042,7 @@
       </c>
       <c r="F1594" t="inlineStr"/>
       <c r="G1594" t="n">
-        <v>61238468.499</v>
+        <v>61238576.499</v>
       </c>
       <c r="H1594" t="inlineStr"/>
     </row>
@@ -35064,7 +35064,7 @@
       </c>
       <c r="F1595" t="inlineStr"/>
       <c r="G1595" t="n">
-        <v>61080610.917</v>
+        <v>61080784.917</v>
       </c>
       <c r="H1595" t="inlineStr"/>
     </row>
@@ -35086,7 +35086,7 @@
       </c>
       <c r="F1596" t="inlineStr"/>
       <c r="G1596" t="n">
-        <v>61218542.503</v>
+        <v>61218624.503</v>
       </c>
       <c r="H1596" t="inlineStr"/>
     </row>
@@ -35108,7 +35108,7 @@
       </c>
       <c r="F1597" t="inlineStr"/>
       <c r="G1597" t="n">
-        <v>60956718.644</v>
+        <v>60956734.644</v>
       </c>
       <c r="H1597" t="inlineStr"/>
     </row>
@@ -35130,7 +35130,7 @@
       </c>
       <c r="F1598" t="inlineStr"/>
       <c r="G1598" t="n">
-        <v>60986727.083</v>
+        <v>60986771.083</v>
       </c>
       <c r="H1598" t="inlineStr"/>
     </row>
@@ -35152,7 +35152,7 @@
       </c>
       <c r="F1599" t="inlineStr"/>
       <c r="G1599" t="n">
-        <v>61282059.16</v>
+        <v>61282075.16</v>
       </c>
       <c r="H1599" t="inlineStr"/>
     </row>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="F1600" t="inlineStr"/>
       <c r="G1600" t="n">
-        <v>61350952.919</v>
+        <v>61350997.919</v>
       </c>
       <c r="H1600" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
       </c>
       <c r="F1601" t="inlineStr"/>
       <c r="G1601" t="n">
-        <v>62941125.868</v>
+        <v>62941345.868</v>
       </c>
       <c r="H1601" t="inlineStr"/>
     </row>
@@ -35218,7 +35218,7 @@
       </c>
       <c r="F1602" t="inlineStr"/>
       <c r="G1602" t="n">
-        <v>63919238.573</v>
+        <v>63919254.573</v>
       </c>
       <c r="H1602" t="inlineStr"/>
     </row>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="F1603" t="inlineStr"/>
       <c r="G1603" t="n">
-        <v>68450812.31200001</v>
+        <v>68450850.31200001</v>
       </c>
       <c r="H1603" t="inlineStr"/>
     </row>
@@ -35264,7 +35264,7 @@
         <v>22.3</v>
       </c>
       <c r="G1604" t="n">
-        <v>70405807.236</v>
+        <v>70406497.236</v>
       </c>
       <c r="H1604" t="n">
         <v>1.9</v>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="F1618" t="inlineStr"/>
       <c r="G1618" t="n">
-        <v>63342457.238</v>
+        <v>63334802.238</v>
       </c>
       <c r="H1618" t="inlineStr"/>
     </row>
@@ -35596,7 +35596,7 @@
       </c>
       <c r="F1619" t="inlineStr"/>
       <c r="G1619" t="n">
-        <v>63711642.033</v>
+        <v>63707734.033</v>
       </c>
       <c r="H1619" t="inlineStr"/>
     </row>
@@ -35618,7 +35618,7 @@
       </c>
       <c r="F1620" t="inlineStr"/>
       <c r="G1620" t="n">
-        <v>63495417.358</v>
+        <v>63509636.358</v>
       </c>
       <c r="H1620" t="inlineStr"/>
     </row>
@@ -35640,7 +35640,7 @@
       </c>
       <c r="F1621" t="inlineStr"/>
       <c r="G1621" t="n">
-        <v>64235463.48</v>
+        <v>64246880.48</v>
       </c>
       <c r="H1621" t="inlineStr"/>
     </row>
@@ -35662,7 +35662,7 @@
       </c>
       <c r="F1622" t="inlineStr"/>
       <c r="G1622" t="n">
-        <v>63920568.385</v>
+        <v>63937633.385</v>
       </c>
       <c r="H1622" t="inlineStr"/>
     </row>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="F1623" t="inlineStr"/>
       <c r="G1623" t="n">
-        <v>64794627.115</v>
+        <v>64760907.009</v>
       </c>
       <c r="H1623" t="inlineStr"/>
     </row>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="F1624" t="inlineStr"/>
       <c r="G1624" t="n">
-        <v>66710168.861</v>
+        <v>66757474.503</v>
       </c>
       <c r="H1624" t="inlineStr"/>
     </row>
@@ -35730,9 +35730,11 @@
         <v>21.8</v>
       </c>
       <c r="G1625" t="n">
-        <v>69382098.93000001</v>
-      </c>
-      <c r="H1625" t="inlineStr"/>
+        <v>69280207.59299999</v>
+      </c>
+      <c r="H1625" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="1626">
       <c r="A1626" s="1" t="n">
@@ -35752,7 +35754,7 @@
       </c>
       <c r="F1626" t="inlineStr"/>
       <c r="G1626" t="n">
-        <v>68184059.208</v>
+        <v>68157949.20999999</v>
       </c>
       <c r="H1626" t="inlineStr"/>
     </row>
@@ -35774,7 +35776,7 @@
       </c>
       <c r="F1627" t="inlineStr"/>
       <c r="G1627" t="n">
-        <v>67786167.662</v>
+        <v>67727855.027</v>
       </c>
       <c r="H1627" t="inlineStr"/>
     </row>
@@ -35795,15 +35797,21 @@
         <v>20.875</v>
       </c>
       <c r="F1628" t="inlineStr"/>
-      <c r="G1628" t="inlineStr"/>
+      <c r="G1628" t="n">
+        <v>67987141.76199999</v>
+      </c>
       <c r="H1628" t="inlineStr"/>
     </row>
     <row r="1629">
       <c r="A1629" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="B1629" t="inlineStr"/>
-      <c r="C1629" t="inlineStr"/>
+      <c r="B1629" t="n">
+        <v>48834</v>
+      </c>
+      <c r="C1629" t="n">
+        <v>46321735</v>
+      </c>
       <c r="D1629" t="n">
         <v>1518.24</v>
       </c>
@@ -35811,22 +35819,126 @@
         <v>22</v>
       </c>
       <c r="F1629" t="inlineStr"/>
-      <c r="G1629" t="inlineStr"/>
+      <c r="G1629" t="n">
+        <v>68900675.61300001</v>
+      </c>
       <c r="H1629" t="inlineStr"/>
     </row>
     <row r="1630">
       <c r="A1630" s="1" t="n">
         <v>46241</v>
       </c>
-      <c r="B1630" t="inlineStr"/>
-      <c r="C1630" t="inlineStr"/>
+      <c r="B1630" t="n">
+        <v>49457</v>
+      </c>
+      <c r="C1630" t="n">
+        <v>46189969</v>
+      </c>
       <c r="D1630" t="n">
         <v>1521.28</v>
       </c>
-      <c r="E1630" t="inlineStr"/>
+      <c r="E1630" t="n">
+        <v>21.5</v>
+      </c>
       <c r="F1630" t="inlineStr"/>
-      <c r="G1630" t="inlineStr"/>
+      <c r="G1630" t="n">
+        <v>66943678.977</v>
+      </c>
       <c r="H1630" t="inlineStr"/>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1631" t="n">
+        <v>49564</v>
+      </c>
+      <c r="C1631" t="n">
+        <v>46031628</v>
+      </c>
+      <c r="D1631" t="n">
+        <v>1520.43</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>21.625</v>
+      </c>
+      <c r="F1631" t="inlineStr"/>
+      <c r="G1631" t="n">
+        <v>65425253.593</v>
+      </c>
+      <c r="H1631" t="inlineStr"/>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B1632" t="n">
+        <v>49586</v>
+      </c>
+      <c r="C1632" t="n">
+        <v>46138834</v>
+      </c>
+      <c r="D1632" t="n">
+        <v>1517.89</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>22.8125</v>
+      </c>
+      <c r="F1632" t="inlineStr"/>
+      <c r="G1632" t="n">
+        <v>64610607.441</v>
+      </c>
+      <c r="H1632" t="inlineStr"/>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B1633" t="n">
+        <v>49628</v>
+      </c>
+      <c r="C1633" t="n">
+        <v>46446862</v>
+      </c>
+      <c r="D1633" t="n">
+        <v>1515.66</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1633" t="inlineStr"/>
+      <c r="G1633" t="inlineStr"/>
+      <c r="H1633" t="inlineStr"/>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1634" t="inlineStr"/>
+      <c r="C1634" t="inlineStr"/>
+      <c r="D1634" t="n">
+        <v>1515.66</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>22.5625</v>
+      </c>
+      <c r="F1634" t="inlineStr"/>
+      <c r="G1634" t="inlineStr"/>
+      <c r="H1634" t="inlineStr"/>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1635" t="inlineStr"/>
+      <c r="C1635" t="inlineStr"/>
+      <c r="D1635" t="n">
+        <v>1512.59</v>
+      </c>
+      <c r="E1635" t="inlineStr"/>
+      <c r="F1635" t="inlineStr"/>
+      <c r="G1635" t="inlineStr"/>
+      <c r="H1635" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1635"/>
+  <dimension ref="A1:H1639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32632,7 +32632,7 @@
       </c>
       <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="n">
-        <v>61885718.993</v>
+        <v>61895383.993</v>
       </c>
       <c r="H1484" t="inlineStr"/>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61208067.519</v>
+        <v>61217732.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="n">
-        <v>61743079.076</v>
+        <v>61765647.076</v>
       </c>
       <c r="H1486" t="inlineStr"/>
     </row>
@@ -32698,7 +32698,7 @@
       </c>
       <c r="F1487" t="inlineStr"/>
       <c r="G1487" t="n">
-        <v>60508250.004</v>
+        <v>60530817.004</v>
       </c>
       <c r="H1487" t="inlineStr"/>
     </row>
@@ -32720,7 +32720,7 @@
       </c>
       <c r="F1488" t="inlineStr"/>
       <c r="G1488" t="n">
-        <v>59554425.211</v>
+        <v>59576993.211</v>
       </c>
       <c r="H1488" t="inlineStr"/>
     </row>
@@ -32742,7 +32742,7 @@
       </c>
       <c r="F1489" t="inlineStr"/>
       <c r="G1489" t="n">
-        <v>57836224.381</v>
+        <v>57858791.381</v>
       </c>
       <c r="H1489" t="inlineStr"/>
     </row>
@@ -32764,7 +32764,7 @@
       </c>
       <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="n">
-        <v>57233592.101</v>
+        <v>57256159.101</v>
       </c>
       <c r="H1490" t="inlineStr"/>
     </row>
@@ -32786,7 +32786,7 @@
       </c>
       <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="n">
-        <v>57172528.244</v>
+        <v>57195095.244</v>
       </c>
       <c r="H1491" t="inlineStr"/>
     </row>
@@ -32808,7 +32808,7 @@
       </c>
       <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="n">
-        <v>57603059.399</v>
+        <v>57625627.399</v>
       </c>
       <c r="H1492" t="inlineStr"/>
     </row>
@@ -32830,7 +32830,7 @@
       </c>
       <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="n">
-        <v>56277371.088</v>
+        <v>56299939.088</v>
       </c>
       <c r="H1493" t="inlineStr"/>
     </row>
@@ -32852,7 +32852,7 @@
       </c>
       <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="n">
-        <v>55654720.47</v>
+        <v>55677288.47</v>
       </c>
       <c r="H1494" t="inlineStr"/>
     </row>
@@ -32874,7 +32874,7 @@
       </c>
       <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="n">
-        <v>55481658.492</v>
+        <v>55504227.492</v>
       </c>
       <c r="H1495" t="inlineStr"/>
     </row>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="n">
-        <v>55311997.796</v>
+        <v>55334565.796</v>
       </c>
       <c r="H1496" t="inlineStr"/>
     </row>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="n">
-        <v>55075460.613</v>
+        <v>55098027.613</v>
       </c>
       <c r="H1497" t="inlineStr"/>
     </row>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="n">
-        <v>54776610.758</v>
+        <v>54740587.758</v>
       </c>
       <c r="H1498" t="inlineStr"/>
     </row>
@@ -32962,7 +32962,7 @@
       </c>
       <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="n">
-        <v>54932391.349</v>
+        <v>54892001.349</v>
       </c>
       <c r="H1499" t="inlineStr"/>
     </row>
@@ -32984,7 +32984,7 @@
       </c>
       <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="n">
-        <v>55186744.773</v>
+        <v>55142535.773</v>
       </c>
       <c r="H1500" t="inlineStr"/>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="n">
-        <v>55943082.062</v>
+        <v>55904141.062</v>
       </c>
       <c r="H1501" t="inlineStr"/>
     </row>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="n">
-        <v>57638505.416</v>
+        <v>57602845.416</v>
       </c>
       <c r="H1502" t="inlineStr"/>
     </row>
@@ -33088,7 +33088,7 @@
       </c>
       <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="n">
-        <v>59044750.841</v>
+        <v>59080793.841</v>
       </c>
       <c r="H1505" t="inlineStr"/>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="n">
-        <v>59738789.587</v>
+        <v>59715476.587</v>
       </c>
       <c r="H1508" t="inlineStr"/>
     </row>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="n">
-        <v>55647569.479</v>
+        <v>55639950.479</v>
       </c>
       <c r="H1515" t="inlineStr"/>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="n">
-        <v>55698491.733</v>
+        <v>55689324.733</v>
       </c>
       <c r="H1516" t="inlineStr"/>
     </row>
@@ -33352,7 +33352,7 @@
       </c>
       <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="n">
-        <v>55270421.15</v>
+        <v>55252350.15</v>
       </c>
       <c r="H1517" t="inlineStr"/>
     </row>
@@ -33588,7 +33588,7 @@
       </c>
       <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="n">
-        <v>57884175.899</v>
+        <v>57873312.899</v>
       </c>
       <c r="H1528" t="inlineStr"/>
     </row>
@@ -33676,7 +33676,7 @@
       </c>
       <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="n">
-        <v>55951130.807</v>
+        <v>55953016.807</v>
       </c>
       <c r="H1532" t="inlineStr"/>
     </row>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="n">
-        <v>54501982.849</v>
+        <v>54499877.849</v>
       </c>
       <c r="H1537" t="inlineStr"/>
     </row>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="n">
-        <v>54975973.591</v>
+        <v>54975706.591</v>
       </c>
       <c r="H1538" t="inlineStr"/>
     </row>
@@ -33944,7 +33944,7 @@
       </c>
       <c r="F1544" t="inlineStr"/>
       <c r="G1544" t="n">
-        <v>59401786.307</v>
+        <v>59437969.307</v>
       </c>
       <c r="H1544" t="inlineStr"/>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="F1545" t="inlineStr"/>
       <c r="G1545" t="n">
-        <v>58874485.314</v>
+        <v>58864928.314</v>
       </c>
       <c r="H1545" t="inlineStr"/>
     </row>
@@ -33988,7 +33988,7 @@
       </c>
       <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="n">
-        <v>58487701.356</v>
+        <v>58465207.356</v>
       </c>
       <c r="H1546" t="inlineStr"/>
     </row>
@@ -34010,7 +34010,7 @@
       </c>
       <c r="F1547" t="inlineStr"/>
       <c r="G1547" t="n">
-        <v>58201633.536</v>
+        <v>58174772.536</v>
       </c>
       <c r="H1547" t="inlineStr"/>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="F1548" t="inlineStr"/>
       <c r="G1548" t="n">
-        <v>57482694.632</v>
+        <v>57453419.632</v>
       </c>
       <c r="H1548" t="inlineStr"/>
     </row>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="n">
-        <v>56939396.446</v>
+        <v>56910120.446</v>
       </c>
       <c r="H1549" t="inlineStr"/>
     </row>
@@ -34076,7 +34076,7 @@
       </c>
       <c r="F1550" t="inlineStr"/>
       <c r="G1550" t="n">
-        <v>55945548.207</v>
+        <v>55901239.207</v>
       </c>
       <c r="H1550" t="inlineStr"/>
     </row>
@@ -34098,7 +34098,7 @@
       </c>
       <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="n">
-        <v>55757413.443</v>
+        <v>55713105.443</v>
       </c>
       <c r="H1551" t="inlineStr"/>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="F1552" t="inlineStr"/>
       <c r="G1552" t="n">
-        <v>56295798.934</v>
+        <v>56251212.934</v>
       </c>
       <c r="H1552" t="inlineStr"/>
     </row>
@@ -34822,7 +34822,7 @@
       </c>
       <c r="F1584" t="inlineStr"/>
       <c r="G1584" t="n">
-        <v>62192509.5</v>
+        <v>62179907.62</v>
       </c>
       <c r="H1584" t="inlineStr"/>
     </row>
@@ -35264,7 +35264,7 @@
         <v>22.3</v>
       </c>
       <c r="G1604" t="n">
-        <v>70406497.236</v>
+        <v>70406860.236</v>
       </c>
       <c r="H1604" t="n">
         <v>1.9</v>
@@ -35486,7 +35486,7 @@
       </c>
       <c r="F1614" t="inlineStr"/>
       <c r="G1614" t="n">
-        <v>65467784.441</v>
+        <v>65568888.283</v>
       </c>
       <c r="H1614" t="inlineStr"/>
     </row>
@@ -35776,7 +35776,7 @@
       </c>
       <c r="F1627" t="inlineStr"/>
       <c r="G1627" t="n">
-        <v>67727855.027</v>
+        <v>67725148.027</v>
       </c>
       <c r="H1627" t="inlineStr"/>
     </row>
@@ -35798,7 +35798,7 @@
       </c>
       <c r="F1628" t="inlineStr"/>
       <c r="G1628" t="n">
-        <v>67987141.76199999</v>
+        <v>67975383.47499999</v>
       </c>
       <c r="H1628" t="inlineStr"/>
     </row>
@@ -35820,7 +35820,7 @@
       </c>
       <c r="F1629" t="inlineStr"/>
       <c r="G1629" t="n">
-        <v>68900675.61300001</v>
+        <v>68801282.51199999</v>
       </c>
       <c r="H1629" t="inlineStr"/>
     </row>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="F1630" t="inlineStr"/>
       <c r="G1630" t="n">
-        <v>66943678.977</v>
+        <v>66816254.598</v>
       </c>
       <c r="H1630" t="inlineStr"/>
     </row>
@@ -35864,7 +35864,7 @@
       </c>
       <c r="F1631" t="inlineStr"/>
       <c r="G1631" t="n">
-        <v>65425253.593</v>
+        <v>65297266.905</v>
       </c>
       <c r="H1631" t="inlineStr"/>
     </row>
@@ -35886,7 +35886,7 @@
       </c>
       <c r="F1632" t="inlineStr"/>
       <c r="G1632" t="n">
-        <v>64610607.441</v>
+        <v>64530612.767</v>
       </c>
       <c r="H1632" t="inlineStr"/>
     </row>
@@ -35907,15 +35907,21 @@
         <v>21</v>
       </c>
       <c r="F1633" t="inlineStr"/>
-      <c r="G1633" t="inlineStr"/>
+      <c r="G1633" t="n">
+        <v>64609903.562</v>
+      </c>
       <c r="H1633" t="inlineStr"/>
     </row>
     <row r="1634">
       <c r="A1634" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="B1634" t="inlineStr"/>
-      <c r="C1634" t="inlineStr"/>
+      <c r="B1634" t="n">
+        <v>49543</v>
+      </c>
+      <c r="C1634" t="n">
+        <v>46636012</v>
+      </c>
       <c r="D1634" t="n">
         <v>1515.66</v>
       </c>
@@ -35923,22 +35929,104 @@
         <v>22.5625</v>
       </c>
       <c r="F1634" t="inlineStr"/>
-      <c r="G1634" t="inlineStr"/>
+      <c r="G1634" t="n">
+        <v>64838834.346</v>
+      </c>
       <c r="H1634" t="inlineStr"/>
     </row>
     <row r="1635">
       <c r="A1635" s="1" t="n">
         <v>46248</v>
       </c>
-      <c r="B1635" t="inlineStr"/>
-      <c r="C1635" t="inlineStr"/>
+      <c r="B1635" t="n">
+        <v>49505</v>
+      </c>
+      <c r="C1635" t="n">
+        <v>46487398</v>
+      </c>
       <c r="D1635" t="n">
         <v>1512.59</v>
       </c>
-      <c r="E1635" t="inlineStr"/>
+      <c r="E1635" t="n">
+        <v>23.3125</v>
+      </c>
       <c r="F1635" t="inlineStr"/>
-      <c r="G1635" t="inlineStr"/>
+      <c r="G1635" t="n">
+        <v>64346561.749</v>
+      </c>
       <c r="H1635" t="inlineStr"/>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B1636" t="n">
+        <v>49593</v>
+      </c>
+      <c r="C1636" t="n">
+        <v>46427239</v>
+      </c>
+      <c r="D1636" t="n">
+        <v>1515.02</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="F1636" t="inlineStr"/>
+      <c r="G1636" t="n">
+        <v>64106355.019</v>
+      </c>
+      <c r="H1636" t="inlineStr"/>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B1637" t="n">
+        <v>50006</v>
+      </c>
+      <c r="C1637" t="n">
+        <v>47824170</v>
+      </c>
+      <c r="D1637" t="n">
+        <v>1517.54</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1637" t="inlineStr"/>
+      <c r="G1637" t="inlineStr"/>
+      <c r="H1637" t="inlineStr"/>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B1638" t="inlineStr"/>
+      <c r="C1638" t="inlineStr"/>
+      <c r="D1638" t="n">
+        <v>1517.58</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>24.3125</v>
+      </c>
+      <c r="F1638" t="inlineStr"/>
+      <c r="G1638" t="inlineStr"/>
+      <c r="H1638" t="inlineStr"/>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B1639" t="inlineStr"/>
+      <c r="C1639" t="inlineStr"/>
+      <c r="D1639" t="n">
+        <v>1518.13</v>
+      </c>
+      <c r="E1639" t="inlineStr"/>
+      <c r="F1639" t="inlineStr"/>
+      <c r="G1639" t="inlineStr"/>
+      <c r="H1639" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1639"/>
+  <dimension ref="A1:H1645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34822,7 +34822,7 @@
       </c>
       <c r="F1584" t="inlineStr"/>
       <c r="G1584" t="n">
-        <v>62179907.62</v>
+        <v>62180123.62</v>
       </c>
       <c r="H1584" t="inlineStr"/>
     </row>
@@ -34844,7 +34844,7 @@
       </c>
       <c r="F1585" t="inlineStr"/>
       <c r="G1585" t="n">
-        <v>62220721.556</v>
+        <v>62220744.556</v>
       </c>
       <c r="H1585" t="inlineStr"/>
     </row>
@@ -34866,7 +34866,7 @@
       </c>
       <c r="F1586" t="inlineStr"/>
       <c r="G1586" t="n">
-        <v>62051536.047</v>
+        <v>62051544.047</v>
       </c>
       <c r="H1586" t="inlineStr"/>
     </row>
@@ -34888,7 +34888,7 @@
       </c>
       <c r="F1587" t="inlineStr"/>
       <c r="G1587" t="n">
-        <v>62801506.612</v>
+        <v>62801514.612</v>
       </c>
       <c r="H1587" t="inlineStr"/>
     </row>
@@ -34910,7 +34910,7 @@
       </c>
       <c r="F1588" t="inlineStr"/>
       <c r="G1588" t="n">
-        <v>61600288.134</v>
+        <v>61554417.134</v>
       </c>
       <c r="H1588" t="inlineStr"/>
     </row>
@@ -34932,7 +34932,7 @@
       </c>
       <c r="F1589" t="inlineStr"/>
       <c r="G1589" t="n">
-        <v>60922808.097</v>
+        <v>60922810.097</v>
       </c>
       <c r="H1589" t="inlineStr"/>
     </row>
@@ -34954,7 +34954,7 @@
       </c>
       <c r="F1590" t="inlineStr"/>
       <c r="G1590" t="n">
-        <v>60711687.135</v>
+        <v>60711691.135</v>
       </c>
       <c r="H1590" t="inlineStr"/>
     </row>
@@ -34976,7 +34976,7 @@
       </c>
       <c r="F1591" t="inlineStr"/>
       <c r="G1591" t="n">
-        <v>60428949.682</v>
+        <v>60428953.682</v>
       </c>
       <c r="H1591" t="inlineStr"/>
     </row>
@@ -34998,7 +34998,7 @@
       </c>
       <c r="F1592" t="inlineStr"/>
       <c r="G1592" t="n">
-        <v>60439115.832</v>
+        <v>60439788.832</v>
       </c>
       <c r="H1592" t="inlineStr"/>
     </row>
@@ -35020,7 +35020,7 @@
       </c>
       <c r="F1593" t="inlineStr"/>
       <c r="G1593" t="n">
-        <v>60559831.856</v>
+        <v>60559788.856</v>
       </c>
       <c r="H1593" t="inlineStr"/>
     </row>
@@ -35042,7 +35042,7 @@
       </c>
       <c r="F1594" t="inlineStr"/>
       <c r="G1594" t="n">
-        <v>61238576.499</v>
+        <v>61238531.499</v>
       </c>
       <c r="H1594" t="inlineStr"/>
     </row>
@@ -35064,7 +35064,7 @@
       </c>
       <c r="F1595" t="inlineStr"/>
       <c r="G1595" t="n">
-        <v>61080784.917</v>
+        <v>61080747.917</v>
       </c>
       <c r="H1595" t="inlineStr"/>
     </row>
@@ -35086,7 +35086,7 @@
       </c>
       <c r="F1596" t="inlineStr"/>
       <c r="G1596" t="n">
-        <v>61218624.503</v>
+        <v>61218623.503</v>
       </c>
       <c r="H1596" t="inlineStr"/>
     </row>
@@ -35108,7 +35108,7 @@
       </c>
       <c r="F1597" t="inlineStr"/>
       <c r="G1597" t="n">
-        <v>60956734.644</v>
+        <v>60956735.644</v>
       </c>
       <c r="H1597" t="inlineStr"/>
     </row>
@@ -35130,7 +35130,7 @@
       </c>
       <c r="F1598" t="inlineStr"/>
       <c r="G1598" t="n">
-        <v>60986771.083</v>
+        <v>60986778.083</v>
       </c>
       <c r="H1598" t="inlineStr"/>
     </row>
@@ -35152,7 +35152,7 @@
       </c>
       <c r="F1599" t="inlineStr"/>
       <c r="G1599" t="n">
-        <v>61282075.16</v>
+        <v>61282073.16</v>
       </c>
       <c r="H1599" t="inlineStr"/>
     </row>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="F1600" t="inlineStr"/>
       <c r="G1600" t="n">
-        <v>61350997.919</v>
+        <v>61350987.919</v>
       </c>
       <c r="H1600" t="inlineStr"/>
     </row>
@@ -35196,7 +35196,7 @@
       </c>
       <c r="F1601" t="inlineStr"/>
       <c r="G1601" t="n">
-        <v>62941345.868</v>
+        <v>62941338.868</v>
       </c>
       <c r="H1601" t="inlineStr"/>
     </row>
@@ -35218,7 +35218,7 @@
       </c>
       <c r="F1602" t="inlineStr"/>
       <c r="G1602" t="n">
-        <v>63919254.573</v>
+        <v>63919248.573</v>
       </c>
       <c r="H1602" t="inlineStr"/>
     </row>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="F1603" t="inlineStr"/>
       <c r="G1603" t="n">
-        <v>68450850.31200001</v>
+        <v>68450859.31200001</v>
       </c>
       <c r="H1603" t="inlineStr"/>
     </row>
@@ -35332,7 +35332,7 @@
       </c>
       <c r="F1607" t="inlineStr"/>
       <c r="G1607" t="n">
-        <v>70587774.83499999</v>
+        <v>70587775.08499999</v>
       </c>
       <c r="H1607" t="inlineStr"/>
     </row>
@@ -35420,7 +35420,7 @@
       </c>
       <c r="F1611" t="inlineStr"/>
       <c r="G1611" t="n">
-        <v>67071887.292</v>
+        <v>67071887.542</v>
       </c>
       <c r="H1611" t="inlineStr"/>
     </row>
@@ -35442,7 +35442,7 @@
       </c>
       <c r="F1612" t="inlineStr"/>
       <c r="G1612" t="n">
-        <v>66241955.61</v>
+        <v>66241955.86</v>
       </c>
       <c r="H1612" t="inlineStr"/>
     </row>
@@ -35464,7 +35464,7 @@
       </c>
       <c r="F1613" t="inlineStr"/>
       <c r="G1613" t="n">
-        <v>65273840.255</v>
+        <v>65273840.505</v>
       </c>
       <c r="H1613" t="inlineStr"/>
     </row>
@@ -35486,7 +35486,7 @@
       </c>
       <c r="F1614" t="inlineStr"/>
       <c r="G1614" t="n">
-        <v>65568888.283</v>
+        <v>65470550.935</v>
       </c>
       <c r="H1614" t="inlineStr"/>
     </row>
@@ -35662,7 +35662,7 @@
       </c>
       <c r="F1622" t="inlineStr"/>
       <c r="G1622" t="n">
-        <v>63937633.385</v>
+        <v>63937633.388</v>
       </c>
       <c r="H1622" t="inlineStr"/>
     </row>
@@ -35730,7 +35730,7 @@
         <v>21.8</v>
       </c>
       <c r="G1625" t="n">
-        <v>69280207.59299999</v>
+        <v>69310455.436</v>
       </c>
       <c r="H1625" t="n">
         <v>2.1</v>
@@ -35754,7 +35754,7 @@
       </c>
       <c r="F1626" t="inlineStr"/>
       <c r="G1626" t="n">
-        <v>68157949.20999999</v>
+        <v>68153020.20999999</v>
       </c>
       <c r="H1626" t="inlineStr"/>
     </row>
@@ -35776,7 +35776,7 @@
       </c>
       <c r="F1627" t="inlineStr"/>
       <c r="G1627" t="n">
-        <v>67725148.027</v>
+        <v>67719831.027</v>
       </c>
       <c r="H1627" t="inlineStr"/>
     </row>
@@ -35798,7 +35798,7 @@
       </c>
       <c r="F1628" t="inlineStr"/>
       <c r="G1628" t="n">
-        <v>67975383.47499999</v>
+        <v>67970065.47499999</v>
       </c>
       <c r="H1628" t="inlineStr"/>
     </row>
@@ -35820,7 +35820,7 @@
       </c>
       <c r="F1629" t="inlineStr"/>
       <c r="G1629" t="n">
-        <v>68801282.51199999</v>
+        <v>68795965.51199999</v>
       </c>
       <c r="H1629" t="inlineStr"/>
     </row>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="F1630" t="inlineStr"/>
       <c r="G1630" t="n">
-        <v>66816254.598</v>
+        <v>66810936.598</v>
       </c>
       <c r="H1630" t="inlineStr"/>
     </row>
@@ -35864,7 +35864,7 @@
       </c>
       <c r="F1631" t="inlineStr"/>
       <c r="G1631" t="n">
-        <v>65297266.905</v>
+        <v>65294247.905</v>
       </c>
       <c r="H1631" t="inlineStr"/>
     </row>
@@ -35886,7 +35886,7 @@
       </c>
       <c r="F1632" t="inlineStr"/>
       <c r="G1632" t="n">
-        <v>64530612.767</v>
+        <v>64477121.441</v>
       </c>
       <c r="H1632" t="inlineStr"/>
     </row>
@@ -35908,7 +35908,7 @@
       </c>
       <c r="F1633" t="inlineStr"/>
       <c r="G1633" t="n">
-        <v>64609903.562</v>
+        <v>64617213.723</v>
       </c>
       <c r="H1633" t="inlineStr"/>
     </row>
@@ -35930,7 +35930,7 @@
       </c>
       <c r="F1634" t="inlineStr"/>
       <c r="G1634" t="n">
-        <v>64838834.346</v>
+        <v>64848131.927</v>
       </c>
       <c r="H1634" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
       </c>
       <c r="F1635" t="inlineStr"/>
       <c r="G1635" t="n">
-        <v>64346561.749</v>
+        <v>64307575.931</v>
       </c>
       <c r="H1635" t="inlineStr"/>
     </row>
@@ -35974,7 +35974,7 @@
       </c>
       <c r="F1636" t="inlineStr"/>
       <c r="G1636" t="n">
-        <v>64106355.019</v>
+        <v>63942179.667</v>
       </c>
       <c r="H1636" t="inlineStr"/>
     </row>
@@ -35995,15 +35995,21 @@
         <v>23</v>
       </c>
       <c r="F1637" t="inlineStr"/>
-      <c r="G1637" t="inlineStr"/>
+      <c r="G1637" t="n">
+        <v>63545343.064</v>
+      </c>
       <c r="H1637" t="inlineStr"/>
     </row>
     <row r="1638">
       <c r="A1638" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="B1638" t="inlineStr"/>
-      <c r="C1638" t="inlineStr"/>
+      <c r="B1638" t="n">
+        <v>50344</v>
+      </c>
+      <c r="C1638" t="n">
+        <v>48175716</v>
+      </c>
       <c r="D1638" t="n">
         <v>1517.58</v>
       </c>
@@ -36011,22 +36017,148 @@
         <v>24.3125</v>
       </c>
       <c r="F1638" t="inlineStr"/>
-      <c r="G1638" t="inlineStr"/>
+      <c r="G1638" t="n">
+        <v>62871184.25</v>
+      </c>
       <c r="H1638" t="inlineStr"/>
     </row>
     <row r="1639">
       <c r="A1639" s="1" t="n">
         <v>46255</v>
       </c>
-      <c r="B1639" t="inlineStr"/>
-      <c r="C1639" t="inlineStr"/>
+      <c r="B1639" t="n">
+        <v>50660</v>
+      </c>
+      <c r="C1639" t="n">
+        <v>46210440</v>
+      </c>
       <c r="D1639" t="n">
         <v>1518.13</v>
       </c>
-      <c r="E1639" t="inlineStr"/>
+      <c r="E1639" t="n">
+        <v>24.125</v>
+      </c>
       <c r="F1639" t="inlineStr"/>
-      <c r="G1639" t="inlineStr"/>
+      <c r="G1639" t="n">
+        <v>62698614.663</v>
+      </c>
       <c r="H1639" t="inlineStr"/>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B1640" t="n">
+        <v>50776</v>
+      </c>
+      <c r="C1640" t="n">
+        <v>47076725</v>
+      </c>
+      <c r="D1640" t="n">
+        <v>1527.33</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="F1640" t="inlineStr"/>
+      <c r="G1640" t="n">
+        <v>62412647.268</v>
+      </c>
+      <c r="H1640" t="inlineStr"/>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B1641" t="n">
+        <v>50913</v>
+      </c>
+      <c r="C1641" t="n">
+        <v>45965061</v>
+      </c>
+      <c r="D1641" t="n">
+        <v>1531.07</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="F1641" t="inlineStr"/>
+      <c r="G1641" t="n">
+        <v>62717921.434</v>
+      </c>
+      <c r="H1641" t="inlineStr"/>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B1642" t="n">
+        <v>50784</v>
+      </c>
+      <c r="C1642" t="n">
+        <v>46038739</v>
+      </c>
+      <c r="D1642" t="n">
+        <v>1533.11</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>23.1875</v>
+      </c>
+      <c r="F1642" t="inlineStr"/>
+      <c r="G1642" t="n">
+        <v>63244690.188</v>
+      </c>
+      <c r="H1642" t="inlineStr"/>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B1643" t="n">
+        <v>50861</v>
+      </c>
+      <c r="C1643" t="n">
+        <v>45621808</v>
+      </c>
+      <c r="D1643" t="n">
+        <v>1533.22</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>23.9375</v>
+      </c>
+      <c r="F1643" t="inlineStr"/>
+      <c r="G1643" t="inlineStr"/>
+      <c r="H1643" t="inlineStr"/>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B1644" t="inlineStr"/>
+      <c r="C1644" t="inlineStr"/>
+      <c r="D1644" t="n">
+        <v>1533.21</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>23.1875</v>
+      </c>
+      <c r="F1644" t="inlineStr"/>
+      <c r="G1644" t="inlineStr"/>
+      <c r="H1644" t="inlineStr"/>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B1645" t="inlineStr"/>
+      <c r="C1645" t="inlineStr"/>
+      <c r="D1645" t="n">
+        <v>1531.51</v>
+      </c>
+      <c r="E1645" t="inlineStr"/>
+      <c r="F1645" t="inlineStr"/>
+      <c r="G1645" t="inlineStr"/>
+      <c r="H1645" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1645"/>
+  <dimension ref="A1:H1649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32138,7 +32138,7 @@
       </c>
       <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="n">
-        <v>56142208.43</v>
+        <v>56142524.43</v>
       </c>
       <c r="H1461" t="inlineStr"/>
     </row>
@@ -35264,7 +35264,7 @@
         <v>22.3</v>
       </c>
       <c r="G1604" t="n">
-        <v>70406860.236</v>
+        <v>70699530.236</v>
       </c>
       <c r="H1604" t="n">
         <v>1.9</v>
@@ -35508,7 +35508,7 @@
       </c>
       <c r="F1615" t="inlineStr"/>
       <c r="G1615" t="n">
-        <v>64017099.835</v>
+        <v>64013507.835</v>
       </c>
       <c r="H1615" t="inlineStr"/>
     </row>
@@ -35730,7 +35730,7 @@
         <v>21.8</v>
       </c>
       <c r="G1625" t="n">
-        <v>69310455.436</v>
+        <v>69577114.436</v>
       </c>
       <c r="H1625" t="n">
         <v>2.1</v>
@@ -35864,7 +35864,7 @@
       </c>
       <c r="F1631" t="inlineStr"/>
       <c r="G1631" t="n">
-        <v>65294247.905</v>
+        <v>65294237.905</v>
       </c>
       <c r="H1631" t="inlineStr"/>
     </row>
@@ -35886,7 +35886,7 @@
       </c>
       <c r="F1632" t="inlineStr"/>
       <c r="G1632" t="n">
-        <v>64477121.441</v>
+        <v>64479744.441</v>
       </c>
       <c r="H1632" t="inlineStr"/>
     </row>
@@ -35908,7 +35908,7 @@
       </c>
       <c r="F1633" t="inlineStr"/>
       <c r="G1633" t="n">
-        <v>64617213.723</v>
+        <v>64617203.723</v>
       </c>
       <c r="H1633" t="inlineStr"/>
     </row>
@@ -35930,7 +35930,7 @@
       </c>
       <c r="F1634" t="inlineStr"/>
       <c r="G1634" t="n">
-        <v>64848131.927</v>
+        <v>64848121.927</v>
       </c>
       <c r="H1634" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
       </c>
       <c r="F1635" t="inlineStr"/>
       <c r="G1635" t="n">
-        <v>64307575.931</v>
+        <v>64307567.931</v>
       </c>
       <c r="H1635" t="inlineStr"/>
     </row>
@@ -35974,7 +35974,7 @@
       </c>
       <c r="F1636" t="inlineStr"/>
       <c r="G1636" t="n">
-        <v>63942179.667</v>
+        <v>63942170.667</v>
       </c>
       <c r="H1636" t="inlineStr"/>
     </row>
@@ -35996,7 +35996,7 @@
       </c>
       <c r="F1637" t="inlineStr"/>
       <c r="G1637" t="n">
-        <v>63545343.064</v>
+        <v>63503581.828</v>
       </c>
       <c r="H1637" t="inlineStr"/>
     </row>
@@ -36018,7 +36018,7 @@
       </c>
       <c r="F1638" t="inlineStr"/>
       <c r="G1638" t="n">
-        <v>62871184.25</v>
+        <v>62866644.53</v>
       </c>
       <c r="H1638" t="inlineStr"/>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="F1639" t="inlineStr"/>
       <c r="G1639" t="n">
-        <v>62698614.663</v>
+        <v>62663843.253</v>
       </c>
       <c r="H1639" t="inlineStr"/>
     </row>
@@ -36062,7 +36062,7 @@
       </c>
       <c r="F1640" t="inlineStr"/>
       <c r="G1640" t="n">
-        <v>62412647.268</v>
+        <v>62355511.352</v>
       </c>
       <c r="H1640" t="inlineStr"/>
     </row>
@@ -36084,7 +36084,7 @@
       </c>
       <c r="F1641" t="inlineStr"/>
       <c r="G1641" t="n">
-        <v>62717921.434</v>
+        <v>62677896.415</v>
       </c>
       <c r="H1641" t="inlineStr"/>
     </row>
@@ -36106,7 +36106,7 @@
       </c>
       <c r="F1642" t="inlineStr"/>
       <c r="G1642" t="n">
-        <v>63244690.188</v>
+        <v>63301175.944</v>
       </c>
       <c r="H1642" t="inlineStr"/>
     </row>
@@ -36127,15 +36127,21 @@
         <v>23.9375</v>
       </c>
       <c r="F1643" t="inlineStr"/>
-      <c r="G1643" t="inlineStr"/>
+      <c r="G1643" t="n">
+        <v>64002119.34</v>
+      </c>
       <c r="H1643" t="inlineStr"/>
     </row>
     <row r="1644">
       <c r="A1644" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B1644" t="inlineStr"/>
-      <c r="C1644" t="inlineStr"/>
+      <c r="B1644" t="n">
+        <v>49793</v>
+      </c>
+      <c r="C1644" t="n">
+        <v>45776921</v>
+      </c>
       <c r="D1644" t="n">
         <v>1533.21</v>
       </c>
@@ -36143,22 +36149,106 @@
         <v>23.1875</v>
       </c>
       <c r="F1644" t="inlineStr"/>
-      <c r="G1644" t="inlineStr"/>
+      <c r="G1644" t="n">
+        <v>65694753.122</v>
+      </c>
       <c r="H1644" t="inlineStr"/>
     </row>
     <row r="1645">
       <c r="A1645" s="1" t="n">
         <v>46265</v>
       </c>
-      <c r="B1645" t="inlineStr"/>
-      <c r="C1645" t="inlineStr"/>
+      <c r="B1645" t="n">
+        <v>48259</v>
+      </c>
+      <c r="C1645" t="n">
+        <v>47451537</v>
+      </c>
       <c r="D1645" t="n">
         <v>1531.51</v>
       </c>
-      <c r="E1645" t="inlineStr"/>
-      <c r="F1645" t="inlineStr"/>
-      <c r="G1645" t="inlineStr"/>
+      <c r="E1645" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1645" t="n">
+        <v>68745902.84299999</v>
+      </c>
       <c r="H1645" t="inlineStr"/>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B1646" t="n">
+        <v>50205</v>
+      </c>
+      <c r="C1646" t="n">
+        <v>47216078</v>
+      </c>
+      <c r="D1646" t="n">
+        <v>1533.63</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>23.0625</v>
+      </c>
+      <c r="F1646" t="inlineStr"/>
+      <c r="G1646" t="n">
+        <v>67792457.311</v>
+      </c>
+      <c r="H1646" t="inlineStr"/>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B1647" t="n">
+        <v>50492</v>
+      </c>
+      <c r="C1647" t="n">
+        <v>46347290</v>
+      </c>
+      <c r="D1647" t="n">
+        <v>1533.58</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>23.125</v>
+      </c>
+      <c r="F1647" t="inlineStr"/>
+      <c r="G1647" t="inlineStr"/>
+      <c r="H1647" t="inlineStr"/>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B1648" t="inlineStr"/>
+      <c r="C1648" t="inlineStr"/>
+      <c r="D1648" t="n">
+        <v>1529.42</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="F1648" t="inlineStr"/>
+      <c r="G1648" t="inlineStr"/>
+      <c r="H1648" t="inlineStr"/>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1649" t="inlineStr"/>
+      <c r="C1649" t="inlineStr"/>
+      <c r="D1649" t="n">
+        <v>1528.6</v>
+      </c>
+      <c r="E1649" t="inlineStr"/>
+      <c r="F1649" t="inlineStr"/>
+      <c r="G1649" t="inlineStr"/>
+      <c r="H1649" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
